--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TDDFT\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A968DC94-9086-4CFD-83B5-C0C98D539A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80EA871-B8AD-4FD9-B187-47287DE5ECF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33303,10 +33303,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4837044-DD50-48A8-AC77-D1678C65813F}">
-  <dimension ref="A1:BH48"/>
+  <dimension ref="A1:BJ48"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
@@ -33355,7 +33355,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -33440,7 +33440,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -33603,7 +33603,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -33764,8 +33764,9 @@
       <c r="BH4">
         <v>94.090999999999994</v>
       </c>
+      <c r="BJ4" s="5"/>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -33926,8 +33927,9 @@
       <c r="BH5">
         <v>94.944999999999993</v>
       </c>
+      <c r="BJ5" s="5"/>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -34083,13 +34085,15 @@
         <v>-0.13300000000000001</v>
       </c>
       <c r="BF6">
-        <v>-0.199318</v>
-      </c>
+        <v>-0.13537299999999999</v>
+      </c>
+      <c r="BG6" s="1"/>
       <c r="BH6">
         <v>94.497</v>
       </c>
+      <c r="BJ6" s="5"/>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -34250,8 +34254,9 @@
       <c r="BH7">
         <v>95.581999999999994</v>
       </c>
+      <c r="BJ7" s="5"/>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -34412,8 +34417,9 @@
       <c r="BH8">
         <v>95.251999999999995</v>
       </c>
+      <c r="BJ8" s="5"/>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -34574,8 +34580,9 @@
       <c r="BH9">
         <v>92.575000000000003</v>
       </c>
+      <c r="BJ9" s="5"/>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -34736,8 +34743,9 @@
       <c r="BH10">
         <v>96.075000000000003</v>
       </c>
+      <c r="BJ10" s="5"/>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -34898,8 +34906,9 @@
       <c r="BH11">
         <v>94.704999999999998</v>
       </c>
+      <c r="BJ11" s="5"/>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -35060,8 +35069,9 @@
       <c r="BH12">
         <v>95.164000000000001</v>
       </c>
+      <c r="BJ12" s="5"/>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -35222,8 +35232,9 @@
       <c r="BH13">
         <v>95.367999999999995</v>
       </c>
+      <c r="BJ13" s="5"/>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -35384,8 +35395,9 @@
       <c r="BH14">
         <v>95.495999999999995</v>
       </c>
+      <c r="BJ14" s="5"/>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -35546,8 +35558,9 @@
       <c r="BH15">
         <v>95.834999999999994</v>
       </c>
+      <c r="BJ15" s="5"/>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -35708,8 +35721,9 @@
       <c r="BH16">
         <v>96.375</v>
       </c>
+      <c r="BJ16" s="5"/>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -35870,8 +35884,9 @@
       <c r="BH17">
         <v>96.097999999999999</v>
       </c>
+      <c r="BJ17" s="5"/>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -36032,8 +36047,9 @@
       <c r="BH18">
         <v>95.159000000000006</v>
       </c>
+      <c r="BJ18" s="5"/>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -36194,8 +36210,9 @@
       <c r="BH19">
         <v>96.212999999999994</v>
       </c>
+      <c r="BJ19" s="5"/>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -36356,8 +36373,9 @@
       <c r="BH20">
         <v>95.498999999999995</v>
       </c>
+      <c r="BJ20" s="5"/>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -36513,13 +36531,14 @@
         <v>-2.1000000000000001E-2</v>
       </c>
       <c r="BF21">
-        <v>-0.16564899999999999</v>
+        <v>-0.14147700000000007</v>
       </c>
       <c r="BH21">
         <v>95.215000000000003</v>
       </c>
+      <c r="BJ21" s="5"/>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -36680,8 +36699,9 @@
       <c r="BH22">
         <v>95.728999999999999</v>
       </c>
+      <c r="BJ22" s="5"/>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -36842,8 +36862,9 @@
       <c r="BH23">
         <v>96.3</v>
       </c>
+      <c r="BJ23" s="5"/>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -37004,8 +37025,9 @@
       <c r="BH24">
         <v>95.245999999999995</v>
       </c>
+      <c r="BJ24" s="5"/>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -37166,8 +37188,9 @@
       <c r="BH25">
         <v>95.906000000000006</v>
       </c>
+      <c r="BJ25" s="5"/>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -37328,8 +37351,9 @@
       <c r="BH26">
         <v>95.638000000000005</v>
       </c>
+      <c r="BJ26" s="5"/>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -37490,8 +37514,9 @@
       <c r="BH27">
         <v>95.947000000000003</v>
       </c>
+      <c r="BJ27" s="5"/>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -37652,8 +37677,9 @@
       <c r="BH28">
         <v>96.048000000000002</v>
       </c>
+      <c r="BJ28" s="5"/>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -37814,8 +37840,9 @@
       <c r="BH29">
         <v>95.977999999999994</v>
       </c>
+      <c r="BJ29" s="5"/>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -37976,8 +38003,9 @@
       <c r="BH30">
         <v>95.373000000000005</v>
       </c>
+      <c r="BJ30" s="5"/>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -38139,8 +38167,9 @@
       <c r="BH31">
         <v>95.462000000000003</v>
       </c>
+      <c r="BJ31" s="5"/>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -38301,8 +38330,9 @@
       <c r="BH32">
         <v>95.822000000000003</v>
       </c>
+      <c r="BJ32" s="5"/>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -38463,8 +38493,9 @@
       <c r="BH33">
         <v>94.881</v>
       </c>
+      <c r="BJ33" s="5"/>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -38625,8 +38656,9 @@
       <c r="BH34">
         <v>95.819000000000003</v>
       </c>
+      <c r="BJ34" s="5"/>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -38787,8 +38819,9 @@
       <c r="BH35">
         <v>95.948999999999998</v>
       </c>
+      <c r="BJ35" s="5"/>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -38949,8 +38982,9 @@
       <c r="BH36">
         <v>95.947000000000003</v>
       </c>
+      <c r="BJ36" s="5"/>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -39111,8 +39145,9 @@
       <c r="BH37">
         <v>95.423000000000002</v>
       </c>
+      <c r="BJ37" s="5"/>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -39273,8 +39308,9 @@
       <c r="BH38">
         <v>96.340999999999994</v>
       </c>
+      <c r="BJ38" s="5"/>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -39435,8 +39471,9 @@
       <c r="BH39">
         <v>91.718000000000004</v>
       </c>
+      <c r="BJ39" s="5"/>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -39597,8 +39634,9 @@
       <c r="BH40">
         <v>96.075999999999993</v>
       </c>
+      <c r="BJ40" s="5"/>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -39759,8 +39797,9 @@
       <c r="BH41">
         <v>95.734999999999999</v>
       </c>
+      <c r="BJ41" s="5"/>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -39921,8 +39960,9 @@
       <c r="BH42">
         <v>95.257000000000005</v>
       </c>
+      <c r="BJ42" s="5"/>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -40083,8 +40123,9 @@
       <c r="BH43">
         <v>96.204999999999998</v>
       </c>
+      <c r="BJ43" s="5"/>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -40245,8 +40286,9 @@
       <c r="BH44">
         <v>96.299000000000007</v>
       </c>
+      <c r="BJ44" s="5"/>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -40407,8 +40449,9 @@
       <c r="BH45">
         <v>96.197000000000003</v>
       </c>
+      <c r="BJ45" s="5"/>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -40425,13 +40468,13 @@
         <v>-2.8604166392080101E-2</v>
       </c>
       <c r="F46" s="6">
-        <v>-8.8749999999999996E-2</v>
+        <v>-3.7330000000000002E-2</v>
       </c>
       <c r="G46" s="6">
         <v>-3.5819999999999998E-2</v>
       </c>
       <c r="H46" s="6">
-        <v>-0.10662000000000001</v>
+        <v>-0.12623000000000001</v>
       </c>
       <c r="I46" s="6">
         <v>-0.1234</v>
@@ -40569,8 +40612,9 @@
       <c r="BH46">
         <v>91.869</v>
       </c>
+      <c r="BJ46" s="5"/>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -40731,8 +40775,9 @@
       <c r="BH47">
         <v>95.031999999999996</v>
       </c>
+      <c r="BJ47" s="5"/>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -40893,6 +40938,7 @@
       <c r="BH48">
         <v>96.32</v>
       </c>
+      <c r="BJ48" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80EA871-B8AD-4FD9-B187-47287DE5ECF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A88DF7-72F5-41ED-B66D-A710CE8205A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TDDFT\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A88DF7-72F5-41ED-B66D-A710CE8205A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF13254-DA31-4A4F-92E5-4CC42398C800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="324">
   <si>
     <t>B3LYP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1122,6 +1122,10 @@
   <si>
     <t>1.769</t>
   </si>
+  <si>
+    <t>BLYP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1132,7 +1136,7 @@
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.000;[Red]0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1180,6 +1184,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1201,7 +1212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1225,6 +1236,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -12892,14 +12908,14 @@
       <c r="F75" s="5">
         <v>3.3820000000000003E-2</v>
       </c>
-      <c r="G75" s="5">
-        <v>-0.10389</v>
+      <c r="G75" s="14">
+        <v>-0.13378999999999999</v>
       </c>
       <c r="H75" s="5">
         <v>-1.8710000000000001E-2</v>
       </c>
-      <c r="I75" s="5">
-        <v>-7.5910000000000005E-2</v>
+      <c r="I75" s="14">
+        <v>-9.9040000000000003E-2</v>
       </c>
       <c r="K75" s="5">
         <v>0.19094</v>
@@ -13693,14 +13709,14 @@
       <c r="N80" s="5">
         <v>0.10224</v>
       </c>
-      <c r="O80" s="5">
-        <v>-7.5500000000000003E-3</v>
+      <c r="O80" s="14">
+        <v>0.14568999999999999</v>
       </c>
       <c r="P80" s="5">
         <v>4.7570000000000001E-2</v>
       </c>
-      <c r="Q80" s="5">
-        <v>3.0030000000000001E-2</v>
+      <c r="Q80" s="14">
+        <v>3.3849999999999998E-2</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="5">
@@ -16679,14 +16695,14 @@
       <c r="V99" s="5">
         <v>0.15242</v>
       </c>
-      <c r="W99" s="5">
-        <v>-0.21625</v>
+      <c r="W99" s="14">
+        <v>-0.51512000000000002</v>
       </c>
       <c r="X99" s="5">
         <v>8.1040000000000001E-2</v>
       </c>
-      <c r="Y99" s="5">
-        <v>1.31E-3</v>
+      <c r="Y99" s="14">
+        <v>-0.15637999999999999</v>
       </c>
       <c r="AA99" s="5">
         <v>0.18748999999999999</v>
@@ -28800,8 +28816,8 @@
       <c r="H16" s="5">
         <v>0.20780000000000001</v>
       </c>
-      <c r="I16" s="6">
-        <v>7.7209E-2</v>
+      <c r="I16" s="15">
+        <v>8.1193570000000007E-2</v>
       </c>
       <c r="K16" s="6">
         <v>0.47310000000000002</v>
@@ -33303,10 +33319,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4837044-DD50-48A8-AC77-D1678C65813F}">
-  <dimension ref="A1:BJ48"/>
+  <dimension ref="A1:BI51"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
@@ -33355,7 +33371,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -33440,7 +33456,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -33603,7 +33619,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -33764,9 +33780,9 @@
       <c r="BH4">
         <v>94.090999999999994</v>
       </c>
-      <c r="BJ4" s="5"/>
+      <c r="BI4" s="5"/>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -33927,9 +33943,9 @@
       <c r="BH5">
         <v>94.944999999999993</v>
       </c>
-      <c r="BJ5" s="5"/>
+      <c r="BI5" s="5"/>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -34091,9 +34107,9 @@
       <c r="BH6">
         <v>94.497</v>
       </c>
-      <c r="BJ6" s="5"/>
+      <c r="BI6" s="5"/>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -34254,9 +34270,9 @@
       <c r="BH7">
         <v>95.581999999999994</v>
       </c>
-      <c r="BJ7" s="5"/>
+      <c r="BI7" s="5"/>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -34417,9 +34433,9 @@
       <c r="BH8">
         <v>95.251999999999995</v>
       </c>
-      <c r="BJ8" s="5"/>
+      <c r="BI8" s="5"/>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -34580,9 +34596,9 @@
       <c r="BH9">
         <v>92.575000000000003</v>
       </c>
-      <c r="BJ9" s="5"/>
+      <c r="BI9" s="5"/>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -34743,9 +34759,9 @@
       <c r="BH10">
         <v>96.075000000000003</v>
       </c>
-      <c r="BJ10" s="5"/>
+      <c r="BI10" s="5"/>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -34906,9 +34922,9 @@
       <c r="BH11">
         <v>94.704999999999998</v>
       </c>
-      <c r="BJ11" s="5"/>
+      <c r="BI11" s="5"/>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -35069,9 +35085,9 @@
       <c r="BH12">
         <v>95.164000000000001</v>
       </c>
-      <c r="BJ12" s="5"/>
+      <c r="BI12" s="5"/>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -35232,9 +35248,9 @@
       <c r="BH13">
         <v>95.367999999999995</v>
       </c>
-      <c r="BJ13" s="5"/>
+      <c r="BI13" s="5"/>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -35395,9 +35411,9 @@
       <c r="BH14">
         <v>95.495999999999995</v>
       </c>
-      <c r="BJ14" s="5"/>
+      <c r="BI14" s="5"/>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -35558,9 +35574,9 @@
       <c r="BH15">
         <v>95.834999999999994</v>
       </c>
-      <c r="BJ15" s="5"/>
+      <c r="BI15" s="5"/>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -35721,9 +35737,9 @@
       <c r="BH16">
         <v>96.375</v>
       </c>
-      <c r="BJ16" s="5"/>
+      <c r="BI16" s="5"/>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -35884,9 +35900,9 @@
       <c r="BH17">
         <v>96.097999999999999</v>
       </c>
-      <c r="BJ17" s="5"/>
+      <c r="BI17" s="5"/>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -36047,9 +36063,9 @@
       <c r="BH18">
         <v>95.159000000000006</v>
       </c>
-      <c r="BJ18" s="5"/>
+      <c r="BI18" s="5"/>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -36210,9 +36226,9 @@
       <c r="BH19">
         <v>96.212999999999994</v>
       </c>
-      <c r="BJ19" s="5"/>
+      <c r="BI19" s="5"/>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -36373,9 +36389,9 @@
       <c r="BH20">
         <v>95.498999999999995</v>
       </c>
-      <c r="BJ20" s="5"/>
+      <c r="BI20" s="5"/>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -36536,9 +36552,9 @@
       <c r="BH21">
         <v>95.215000000000003</v>
       </c>
-      <c r="BJ21" s="5"/>
+      <c r="BI21" s="5"/>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -36699,9 +36715,9 @@
       <c r="BH22">
         <v>95.728999999999999</v>
       </c>
-      <c r="BJ22" s="5"/>
+      <c r="BI22" s="5"/>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -36862,9 +36878,9 @@
       <c r="BH23">
         <v>96.3</v>
       </c>
-      <c r="BJ23" s="5"/>
+      <c r="BI23" s="5"/>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -37025,9 +37041,9 @@
       <c r="BH24">
         <v>95.245999999999995</v>
       </c>
-      <c r="BJ24" s="5"/>
+      <c r="BI24" s="5"/>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -37188,9 +37204,9 @@
       <c r="BH25">
         <v>95.906000000000006</v>
       </c>
-      <c r="BJ25" s="5"/>
+      <c r="BI25" s="5"/>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -37351,9 +37367,9 @@
       <c r="BH26">
         <v>95.638000000000005</v>
       </c>
-      <c r="BJ26" s="5"/>
+      <c r="BI26" s="5"/>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -37514,9 +37530,9 @@
       <c r="BH27">
         <v>95.947000000000003</v>
       </c>
-      <c r="BJ27" s="5"/>
+      <c r="BI27" s="5"/>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -37677,9 +37693,9 @@
       <c r="BH28">
         <v>96.048000000000002</v>
       </c>
-      <c r="BJ28" s="5"/>
+      <c r="BI28" s="5"/>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -37840,9 +37856,9 @@
       <c r="BH29">
         <v>95.977999999999994</v>
       </c>
-      <c r="BJ29" s="5"/>
+      <c r="BI29" s="5"/>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -38003,9 +38019,9 @@
       <c r="BH30">
         <v>95.373000000000005</v>
       </c>
-      <c r="BJ30" s="5"/>
+      <c r="BI30" s="5"/>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -38167,9 +38183,9 @@
       <c r="BH31">
         <v>95.462000000000003</v>
       </c>
-      <c r="BJ31" s="5"/>
+      <c r="BI31" s="5"/>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -38330,9 +38346,9 @@
       <c r="BH32">
         <v>95.822000000000003</v>
       </c>
-      <c r="BJ32" s="5"/>
+      <c r="BI32" s="5"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -38493,9 +38509,9 @@
       <c r="BH33">
         <v>94.881</v>
       </c>
-      <c r="BJ33" s="5"/>
+      <c r="BI33" s="5"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -38656,9 +38672,9 @@
       <c r="BH34">
         <v>95.819000000000003</v>
       </c>
-      <c r="BJ34" s="5"/>
+      <c r="BI34" s="5"/>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -38819,9 +38835,9 @@
       <c r="BH35">
         <v>95.948999999999998</v>
       </c>
-      <c r="BJ35" s="5"/>
+      <c r="BI35" s="5"/>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -38982,9 +38998,9 @@
       <c r="BH36">
         <v>95.947000000000003</v>
       </c>
-      <c r="BJ36" s="5"/>
+      <c r="BI36" s="5"/>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -39145,9 +39161,9 @@
       <c r="BH37">
         <v>95.423000000000002</v>
       </c>
-      <c r="BJ37" s="5"/>
+      <c r="BI37" s="5"/>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -39308,9 +39324,9 @@
       <c r="BH38">
         <v>96.340999999999994</v>
       </c>
-      <c r="BJ38" s="5"/>
+      <c r="BI38" s="5"/>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -39471,9 +39487,9 @@
       <c r="BH39">
         <v>91.718000000000004</v>
       </c>
-      <c r="BJ39" s="5"/>
+      <c r="BI39" s="5"/>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -39634,9 +39650,9 @@
       <c r="BH40">
         <v>96.075999999999993</v>
       </c>
-      <c r="BJ40" s="5"/>
+      <c r="BI40" s="5"/>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -39797,9 +39813,9 @@
       <c r="BH41">
         <v>95.734999999999999</v>
       </c>
-      <c r="BJ41" s="5"/>
+      <c r="BI41" s="5"/>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -39960,9 +39976,9 @@
       <c r="BH42">
         <v>95.257000000000005</v>
       </c>
-      <c r="BJ42" s="5"/>
+      <c r="BI42" s="5"/>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -40123,9 +40139,9 @@
       <c r="BH43">
         <v>96.204999999999998</v>
       </c>
-      <c r="BJ43" s="5"/>
+      <c r="BI43" s="5"/>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -40286,9 +40302,9 @@
       <c r="BH44">
         <v>96.299000000000007</v>
       </c>
-      <c r="BJ44" s="5"/>
+      <c r="BI44" s="5"/>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -40449,9 +40465,9 @@
       <c r="BH45">
         <v>96.197000000000003</v>
       </c>
-      <c r="BJ45" s="5"/>
+      <c r="BI45" s="5"/>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -40467,14 +40483,14 @@
       <c r="E46" s="6">
         <v>-2.8604166392080101E-2</v>
       </c>
-      <c r="F46" s="6">
-        <v>-3.7330000000000002E-2</v>
+      <c r="F46" s="13">
+        <v>-8.8739999999999999E-2</v>
       </c>
       <c r="G46" s="6">
         <v>-3.5819999999999998E-2</v>
       </c>
-      <c r="H46" s="6">
-        <v>-0.12623000000000001</v>
+      <c r="H46" s="13">
+        <v>-0.12614</v>
       </c>
       <c r="I46" s="6">
         <v>-0.1234</v>
@@ -40612,9 +40628,9 @@
       <c r="BH46">
         <v>91.869</v>
       </c>
-      <c r="BJ46" s="5"/>
+      <c r="BI46" s="5"/>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -40775,9 +40791,9 @@
       <c r="BH47">
         <v>95.031999999999996</v>
       </c>
-      <c r="BJ47" s="5"/>
+      <c r="BI47" s="5"/>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -40938,11 +40954,15 @@
       <c r="BH48">
         <v>96.32</v>
       </c>
-      <c r="BJ48" s="5"/>
+      <c r="BI48" s="5"/>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D51" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45542,10 +45562,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4750BC-1188-421B-BE5C-F526F345B7FA}">
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -45553,10 +45573,13 @@
         <v>169</v>
       </c>
       <c r="Q1" t="s">
-        <v>257</v>
+        <v>233</v>
+      </c>
+      <c r="X1" t="s">
+        <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>222</v>
       </c>
@@ -45617,8 +45640,41 @@
       <c r="V2">
         <v>0.5</v>
       </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0.1</v>
+      </c>
+      <c r="Z2">
+        <v>0.2</v>
+      </c>
+      <c r="AA2">
+        <v>0.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.4</v>
+      </c>
+      <c r="AC2">
+        <v>0.5</v>
+      </c>
+      <c r="AD2">
+        <v>0.6</v>
+      </c>
+      <c r="AE2">
+        <v>0.7</v>
+      </c>
+      <c r="AF2">
+        <v>0.8</v>
+      </c>
+      <c r="AG2">
+        <v>0.9</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -45662,25 +45718,58 @@
         <v>-0.27734256639983113</v>
       </c>
       <c r="Q3">
-        <v>-0.27408865659817028</v>
+        <v>-0.27408865700000001</v>
       </c>
       <c r="R3">
-        <v>-0.33523172841084758</v>
+        <v>-0.33523172800000001</v>
       </c>
       <c r="S3">
-        <v>-0.3988666725676156</v>
+        <v>-0.398866673</v>
       </c>
       <c r="T3">
-        <v>-0.46480048395160678</v>
+        <v>-0.46480048400000001</v>
       </c>
       <c r="U3">
-        <v>-0.53285906583756004</v>
+        <v>-0.53285906599999999</v>
       </c>
       <c r="V3">
-        <v>-0.60288523172795638</v>
+        <v>-0.60288523199999999</v>
+      </c>
+      <c r="X3">
+        <v>2.682E-2</v>
+      </c>
+      <c r="Y3">
+        <v>1.2760000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>-2.4599999999999999E-3</v>
+      </c>
+      <c r="AA3">
+        <v>-1.8780000000000002E-2</v>
+      </c>
+      <c r="AB3">
+        <v>-3.6170000000000001E-2</v>
+      </c>
+      <c r="AC3">
+        <v>-5.4579999999999997E-2</v>
+      </c>
+      <c r="AD3">
+        <v>-7.3980000000000004E-2</v>
+      </c>
+      <c r="AE3">
+        <v>-9.4320000000000001E-2</v>
+      </c>
+      <c r="AF3">
+        <v>-0.11557000000000001</v>
+      </c>
+      <c r="AG3">
+        <v>-0.13769000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>-0.16064999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -45724,25 +45813,58 @@
         <v>-0.21953647554575689</v>
       </c>
       <c r="Q4">
-        <v>-0.2063656093413207</v>
+        <v>-0.20636560900000001</v>
       </c>
       <c r="R4">
-        <v>-0.25783493943277869</v>
+        <v>-0.25783493899999999</v>
       </c>
       <c r="S4">
-        <v>-0.31149030123924659</v>
+        <v>-0.31149030100000002</v>
       </c>
       <c r="T4">
-        <v>-0.36717189209667628</v>
+        <v>-0.367171892</v>
       </c>
       <c r="U4">
-        <v>-0.42473488976749241</v>
+        <v>-0.42473488999999998</v>
       </c>
       <c r="V4">
-        <v>-0.48404794750937019</v>
+        <v>-0.48404794800000001</v>
+      </c>
+      <c r="X4">
+        <v>3.4810000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.2460000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>9.1199999999999996E-3</v>
+      </c>
+      <c r="AA4">
+        <v>-5.1700000000000001E-3</v>
+      </c>
+      <c r="AB4">
+        <v>-2.0369999999999999E-2</v>
+      </c>
+      <c r="AC4">
+        <v>-3.6450000000000003E-2</v>
+      </c>
+      <c r="AD4">
+        <v>-5.3379999999999997E-2</v>
+      </c>
+      <c r="AE4">
+        <v>-7.1110000000000007E-2</v>
+      </c>
+      <c r="AF4">
+        <v>-8.9630000000000001E-2</v>
+      </c>
+      <c r="AG4">
+        <v>-0.10891000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>-0.12889999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -45786,25 +45908,58 @@
         <v>-0.17775379440728689</v>
       </c>
       <c r="Q5">
-        <v>-9.6803934852994517E-2</v>
+        <v>-9.6803934999999994E-2</v>
       </c>
       <c r="R5">
-        <v>-0.15100649944975139</v>
+        <v>-0.15100649899999999</v>
       </c>
       <c r="S5">
-        <v>-0.20737255955896369</v>
+        <v>-0.20737256000000001</v>
       </c>
       <c r="T5">
-        <v>-0.26574688946047698</v>
+        <v>-0.26574688899999999</v>
       </c>
       <c r="U5">
-        <v>-0.32598851328196121</v>
+        <v>-0.32598851299999998</v>
       </c>
       <c r="V5">
-        <v>-0.38796929280759718</v>
+        <v>-0.38796929299999999</v>
+      </c>
+      <c r="X5">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="Y5">
+        <v>3.7139999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.367E-2</v>
+      </c>
+      <c r="AA5">
+        <v>9.2300000000000004E-3</v>
+      </c>
+      <c r="AB5">
+        <v>-6.1500000000000001E-3</v>
+      </c>
+      <c r="AC5">
+        <v>-2.2419999999999999E-2</v>
+      </c>
+      <c r="AD5">
+        <v>-3.9550000000000002E-2</v>
+      </c>
+      <c r="AE5">
+        <v>-5.7520000000000002E-2</v>
+      </c>
+      <c r="AF5">
+        <v>-7.6280000000000001E-2</v>
+      </c>
+      <c r="AG5">
+        <v>-9.5820000000000002E-2</v>
+      </c>
+      <c r="AH5">
+        <v>-0.11611</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -45848,25 +46003,58 @@
         <v>-0.16306155922403159</v>
       </c>
       <c r="Q6">
-        <v>-5.5137944905059178E-3</v>
+        <v>-5.5137939999999998E-3</v>
       </c>
       <c r="R6">
-        <v>-6.1069144512209322E-2</v>
+        <v>-6.1069144999999998E-2</v>
       </c>
       <c r="S6">
-        <v>-0.11883357805277329</v>
+        <v>-0.118833578</v>
       </c>
       <c r="T6">
-        <v>-0.1786475913921983</v>
+        <v>-0.17864759099999999</v>
       </c>
       <c r="U6">
-        <v>-0.240366767000599</v>
+        <v>-0.24036676700000001</v>
       </c>
       <c r="V6">
-        <v>-0.30386011293906351</v>
+        <v>-0.30386011299999999</v>
+      </c>
+      <c r="X6">
+        <v>5.5320000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>4.265E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.894E-2</v>
+      </c>
+      <c r="AA6">
+        <v>1.423E-2</v>
+      </c>
+      <c r="AB6">
+        <v>-1.4400000000000001E-3</v>
+      </c>
+      <c r="AC6">
+        <v>-1.804E-2</v>
+      </c>
+      <c r="AD6">
+        <v>-3.5520000000000003E-2</v>
+      </c>
+      <c r="AE6">
+        <v>-5.3870000000000001E-2</v>
+      </c>
+      <c r="AF6">
+        <v>-7.3039999999999994E-2</v>
+      </c>
+      <c r="AG6">
+        <v>-9.2999999999999999E-2</v>
+      </c>
+      <c r="AH6">
+        <v>-0.11373999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -45910,25 +46098,58 @@
         <v>-0.16241827088485161</v>
       </c>
       <c r="Q7">
-        <v>2.8673547902512519E-3</v>
+        <v>2.8673549999999998E-3</v>
       </c>
       <c r="R7">
-        <v>-5.4679327466500137E-2</v>
+        <v>-5.4679327E-2</v>
       </c>
       <c r="S7">
-        <v>-0.1144077022057453</v>
+        <v>-0.114407702</v>
       </c>
       <c r="T7">
-        <v>-0.17615600893335859</v>
+        <v>-0.176156009</v>
       </c>
       <c r="U7">
-        <v>-0.23977792031587489</v>
+        <v>-0.23977792000000001</v>
       </c>
       <c r="V7">
-        <v>-0.30514089986216458</v>
+        <v>-0.30514089999999999</v>
+      </c>
+      <c r="X7">
+        <v>5.2929999999999998E-2</v>
+      </c>
+      <c r="Y7">
+        <v>3.9949999999999999E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.5940000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>1.091E-2</v>
+      </c>
+      <c r="AB7">
+        <v>-5.0800000000000003E-3</v>
+      </c>
+      <c r="AC7">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="AD7">
+        <v>-3.9820000000000001E-2</v>
+      </c>
+      <c r="AE7">
+        <v>-5.8500000000000003E-2</v>
+      </c>
+      <c r="AF7">
+        <v>-7.8009999999999996E-2</v>
+      </c>
+      <c r="AG7">
+        <v>-9.8320000000000005E-2</v>
+      </c>
+      <c r="AH7">
+        <v>-0.11940000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -45972,25 +46193,58 @@
         <v>-0.16277384319369759</v>
       </c>
       <c r="Q8">
-        <v>-0.1067800977176491</v>
+        <v>-0.106780098</v>
       </c>
       <c r="R8">
-        <v>-0.15863750302787591</v>
+        <v>-0.15863750300000001</v>
       </c>
       <c r="S8">
-        <v>-0.21262815678983291</v>
+        <v>-0.21262815700000001</v>
       </c>
       <c r="T8">
-        <v>-0.26860271409080178</v>
+        <v>-0.26860271400000002</v>
       </c>
       <c r="U8">
-        <v>-0.3264253133435005</v>
+        <v>-0.32642531299999999</v>
       </c>
       <c r="V8">
-        <v>-0.38597228033259912</v>
+        <v>-0.38597228</v>
+      </c>
+      <c r="X8">
+        <v>6.2460000000000002E-2</v>
+      </c>
+      <c r="Y8">
+        <v>5.0209999999999998E-2</v>
+      </c>
+      <c r="Z8">
+        <v>3.6970000000000003E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>7.7200000000000003E-3</v>
+      </c>
+      <c r="AC8">
+        <v>-8.2299999999999995E-3</v>
+      </c>
+      <c r="AD8">
+        <v>-2.5020000000000001E-2</v>
+      </c>
+      <c r="AE8">
+        <v>-4.2619999999999998E-2</v>
+      </c>
+      <c r="AF8">
+        <v>-6.0990000000000003E-2</v>
+      </c>
+      <c r="AG8">
+        <v>-8.0119999999999997E-2</v>
+      </c>
+      <c r="AH8">
+        <v>-9.9970000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -46034,25 +46288,58 @@
         <v>-0.14457623501814859</v>
       </c>
       <c r="Q9">
-        <v>-9.3796045289907912E-2</v>
+        <v>-9.3796044999999995E-2</v>
       </c>
       <c r="R9">
-        <v>-0.14568030520124131</v>
+        <v>-0.14568030500000001</v>
       </c>
       <c r="S9">
-        <v>-0.1996928607081864</v>
+        <v>-0.199692861</v>
       </c>
       <c r="T9">
-        <v>-0.25568431539730108</v>
+        <v>-0.255684315</v>
       </c>
       <c r="U9">
-        <v>-0.31351889404449029</v>
+        <v>-0.31351889399999999</v>
       </c>
       <c r="V9">
-        <v>-0.37307309333010769</v>
+        <v>-0.37307309300000002</v>
+      </c>
+      <c r="X9">
+        <v>7.7649999999999997E-2</v>
+      </c>
+      <c r="Y9">
+        <v>6.5449999999999994E-2</v>
+      </c>
+      <c r="Z9">
+        <v>5.2269999999999997E-2</v>
+      </c>
+      <c r="AA9">
+        <v>3.814E-2</v>
+      </c>
+      <c r="AB9">
+        <v>2.3109999999999999E-2</v>
+      </c>
+      <c r="AC9">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="AD9">
+        <v>-9.5499999999999995E-3</v>
+      </c>
+      <c r="AE9">
+        <v>-2.7109999999999999E-2</v>
+      </c>
+      <c r="AF9">
+        <v>-4.5449999999999997E-2</v>
+      </c>
+      <c r="AG9">
+        <v>-6.4549999999999996E-2</v>
+      </c>
+      <c r="AH9">
+        <v>-8.4370000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -46096,25 +46383,58 @@
         <v>-0.14347909064678041</v>
       </c>
       <c r="Q10">
-        <v>-0.12018608183167299</v>
+        <v>-0.120186082</v>
       </c>
       <c r="R10">
-        <v>-0.17067107613877031</v>
+        <v>-0.170671076</v>
       </c>
       <c r="S10">
-        <v>-0.22333318087924231</v>
+        <v>-0.22333318099999999</v>
       </c>
       <c r="T10">
-        <v>-0.27802027122011519</v>
+        <v>-0.27802027099999999</v>
       </c>
       <c r="U10">
-        <v>-0.33459407556579063</v>
+        <v>-0.33459407600000002</v>
       </c>
       <c r="V10">
-        <v>-0.39292883313158922</v>
+        <v>-0.39292883299999998</v>
+      </c>
+      <c r="X10">
+        <v>8.5290000000000005E-2</v>
+      </c>
+      <c r="Y10">
+        <v>7.3230000000000003E-2</v>
+      </c>
+      <c r="Z10">
+        <v>6.0179999999999997E-2</v>
+      </c>
+      <c r="AA10">
+        <v>4.6190000000000002E-2</v>
+      </c>
+      <c r="AB10">
+        <v>3.1280000000000002E-2</v>
+      </c>
+      <c r="AC10">
+        <v>1.55E-2</v>
+      </c>
+      <c r="AD10">
+        <v>-1.14E-3</v>
+      </c>
+      <c r="AE10">
+        <v>-1.8589999999999999E-2</v>
+      </c>
+      <c r="AF10">
+        <v>-3.6830000000000002E-2</v>
+      </c>
+      <c r="AG10">
+        <v>-5.5820000000000002E-2</v>
+      </c>
+      <c r="AH10">
+        <v>-7.5550000000000006E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -46158,25 +46478,58 @@
         <v>-0.2309767555804062</v>
       </c>
       <c r="Q11">
-        <v>-0.1016624186624326</v>
+        <v>-0.101662419</v>
       </c>
       <c r="R11">
-        <v>-0.15666648381834511</v>
+        <v>-0.15666648399999999</v>
       </c>
       <c r="S11">
-        <v>-0.2137000584319545</v>
+        <v>-0.213700058</v>
       </c>
       <c r="T11">
-        <v>-0.27261286631794812</v>
+        <v>-0.27261286600000001</v>
       </c>
       <c r="U11">
-        <v>-0.33326865777550829</v>
+        <v>-0.333268658</v>
       </c>
       <c r="V11">
-        <v>-0.3955437945222785</v>
+        <v>-0.39554379499999998</v>
+      </c>
+      <c r="X11">
+        <v>-8.8500000000000002E-3</v>
+      </c>
+      <c r="Y11">
+        <v>-5.1799999999999997E-3</v>
+      </c>
+      <c r="Z11">
+        <v>-2.1729999999999999E-2</v>
+      </c>
+      <c r="AA11">
+        <v>-4.147E-2</v>
+      </c>
+      <c r="AB11">
+        <v>-6.2089999999999999E-2</v>
+      </c>
+      <c r="AC11">
+        <v>-8.3449999999999996E-2</v>
+      </c>
+      <c r="AD11">
+        <v>-0.10549</v>
+      </c>
+      <c r="AE11">
+        <v>-0.12816</v>
+      </c>
+      <c r="AF11">
+        <v>-0.15145</v>
+      </c>
+      <c r="AG11">
+        <v>-0.17532</v>
+      </c>
+      <c r="AH11">
+        <v>-0.19975999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -46220,22 +46573,55 @@
         <v>-0.35518528603498473</v>
       </c>
       <c r="Q12">
-        <v>-0.34264759718660931</v>
+        <v>-0.34264759700000003</v>
       </c>
       <c r="R12">
-        <v>-0.40116904506667039</v>
+        <v>-0.401169045</v>
       </c>
       <c r="S12">
-        <v>-0.46199827945190292</v>
+        <v>-0.46199827900000001</v>
       </c>
       <c r="T12">
-        <v>-0.52494490367018387</v>
+        <v>-0.52494490400000005</v>
       </c>
       <c r="U12">
-        <v>-0.58983831486538429</v>
+        <v>-0.58983831499999995</v>
       </c>
       <c r="V12">
-        <v>-0.65652546523116284</v>
+        <v>-0.65652546499999997</v>
+      </c>
+      <c r="X12">
+        <v>-0.19067999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>-0.19116</v>
+      </c>
+      <c r="Z12">
+        <v>-0.19273999999999999</v>
+      </c>
+      <c r="AA12">
+        <v>-0.19544</v>
+      </c>
+      <c r="AB12">
+        <v>-0.19922999999999999</v>
+      </c>
+      <c r="AC12">
+        <v>-0.20411000000000001</v>
+      </c>
+      <c r="AD12">
+        <v>-0.21007000000000001</v>
+      </c>
+      <c r="AE12">
+        <v>-0.21711</v>
+      </c>
+      <c r="AF12">
+        <v>-0.22523000000000001</v>
+      </c>
+      <c r="AG12">
+        <v>-0.2344</v>
+      </c>
+      <c r="AH12">
+        <v>-0.24462</v>
       </c>
     </row>
   </sheetData>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TDDFT\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF13254-DA31-4A4F-92E5-4CC42398C800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1215FAA2-1529-4B3F-A1D3-1E3DEA636754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
@@ -1212,7 +1212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1239,6 +1239,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -27287,7 +27291,7 @@
       <c r="T6" s="5">
         <v>0.94531000000000009</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="16">
         <v>1.00101</v>
       </c>
       <c r="V6" s="5">
@@ -28067,7 +28071,7 @@
       <c r="T11" s="5">
         <v>0.7593399999999999</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11" s="16">
         <v>0.61880999999999997</v>
       </c>
       <c r="V11" s="5">
@@ -28250,14 +28254,14 @@
       <c r="AD12" s="5">
         <v>0.71404000000000001</v>
       </c>
-      <c r="AE12" s="6">
-        <v>0.33756999999999998</v>
+      <c r="AE12" s="15">
+        <v>0.31489</v>
       </c>
       <c r="AF12" s="5">
         <v>0.65507000000000004</v>
       </c>
-      <c r="AG12" s="6">
-        <v>0.54018999999999995</v>
+      <c r="AG12" s="15">
+        <v>0.24240999999999999</v>
       </c>
       <c r="AI12" s="5">
         <v>1.98</v>
@@ -29972,8 +29976,8 @@
       <c r="AF23" s="5">
         <v>0.52712999999999999</v>
       </c>
-      <c r="AG23" s="5">
-        <v>0.36530000000000001</v>
+      <c r="AG23" s="14">
+        <v>0.36473</v>
       </c>
       <c r="AI23" s="5">
         <v>2.21</v>
@@ -30875,7 +30879,7 @@
       <c r="T29" s="6">
         <v>1.1661700000000002</v>
       </c>
-      <c r="U29" s="6">
+      <c r="U29" s="17">
         <v>1.095</v>
       </c>
       <c r="V29" s="6">
@@ -32123,7 +32127,7 @@
       <c r="T37" s="6">
         <v>1.20804</v>
       </c>
-      <c r="U37" s="6">
+      <c r="U37" s="17">
         <v>0.85680000000000001</v>
       </c>
       <c r="V37" s="6">
@@ -32150,14 +32154,14 @@
       <c r="AD37" s="5">
         <v>0.72779000000000005</v>
       </c>
-      <c r="AE37" s="5">
-        <v>0.30520999999999998</v>
+      <c r="AE37" s="14">
+        <v>0.30620999999999998</v>
       </c>
       <c r="AF37" s="5">
         <v>0.67503999999999997</v>
       </c>
-      <c r="AG37" s="5">
-        <v>0.51502000000000003</v>
+      <c r="AG37" s="14">
+        <v>0.51602999999999999</v>
       </c>
       <c r="AI37" s="5">
         <v>1.9830000000000001</v>
@@ -34277,7 +34281,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6">
-        <v>-0.1447</v>
+        <v>-0.1449</v>
       </c>
       <c r="C8" s="6">
         <v>0.19769999999999999</v>
@@ -34494,8 +34498,8 @@
       <c r="U9" s="6">
         <v>0.30275000000000002</v>
       </c>
-      <c r="V9" s="6">
-        <v>0.12742000000000001</v>
+      <c r="V9" s="17">
+        <v>0.12741886999999999</v>
       </c>
       <c r="W9" s="6">
         <v>-0.40218999999999999</v>
@@ -35581,7 +35585,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="6">
-        <v>-9.2000000000000096E-2</v>
+        <v>-8.9599999999999999E-2</v>
       </c>
       <c r="C16" s="6">
         <v>0.21484</v>
@@ -36917,8 +36921,8 @@
       <c r="M24" s="6">
         <v>-0.22427424111503499</v>
       </c>
-      <c r="N24" s="6">
-        <v>0.13147</v>
+      <c r="N24" s="15">
+        <v>0.3196</v>
       </c>
       <c r="O24" s="6">
         <v>-0.18517</v>
@@ -37863,7 +37867,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="6">
-        <v>-0.1409</v>
+        <v>-0.13969999999999999</v>
       </c>
       <c r="C30" s="6">
         <v>0.19772000000000001</v>
@@ -38244,14 +38248,14 @@
       <c r="U32" s="6">
         <v>1.2295499999999999</v>
       </c>
-      <c r="V32" s="6">
-        <v>-3.6810000000000002E-2</v>
+      <c r="V32" s="15">
+        <v>-0.12889999999999999</v>
       </c>
       <c r="W32" s="6">
         <v>-0.59506000000000003</v>
       </c>
-      <c r="X32" s="6">
-        <v>-0.1197</v>
+      <c r="X32" s="15">
+        <v>-0.19051000000000001</v>
       </c>
       <c r="Y32">
         <v>-0.18176999999999999</v>
@@ -38385,8 +38389,8 @@
       <c r="M33" s="6">
         <v>-0.57673901628125401</v>
       </c>
-      <c r="N33" s="6">
-        <v>7.0250000000000007E-2</v>
+      <c r="N33" s="15">
+        <v>0.24329999999999999</v>
       </c>
       <c r="O33" s="6">
         <v>-0.24883</v>
@@ -38896,14 +38900,14 @@
       <c r="U36" s="6">
         <v>-0.92978000000000005</v>
       </c>
-      <c r="V36" s="6">
-        <v>-8.2129999999999995E-2</v>
+      <c r="V36" s="15">
+        <v>-6.6409999999999997E-2</v>
       </c>
       <c r="W36" s="6">
         <v>-0.62870000000000004</v>
       </c>
-      <c r="X36" s="6">
-        <v>-0.14899999999999999</v>
+      <c r="X36" s="15">
+        <v>-0.13780000000000001</v>
       </c>
       <c r="Y36">
         <v>-0.20404</v>
@@ -39168,7 +39172,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="6">
-        <v>-0.1028</v>
+        <v>-0.1009</v>
       </c>
       <c r="C38" s="6">
         <v>0.17968999999999999</v>
@@ -39206,8 +39210,8 @@
       <c r="O38" s="6">
         <v>-0.21840000000000001</v>
       </c>
-      <c r="P38" s="6">
-        <v>0.12353</v>
+      <c r="P38" s="15">
+        <v>-2.3999999999999998E-3</v>
       </c>
       <c r="Q38" s="6">
         <v>-0.10953</v>
@@ -39385,17 +39389,17 @@
       <c r="U39" s="6">
         <v>-0.33368999999999999</v>
       </c>
-      <c r="V39" s="6">
-        <v>-1.37E-2</v>
+      <c r="V39" s="15">
+        <v>7.6380000000000003E-2</v>
       </c>
       <c r="W39" s="6">
         <v>-0.22835</v>
       </c>
-      <c r="X39" s="6">
-        <v>-7.281E-2</v>
-      </c>
-      <c r="Y39">
-        <v>-0.10317</v>
+      <c r="X39" s="15">
+        <v>3.5699999999999998E-3</v>
+      </c>
+      <c r="Y39" s="13">
+        <v>3.517E-2</v>
       </c>
       <c r="AA39" s="6">
         <v>0.27585999999999999</v>
@@ -39711,14 +39715,14 @@
       <c r="U41" s="6">
         <v>0.60577999999999999</v>
       </c>
-      <c r="V41" s="6">
-        <v>-6.0929999999999998E-2</v>
+      <c r="V41" s="15">
+        <v>-6.5300000000000002E-3</v>
       </c>
       <c r="W41" s="6">
         <v>-0.51549999999999996</v>
       </c>
-      <c r="X41" s="6">
-        <v>-0.13663</v>
+      <c r="X41" s="15">
+        <v>-6.5339999999999995E-2</v>
       </c>
       <c r="Y41">
         <v>-0.15689</v>
@@ -40526,14 +40530,14 @@
       <c r="U46" s="6">
         <v>-4.99E-2</v>
       </c>
-      <c r="V46" s="6">
-        <v>0.32911000000000001</v>
+      <c r="V46" s="15">
+        <v>0.45222000000000001</v>
       </c>
       <c r="W46" s="6">
         <v>-0.25359999999999999</v>
       </c>
-      <c r="X46" s="6">
-        <v>3.3079999999999998E-2</v>
+      <c r="X46" s="15">
+        <v>0.40239000000000003</v>
       </c>
       <c r="Y46">
         <v>-0.15093000000000001</v>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1215FAA2-1529-4B3F-A1D3-1E3DEA636754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49030A4-2831-4551-A714-437020A7E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
@@ -32134,7 +32134,7 @@
         <v>0.80462999999999996</v>
       </c>
       <c r="W37" s="6">
-        <v>0.24847</v>
+        <v>0.25475999999999999</v>
       </c>
       <c r="X37" s="6">
         <v>0.75363999999999998</v>
@@ -40654,7 +40654,7 @@
         <v>0.19158</v>
       </c>
       <c r="G47" s="6">
-        <v>-0.14889723999999999</v>
+        <v>-0.15654999999999999</v>
       </c>
       <c r="H47" s="6">
         <v>8.1699999999999995E-2</v>
@@ -40817,7 +40817,7 @@
         <v>0.20326</v>
       </c>
       <c r="G48" s="6">
-        <v>-0.20550102000000001</v>
+        <v>-0.21245</v>
       </c>
       <c r="H48" s="6">
         <v>-1.12E-2</v>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49030A4-2831-4551-A714-437020A7E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89106177-EE8D-4EF4-A709-DA70C75F8AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1212,7 +1212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1245,6 +1245,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -16741,11 +16742,11 @@
       <c r="AL99" s="6">
         <v>1.754</v>
       </c>
-      <c r="AM99" s="6">
-        <v>5.617</v>
-      </c>
-      <c r="AN99" s="6">
-        <v>4.085</v>
+      <c r="AM99" s="15">
+        <v>6.1989999999999998</v>
+      </c>
+      <c r="AN99" s="15">
+        <v>3.3479999999999999</v>
       </c>
       <c r="AO99" s="6">
         <v>5.26</v>
@@ -28055,8 +28056,8 @@
       <c r="N11" s="5">
         <v>0.24238999999999999</v>
       </c>
-      <c r="O11" s="5">
-        <v>-2.8500000000000001E-2</v>
+      <c r="O11" s="14">
+        <v>-2.8369999999999999E-2</v>
       </c>
       <c r="P11" s="5">
         <v>0.17704</v>
@@ -28281,11 +28282,11 @@
       <c r="AN12" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="AO12" s="6">
-        <v>3.3690000000000002</v>
-      </c>
-      <c r="AP12" s="6">
-        <v>2.052</v>
+      <c r="AO12" s="15">
+        <v>5.2729999999999997</v>
+      </c>
+      <c r="AP12" s="15">
+        <v>4.968</v>
       </c>
       <c r="AR12">
         <v>-1.706968874</v>
@@ -32175,11 +32176,11 @@
       <c r="AL37" s="6">
         <v>3.1349999999999998</v>
       </c>
-      <c r="AM37" s="6">
-        <v>4.2380000000000004</v>
-      </c>
-      <c r="AN37" s="6">
-        <v>3.52413</v>
+      <c r="AM37" s="15">
+        <v>6.0750000000000002</v>
+      </c>
+      <c r="AN37" s="15">
+        <v>6.3170000000000002</v>
       </c>
       <c r="AO37" s="5">
         <v>3.508</v>
@@ -32295,8 +32296,8 @@
       <c r="X38" s="6">
         <v>0.16058</v>
       </c>
-      <c r="Y38" s="6">
-        <v>0.39316000000000001</v>
+      <c r="Y38" s="15">
+        <v>0.39323000000000002</v>
       </c>
       <c r="AA38" s="6">
         <v>0.69359999999999999</v>
@@ -32334,8 +32335,8 @@
       <c r="AM38" s="6">
         <v>4.3780000000000001</v>
       </c>
-      <c r="AN38" s="6">
-        <v>3.2746300000000002</v>
+      <c r="AN38" s="15">
+        <v>2.262</v>
       </c>
       <c r="AO38" s="5">
         <v>3.5459999999999998</v>
@@ -36858,8 +36859,8 @@
       <c r="AX23">
         <v>-1.5508</v>
       </c>
-      <c r="AY23">
-        <v>-1.4</v>
+      <c r="AY23" s="13">
+        <v>-1.41</v>
       </c>
       <c r="AZ23">
         <v>-1.58</v>
@@ -37012,8 +37013,8 @@
       <c r="AU24" s="1">
         <v>-1.7420897212870401</v>
       </c>
-      <c r="AV24">
-        <v>-0.88</v>
+      <c r="AV24" s="13">
+        <v>-0.89</v>
       </c>
       <c r="AW24">
         <v>-0.9</v>
@@ -38168,9 +38169,8 @@
       <c r="AZ31">
         <v>-1.36</v>
       </c>
-      <c r="BA31" s="1">
-        <f>BA35-AQ11</f>
-        <v>-1.3963418175986499</v>
+      <c r="BA31" s="13">
+        <v>-0.83338181759864993</v>
       </c>
       <c r="BB31">
         <v>-1.33</v>
@@ -38326,11 +38326,11 @@
       <c r="AX32">
         <v>-0.81010000000000004</v>
       </c>
-      <c r="AY32">
-        <v>-1.28</v>
-      </c>
-      <c r="AZ32">
-        <v>-1.3</v>
+      <c r="AY32" s="13">
+        <v>-1.29</v>
+      </c>
+      <c r="AZ32" s="13">
+        <v>-1.32</v>
       </c>
       <c r="BA32" s="1">
         <v>-1.4200581010194899</v>
@@ -38480,8 +38480,8 @@
       <c r="AU33" s="1">
         <v>-1.70297546347597</v>
       </c>
-      <c r="AV33">
-        <v>-0.94</v>
+      <c r="AV33" s="13">
+        <v>-0.97</v>
       </c>
       <c r="AW33">
         <v>-1.1000000000000001</v>
@@ -38978,11 +38978,11 @@
       <c r="AX36">
         <v>-0.80160000000000009</v>
       </c>
-      <c r="AY36">
-        <v>-1.28</v>
-      </c>
-      <c r="AZ36">
+      <c r="AY36" s="13">
         <v>-1.32</v>
+      </c>
+      <c r="AZ36" s="13">
+        <v>-1.35</v>
       </c>
       <c r="BA36" s="1">
         <v>-1.39139107300034</v>
@@ -39298,8 +39298,8 @@
       <c r="AV38">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="AW38">
-        <v>-0.93</v>
+      <c r="AW38" s="13">
+        <v>-0.97</v>
       </c>
       <c r="AX38">
         <v>-1.5481</v>
@@ -39467,11 +39467,11 @@
       <c r="AX39">
         <v>-0.91900000000000004</v>
       </c>
-      <c r="AY39">
-        <v>-1.1599999999999999</v>
-      </c>
-      <c r="AZ39">
-        <v>-1.1599999999999999</v>
+      <c r="AY39" s="13">
+        <v>-1.33</v>
+      </c>
+      <c r="AZ39" s="13">
+        <v>-1.34</v>
       </c>
       <c r="BA39" s="1">
         <v>-1.00104149966598</v>
@@ -39793,11 +39793,11 @@
       <c r="AX41">
         <v>-0.85820000000000007</v>
       </c>
-      <c r="AY41">
-        <v>-1.21</v>
-      </c>
-      <c r="AZ41">
-        <v>-1.22</v>
+      <c r="AY41" s="13">
+        <v>-1.29</v>
+      </c>
+      <c r="AZ41" s="13">
+        <v>-1.32</v>
       </c>
       <c r="BA41" s="1">
         <v>-0.98804249768075203</v>
@@ -40590,8 +40590,8 @@
       <c r="AR46">
         <v>-1.9410286965421899</v>
       </c>
-      <c r="AS46" s="9">
-        <v>-0.99</v>
+      <c r="AS46" s="18">
+        <v>-1</v>
       </c>
       <c r="AT46">
         <v>-1</v>
@@ -40608,11 +40608,11 @@
       <c r="AX46">
         <v>-1.6778</v>
       </c>
-      <c r="AY46">
-        <v>-0.96</v>
-      </c>
-      <c r="AZ46">
-        <v>-1</v>
+      <c r="AY46" s="13">
+        <v>-1.01</v>
+      </c>
+      <c r="AZ46" s="13">
+        <v>-1.01</v>
       </c>
       <c r="BA46" s="1">
         <v>-1.86135507799483</v>
@@ -40629,8 +40629,8 @@
       <c r="BF46">
         <v>-9.7430000000000606E-3</v>
       </c>
-      <c r="BH46">
-        <v>91.869</v>
+      <c r="BH46" s="13">
+        <v>91.870999999999995</v>
       </c>
       <c r="BI46" s="5"/>
     </row>
@@ -41803,7 +41803,7 @@
         <v>1.6970799999999999</v>
       </c>
       <c r="U11">
-        <v>1.7389600000000001</v>
+        <v>1.63636</v>
       </c>
       <c r="V11">
         <v>1.5765899999999999</v>
@@ -41818,7 +41818,7 @@
         <v>1.72082</v>
       </c>
       <c r="AA11">
-        <v>1.7389600000000001</v>
+        <v>1.63636</v>
       </c>
       <c r="AB11">
         <v>1.5262199999999999</v>
@@ -42736,7 +42736,7 @@
         <v>1.24682</v>
       </c>
       <c r="U25">
-        <v>1.4182699999999999</v>
+        <v>1.4366000000000001</v>
       </c>
       <c r="V25">
         <v>1.1994</v>
@@ -42751,7 +42751,7 @@
         <v>1.1541399999999999</v>
       </c>
       <c r="AA25">
-        <v>1.4182699999999999</v>
+        <v>1.4366000000000001</v>
       </c>
       <c r="AB25">
         <v>1.38422</v>
@@ -43746,8 +43746,8 @@
       <c r="S39">
         <v>-0.45025999999999999</v>
       </c>
-      <c r="U39">
-        <v>-0.32068999999999998</v>
+      <c r="U39" s="13">
+        <v>-0.19975999999999999</v>
       </c>
       <c r="V39">
         <v>-0.37719000000000003</v>
@@ -43761,8 +43761,8 @@
       <c r="Y39">
         <v>-0.56667999999999996</v>
       </c>
-      <c r="AA39">
-        <v>-0.32068999999999998</v>
+      <c r="AA39" s="13">
+        <v>-0.19975999999999999</v>
       </c>
       <c r="AB39">
         <v>-0.14199999999999999</v>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89106177-EE8D-4EF4-A709-DA70C75F8AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0417CAE0-A2A4-4632-845D-3DD285CE6F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0417CAE0-A2A4-4632-845D-3DD285CE6F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F53CDA-4CE5-4A0D-8274-C1185BE13507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
-    <sheet name="MR-TADF" sheetId="2" r:id="rId2"/>
-    <sheet name="Miyajima" sheetId="3" r:id="rId3"/>
-    <sheet name="Peng" sheetId="4" r:id="rId4"/>
-    <sheet name="Fig5" sheetId="5" r:id="rId5"/>
-    <sheet name="Fig3" sheetId="6" r:id="rId6"/>
+    <sheet name="MR-TADF-35" sheetId="2" r:id="rId2"/>
+    <sheet name="Heptazine-4" sheetId="3" r:id="rId3"/>
+    <sheet name="INVEST-45" sheetId="4" r:id="rId4"/>
+    <sheet name="Fig3c" sheetId="5" r:id="rId5"/>
+    <sheet name="Fig3a" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1136,7 +1136,7 @@
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.000;[Red]0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1191,6 +1191,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1212,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1231,21 +1239,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1527,7 +1530,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE162"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -1778,7 +1781,7 @@
       <c r="AP3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -1787,7 +1790,7 @@
       <c r="AT3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AV3" s="2" t="s">
@@ -1796,7 +1799,7 @@
       <c r="AW3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AY3" s="2" t="s">
@@ -1935,7 +1938,7 @@
         <v>5.3609999999999998</v>
       </c>
       <c r="AR4">
-        <v>-0.97249475943793695</v>
+        <v>-0.991059559437937</v>
       </c>
       <c r="AS4">
         <v>-0.98</v>
@@ -1944,7 +1947,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU4">
-        <v>-0.96252615758597504</v>
+        <v>-0.98875755758597483</v>
       </c>
       <c r="AV4">
         <v>-0.97</v>
@@ -1953,7 +1956,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX4">
-        <v>-0.91050000000000009</v>
+        <v>-0.97694490000000012</v>
       </c>
       <c r="AY4">
         <v>-0.95</v>
@@ -1962,7 +1965,7 @@
         <v>-0.95</v>
       </c>
       <c r="BA4">
-        <v>-0.94040000000000001</v>
+        <v>-0.98014309999999982</v>
       </c>
       <c r="BB4">
         <v>-0.96</v>
@@ -2091,7 +2094,7 @@
         <v>4.843</v>
       </c>
       <c r="AR5">
-        <v>-0.96724127302514995</v>
+        <v>-0.98584557302514986</v>
       </c>
       <c r="AS5">
         <v>-0.98</v>
@@ -2100,7 +2103,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU5">
-        <v>-0.95661222041414395</v>
+        <v>-0.98279462041414423</v>
       </c>
       <c r="AV5">
         <v>-0.97</v>
@@ -2109,7 +2112,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX5">
-        <v>-1.0410999999999999</v>
+        <v>-1.1517755000000001</v>
       </c>
       <c r="AY5">
         <v>-0.99</v>
@@ -2118,7 +2121,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA5">
-        <v>-0.98050000000000004</v>
+        <v>-1.0339537000000001</v>
       </c>
       <c r="BB5">
         <v>-0.92</v>
@@ -2247,7 +2250,7 @@
         <v>2.4409999999999998</v>
       </c>
       <c r="AR6">
-        <v>-1.9371136689999999</v>
+        <v>-1.9440799689999999</v>
       </c>
       <c r="AS6">
         <v>-1.97</v>
@@ -2256,7 +2259,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU6">
-        <v>-1.9156836429999999</v>
+        <v>-1.925106743</v>
       </c>
       <c r="AV6">
         <v>-1.95</v>
@@ -2265,7 +2268,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX6">
-        <v>-1.4328000000000001</v>
+        <v>-1.4836422</v>
       </c>
       <c r="AY6">
         <v>-0.76</v>
@@ -2274,7 +2277,7 @@
         <v>-0.83</v>
       </c>
       <c r="BA6">
-        <v>-1.8855494509999999</v>
+        <v>-1.8993265509999999</v>
       </c>
       <c r="BB6">
         <v>-1.94</v>
@@ -2403,7 +2406,7 @@
         <v>5.2709999999999999</v>
       </c>
       <c r="AR7">
-        <v>-0.96721558465072799</v>
+        <v>-0.9899476846507278</v>
       </c>
       <c r="AS7">
         <v>-0.98</v>
@@ -2412,7 +2415,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU7">
-        <v>-0.95509471600774198</v>
+        <v>-0.98746501600774206</v>
       </c>
       <c r="AV7">
         <v>-0.98</v>
@@ -2421,7 +2424,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX7">
-        <v>-1.0188999999999999</v>
+        <v>-1.1176143999999999</v>
       </c>
       <c r="AY7">
         <v>-0.79</v>
@@ -2430,7 +2433,7 @@
         <v>-0.73</v>
       </c>
       <c r="BA7">
-        <v>-0.92949999999999999</v>
+        <v>-0.98263549999999977</v>
       </c>
       <c r="BB7">
         <v>-0.97</v>
@@ -2559,7 +2562,7 @@
         <v>2.4590000000000001</v>
       </c>
       <c r="AR8">
-        <v>-1.931025744</v>
+        <v>-1.939636044</v>
       </c>
       <c r="AS8">
         <v>-1.94</v>
@@ -2568,7 +2571,7 @@
         <v>-1.93</v>
       </c>
       <c r="AU8">
-        <v>-1.9080280169999999</v>
+        <v>-1.9198704170000001</v>
       </c>
       <c r="AV8">
         <v>-1.89</v>
@@ -2577,7 +2580,7 @@
         <v>-1.91</v>
       </c>
       <c r="AX8">
-        <v>-1.2719</v>
+        <v>-1.3385963999999999</v>
       </c>
       <c r="AY8">
         <v>-1.2</v>
@@ -2586,7 +2589,7 @@
         <v>-1.18</v>
       </c>
       <c r="BA8">
-        <v>-1.6225541160000001</v>
+        <v>-1.6507332159999999</v>
       </c>
       <c r="BB8">
         <v>-1.45</v>
@@ -2715,7 +2718,7 @@
         <v>5.0350000000000001</v>
       </c>
       <c r="AR9">
-        <v>-0.96915271704134498</v>
+        <v>-0.98925551704134507</v>
       </c>
       <c r="AS9">
         <v>-0.98</v>
@@ -2724,7 +2727,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU9">
-        <v>-0.957158120006532</v>
+        <v>-0.98544702000653217</v>
       </c>
       <c r="AV9">
         <v>-0.97</v>
@@ -2733,7 +2736,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX9">
-        <v>-0.89539999999999997</v>
+        <v>-0.96744379999999985</v>
       </c>
       <c r="AY9">
         <v>-0.95</v>
@@ -2742,7 +2745,7 @@
         <v>-0.95</v>
       </c>
       <c r="BA9">
-        <v>-0.93030000000000002</v>
+        <v>-0.97563010000000006</v>
       </c>
       <c r="BB9">
         <v>-0.96</v>
@@ -2871,7 +2874,7 @@
         <v>2.2810000000000001</v>
       </c>
       <c r="AR10">
-        <v>-1.9374316309999999</v>
+        <v>-1.946337531</v>
       </c>
       <c r="AS10">
         <v>-1.93</v>
@@ -2880,7 +2883,7 @@
         <v>-1.94</v>
       </c>
       <c r="AU10">
-        <v>-1.915872383</v>
+        <v>-1.928126083</v>
       </c>
       <c r="AV10">
         <v>-1.88</v>
@@ -2889,7 +2892,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX10">
-        <v>-1.556</v>
+        <v>-1.5975497999999999</v>
       </c>
       <c r="AY10">
         <v>-1.58</v>
@@ -2898,7 +2901,7 @@
         <v>-1.65</v>
       </c>
       <c r="BA10">
-        <v>-1.8909684899999999</v>
+        <v>-1.90746229</v>
       </c>
       <c r="BB10">
         <v>-1.93</v>
@@ -3027,7 +3030,7 @@
         <v>2.3260000000000001</v>
       </c>
       <c r="AR11">
-        <v>-1.9392559069999999</v>
+        <v>-1.948625907</v>
       </c>
       <c r="AS11">
         <v>-1.96</v>
@@ -3036,7 +3039,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU11">
-        <v>-1.917265507</v>
+        <v>-1.9305086069999999</v>
       </c>
       <c r="AV11">
         <v>-1.93</v>
@@ -3045,7 +3048,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX11">
-        <v>-1.2396</v>
+        <v>-1.3229963</v>
       </c>
       <c r="AY11">
         <v>-1.27</v>
@@ -3054,7 +3057,7 @@
         <v>-1.28</v>
       </c>
       <c r="BA11">
-        <v>-1.702043382</v>
+        <v>-1.7292908819999999</v>
       </c>
       <c r="BB11">
         <v>-1.65</v>
@@ -3183,7 +3186,7 @@
         <v>3.5470000000000002</v>
       </c>
       <c r="AR12">
-        <v>-1.6339999999999999</v>
+        <v>-1.6672232</v>
       </c>
       <c r="AS12">
         <v>-1.17</v>
@@ -3192,7 +3195,7 @@
         <v>-1.17</v>
       </c>
       <c r="AU12">
-        <v>-1.0263497316405901</v>
+        <v>-1.07842063164059</v>
       </c>
       <c r="AV12">
         <v>-1.1299999999999999</v>
@@ -3201,7 +3204,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AX12">
-        <v>-1.1671</v>
+        <v>-1.2801693999999999</v>
       </c>
       <c r="AY12">
         <v>-1.1200000000000001</v>
@@ -3210,7 +3213,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BA12">
-        <v>-1.4418</v>
+        <v>-1.5101145</v>
       </c>
       <c r="BB12">
         <v>-1.1399999999999999</v>
@@ -3339,7 +3342,7 @@
         <v>2.3239999999999998</v>
       </c>
       <c r="AR13">
-        <v>-1.9322569759999999</v>
+        <v>-1.940730676</v>
       </c>
       <c r="AS13">
         <v>-1.94</v>
@@ -3348,7 +3351,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU13">
-        <v>-1.8994558619999999</v>
+        <v>-1.911673062</v>
       </c>
       <c r="AV13">
         <v>-1.87</v>
@@ -3357,7 +3360,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX13">
-        <v>-1.3228</v>
+        <v>-1.3880498999999999</v>
       </c>
       <c r="AY13">
         <v>-1.24</v>
@@ -3366,7 +3369,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BA13">
-        <v>-1.598015054</v>
+        <v>-1.6196884540000001</v>
       </c>
       <c r="BB13">
         <v>-1.73</v>
@@ -3495,7 +3498,7 @@
         <v>2.9910000000000001</v>
       </c>
       <c r="AR14">
-        <v>-1.929636997</v>
+        <v>-1.9361718969999999</v>
       </c>
       <c r="AS14">
         <v>-1.8</v>
@@ -3504,7 +3507,7 @@
         <v>-1.7</v>
       </c>
       <c r="AU14">
-        <v>-1.8975275439999999</v>
+        <v>-1.907082044</v>
       </c>
       <c r="AV14">
         <v>-1.62</v>
@@ -3513,7 +3516,7 @@
         <v>-1.53</v>
       </c>
       <c r="AX14">
-        <v>-0.8387</v>
+        <v>-0.92194689999999979</v>
       </c>
       <c r="AY14">
         <v>-1.02</v>
@@ -3522,7 +3525,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA14">
-        <v>-1.845770117</v>
+        <v>-1.8628294169999999</v>
       </c>
       <c r="BB14">
         <v>-1.02</v>
@@ -3651,7 +3654,7 @@
         <v>2.6259999999999999</v>
       </c>
       <c r="AR15">
-        <v>-1.447591214</v>
+        <v>-1.4667725140000001</v>
       </c>
       <c r="AS15">
         <v>-0.9</v>
@@ -3660,7 +3663,7 @@
         <v>-1.32</v>
       </c>
       <c r="AU15">
-        <v>-1.3059478929999999</v>
+        <v>-1.337214793</v>
       </c>
       <c r="AV15">
         <v>-0.97</v>
@@ -3669,7 +3672,7 @@
         <v>-1.2</v>
       </c>
       <c r="AX15">
-        <v>-1.2883</v>
+        <v>-1.3744559999999999</v>
       </c>
       <c r="AY15">
         <v>-1.17</v>
@@ -3678,7 +3681,7 @@
         <v>-0.78</v>
       </c>
       <c r="BA15">
-        <v>-1.452331799</v>
+        <v>-1.5003101990000001</v>
       </c>
       <c r="BB15">
         <v>-1.32</v>
@@ -3807,7 +3810,7 @@
         <v>2.9159999999999999</v>
       </c>
       <c r="AR16">
-        <v>-1.9016319740000001</v>
+        <v>-1.9106109739999999</v>
       </c>
       <c r="AS16">
         <v>-1.88</v>
@@ -3816,7 +3819,7 @@
         <v>-1.83</v>
       </c>
       <c r="AU16">
-        <v>-1.7412460830000001</v>
+        <v>-1.7599702829999999</v>
       </c>
       <c r="AV16">
         <v>-1.61</v>
@@ -3825,7 +3828,7 @@
         <v>-1.59</v>
       </c>
       <c r="AX16">
-        <v>-1.0710999999999999</v>
+        <v>-1.172536</v>
       </c>
       <c r="AY16">
         <v>-0.95</v>
@@ -3834,7 +3837,7 @@
         <v>-0.85</v>
       </c>
       <c r="BA16">
-        <v>-1.763292021</v>
+        <v>-1.804789921</v>
       </c>
       <c r="BB16">
         <v>-1.47</v>
@@ -3963,7 +3966,7 @@
         <v>2.907</v>
       </c>
       <c r="AR17">
-        <v>-1.40127157</v>
+        <v>-1.4223102700000001</v>
       </c>
       <c r="AS17">
         <v>-0.94</v>
@@ -3972,7 +3975,7 @@
         <v>-1.33</v>
       </c>
       <c r="AU17">
-        <v>-1.556104232</v>
+        <v>-1.589929232</v>
       </c>
       <c r="AV17">
         <v>-1.1200000000000001</v>
@@ -3981,7 +3984,7 @@
         <v>-1.24</v>
       </c>
       <c r="AX17">
-        <v>-1.1815</v>
+        <v>-1.2924617</v>
       </c>
       <c r="AY17">
         <v>-1.1200000000000001</v>
@@ -3990,7 +3993,7 @@
         <v>-1.03</v>
       </c>
       <c r="BA17">
-        <v>-1.2618</v>
+        <v>-1.3268211999999999</v>
       </c>
       <c r="BB17">
         <v>-1.02</v>
@@ -4119,7 +4122,7 @@
         <v>2.9329999999999998</v>
       </c>
       <c r="AR18">
-        <v>-1.9040444080000001</v>
+        <v>-1.911524708</v>
       </c>
       <c r="AS18">
         <v>-1.87</v>
@@ -4128,7 +4131,7 @@
         <v>-1.83</v>
       </c>
       <c r="AU18">
-        <v>-1.866911279</v>
+        <v>-1.878929579</v>
       </c>
       <c r="AV18">
         <v>-1.77</v>
@@ -4137,7 +4140,7 @@
         <v>-1.73</v>
       </c>
       <c r="AX18">
-        <v>-1.3063</v>
+        <v>-1.3952088</v>
       </c>
       <c r="AY18">
         <v>-0.79</v>
@@ -4146,7 +4149,7 @@
         <v>-0.74</v>
       </c>
       <c r="BA18">
-        <v>-1.7574716800000001</v>
+        <v>-1.7954035800000001</v>
       </c>
       <c r="BB18">
         <v>-1.44</v>
@@ -4275,7 +4278,7 @@
         <v>2.9159999999999999</v>
       </c>
       <c r="AR19">
-        <v>-1.467711727</v>
+        <v>-1.4864444269999999</v>
       </c>
       <c r="AS19">
         <v>-0.71</v>
@@ -4284,7 +4287,7 @@
         <v>-1.39</v>
       </c>
       <c r="AU19">
-        <v>-1.328405748</v>
+        <v>-1.3593635479999999</v>
       </c>
       <c r="AV19">
         <v>-1.1299999999999999</v>
@@ -4293,7 +4296,7 @@
         <v>-1.28</v>
       </c>
       <c r="AX19">
-        <v>-1.1108</v>
+        <v>-1.1946622</v>
       </c>
       <c r="AY19">
         <v>-1.22</v>
@@ -4302,7 +4305,7 @@
         <v>-1.22</v>
       </c>
       <c r="BA19">
-        <v>-1.2230000000000001</v>
+        <v>-1.2807134</v>
       </c>
       <c r="BB19">
         <v>-0.84</v>
@@ -4431,7 +4434,7 @@
         <v>3.1680000000000001</v>
       </c>
       <c r="AR20">
-        <v>-1.939200635</v>
+        <v>-1.943098735</v>
       </c>
       <c r="AS20">
         <v>-1.98</v>
@@ -4440,7 +4443,7 @@
         <v>-1.89</v>
       </c>
       <c r="AU20">
-        <v>-1.913012393</v>
+        <v>-1.9182629929999999</v>
       </c>
       <c r="AV20">
         <v>-1.94</v>
@@ -4449,7 +4452,7 @@
         <v>-1.72</v>
       </c>
       <c r="AX20">
-        <v>-1.5506</v>
+        <v>-1.6412983000000001</v>
       </c>
       <c r="AY20">
         <v>-0.95</v>
@@ -4458,7 +4461,7 @@
         <v>-0.96</v>
       </c>
       <c r="BA20">
-        <v>-1.7326372889999999</v>
+        <v>-1.7796270890000001</v>
       </c>
       <c r="BB20">
         <v>-0.96</v>
@@ -4587,7 +4590,7 @@
         <v>3.3250000000000002</v>
       </c>
       <c r="AR21">
-        <v>-1.969394613</v>
+        <v>-1.9922003129999999</v>
       </c>
       <c r="AS21">
         <v>-0.99</v>
@@ -4596,7 +4599,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU21">
-        <v>-1.0169999999999999</v>
+        <v>-1.048397</v>
       </c>
       <c r="AV21">
         <v>-0.99</v>
@@ -4605,7 +4608,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX21">
-        <v>-1.5761000000000001</v>
+        <v>-1.6504738999999999</v>
       </c>
       <c r="AY21">
         <v>-0.98</v>
@@ -4614,7 +4617,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA21">
-        <v>-1.7606999999999999</v>
+        <v>-1.8135391999999999</v>
       </c>
       <c r="BB21">
         <v>-0.98</v>
@@ -4743,7 +4746,7 @@
         <v>2.8159999999999998</v>
       </c>
       <c r="AR22">
-        <v>-1.9680880039999999</v>
+        <v>-1.994325704</v>
       </c>
       <c r="AS22">
         <v>-0.99</v>
@@ -4752,7 +4755,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU22">
-        <v>-1.9558043759999999</v>
+        <v>-1.992074176</v>
       </c>
       <c r="AV22">
         <v>-0.99</v>
@@ -4761,7 +4764,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX22">
-        <v>-1.7675000000000001</v>
+        <v>-1.8490994000000001</v>
       </c>
       <c r="AY22">
         <v>-0.98</v>
@@ -4770,7 +4773,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA22">
-        <v>-0.98080000000000001</v>
+        <v>-1.0418152000000001</v>
       </c>
       <c r="BB22">
         <v>-0.98</v>
@@ -4899,7 +4902,7 @@
         <v>3.2490000000000001</v>
       </c>
       <c r="AR23">
-        <v>-1.964919563</v>
+        <v>-1.9933063630000001</v>
       </c>
       <c r="AS23">
         <v>-0.99</v>
@@ -4908,7 +4911,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU23">
-        <v>-0.98080000000000001</v>
+        <v>-1.0199533999999999</v>
       </c>
       <c r="AV23">
         <v>-0.99</v>
@@ -4917,7 +4920,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX23">
-        <v>-0.92209999999999992</v>
+        <v>-1.0101686999999999</v>
       </c>
       <c r="AY23">
         <v>-0.98</v>
@@ -4926,7 +4929,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA23">
-        <v>-0.89053607099999998</v>
+        <v>-0.95153367099999997</v>
       </c>
       <c r="BB23">
         <v>-0.98</v>
@@ -5055,7 +5058,7 @@
         <v>1.976</v>
       </c>
       <c r="AR24">
-        <v>-1.96486166</v>
+        <v>-1.9922926599999999</v>
       </c>
       <c r="AS24">
         <v>-0.99</v>
@@ -5064,7 +5067,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU24">
-        <v>-1.9514060529999999</v>
+        <v>-1.989350253</v>
       </c>
       <c r="AV24">
         <v>-0.99</v>
@@ -5073,7 +5076,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX24">
-        <v>-0.74089999999999989</v>
+        <v>-0.83031720000000009</v>
       </c>
       <c r="AY24">
         <v>-0.98</v>
@@ -5082,7 +5085,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA24">
-        <v>-1.9148320910000001</v>
+        <v>-1.981618391</v>
       </c>
       <c r="BB24">
         <v>-0.98</v>
@@ -5211,7 +5214,7 @@
         <v>2</v>
       </c>
       <c r="AR25">
-        <v>-1.967352773</v>
+        <v>-1.993993473</v>
       </c>
       <c r="AS25">
         <v>-0.99</v>
@@ -5220,7 +5223,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU25">
-        <v>-1.955152389</v>
+        <v>-1.991896289</v>
       </c>
       <c r="AV25">
         <v>-0.99</v>
@@ -5229,7 +5232,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX25">
-        <v>-0.75869999999999993</v>
+        <v>-0.84655839999999993</v>
       </c>
       <c r="AY25">
         <v>-0.98</v>
@@ -5238,7 +5241,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA25">
-        <v>-1.9182143620000001</v>
+        <v>-1.984294462</v>
       </c>
       <c r="BB25">
         <v>-0.98</v>
@@ -5367,7 +5370,7 @@
         <v>2.9470000000000001</v>
       </c>
       <c r="AR26">
-        <v>-1.971042076</v>
+        <v>-1.9952333760000001</v>
       </c>
       <c r="AS26">
         <v>-0.99</v>
@@ -5376,7 +5379,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU26">
-        <v>-1.9597609039999999</v>
+        <v>-1.993320204</v>
       </c>
       <c r="AV26">
         <v>-0.99</v>
@@ -5385,7 +5388,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX26">
-        <v>-0.74130000000000007</v>
+        <v>-0.81849450000000012</v>
       </c>
       <c r="AY26">
         <v>-0.98</v>
@@ -5394,7 +5397,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA26">
-        <v>-1.787655733</v>
+        <v>-1.8444240329999999</v>
       </c>
       <c r="BB26">
         <v>-0.98</v>
@@ -5523,7 +5526,7 @@
         <v>3.863</v>
       </c>
       <c r="AR27">
-        <v>-1.9133586220000001</v>
+        <v>-1.923078622</v>
       </c>
       <c r="AS27">
         <v>-1.21</v>
@@ -5532,7 +5535,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU27">
-        <v>-1.875877676</v>
+        <v>-1.889566876</v>
       </c>
       <c r="AV27">
         <v>-1.06</v>
@@ -5541,7 +5544,7 @@
         <v>-1.06</v>
       </c>
       <c r="AX27">
-        <v>-1.9374</v>
+        <v>-1.9674248999999999</v>
       </c>
       <c r="AY27">
         <v>-1.25</v>
@@ -5550,7 +5553,7 @@
         <v>-1.34</v>
       </c>
       <c r="BA27">
-        <v>-1.8010880250000001</v>
+        <v>-1.821245625</v>
       </c>
       <c r="BB27">
         <v>-1.28</v>
@@ -5679,7 +5682,7 @@
         <v>3.8210000000000002</v>
       </c>
       <c r="AR28">
-        <v>-1.914449965</v>
+        <v>-1.923483665</v>
       </c>
       <c r="AS28">
         <v>-1.26</v>
@@ -5688,7 +5691,7 @@
         <v>-1</v>
       </c>
       <c r="AU28">
-        <v>-1.877615679</v>
+        <v>-1.890300579</v>
       </c>
       <c r="AV28">
         <v>-1.08</v>
@@ -5697,7 +5700,7 @@
         <v>-1.05</v>
       </c>
       <c r="AX28">
-        <v>-1.6628000000000001</v>
+        <v>-1.691972</v>
       </c>
       <c r="AY28">
         <v>-1.24</v>
@@ -5706,7 +5709,7 @@
         <v>-1.34</v>
       </c>
       <c r="BA28">
-        <v>-1.8018450800000001</v>
+        <v>-1.82129728</v>
       </c>
       <c r="BB28">
         <v>-1.27</v>
@@ -5835,7 +5838,7 @@
         <v>3.7229999999999999</v>
       </c>
       <c r="AR29">
-        <v>-1.9128112719999999</v>
+        <v>-1.923917672</v>
       </c>
       <c r="AS29">
         <v>-1.34</v>
@@ -5844,7 +5847,7 @@
         <v>-1.22</v>
       </c>
       <c r="AU29">
-        <v>-1.8761250380000001</v>
+        <v>-1.892122638</v>
       </c>
       <c r="AV29">
         <v>-1.17</v>
@@ -5853,7 +5856,7 @@
         <v>-1.07</v>
       </c>
       <c r="AX29">
-        <v>-1.7258</v>
+        <v>-1.7675757000000001</v>
       </c>
       <c r="AY29">
         <v>-1.0900000000000001</v>
@@ -5862,7 +5865,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA29">
-        <v>-1.802491007</v>
+        <v>-1.8283163069999999</v>
       </c>
       <c r="BB29">
         <v>-1.1100000000000001</v>
@@ -5991,7 +5994,7 @@
         <v>3.738</v>
       </c>
       <c r="AR30">
-        <v>-1.910944424</v>
+        <v>-1.9208347240000001</v>
       </c>
       <c r="AS30">
         <v>-1.38</v>
@@ -6000,7 +6003,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AU30">
-        <v>-1.8729074830000001</v>
+        <v>-1.8870504829999999</v>
       </c>
       <c r="AV30">
         <v>-1.17</v>
@@ -6009,7 +6012,7 @@
         <v>-1</v>
       </c>
       <c r="AX30">
-        <v>-1.6700999999999999</v>
+        <v>-1.7109979</v>
       </c>
       <c r="AY30">
         <v>-1.18</v>
@@ -6018,7 +6021,7 @@
         <v>-1.26</v>
       </c>
       <c r="BA30">
-        <v>-1.786370413</v>
+        <v>-1.8111950130000001</v>
       </c>
       <c r="BB30">
         <v>-1.2</v>
@@ -6147,7 +6150,7 @@
         <v>3.7450000000000001</v>
       </c>
       <c r="AR31">
-        <v>-1.8982473120000001</v>
+        <v>-1.9126732120000001</v>
       </c>
       <c r="AS31">
         <v>-1.32</v>
@@ -6156,7 +6159,7 @@
         <v>-1.26</v>
       </c>
       <c r="AU31">
-        <v>-1.852291009</v>
+        <v>-1.8735902090000001</v>
       </c>
       <c r="AV31">
         <v>-1.17</v>
@@ -6165,7 +6168,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AX31">
-        <v>-1.5424</v>
+        <v>-1.603432</v>
       </c>
       <c r="AY31">
         <v>-1.01</v>
@@ -6174,7 +6177,7 @@
         <v>-1.06</v>
       </c>
       <c r="BA31">
-        <v>-1.751727601</v>
+        <v>-1.788896501</v>
       </c>
       <c r="BB31">
         <v>-1</v>
@@ -6303,7 +6306,7 @@
         <v>3.286</v>
       </c>
       <c r="AR32">
-        <v>-1.9305532160000001</v>
+        <v>-1.9396440159999999</v>
       </c>
       <c r="AS32">
         <v>-1.72</v>
@@ -6312,7 +6315,7 @@
         <v>-1.7</v>
       </c>
       <c r="AU32">
-        <v>-1.90519306</v>
+        <v>-1.9181824599999999</v>
       </c>
       <c r="AV32">
         <v>-1.54</v>
@@ -6321,7 +6324,7 @@
         <v>-1.54</v>
       </c>
       <c r="AX32">
-        <v>-1.7914000000000001</v>
+        <v>-1.8271868</v>
       </c>
       <c r="AY32">
         <v>-1.03</v>
@@ -6330,7 +6333,7 @@
         <v>-0.99</v>
       </c>
       <c r="BA32">
-        <v>-1.850917615</v>
+        <v>-1.873571015</v>
       </c>
       <c r="BB32">
         <v>-1.06</v>
@@ -6459,7 +6462,7 @@
         <v>3.593</v>
       </c>
       <c r="AR33">
-        <v>-1.9228604540000001</v>
+        <v>-1.932076854</v>
       </c>
       <c r="AS33">
         <v>-1.48</v>
@@ -6468,7 +6471,7 @@
         <v>-1.37</v>
       </c>
       <c r="AU33">
-        <v>-1.892759557</v>
+        <v>-1.905819457</v>
       </c>
       <c r="AV33">
         <v>-1.28</v>
@@ -6477,7 +6480,7 @@
         <v>-1.18</v>
       </c>
       <c r="AX33">
-        <v>-1.7825</v>
+        <v>-1.8152549</v>
       </c>
       <c r="AY33">
         <v>-1.08</v>
@@ -6486,7 +6489,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BA33">
-        <v>-1.8373492840000001</v>
+        <v>-1.8584258840000001</v>
       </c>
       <c r="BB33">
         <v>-1.1000000000000001</v>
@@ -6615,7 +6618,7 @@
         <v>3.2610000000000001</v>
       </c>
       <c r="AR34">
-        <v>-1.9281375780000001</v>
+        <v>-1.9382673779999999</v>
       </c>
       <c r="AS34">
         <v>-1.69</v>
@@ -6624,7 +6627,7 @@
         <v>-1.69</v>
       </c>
       <c r="AU34">
-        <v>-1.901896987</v>
+        <v>-1.916476587</v>
       </c>
       <c r="AV34">
         <v>-1.52</v>
@@ -6633,7 +6636,7 @@
         <v>-1.54</v>
       </c>
       <c r="AX34">
-        <v>-1.7766</v>
+        <v>-1.8177741000000001</v>
       </c>
       <c r="AY34">
         <v>-1.06</v>
@@ -6642,7 +6645,7 @@
         <v>-1.03</v>
       </c>
       <c r="BA34">
-        <v>-1.8425921279999999</v>
+        <v>-1.8683186279999999</v>
       </c>
       <c r="BB34">
         <v>-1.1000000000000001</v>
@@ -6771,7 +6774,7 @@
         <v>3.2440000000000002</v>
       </c>
       <c r="AR35">
-        <v>-1.929595698</v>
+        <v>-1.939720798</v>
       </c>
       <c r="AS35">
         <v>-1.71</v>
@@ -6780,7 +6783,7 @@
         <v>-1.71</v>
       </c>
       <c r="AU35">
-        <v>-1.903576089</v>
+        <v>-1.918175789</v>
       </c>
       <c r="AV35">
         <v>-1.54</v>
@@ -6789,7 +6792,7 @@
         <v>-1.56</v>
       </c>
       <c r="AX35">
-        <v>-1.776</v>
+        <v>-1.8174777</v>
       </c>
       <c r="AY35">
         <v>-1.07</v>
@@ -6798,7 +6801,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA35">
-        <v>-1.8454365399999999</v>
+        <v>-1.8713828400000001</v>
       </c>
       <c r="BB35">
         <v>-1.1100000000000001</v>
@@ -6927,7 +6930,7 @@
         <v>3.871</v>
       </c>
       <c r="AR36">
-        <v>-1.9130818380000001</v>
+        <v>-1.9219983380000001</v>
       </c>
       <c r="AS36">
         <v>-1.23</v>
@@ -6936,7 +6939,7 @@
         <v>-1</v>
       </c>
       <c r="AU36">
-        <v>-1.8749607639999999</v>
+        <v>-1.887548464</v>
       </c>
       <c r="AV36">
         <v>-1.05</v>
@@ -6945,7 +6948,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AX36">
-        <v>-1.5236000000000001</v>
+        <v>-1.5558041</v>
       </c>
       <c r="AY36">
         <v>-1.26</v>
@@ -6954,7 +6957,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA36">
-        <v>-1.7922011920000001</v>
+        <v>-1.8121811919999999</v>
       </c>
       <c r="BB36">
         <v>-1.29</v>
@@ -7083,7 +7086,7 @@
         <v>3.766</v>
       </c>
       <c r="AR37">
-        <v>-1.91610134</v>
+        <v>-1.9241596400000001</v>
       </c>
       <c r="AS37">
         <v>-1.31</v>
@@ -7092,7 +7095,7 @@
         <v>-1.03</v>
       </c>
       <c r="AU37">
-        <v>-1.8799192419999999</v>
+        <v>-1.8911049419999999</v>
       </c>
       <c r="AV37">
         <v>-1.1100000000000001</v>
@@ -7101,7 +7104,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX37">
-        <v>-1.6012999999999999</v>
+        <v>-1.6269925000000001</v>
       </c>
       <c r="AY37">
         <v>-1.25</v>
@@ -7110,7 +7113,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA37">
-        <v>-1.804377028</v>
+        <v>-1.821766928</v>
       </c>
       <c r="BB37">
         <v>-1.28</v>
@@ -7239,7 +7242,7 @@
         <v>3.8130000000000002</v>
       </c>
       <c r="AR38">
-        <v>-1.903784173</v>
+        <v>-1.919103073</v>
       </c>
       <c r="AS38">
         <v>-1.33</v>
@@ -7248,7 +7251,7 @@
         <v>-1.31</v>
       </c>
       <c r="AU38">
-        <v>-1.861653639</v>
+        <v>-1.883800739</v>
       </c>
       <c r="AV38">
         <v>-1.19</v>
@@ -7257,7 +7260,7 @@
         <v>-1.17</v>
       </c>
       <c r="AX38">
-        <v>-1.7547999999999999</v>
+        <v>-1.8084282</v>
       </c>
       <c r="AY38">
         <v>-1</v>
@@ -7266,7 +7269,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA38">
-        <v>-1.7772597990000001</v>
+        <v>-1.8106006990000001</v>
       </c>
       <c r="BB38">
         <v>-1.01</v>
@@ -7395,7 +7398,7 @@
         <v>3.6859999999999999</v>
       </c>
       <c r="AR39">
-        <v>-1.884285448</v>
+        <v>-1.8974102479999999</v>
       </c>
       <c r="AS39">
         <v>-1.35</v>
@@ -7404,7 +7407,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AU39">
-        <v>-1.829042346</v>
+        <v>-1.849444546</v>
       </c>
       <c r="AV39">
         <v>-1.0900000000000001</v>
@@ -7413,7 +7416,7 @@
         <v>-0.95</v>
       </c>
       <c r="AX39">
-        <v>-1.4674</v>
+        <v>-1.5435620000000001</v>
       </c>
       <c r="AY39">
         <v>-1.1399999999999999</v>
@@ -7422,7 +7425,7 @@
         <v>-1.17</v>
       </c>
       <c r="BA39">
-        <v>-1.668974441</v>
+        <v>-1.7135412409999999</v>
       </c>
       <c r="BB39">
         <v>-1.1100000000000001</v>
@@ -7551,7 +7554,7 @@
         <v>3.782</v>
       </c>
       <c r="AR40">
-        <v>-1.914816523</v>
+        <v>-1.923476623</v>
       </c>
       <c r="AS40">
         <v>-1.44</v>
@@ -7560,7 +7563,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AU40">
-        <v>-1.8774864680000001</v>
+        <v>-1.889385568</v>
       </c>
       <c r="AV40">
         <v>-1.2</v>
@@ -7569,7 +7572,7 @@
         <v>-0.96</v>
       </c>
       <c r="AX40">
-        <v>-1.5585</v>
+        <v>-1.5876809999999999</v>
       </c>
       <c r="AY40">
         <v>-1.25</v>
@@ -7578,7 +7581,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA40">
-        <v>-1.795594774</v>
+        <v>-1.8142215740000001</v>
       </c>
       <c r="BB40">
         <v>-1.28</v>
@@ -7707,7 +7710,7 @@
         <v>3.5390000000000001</v>
       </c>
       <c r="AR41">
-        <v>-1.8702911879999999</v>
+        <v>-1.8817376880000001</v>
       </c>
       <c r="AS41">
         <v>-1.3</v>
@@ -7716,7 +7719,7 @@
         <v>-1.18</v>
       </c>
       <c r="AU41">
-        <v>-1.8185128820000001</v>
+        <v>-1.8355907819999999</v>
       </c>
       <c r="AV41">
         <v>-1.1200000000000001</v>
@@ -7725,7 +7728,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX41">
-        <v>-1.5459000000000001</v>
+        <v>-1.5966309999999999</v>
       </c>
       <c r="AY41">
         <v>-0.97</v>
@@ -7734,7 +7737,7 @@
         <v>-1.01</v>
       </c>
       <c r="BA41">
-        <v>-1.6886301720000001</v>
+        <v>-1.722148172</v>
       </c>
       <c r="BB41">
         <v>-0.86</v>
@@ -7863,7 +7866,7 @@
         <v>3.45</v>
       </c>
       <c r="AR42">
-        <v>-1.9279841740000001</v>
+        <v>-1.937061774</v>
       </c>
       <c r="AS42">
         <v>-1.66</v>
@@ -7872,7 +7875,7 @@
         <v>-1.56</v>
       </c>
       <c r="AU42">
-        <v>-1.900671811</v>
+        <v>-1.913654411</v>
       </c>
       <c r="AV42">
         <v>-1.44</v>
@@ -7881,7 +7884,7 @@
         <v>-1.36</v>
       </c>
       <c r="AX42">
-        <v>-1.8007</v>
+        <v>-1.8357943000000001</v>
       </c>
       <c r="AY42">
         <v>-1</v>
@@ -7890,7 +7893,7 @@
         <v>-1.07</v>
       </c>
       <c r="BA42">
-        <v>-1.8460024500000001</v>
+        <v>-1.8689847500000001</v>
       </c>
       <c r="BB42">
         <v>-1.03</v>
@@ -8019,7 +8022,7 @@
         <v>3.3079999999999998</v>
       </c>
       <c r="AR43">
-        <v>-1.9218456719999999</v>
+        <v>-1.9294059720000001</v>
       </c>
       <c r="AS43">
         <v>-1.73</v>
@@ -8028,7 +8031,7 @@
         <v>-1.66</v>
       </c>
       <c r="AU43">
-        <v>-1.892062801</v>
+        <v>-1.9027748010000001</v>
       </c>
       <c r="AV43">
         <v>-1.53</v>
@@ -8037,7 +8040,7 @@
         <v>-1.48</v>
       </c>
       <c r="AX43">
-        <v>-1.7763</v>
+        <v>-1.8079904</v>
       </c>
       <c r="AY43">
         <v>-0.98</v>
@@ -8046,7 +8049,7 @@
         <v>-0.92</v>
       </c>
       <c r="BA43">
-        <v>-1.8206067180000001</v>
+        <v>-1.840376518</v>
       </c>
       <c r="BB43">
         <v>-1.06</v>
@@ -8175,7 +8178,7 @@
         <v>3.6760000000000002</v>
       </c>
       <c r="AR44">
-        <v>-1.8830089290000001</v>
+        <v>-1.8937506289999999</v>
       </c>
       <c r="AS44">
         <v>-1.22</v>
@@ -8184,7 +8187,7 @@
         <v>-1</v>
       </c>
       <c r="AU44">
-        <v>-1.8328717990000001</v>
+        <v>-1.8489999989999999</v>
       </c>
       <c r="AV44">
         <v>-1.04</v>
@@ -8193,7 +8196,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX44">
-        <v>-1.5377000000000001</v>
+        <v>-1.5880722</v>
       </c>
       <c r="AY44">
         <v>-1.1000000000000001</v>
@@ -8202,7 +8205,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BA44">
-        <v>-1.7064654859999999</v>
+        <v>-1.7389639859999999</v>
       </c>
       <c r="BB44">
         <v>-1.04</v>
@@ -8331,7 +8334,7 @@
         <v>3.7490000000000001</v>
       </c>
       <c r="AR45">
-        <v>-1.8920947379999999</v>
+        <v>-1.902045038</v>
       </c>
       <c r="AS45">
         <v>-1.23</v>
@@ -8340,7 +8343,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU45">
-        <v>-1.8462107990000001</v>
+        <v>-1.861116099</v>
       </c>
       <c r="AV45">
         <v>-1.04</v>
@@ -8349,7 +8352,7 @@
         <v>-1.02</v>
       </c>
       <c r="AX45">
-        <v>-1.5366</v>
+        <v>-1.5838877</v>
       </c>
       <c r="AY45">
         <v>-1.17</v>
@@ -8358,7 +8361,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA45">
-        <v>-1.7303560339999999</v>
+        <v>-1.760228334</v>
       </c>
       <c r="BB45">
         <v>-1.1299999999999999</v>
@@ -8487,7 +8490,7 @@
         <v>3.419</v>
       </c>
       <c r="AR46">
-        <v>-1.927058846</v>
+        <v>-1.937047846</v>
       </c>
       <c r="AS46">
         <v>-1.61</v>
@@ -8496,7 +8499,7 @@
         <v>-1.56</v>
       </c>
       <c r="AU46">
-        <v>-1.900603539</v>
+        <v>-1.914899039</v>
       </c>
       <c r="AV46">
         <v>-1.42</v>
@@ -8505,7 +8508,7 @@
         <v>-1.39</v>
       </c>
       <c r="AX46">
-        <v>-1.7968999999999999</v>
+        <v>-1.8361242</v>
       </c>
       <c r="AY46">
         <v>-0.93</v>
@@ -8514,7 +8517,7 @@
         <v>-0.97</v>
       </c>
       <c r="BA46">
-        <v>-1.8475662660000001</v>
+        <v>-1.8724782659999999</v>
       </c>
       <c r="BB46">
         <v>-0.94</v>
@@ -8643,7 +8646,7 @@
         <v>3.319</v>
       </c>
       <c r="AR47">
-        <v>-1.923633028</v>
+        <v>-1.932292428</v>
       </c>
       <c r="AS47">
         <v>-1.65</v>
@@ -8652,7 +8655,7 @@
         <v>-1.62</v>
       </c>
       <c r="AU47">
-        <v>-1.895933552</v>
+        <v>-1.908235052</v>
       </c>
       <c r="AV47">
         <v>-1.47</v>
@@ -8661,7 +8664,7 @@
         <v>-1.45</v>
       </c>
       <c r="AX47">
-        <v>-1.7910999999999999</v>
+        <v>-1.8263548000000001</v>
       </c>
       <c r="AY47">
         <v>-0.98</v>
@@ -8670,7 +8673,7 @@
         <v>-0.93</v>
       </c>
       <c r="BA47">
-        <v>-1.836793374</v>
+        <v>-1.858607374</v>
       </c>
       <c r="BB47">
         <v>-1.04</v>
@@ -8799,7 +8802,7 @@
         <v>3.653</v>
       </c>
       <c r="AR48">
-        <v>-1.887062169</v>
+        <v>-1.8988546690000001</v>
       </c>
       <c r="AS48">
         <v>-1.24</v>
@@ -8808,7 +8811,7 @@
         <v>-1.05</v>
       </c>
       <c r="AU48">
-        <v>-1.8386384010000001</v>
+        <v>-1.8561078010000001</v>
       </c>
       <c r="AV48">
         <v>-1.06</v>
@@ -8817,7 +8820,7 @@
         <v>-0.94</v>
       </c>
       <c r="AX48">
-        <v>-1.5519000000000001</v>
+        <v>-1.6024332999999999</v>
       </c>
       <c r="AY48">
         <v>-1.1100000000000001</v>
@@ -8826,7 +8829,7 @@
         <v>-1.17</v>
       </c>
       <c r="BA48">
-        <v>-1.720952271</v>
+        <v>-1.7539092709999999</v>
       </c>
       <c r="BB48">
         <v>-1.05</v>
@@ -8955,7 +8958,7 @@
         <v>3.4470000000000001</v>
       </c>
       <c r="AR49">
-        <v>-1.9228700540000001</v>
+        <v>-1.933439854</v>
       </c>
       <c r="AS49">
         <v>-1.62</v>
@@ -8964,7 +8967,7 @@
         <v>-1.55</v>
       </c>
       <c r="AU49">
-        <v>-1.8923421979999999</v>
+        <v>-1.9075479980000001</v>
       </c>
       <c r="AV49">
         <v>-1.41</v>
@@ -8973,7 +8976,7 @@
         <v>-1.37</v>
       </c>
       <c r="AX49">
-        <v>-1.7558</v>
+        <v>-1.7972102000000001</v>
       </c>
       <c r="AY49">
         <v>-0.95</v>
@@ -8982,7 +8985,7 @@
         <v>-1</v>
       </c>
       <c r="BA49">
-        <v>-1.820952994</v>
+        <v>-1.8478954940000001</v>
       </c>
       <c r="BB49">
         <v>-0.96</v>
@@ -9111,7 +9114,7 @@
         <v>3.3180000000000001</v>
       </c>
       <c r="AR50">
-        <v>-1.9190351779999999</v>
+        <v>-1.9279775779999999</v>
       </c>
       <c r="AS50">
         <v>-1.65</v>
@@ -9120,7 +9123,7 @@
         <v>-1.61</v>
       </c>
       <c r="AU50">
-        <v>-1.8882454470000001</v>
+        <v>-1.901008247</v>
       </c>
       <c r="AV50">
         <v>-1.46</v>
@@ -9129,7 +9132,7 @@
         <v>-1.44</v>
       </c>
       <c r="AX50">
-        <v>-1.7683</v>
+        <v>-1.8057702</v>
       </c>
       <c r="AY50">
         <v>-0.98</v>
@@ -9138,7 +9141,7 @@
         <v>-0.93</v>
       </c>
       <c r="BA50">
-        <v>-1.816226471</v>
+        <v>-1.8394107710000001</v>
       </c>
       <c r="BB50">
         <v>-1.06</v>
@@ -9267,7 +9270,7 @@
         <v>3.8809999999999998</v>
       </c>
       <c r="AR51">
-        <v>-1.9156172659999999</v>
+        <v>-1.924293166</v>
       </c>
       <c r="AS51">
         <v>-1.43</v>
@@ -9276,7 +9279,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AU51">
-        <v>-1.879533479</v>
+        <v>-1.891656979</v>
       </c>
       <c r="AV51">
         <v>-1.18</v>
@@ -9285,7 +9288,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX51">
-        <v>-0.92569999999999997</v>
+        <v>-0.95619399999999999</v>
       </c>
       <c r="AY51">
         <v>-1.25</v>
@@ -9294,7 +9297,7 @@
         <v>-1.34</v>
       </c>
       <c r="BA51">
-        <v>-1.800139808</v>
+        <v>-1.819846208</v>
       </c>
       <c r="BB51">
         <v>-1.3</v>
@@ -9423,7 +9426,7 @@
         <v>3.786</v>
       </c>
       <c r="AR52">
-        <v>-1.913503714</v>
+        <v>-1.929153914</v>
       </c>
       <c r="AS52">
         <v>-1.37</v>
@@ -9432,7 +9435,7 @@
         <v>-1.39</v>
       </c>
       <c r="AU52">
-        <v>-1.8805702289999999</v>
+        <v>-1.9028648290000001</v>
       </c>
       <c r="AV52">
         <v>-1.23</v>
@@ -9441,7 +9444,7 @@
         <v>-1.25</v>
       </c>
       <c r="AX52">
-        <v>-1.8301000000000001</v>
+        <v>-1.8763643000000001</v>
       </c>
       <c r="AY52">
         <v>-0.98</v>
@@ -9450,7 +9453,7 @@
         <v>-1.02</v>
       </c>
       <c r="BA52">
-        <v>-1.836802179</v>
+        <v>-1.866497479</v>
       </c>
       <c r="BB52">
         <v>-1.01</v>
@@ -9579,7 +9582,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="AR53">
-        <v>-1.916421747</v>
+        <v>-1.9233418470000001</v>
       </c>
       <c r="AS53">
         <v>-1.2</v>
@@ -9588,7 +9591,7 @@
         <v>-1.57</v>
       </c>
       <c r="AU53">
-        <v>-1.8822520949999999</v>
+        <v>-1.8915377950000001</v>
       </c>
       <c r="AV53">
         <v>-1.25</v>
@@ -9597,7 +9600,7 @@
         <v>-1.55</v>
       </c>
       <c r="AX53">
-        <v>-1.3261000000000001</v>
+        <v>-1.3470247</v>
       </c>
       <c r="AY53">
         <v>-1.51</v>
@@ -9606,7 +9609,7 @@
         <v>-1.6</v>
       </c>
       <c r="BA53">
-        <v>-1.7877530669999999</v>
+        <v>-1.8009554670000001</v>
       </c>
       <c r="BB53">
         <v>-1.56</v>
@@ -9735,7 +9738,7 @@
         <v>4.0090000000000003</v>
       </c>
       <c r="AR54">
-        <v>-1.9204546840000001</v>
+        <v>-1.928934884</v>
       </c>
       <c r="AS54">
         <v>-1.1000000000000001</v>
@@ -9744,7 +9747,7 @@
         <v>-1.44</v>
       </c>
       <c r="AU54">
-        <v>-1.8881070310000001</v>
+        <v>-1.899401031</v>
       </c>
       <c r="AV54">
         <v>-1.17</v>
@@ -9753,7 +9756,7 @@
         <v>-1.45</v>
       </c>
       <c r="AX54">
-        <v>-1.5248999999999999</v>
+        <v>-1.5506388</v>
       </c>
       <c r="AY54">
         <v>-1.43</v>
@@ -9762,7 +9765,7 @@
         <v>-1.53</v>
       </c>
       <c r="BA54">
-        <v>-1.7997405049999999</v>
+        <v>-1.8151027049999999</v>
       </c>
       <c r="BB54">
         <v>-1.49</v>
@@ -9891,7 +9894,7 @@
         <v>4.08</v>
       </c>
       <c r="AR55">
-        <v>-1.915234651</v>
+        <v>-1.9219817509999999</v>
       </c>
       <c r="AS55">
         <v>-1.1499999999999999</v>
@@ -9900,7 +9903,7 @@
         <v>-1.55</v>
       </c>
       <c r="AU55">
-        <v>-1.8805317399999999</v>
+        <v>-1.8896452399999999</v>
       </c>
       <c r="AV55">
         <v>-1.22</v>
@@ -9909,7 +9912,7 @@
         <v>-1.53</v>
       </c>
       <c r="AX55">
-        <v>-1.3685</v>
+        <v>-1.3875358</v>
       </c>
       <c r="AY55">
         <v>-1.51</v>
@@ -9918,7 +9921,7 @@
         <v>-1.61</v>
       </c>
       <c r="BA55">
-        <v>-1.7929869030000001</v>
+        <v>-1.806383903</v>
       </c>
       <c r="BB55">
         <v>-1.54</v>
@@ -10047,7 +10050,7 @@
         <v>3.9420000000000002</v>
       </c>
       <c r="AR56">
-        <v>-1.918903421</v>
+        <v>-1.9265137210000001</v>
       </c>
       <c r="AS56">
         <v>-1.01</v>
@@ -10056,7 +10059,7 @@
         <v>-1.32</v>
       </c>
       <c r="AU56">
-        <v>-1.8864622280000001</v>
+        <v>-1.8967536279999999</v>
       </c>
       <c r="AV56">
         <v>-1.06</v>
@@ -10065,7 +10068,7 @@
         <v>-1.35</v>
       </c>
       <c r="AX56">
-        <v>-0.94779999999999998</v>
+        <v>-0.96904129999999977</v>
       </c>
       <c r="AY56">
         <v>-1.41</v>
@@ -10074,7 +10077,7 @@
         <v>-1.51</v>
       </c>
       <c r="BA56">
-        <v>-1.8120654490000001</v>
+        <v>-1.826967349</v>
       </c>
       <c r="BB56">
         <v>-1.44</v>
@@ -10203,7 +10206,7 @@
         <v>3.9</v>
       </c>
       <c r="AR57">
-        <v>-1.9032165590539301</v>
+        <v>-1.91272845905393</v>
       </c>
       <c r="AS57">
         <v>-1.07</v>
@@ -10212,7 +10215,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AU57">
-        <v>-1.86581680302576</v>
+        <v>-1.8781163030257599</v>
       </c>
       <c r="AV57">
         <v>-1</v>
@@ -10221,7 +10224,7 @@
         <v>-1.22</v>
       </c>
       <c r="AX57">
-        <v>-1.2303999999999999</v>
+        <v>-1.2644504000000001</v>
       </c>
       <c r="AY57">
         <v>-1.27</v>
@@ -10230,7 +10233,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA57">
-        <v>-1.7939000000000001</v>
+        <v>-1.8118514999999999</v>
       </c>
       <c r="BB57">
         <v>-1.32</v>
@@ -10359,7 +10362,7 @@
         <v>3.8519999999999999</v>
       </c>
       <c r="AR58">
-        <v>-1.8995752278076801</v>
+        <v>-1.9098704278076799</v>
       </c>
       <c r="AS58">
         <v>-1.1100000000000001</v>
@@ -10368,7 +10371,7 @@
         <v>-1.06</v>
       </c>
       <c r="AU58">
-        <v>-1.85902979864659</v>
+        <v>-1.8727283986465899</v>
       </c>
       <c r="AV58">
         <v>-0.97</v>
@@ -10377,7 +10380,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AX58">
-        <v>-1.4268000000000001</v>
+        <v>-1.4824355</v>
       </c>
       <c r="AY58">
         <v>-1.19</v>
@@ -10386,7 +10389,7 @@
         <v>-1.24</v>
       </c>
       <c r="BA58">
-        <v>-1.7623</v>
+        <v>-1.7859094</v>
       </c>
       <c r="BB58">
         <v>-1.24</v>
@@ -10515,7 +10518,7 @@
         <v>3.7509999999999999</v>
       </c>
       <c r="AR59">
-        <v>-1.8916592290000001</v>
+        <v>-1.905339229</v>
       </c>
       <c r="AS59">
         <v>-1.1499999999999999</v>
@@ -10524,7 +10527,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU59">
-        <v>-1.844647135</v>
+        <v>-1.863904335</v>
       </c>
       <c r="AV59">
         <v>-1.02</v>
@@ -10533,7 +10536,7 @@
         <v>-1.01</v>
       </c>
       <c r="AX59">
-        <v>-1.4396</v>
+        <v>-1.5174979</v>
       </c>
       <c r="AY59">
         <v>-1.08</v>
@@ -10542,7 +10545,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="BA59">
-        <v>-1.7341810470000001</v>
+        <v>-1.7707308470000001</v>
       </c>
       <c r="BB59">
         <v>-1.0900000000000001</v>
@@ -10671,7 +10674,7 @@
         <v>3.1549999999999998</v>
       </c>
       <c r="AR60">
-        <v>-1.883085044</v>
+        <v>-1.895059244</v>
       </c>
       <c r="AS60">
         <v>-1.45</v>
@@ -10680,7 +10683,7 @@
         <v>-1.36</v>
       </c>
       <c r="AU60">
-        <v>-1.8425038460000001</v>
+        <v>-1.8587445460000001</v>
       </c>
       <c r="AV60">
         <v>-1.32</v>
@@ -10689,7 +10692,7 @@
         <v>-1.23</v>
       </c>
       <c r="AX60">
-        <v>-1.5748</v>
+        <v>-1.6242118000000001</v>
       </c>
       <c r="AY60">
         <v>-0.83</v>
@@ -10698,7 +10701,7 @@
         <v>-0.84</v>
       </c>
       <c r="BA60">
-        <v>-1.739398612</v>
+        <v>-1.7666621119999999</v>
       </c>
       <c r="BB60">
         <v>-1.0900000000000001</v>
@@ -10827,7 +10830,7 @@
         <v>3.0510000000000002</v>
       </c>
       <c r="AR61">
-        <v>-1.879792702</v>
+        <v>-1.8919910019999999</v>
       </c>
       <c r="AS61">
         <v>-1.5</v>
@@ -10836,7 +10839,7 @@
         <v>-1.45</v>
       </c>
       <c r="AU61">
-        <v>-1.839402143</v>
+        <v>-1.855855743</v>
       </c>
       <c r="AV61">
         <v>-1.39</v>
@@ -10845,7 +10848,7 @@
         <v>-1.34</v>
       </c>
       <c r="AX61">
-        <v>-1.5821000000000001</v>
+        <v>-1.6302589999999999</v>
       </c>
       <c r="AY61">
         <v>-0.9</v>
@@ -10854,7 +10857,7 @@
         <v>-0.9</v>
       </c>
       <c r="BA61">
-        <v>-1.7358165059999999</v>
+        <v>-1.762720906</v>
       </c>
       <c r="BB61">
         <v>-1.19</v>
@@ -10983,7 +10986,7 @@
         <v>3.375</v>
       </c>
       <c r="AR62">
-        <v>-1.88396396491855</v>
+        <v>-1.8949193649185501</v>
       </c>
       <c r="AS62">
         <v>-1.28</v>
@@ -10992,7 +10995,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AU62">
-        <v>-1.8405830471006801</v>
+        <v>-1.8555562471006799</v>
       </c>
       <c r="AV62">
         <v>-1.1299999999999999</v>
@@ -11001,7 +11004,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX62">
-        <v>-1.5504</v>
+        <v>-1.6007567</v>
       </c>
       <c r="AY62">
         <v>-1.02</v>
@@ -11010,7 +11013,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA62">
-        <v>-1.7271000000000001</v>
+        <v>-1.7537176999999999</v>
       </c>
       <c r="BB62">
         <v>-0.91</v>
@@ -11139,7 +11142,7 @@
         <v>3.3650000000000002</v>
       </c>
       <c r="AR63">
-        <v>-1.8910794959999999</v>
+        <v>-1.9022686959999999</v>
       </c>
       <c r="AS63">
         <v>-1.28</v>
@@ -11148,7 +11151,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="AU63">
-        <v>-1.83992105022622</v>
+        <v>-1.8552108502262199</v>
       </c>
       <c r="AV63">
         <v>-1.1399999999999999</v>
@@ -11157,7 +11160,7 @@
         <v>-1</v>
       </c>
       <c r="AX63">
-        <v>-1.5486</v>
+        <v>-1.5996018000000001</v>
       </c>
       <c r="AY63">
         <v>-1.01</v>
@@ -11166,7 +11169,7 @@
         <v>-1.04</v>
       </c>
       <c r="BA63">
-        <v>-1.7430355280000001</v>
+        <v>-1.7699809280000001</v>
       </c>
       <c r="BB63">
         <v>-0.91</v>
@@ -11295,7 +11298,7 @@
         <v>3.8730000000000002</v>
       </c>
       <c r="AR64">
-        <v>-1.8958303000000001</v>
+        <v>-1.9104171999999999</v>
       </c>
       <c r="AS64">
         <v>-1.1599999999999999</v>
@@ -11304,7 +11307,7 @@
         <v>-1.03</v>
       </c>
       <c r="AU64">
-        <v>-1.8523255059999999</v>
+        <v>-1.8721942060000001</v>
       </c>
       <c r="AV64">
         <v>-1.04</v>
@@ -11313,7 +11316,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX64">
-        <v>-1.3802000000000001</v>
+        <v>-1.4463347</v>
       </c>
       <c r="AY64">
         <v>-1.1200000000000001</v>
@@ -11322,7 +11325,7 @@
         <v>-1.17</v>
       </c>
       <c r="BA64">
-        <v>-1.7541741209999999</v>
+        <v>-1.785806121</v>
       </c>
       <c r="BB64">
         <v>-1.1399999999999999</v>
@@ -11451,7 +11454,7 @@
         <v>2.4849999999999999</v>
       </c>
       <c r="AR65">
-        <v>-1.8361463769999999</v>
+        <v>-1.8500089770000001</v>
       </c>
       <c r="AS65">
         <v>-1.59</v>
@@ -11460,7 +11463,7 @@
         <v>-1.6</v>
       </c>
       <c r="AU65">
-        <v>-1.803582005</v>
+        <v>-1.821963105</v>
       </c>
       <c r="AV65">
         <v>-1.52</v>
@@ -11469,7 +11472,7 @@
         <v>-1.54</v>
       </c>
       <c r="AX65">
-        <v>-1.6473</v>
+        <v>-1.6927882000000001</v>
       </c>
       <c r="AY65">
         <v>-1.3</v>
@@ -11478,7 +11481,7 @@
         <v>-1.31</v>
       </c>
       <c r="BA65">
-        <v>-1.73688993</v>
+        <v>-1.76496213</v>
       </c>
       <c r="BB65">
         <v>-1.51</v>
@@ -11607,7 +11610,7 @@
         <v>2.278</v>
       </c>
       <c r="AR66">
-        <v>-1.0698000000000001</v>
+        <v>-1.0820817</v>
       </c>
       <c r="AS66">
         <v>-1.69</v>
@@ -11616,7 +11619,7 @@
         <v>-1.71</v>
       </c>
       <c r="AU66">
-        <v>-1.827175322</v>
+        <v>-1.843165422</v>
       </c>
       <c r="AV66">
         <v>-1.64</v>
@@ -11625,7 +11628,7 @@
         <v>-1.67</v>
       </c>
       <c r="AX66">
-        <v>-1.6863999999999999</v>
+        <v>-1.7255088000000001</v>
       </c>
       <c r="AY66">
         <v>-1.45</v>
@@ -11634,7 +11637,7 @@
         <v>-1.48</v>
       </c>
       <c r="BA66">
-        <v>-1.3813035250000001</v>
+        <v>-1.4057237250000001</v>
       </c>
       <c r="BB66">
         <v>-1.62</v>
@@ -11763,7 +11766,7 @@
         <v>2.8380000000000001</v>
       </c>
       <c r="AR67">
-        <v>-1.8483157610000001</v>
+        <v>-1.8605942609999999</v>
       </c>
       <c r="AS67">
         <v>-1.4</v>
@@ -11772,7 +11775,7 @@
         <v>-1.33</v>
       </c>
       <c r="AU67">
-        <v>-1.805136898</v>
+        <v>-1.822159098</v>
       </c>
       <c r="AV67">
         <v>-1.27</v>
@@ -11781,7 +11784,7 @@
         <v>-1.24</v>
       </c>
       <c r="AX67">
-        <v>-1.5952999999999999</v>
+        <v>-1.6445179999999999</v>
       </c>
       <c r="AY67">
         <v>-0.91</v>
@@ -11790,7 +11793,7 @@
         <v>-0.91</v>
       </c>
       <c r="BA67">
-        <v>-1.715624671</v>
+        <v>-1.744279871</v>
       </c>
       <c r="BB67">
         <v>-1.21</v>
@@ -11919,7 +11922,7 @@
         <v>2.7909999999999999</v>
       </c>
       <c r="AR68">
-        <v>-1.8547358940000001</v>
+        <v>-1.8658795939999999</v>
       </c>
       <c r="AS68">
         <v>-1.32</v>
@@ -11928,7 +11931,7 @@
         <v>-1.27</v>
       </c>
       <c r="AU68">
-        <v>-1.8090944849999999</v>
+        <v>-1.824673285</v>
       </c>
       <c r="AV68">
         <v>-1.19</v>
@@ -11937,7 +11940,7 @@
         <v>-1.19</v>
       </c>
       <c r="AX68">
-        <v>-1.5972</v>
+        <v>-1.6441908000000001</v>
       </c>
       <c r="AY68">
         <v>-0.89</v>
@@ -11946,7 +11949,7 @@
         <v>-0.9</v>
       </c>
       <c r="BA68">
-        <v>-1.707934882</v>
+        <v>-1.7350454820000001</v>
       </c>
       <c r="BB68">
         <v>-1.17</v>
@@ -12075,7 +12078,7 @@
         <v>4.04</v>
       </c>
       <c r="AR69">
-        <v>-1.9010120420000001</v>
+        <v>-1.9157049420000001</v>
       </c>
       <c r="AS69">
         <v>-1.1399999999999999</v>
@@ -12084,7 +12087,7 @@
         <v>-1</v>
       </c>
       <c r="AU69">
-        <v>-1.860383774</v>
+        <v>-1.8796853739999999</v>
       </c>
       <c r="AV69">
         <v>-1.02</v>
@@ -12093,7 +12096,7 @@
         <v>-1.02</v>
       </c>
       <c r="AX69">
-        <v>-0.9104000000000001</v>
+        <v>-0.95961929999999995</v>
       </c>
       <c r="AY69">
         <v>-1.17</v>
@@ -12102,7 +12105,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA69">
-        <v>-1.7746699669999999</v>
+        <v>-1.800127767</v>
       </c>
       <c r="BB69">
         <v>-1.21</v>
@@ -12198,13 +12201,13 @@
         <v>0.31455</v>
       </c>
       <c r="AE70" s="5">
-        <v>-0.12934000000000001</v>
+        <v>-0.1293</v>
       </c>
       <c r="AF70" s="5">
         <v>0.20619000000000001</v>
       </c>
       <c r="AG70" s="5">
-        <v>0.14066000000000001</v>
+        <v>0.14072999999999999</v>
       </c>
       <c r="AI70" s="6">
         <v>4.3280000000000003</v>
@@ -12231,7 +12234,7 @@
         <v>2.004</v>
       </c>
       <c r="AR70">
-        <v>-1.928934511</v>
+        <v>-1.9357458110000001</v>
       </c>
       <c r="AS70">
         <v>-1.31</v>
@@ -12240,7 +12243,7 @@
         <v>-1.58</v>
       </c>
       <c r="AU70">
-        <v>-0.98129999999999995</v>
+        <v>-0.98973980000000017</v>
       </c>
       <c r="AV70">
         <v>-1.37</v>
@@ -12249,7 +12252,7 @@
         <v>-1.58</v>
       </c>
       <c r="AX70">
-        <v>-1.3982000000000001</v>
+        <v>-1.4362144999999999</v>
       </c>
       <c r="AY70">
         <v>-0.66</v>
@@ -12258,7 +12261,7 @@
         <v>-0.82</v>
       </c>
       <c r="BA70">
-        <v>-0.96509999999999996</v>
+        <v>-0.9878461999999999</v>
       </c>
       <c r="BB70">
         <v>-0.7</v>
@@ -12387,7 +12390,7 @@
         <v>1.591</v>
       </c>
       <c r="AR71">
-        <v>-1.737977068</v>
+        <v>-1.7460514680000001</v>
       </c>
       <c r="AS71">
         <v>-1.02</v>
@@ -12396,7 +12399,7 @@
         <v>-1.21</v>
       </c>
       <c r="AU71">
-        <v>-1.666688731</v>
+        <v>-1.677388831</v>
       </c>
       <c r="AV71">
         <v>-1.03</v>
@@ -12405,7 +12408,7 @@
         <v>-1.31</v>
       </c>
       <c r="AX71">
-        <v>-0.94629999999999992</v>
+        <v>-0.97248549999999989</v>
       </c>
       <c r="AY71">
         <v>-1.1599999999999999</v>
@@ -12414,7 +12417,7 @@
         <v>-1.28</v>
       </c>
       <c r="BA71">
-        <v>-1.0328999999999999</v>
+        <v>-1.0479160000000001</v>
       </c>
       <c r="BB71">
         <v>-1.26</v>
@@ -12543,7 +12546,7 @@
         <v>2.8959999999999999</v>
       </c>
       <c r="AR72">
-        <v>-1.9241290769999999</v>
+        <v>-1.9308496770000001</v>
       </c>
       <c r="AS72">
         <v>-1.27</v>
@@ -12552,7 +12555,7 @@
         <v>-1.55</v>
       </c>
       <c r="AU72">
-        <v>-1.897713904</v>
+        <v>-1.9060940040000001</v>
       </c>
       <c r="AV72">
         <v>-1.35</v>
@@ -12561,7 +12564,7 @@
         <v>-1.56</v>
       </c>
       <c r="AX72">
-        <v>-1.4464999999999999</v>
+        <v>-1.4941173999999999</v>
       </c>
       <c r="AY72">
         <v>-1.07</v>
@@ -12570,7 +12573,7 @@
         <v>-1.06</v>
       </c>
       <c r="BA72">
-        <v>-1.5874123529999999</v>
+        <v>-1.615383453</v>
       </c>
       <c r="BB72">
         <v>-1.2</v>
@@ -12699,7 +12702,7 @@
         <v>3.298</v>
       </c>
       <c r="AR73">
-        <v>-1.912648627</v>
+        <v>-1.9210274270000001</v>
       </c>
       <c r="AS73">
         <v>-1.22</v>
@@ -12708,7 +12711,7 @@
         <v>-1.49</v>
       </c>
       <c r="AU73">
-        <v>-1.8701000000000001</v>
+        <v>-1.8818311000000001</v>
       </c>
       <c r="AV73">
         <v>-1.31</v>
@@ -12717,7 +12720,7 @@
         <v>-1.5</v>
       </c>
       <c r="AX73">
-        <v>-1.3918999999999999</v>
+        <v>-1.4584914</v>
       </c>
       <c r="AY73">
         <v>-1.22</v>
@@ -12726,7 +12729,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA73">
-        <v>-1.5772152340000001</v>
+        <v>-1.6127794339999999</v>
       </c>
       <c r="BB73">
         <v>-1.27</v>
@@ -12855,7 +12858,7 @@
         <v>2.6880000000000002</v>
       </c>
       <c r="AR74">
-        <v>-1.477568558</v>
+        <v>-1.5112181579999999</v>
       </c>
       <c r="AS74">
         <v>-1.1100000000000001</v>
@@ -12864,7 +12867,7 @@
         <v>-1.25</v>
       </c>
       <c r="AU74">
-        <v>-1.4758748610000001</v>
+        <v>-1.525205261</v>
       </c>
       <c r="AV74">
         <v>-1.1200000000000001</v>
@@ -12873,7 +12876,7 @@
         <v>-1.25</v>
       </c>
       <c r="AX74">
-        <v>-1.1589</v>
+        <v>-1.2894104</v>
       </c>
       <c r="AY74">
         <v>-1.27</v>
@@ -12882,7 +12885,7 @@
         <v>-1.3</v>
       </c>
       <c r="BA74">
-        <v>-1.0931</v>
+        <v>-1.1430087</v>
       </c>
       <c r="BB74">
         <v>-1.37</v>
@@ -12913,13 +12916,13 @@
       <c r="F75" s="5">
         <v>3.3820000000000003E-2</v>
       </c>
-      <c r="G75" s="14">
+      <c r="G75" s="12">
         <v>-0.13378999999999999</v>
       </c>
       <c r="H75" s="5">
         <v>-1.8710000000000001E-2</v>
       </c>
-      <c r="I75" s="14">
+      <c r="I75" s="12">
         <v>-9.9040000000000003E-2</v>
       </c>
       <c r="K75" s="5">
@@ -13011,7 +13014,7 @@
         <v>2.8690000000000002</v>
       </c>
       <c r="AR75">
-        <v>-1.7285484360000001</v>
+        <v>-1.768314336</v>
       </c>
       <c r="AS75">
         <v>-1.07</v>
@@ -13020,7 +13023,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AU75">
-        <v>-1.638053843</v>
+        <v>-1.694589643</v>
       </c>
       <c r="AV75">
         <v>-1.08</v>
@@ -13029,7 +13032,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AX75">
-        <v>-1.0879000000000001</v>
+        <v>-1.2157178</v>
       </c>
       <c r="AY75">
         <v>-1.19</v>
@@ -13038,7 +13041,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA75">
-        <v>-1.50104445</v>
+        <v>-1.5635240500000001</v>
       </c>
       <c r="BB75">
         <v>-1.26</v>
@@ -13167,7 +13170,7 @@
         <v>2.8660000000000001</v>
       </c>
       <c r="AR76">
-        <v>-1.7380525389999999</v>
+        <v>-1.778845939</v>
       </c>
       <c r="AS76">
         <v>-1.02</v>
@@ -13176,7 +13179,7 @@
         <v>-1.04</v>
       </c>
       <c r="AU76">
-        <v>-1.6317757289999999</v>
+        <v>-1.6902583289999999</v>
       </c>
       <c r="AV76">
         <v>-1.05</v>
@@ -13185,7 +13188,7 @@
         <v>-1.08</v>
       </c>
       <c r="AX76">
-        <v>-1.1536</v>
+        <v>-1.2904731</v>
       </c>
       <c r="AY76">
         <v>-1.17</v>
@@ -13194,7 +13197,7 @@
         <v>-1.21</v>
       </c>
       <c r="BA76">
-        <v>-1.1412</v>
+        <v>-1.2148920999999999</v>
       </c>
       <c r="BB76">
         <v>-1.3</v>
@@ -13323,7 +13326,7 @@
         <v>2.544</v>
       </c>
       <c r="AR77">
-        <v>-1.6948615950000001</v>
+        <v>-1.729453795</v>
       </c>
       <c r="AS77">
         <v>-1.03</v>
@@ -13332,7 +13335,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AU77">
-        <v>-1.654445546</v>
+        <v>-1.7045535460000001</v>
       </c>
       <c r="AV77">
         <v>-1.06</v>
@@ -13341,7 +13344,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AX77">
-        <v>-1.5144</v>
+        <v>-1.6600644</v>
       </c>
       <c r="AY77">
         <v>-1.08</v>
@@ -13350,7 +13353,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BA77">
-        <v>-1.395367504</v>
+        <v>-1.474007804</v>
       </c>
       <c r="BB77">
         <v>-1.23</v>
@@ -13479,7 +13482,7 @@
         <v>2.6429999999999998</v>
       </c>
       <c r="AR78">
-        <v>-1.4935296899999999</v>
+        <v>-1.5256984899999999</v>
       </c>
       <c r="AS78">
         <v>-0.83</v>
@@ -13488,7 +13491,7 @@
         <v>-0.84</v>
       </c>
       <c r="AU78">
-        <v>-1.4396630180000001</v>
+        <v>-1.486397118</v>
       </c>
       <c r="AV78">
         <v>-0.97</v>
@@ -13497,7 +13500,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX78">
-        <v>-1.2222</v>
+        <v>-1.3350906</v>
       </c>
       <c r="AY78">
         <v>-1.26</v>
@@ -13506,7 +13509,7 @@
         <v>-1.36</v>
       </c>
       <c r="BA78">
-        <v>-1.5575066639999999</v>
+        <v>-1.6200739639999999</v>
       </c>
       <c r="BB78">
         <v>-1.28</v>
@@ -13635,7 +13638,7 @@
         <v>2.1789999999999998</v>
       </c>
       <c r="AR79">
-        <v>-1.6807057219999999</v>
+        <v>-1.7009837219999999</v>
       </c>
       <c r="AS79">
         <v>-1.53</v>
@@ -13644,7 +13647,7 @@
         <v>-1.64</v>
       </c>
       <c r="AU79">
-        <v>-1.659285817</v>
+        <v>-1.6883816169999999</v>
       </c>
       <c r="AV79">
         <v>-1.47</v>
@@ -13653,7 +13656,7 @@
         <v>-1.62</v>
       </c>
       <c r="AX79">
-        <v>-0.87660000000000005</v>
+        <v>-0.96757579999999987</v>
       </c>
       <c r="AY79">
         <v>-0.84</v>
@@ -13662,7 +13665,7 @@
         <v>-1.52</v>
       </c>
       <c r="BA79">
-        <v>-1.5823695330000001</v>
+        <v>-1.6355215329999999</v>
       </c>
       <c r="BB79">
         <v>-1.48</v>
@@ -13714,13 +13717,13 @@
       <c r="N80" s="5">
         <v>0.10224</v>
       </c>
-      <c r="O80" s="14">
+      <c r="O80" s="12">
         <v>0.14568999999999999</v>
       </c>
       <c r="P80" s="5">
         <v>4.7570000000000001E-2</v>
       </c>
-      <c r="Q80" s="14">
+      <c r="Q80" s="12">
         <v>3.3849999999999998E-2</v>
       </c>
       <c r="R80" s="5"/>
@@ -13791,7 +13794,7 @@
         <v>2.379</v>
       </c>
       <c r="AR80">
-        <v>-1.855340955</v>
+        <v>-1.8879789549999999</v>
       </c>
       <c r="AS80">
         <v>-1.01</v>
@@ -13800,7 +13803,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU80">
-        <v>-1.0778000000000001</v>
+        <v>-1.125238</v>
       </c>
       <c r="AV80">
         <v>-1.03</v>
@@ -13809,7 +13812,7 @@
         <v>-1.06</v>
       </c>
       <c r="AX80">
-        <v>-1.3312999999999999</v>
+        <v>-1.4370505</v>
       </c>
       <c r="AY80">
         <v>-1.1000000000000001</v>
@@ -13818,7 +13821,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA80">
-        <v>-1.419310659</v>
+        <v>-1.4604392589999999</v>
       </c>
       <c r="BB80">
         <v>-0.87</v>
@@ -13947,7 +13950,7 @@
         <v>2.8290000000000002</v>
       </c>
       <c r="AR81">
-        <v>-1.3292571310000001</v>
+        <v>-1.3678348309999999</v>
       </c>
       <c r="AS81">
         <v>-1.1100000000000001</v>
@@ -13956,7 +13959,7 @@
         <v>-1.2</v>
       </c>
       <c r="AU81">
-        <v>-1.3223083819999999</v>
+        <v>-1.3779602820000001</v>
       </c>
       <c r="AV81">
         <v>-1.1100000000000001</v>
@@ -13965,7 +13968,7 @@
         <v>-1.2</v>
       </c>
       <c r="AX81">
-        <v>-1.0498000000000001</v>
+        <v>-1.2006319000000001</v>
       </c>
       <c r="AY81">
         <v>-1.23</v>
@@ -13974,7 +13977,7 @@
         <v>-1.27</v>
       </c>
       <c r="BA81">
-        <v>-1.5922316489999999</v>
+        <v>-1.651253249</v>
       </c>
       <c r="BB81">
         <v>-1.32</v>
@@ -14103,7 +14106,7 @@
         <v>2.71</v>
       </c>
       <c r="AR82">
-        <v>-1.9456457899999999</v>
+        <v>-1.95469469</v>
       </c>
       <c r="AS82">
         <v>-1.47</v>
@@ -14112,7 +14115,7 @@
         <v>-1.59</v>
       </c>
       <c r="AU82">
-        <v>-1.926535331</v>
+        <v>-1.938299531</v>
       </c>
       <c r="AV82">
         <v>-1.32</v>
@@ -14121,7 +14124,7 @@
         <v>-1.36</v>
       </c>
       <c r="AX82">
-        <v>-1.83</v>
+        <v>-1.8529424999999999</v>
       </c>
       <c r="AY82">
         <v>-1.36</v>
@@ -14130,7 +14133,7 @@
         <v>-1.91</v>
       </c>
       <c r="BA82">
-        <v>-1.8986568850000001</v>
+        <v>-1.914521785</v>
       </c>
       <c r="BB82">
         <v>-1.28</v>
@@ -14259,7 +14262,7 @@
         <v>3.1059999999999999</v>
       </c>
       <c r="AR83">
-        <v>-1.8781307229999999</v>
+        <v>-1.915906023</v>
       </c>
       <c r="AS83">
         <v>-1.01</v>
@@ -14268,7 +14271,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU83">
-        <v>-1.7689696260000001</v>
+        <v>-1.8283056259999999</v>
       </c>
       <c r="AV83">
         <v>-1.04</v>
@@ -14277,7 +14280,7 @@
         <v>-1.06</v>
       </c>
       <c r="AX83">
-        <v>-1.3321000000000001</v>
+        <v>-1.4843793999999999</v>
       </c>
       <c r="AY83">
         <v>-1.1299999999999999</v>
@@ -14286,7 +14289,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA83">
-        <v>-1.455857634</v>
+        <v>-1.550133234</v>
       </c>
       <c r="BB83">
         <v>-1.1599999999999999</v>
@@ -14415,7 +14418,7 @@
         <v>2.56</v>
       </c>
       <c r="AR84">
-        <v>-1.9568890880000001</v>
+        <v>-1.986834988</v>
       </c>
       <c r="AS84">
         <v>-0.99</v>
@@ -14424,7 +14427,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU84">
-        <v>-1.9416022509999999</v>
+        <v>-1.9832568509999999</v>
       </c>
       <c r="AV84">
         <v>-0.99</v>
@@ -14433,7 +14436,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX84">
-        <v>-1.4581</v>
+        <v>-1.6082959999999999</v>
       </c>
       <c r="AY84">
         <v>-1.1100000000000001</v>
@@ -14442,7 +14445,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BA84">
-        <v>-1.51</v>
+        <v>-1.6059013</v>
       </c>
       <c r="BB84">
         <v>-1.1499999999999999</v>
@@ -14571,7 +14574,7 @@
         <v>2.4289999999999998</v>
       </c>
       <c r="AR85">
-        <v>-1.6647054990000001</v>
+        <v>-1.698039799</v>
       </c>
       <c r="AS85">
         <v>-0.6</v>
@@ -14580,7 +14583,7 @@
         <v>-1.21</v>
       </c>
       <c r="AU85">
-        <v>-1.6394749850000001</v>
+        <v>-1.6884849850000001</v>
       </c>
       <c r="AV85">
         <v>-0.95</v>
@@ -14589,7 +14592,7 @@
         <v>-1.18</v>
       </c>
       <c r="AX85">
-        <v>-1.3588</v>
+        <v>-1.4872078</v>
       </c>
       <c r="AY85">
         <v>-1.22</v>
@@ -14598,7 +14601,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA85">
-        <v>-1.3247694619999999</v>
+        <v>-1.411326562</v>
       </c>
       <c r="BB85">
         <v>-1.27</v>
@@ -14727,7 +14730,7 @@
         <v>2.7519999999999998</v>
       </c>
       <c r="AR86">
-        <v>-1.9426141109999999</v>
+        <v>-1.952835211</v>
       </c>
       <c r="AS86">
         <v>-1.48</v>
@@ -14736,7 +14739,7 @@
         <v>-1.67</v>
       </c>
       <c r="AU86">
-        <v>-1.9216711289999999</v>
+        <v>-1.9351208289999999</v>
       </c>
       <c r="AV86">
         <v>-1.34</v>
@@ -14745,7 +14748,7 @@
         <v>-1.49</v>
       </c>
       <c r="AX86">
-        <v>-1.3816999999999999</v>
+        <v>-1.4779859</v>
       </c>
       <c r="AY86">
         <v>-1.3</v>
@@ -14754,7 +14757,7 @@
         <v>-1.41</v>
       </c>
       <c r="BA86">
-        <v>-1.886486608</v>
+        <v>-1.906291108</v>
       </c>
       <c r="BB86">
         <v>-1.17</v>
@@ -14883,7 +14886,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="AR87">
-        <v>-1.321481677</v>
+        <v>-1.351267177</v>
       </c>
       <c r="AS87">
         <v>-1.03</v>
@@ -14892,7 +14895,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="AU87">
-        <v>-1.455211099</v>
+        <v>-1.4961600989999999</v>
       </c>
       <c r="AV87">
         <v>-1.04</v>
@@ -14901,7 +14904,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AX87">
-        <v>-1.1677999999999999</v>
+        <v>-1.2686771999999999</v>
       </c>
       <c r="AY87">
         <v>-1.22</v>
@@ -14910,7 +14913,7 @@
         <v>-1.32</v>
       </c>
       <c r="BA87">
-        <v>-1.832190419</v>
+        <v>-1.8489451189999999</v>
       </c>
       <c r="BB87">
         <v>-1.7</v>
@@ -15039,7 +15042,7 @@
         <v>2.15</v>
       </c>
       <c r="AR88">
-        <v>-1.8231378730000001</v>
+        <v>-1.836188073</v>
       </c>
       <c r="AS88">
         <v>-1.76</v>
@@ -15048,7 +15051,7 @@
         <v>-1.83</v>
       </c>
       <c r="AU88">
-        <v>-1.7990126559999999</v>
+        <v>-1.8174559560000001</v>
       </c>
       <c r="AV88">
         <v>-1.69</v>
@@ -15057,7 +15060,7 @@
         <v>-1.8</v>
       </c>
       <c r="AX88">
-        <v>-1.6782999999999999</v>
+        <v>-1.7220807</v>
       </c>
       <c r="AY88">
         <v>-1.7</v>
@@ -15066,7 +15069,7 @@
         <v>-1.54</v>
       </c>
       <c r="BA88">
-        <v>-1.7081143459999999</v>
+        <v>-1.742870046</v>
       </c>
       <c r="BB88">
         <v>-1.69</v>
@@ -15195,7 +15198,7 @@
         <v>2.04</v>
       </c>
       <c r="AR89">
-        <v>-1.9617986270000001</v>
+        <v>-1.9696299269999999</v>
       </c>
       <c r="AS89">
         <v>-1.93</v>
@@ -15204,7 +15207,7 @@
         <v>-1.93</v>
       </c>
       <c r="AU89">
-        <v>-1.9490396459999999</v>
+        <v>-1.9593886460000001</v>
       </c>
       <c r="AV89">
         <v>-1.91</v>
@@ -15213,7 +15216,7 @@
         <v>-1.89</v>
       </c>
       <c r="AX89">
-        <v>-0.91290000000000004</v>
+        <v>-0.93456800000000007</v>
       </c>
       <c r="AY89">
         <v>-1.66</v>
@@ -15222,7 +15225,7 @@
         <v>-1.61</v>
       </c>
       <c r="BA89">
-        <v>-1.920356967</v>
+        <v>-1.937126567</v>
       </c>
       <c r="BB89">
         <v>-1.66</v>
@@ -15351,7 +15354,7 @@
         <v>2.605</v>
       </c>
       <c r="AR90">
-        <v>-1.9381696239999999</v>
+        <v>-1.9461470240000001</v>
       </c>
       <c r="AS90">
         <v>-1.48</v>
@@ -15360,7 +15363,7 @@
         <v>-1.65</v>
       </c>
       <c r="AU90">
-        <v>-1.78663098</v>
+        <v>-1.80478388</v>
       </c>
       <c r="AV90">
         <v>-0.83</v>
@@ -15369,7 +15372,7 @@
         <v>-0.89</v>
       </c>
       <c r="AX90">
-        <v>-1.048</v>
+        <v>-1.1285797</v>
       </c>
       <c r="AY90">
         <v>-1.26</v>
@@ -15378,7 +15381,7 @@
         <v>-1.39</v>
       </c>
       <c r="BA90">
-        <v>-1.8887146399999999</v>
+        <v>-1.9029736399999999</v>
       </c>
       <c r="BB90">
         <v>-1</v>
@@ -15507,7 +15510,7 @@
         <v>2.1179999999999999</v>
       </c>
       <c r="AR91">
-        <v>-1.9591270439999999</v>
+        <v>-1.966282144</v>
       </c>
       <c r="AS91">
         <v>-1.98</v>
@@ -15516,7 +15519,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU91">
-        <v>-1.9454119590000001</v>
+        <v>-1.9547928590000001</v>
       </c>
       <c r="AV91">
         <v>-1.97</v>
@@ -15525,7 +15528,7 @@
         <v>-1.93</v>
       </c>
       <c r="AX91">
-        <v>-1.8703000000000001</v>
+        <v>-1.8895360999999999</v>
       </c>
       <c r="AY91">
         <v>-1.77</v>
@@ -15534,7 +15537,7 @@
         <v>-1.65</v>
       </c>
       <c r="BA91">
-        <v>-1.9169667909999999</v>
+        <v>-1.931776691</v>
       </c>
       <c r="BB91">
         <v>-1.76</v>
@@ -15663,7 +15666,7 @@
         <v>2.6440000000000001</v>
       </c>
       <c r="AR92">
-        <v>-1.9414636830000001</v>
+        <v>-1.949559383</v>
       </c>
       <c r="AS92">
         <v>-1.44</v>
@@ -15672,7 +15675,7 @@
         <v>-1.56</v>
       </c>
       <c r="AU92">
-        <v>-1.920827356</v>
+        <v>-1.931531756</v>
       </c>
       <c r="AV92">
         <v>-1.31</v>
@@ -15681,7 +15684,7 @@
         <v>-1.4</v>
       </c>
       <c r="AX92">
-        <v>-1.8204</v>
+        <v>-1.8412244</v>
       </c>
       <c r="AY92">
         <v>-1.1299999999999999</v>
@@ -15690,7 +15693,7 @@
         <v>-1.68</v>
       </c>
       <c r="BA92">
-        <v>-1.8923005639999999</v>
+        <v>-1.906157264</v>
       </c>
       <c r="BB92">
         <v>-1.03</v>
@@ -15819,7 +15822,7 @@
         <v>2.1230000000000002</v>
       </c>
       <c r="AR93">
-        <v>-1.9581634409999999</v>
+        <v>-1.9654259409999999</v>
       </c>
       <c r="AS93">
         <v>-1.97</v>
@@ -15828,7 +15831,7 @@
         <v>-1.94</v>
       </c>
       <c r="AU93">
-        <v>-1.9437215379999999</v>
+        <v>-1.953290038</v>
       </c>
       <c r="AV93">
         <v>-1.96</v>
@@ -15837,7 +15840,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX93">
-        <v>-1.8621000000000001</v>
+        <v>-1.8818516000000001</v>
       </c>
       <c r="AY93">
         <v>-1.75</v>
@@ -15846,7 +15849,7 @@
         <v>-1.65</v>
       </c>
       <c r="BA93">
-        <v>-1.9121638649999999</v>
+        <v>-1.927107165</v>
       </c>
       <c r="BB93">
         <v>-1.74</v>
@@ -15975,7 +15978,7 @@
         <v>1.907</v>
       </c>
       <c r="AR94">
-        <v>-1.9601389229999999</v>
+        <v>-1.9889314229999999</v>
       </c>
       <c r="AS94">
         <v>-0.99</v>
@@ -15984,7 +15987,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU94">
-        <v>-1.94588407</v>
+        <v>-1.9852875699999999</v>
       </c>
       <c r="AV94">
         <v>-0.99</v>
@@ -15993,7 +15996,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX94">
-        <v>-1.7072000000000001</v>
+        <v>-1.8249</v>
       </c>
       <c r="AY94">
         <v>-0.98</v>
@@ -16002,7 +16005,7 @@
         <v>-0.95</v>
       </c>
       <c r="BA94">
-        <v>-1.8335999999999999</v>
+        <v>-1.9169033</v>
       </c>
       <c r="BB94">
         <v>-0.98</v>
@@ -16131,7 +16134,7 @@
         <v>2.899</v>
       </c>
       <c r="AR95">
-        <v>-1.938110606</v>
+        <v>-1.9506041059999999</v>
       </c>
       <c r="AS95">
         <v>-1.46</v>
@@ -16140,7 +16143,7 @@
         <v>-1.75</v>
       </c>
       <c r="AU95">
-        <v>-1.9145923570000001</v>
+        <v>-1.9312145570000001</v>
       </c>
       <c r="AV95">
         <v>-1.33</v>
@@ -16149,7 +16152,7 @@
         <v>-1.59</v>
       </c>
       <c r="AX95">
-        <v>-1.7794000000000001</v>
+        <v>-1.8141902000000001</v>
       </c>
       <c r="AY95">
         <v>-1.93</v>
@@ -16158,7 +16161,7 @@
         <v>-1.62</v>
       </c>
       <c r="BA95">
-        <v>-1.875275289</v>
+        <v>-1.899344089</v>
       </c>
       <c r="BB95">
         <v>-1.89</v>
@@ -16287,7 +16290,7 @@
         <v>2.7290000000000001</v>
       </c>
       <c r="AR96">
-        <v>-1.878934629</v>
+        <v>-1.8910542290000001</v>
       </c>
       <c r="AS96">
         <v>-1.03</v>
@@ -16296,7 +16299,7 @@
         <v>-0.96</v>
       </c>
       <c r="AU96">
-        <v>-1.687793656</v>
+        <v>-1.7181896560000001</v>
       </c>
       <c r="AV96">
         <v>-1.05</v>
@@ -16305,7 +16308,7 @@
         <v>-1.26</v>
       </c>
       <c r="AX96">
-        <v>-1.4252</v>
+        <v>-1.5202232</v>
       </c>
       <c r="AY96">
         <v>-1.29</v>
@@ -16314,7 +16317,7 @@
         <v>-1.39</v>
       </c>
       <c r="BA96">
-        <v>-1.8990040560000001</v>
+        <v>-1.9133615559999999</v>
       </c>
       <c r="BB96">
         <v>-1.3</v>
@@ -16443,7 +16446,7 @@
         <v>6.891</v>
       </c>
       <c r="AR97">
-        <v>-1.935849197</v>
+        <v>-1.9403980970000001</v>
       </c>
       <c r="AS97">
         <v>-0.98</v>
@@ -16452,7 +16455,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU97">
-        <v>-1.9108398879999999</v>
+        <v>-1.916516288</v>
       </c>
       <c r="AV97">
         <v>-0.97</v>
@@ -16461,7 +16464,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX97">
-        <v>-0.82739999999999991</v>
+        <v>-0.83951120000000001</v>
       </c>
       <c r="AY97">
         <v>-0.93</v>
@@ -16470,7 +16473,7 @@
         <v>-0.93</v>
       </c>
       <c r="BA97">
-        <v>-0.86680000000000001</v>
+        <v>-0.87815030000000016</v>
       </c>
       <c r="BB97">
         <v>-0.94</v>
@@ -16599,7 +16602,7 @@
         <v>2.6669999999999998</v>
       </c>
       <c r="AR98">
-        <v>-1.3046937409999999</v>
+        <v>-1.342590741</v>
       </c>
       <c r="AS98">
         <v>-1.1000000000000001</v>
@@ -16608,7 +16611,7 @@
         <v>-1.19</v>
       </c>
       <c r="AU98">
-        <v>-1.47275896</v>
+        <v>-1.52563296</v>
       </c>
       <c r="AV98">
         <v>-1.1100000000000001</v>
@@ -16617,7 +16620,7 @@
         <v>-1.21</v>
       </c>
       <c r="AX98">
-        <v>-1.1072</v>
+        <v>-1.2543141</v>
       </c>
       <c r="AY98">
         <v>-1.26</v>
@@ -16626,7 +16629,7 @@
         <v>-1.29</v>
       </c>
       <c r="BA98">
-        <v>-1.643272302</v>
+        <v>-1.695399702</v>
       </c>
       <c r="BB98">
         <v>-1.31</v>
@@ -16700,13 +16703,13 @@
       <c r="V99" s="5">
         <v>0.15242</v>
       </c>
-      <c r="W99" s="14">
+      <c r="W99" s="12">
         <v>-0.51512000000000002</v>
       </c>
       <c r="X99" s="5">
         <v>8.1040000000000001E-2</v>
       </c>
-      <c r="Y99" s="14">
+      <c r="Y99" s="12">
         <v>-0.15637999999999999</v>
       </c>
       <c r="AA99" s="5">
@@ -16722,7 +16725,7 @@
         <v>8.1680000000000003E-2</v>
       </c>
       <c r="AE99" s="5">
-        <v>-0.37975999999999999</v>
+        <v>-0.37974000000000002</v>
       </c>
       <c r="AF99" s="5">
         <v>1.9789999999999999E-2</v>
@@ -16742,10 +16745,10 @@
       <c r="AL99" s="6">
         <v>1.754</v>
       </c>
-      <c r="AM99" s="15">
+      <c r="AM99" s="13">
         <v>6.1989999999999998</v>
       </c>
-      <c r="AN99" s="15">
+      <c r="AN99" s="13">
         <v>3.3479999999999999</v>
       </c>
       <c r="AO99" s="6">
@@ -16755,7 +16758,7 @@
         <v>3.0979999999999999</v>
       </c>
       <c r="AR99">
-        <v>-1.7078</v>
+        <v>-1.7394094</v>
       </c>
       <c r="AS99">
         <v>-0.97</v>
@@ -16764,7 +16767,7 @@
         <v>-0.94</v>
       </c>
       <c r="AU99">
-        <v>-1.5686</v>
+        <v>-1.6231958</v>
       </c>
       <c r="AV99">
         <v>-1.01</v>
@@ -16773,7 +16776,7 @@
         <v>-1</v>
       </c>
       <c r="AX99">
-        <v>-1.034</v>
+        <v>-1.2325435</v>
       </c>
       <c r="AY99">
         <v>-1.1200000000000001</v>
@@ -16782,7 +16785,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BA99">
-        <v>-1.2406999999999999</v>
+        <v>-1.3595542</v>
       </c>
       <c r="BB99">
         <v>-1.1599999999999999</v>
@@ -16911,7 +16914,7 @@
         <v>2.4889999999999999</v>
       </c>
       <c r="AR100">
-        <v>-1.880737645</v>
+        <v>-1.896086945</v>
       </c>
       <c r="AS100">
         <v>-1.87</v>
@@ -16920,7 +16923,7 @@
         <v>-1.89</v>
       </c>
       <c r="AU100">
-        <v>-1.8256767149999999</v>
+        <v>-1.8489079150000001</v>
       </c>
       <c r="AV100">
         <v>-1.77</v>
@@ -16929,7 +16932,7 @@
         <v>-1.84</v>
       </c>
       <c r="AX100">
-        <v>-1.4241999999999999</v>
+        <v>-1.499986</v>
       </c>
       <c r="AY100">
         <v>-1.33</v>
@@ -16938,7 +16941,7 @@
         <v>-1.43</v>
       </c>
       <c r="BA100">
-        <v>-1.7131161880000001</v>
+        <v>-1.7484791879999999</v>
       </c>
       <c r="BB100">
         <v>-1.69</v>
@@ -17067,7 +17070,7 @@
         <v>4.6909999999999998</v>
       </c>
       <c r="AR101">
-        <v>-0.93810000000000004</v>
+        <v>-0.96170100000000014</v>
       </c>
       <c r="AS101">
         <v>-0.99</v>
@@ -17076,7 +17079,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU101">
-        <v>-0.9073</v>
+        <v>-0.94216190000000011</v>
       </c>
       <c r="AV101">
         <v>-0.97</v>
@@ -17085,7 +17088,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX101">
-        <v>-0.9467000000000001</v>
+        <v>-1.0574256</v>
       </c>
       <c r="AY101">
         <v>-0.44</v>
@@ -17094,7 +17097,7 @@
         <v>-0.54</v>
       </c>
       <c r="BA101">
-        <v>-1.0017</v>
+        <v>-1.0610279</v>
       </c>
       <c r="BB101">
         <v>-0.86</v>
@@ -17223,7 +17226,7 @@
         <v>3.6440000000000001</v>
       </c>
       <c r="AR102">
-        <v>-0.95709999999999995</v>
+        <v>-0.98730079999999987</v>
       </c>
       <c r="AS102">
         <v>-0.96</v>
@@ -17232,7 +17235,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU102">
-        <v>-1.4874145480000001</v>
+        <v>-1.533702348</v>
       </c>
       <c r="AV102">
         <v>-0.8</v>
@@ -17241,7 +17244,7 @@
         <v>-0.89</v>
       </c>
       <c r="AX102">
-        <v>-0.92080000000000006</v>
+        <v>-1.0641274000000001</v>
       </c>
       <c r="AY102">
         <v>-0.98</v>
@@ -17250,7 +17253,7 @@
         <v>-0.97</v>
       </c>
       <c r="BA102">
-        <v>-1.0008999999999999</v>
+        <v>-1.0802239</v>
       </c>
       <c r="BB102">
         <v>-0.92</v>
@@ -17379,7 +17382,7 @@
         <v>2.5110000000000001</v>
       </c>
       <c r="AR103">
-        <v>-1.9296242299999999</v>
+        <v>-1.9473172299999999</v>
       </c>
       <c r="AS103">
         <v>-1.25</v>
@@ -17388,7 +17391,7 @@
         <v>-1.93</v>
       </c>
       <c r="AU103">
-        <v>-1.9059961670000001</v>
+        <v>-1.932385767</v>
       </c>
       <c r="AV103">
         <v>-1.84</v>
@@ -17397,7 +17400,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX103">
-        <v>-0.76279999999999992</v>
+        <v>-0.86996739999999972</v>
       </c>
       <c r="AY103">
         <v>-1.57</v>
@@ -17406,7 +17409,7 @@
         <v>-1.62</v>
       </c>
       <c r="BA103">
-        <v>-1.855737588</v>
+        <v>-1.8952824880000001</v>
       </c>
       <c r="BB103">
         <v>-1.9</v>
@@ -17535,7 +17538,7 @@
         <v>4.1760000000000002</v>
       </c>
       <c r="AR104">
-        <v>-1.5918000000000001</v>
+        <v>-1.6116303000000001</v>
       </c>
       <c r="AS104">
         <v>-0.92</v>
@@ -17544,7 +17547,7 @@
         <v>-0.95</v>
       </c>
       <c r="AU104">
-        <v>-1.1565000000000001</v>
+        <v>-1.1921489999999999</v>
       </c>
       <c r="AV104">
         <v>-0.65</v>
@@ -17553,7 +17556,7 @@
         <v>-0.84</v>
       </c>
       <c r="AX104">
-        <v>-1.0625</v>
+        <v>-1.2343961000000001</v>
       </c>
       <c r="AY104">
         <v>-0.98</v>
@@ -17562,7 +17565,7 @@
         <v>-0.97</v>
       </c>
       <c r="BA104">
-        <v>-1.2178</v>
+        <v>-1.3081418</v>
       </c>
       <c r="BB104">
         <v>-0.85</v>
@@ -17691,7 +17694,7 @@
         <v>3.01</v>
       </c>
       <c r="AR105">
-        <v>-1.9365578809999999</v>
+        <v>-1.941263481</v>
       </c>
       <c r="AS105">
         <v>-1.97</v>
@@ -17700,7 +17703,7 @@
         <v>-1.93</v>
       </c>
       <c r="AU105">
-        <v>-1.911230566</v>
+        <v>-1.9174209659999999</v>
       </c>
       <c r="AV105">
         <v>-1.94</v>
@@ -17709,7 +17712,7 @@
         <v>-1.87</v>
       </c>
       <c r="AX105">
-        <v>-1.7668999999999999</v>
+        <v>-1.7799583999999999</v>
       </c>
       <c r="AY105">
         <v>-1.36</v>
@@ -17718,7 +17721,7 @@
         <v>-1.03</v>
       </c>
       <c r="BA105">
-        <v>-1.8398837370000001</v>
+        <v>-1.851415737</v>
       </c>
       <c r="BB105">
         <v>-1.46</v>
@@ -17847,7 +17850,7 @@
         <v>3.4420000000000002</v>
       </c>
       <c r="AR106">
-        <v>-1.9212328270000001</v>
+        <v>-1.9275872270000001</v>
       </c>
       <c r="AS106">
         <v>-1.8</v>
@@ -17856,7 +17859,7 @@
         <v>-1.81</v>
       </c>
       <c r="AU106">
-        <v>-1.883194926</v>
+        <v>-1.8919156260000001</v>
       </c>
       <c r="AV106">
         <v>-1.69</v>
@@ -17865,7 +17868,7 @@
         <v>-1.7</v>
       </c>
       <c r="AX106">
-        <v>-1.6266</v>
+        <v>-1.6472918999999999</v>
       </c>
       <c r="AY106">
         <v>-1.27</v>
@@ -17874,7 +17877,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BA106">
-        <v>-1.7929892860000001</v>
+        <v>-1.8094917859999999</v>
       </c>
       <c r="BB106">
         <v>-1.4</v>
@@ -18003,7 +18006,7 @@
         <v>3.452</v>
       </c>
       <c r="AR107">
-        <v>-1.921822854</v>
+        <v>-1.9287741540000001</v>
       </c>
       <c r="AS107">
         <v>-1.83</v>
@@ -18012,7 +18015,7 @@
         <v>-1.81</v>
       </c>
       <c r="AU107">
-        <v>-1.8835701149999999</v>
+        <v>-1.8933277150000001</v>
       </c>
       <c r="AV107">
         <v>-1.72</v>
@@ -18021,7 +18024,7 @@
         <v>-1.7</v>
       </c>
       <c r="AX107">
-        <v>-1.6158999999999999</v>
+        <v>-1.6427991</v>
       </c>
       <c r="AY107">
         <v>-1.28</v>
@@ -18030,7 +18033,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA107">
-        <v>-1.7908326640000001</v>
+        <v>-1.8112471640000001</v>
       </c>
       <c r="BB107">
         <v>-1.41</v>
@@ -18159,7 +18162,7 @@
         <v>3.964</v>
       </c>
       <c r="AR108">
-        <v>-1.9212392659999999</v>
+        <v>-1.927667266</v>
       </c>
       <c r="AS108">
         <v>-1.32</v>
@@ -18168,7 +18171,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AU108">
-        <v>-1.8862593080000001</v>
+        <v>-1.894848608</v>
       </c>
       <c r="AV108">
         <v>-1.08</v>
@@ -18177,7 +18180,7 @@
         <v>-1.41</v>
       </c>
       <c r="AX108">
-        <v>-1.5224</v>
+        <v>-1.5416707000000001</v>
       </c>
       <c r="AY108">
         <v>-1.69</v>
@@ -18186,7 +18189,7 @@
         <v>-1.81</v>
       </c>
       <c r="BA108">
-        <v>-1.7758230829999999</v>
+        <v>-1.791371483</v>
       </c>
       <c r="BB108">
         <v>-1.74</v>
@@ -18315,7 +18318,7 @@
         <v>3.8849999999999998</v>
       </c>
       <c r="AR109">
-        <v>-1.920077759</v>
+        <v>-1.926697959</v>
       </c>
       <c r="AS109">
         <v>-1.47</v>
@@ -18324,7 +18327,7 @@
         <v>-1.04</v>
       </c>
       <c r="AU109">
-        <v>-1.8836942940000001</v>
+        <v>-1.8927092940000001</v>
       </c>
       <c r="AV109">
         <v>-1.2</v>
@@ -18333,7 +18336,7 @@
         <v>-1.36</v>
       </c>
       <c r="AX109">
-        <v>-1.5154000000000001</v>
+        <v>-1.5395342000000001</v>
       </c>
       <c r="AY109">
         <v>-1.63</v>
@@ -18342,7 +18345,7 @@
         <v>-1.76</v>
       </c>
       <c r="BA109">
-        <v>-1.776138835</v>
+        <v>-1.7936631350000001</v>
       </c>
       <c r="BB109">
         <v>-1.64</v>
@@ -18471,7 +18474,7 @@
         <v>3.081</v>
       </c>
       <c r="AR110">
-        <v>-1.9354409640000001</v>
+        <v>-1.940050464</v>
       </c>
       <c r="AS110">
         <v>-1.97</v>
@@ -18480,7 +18483,7 @@
         <v>-1.91</v>
       </c>
       <c r="AU110">
-        <v>-1.9082738299999999</v>
+        <v>-1.9143779299999999</v>
       </c>
       <c r="AV110">
         <v>-1.93</v>
@@ -18489,7 +18492,7 @@
         <v>-1.82</v>
       </c>
       <c r="AX110">
-        <v>-1.6752</v>
+        <v>-1.6945994</v>
       </c>
       <c r="AY110">
         <v>-0.98</v>
@@ -18498,7 +18501,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA110">
-        <v>-1.791850556</v>
+        <v>-1.8063501559999999</v>
       </c>
       <c r="BB110">
         <v>-1.08</v>
@@ -18627,7 +18630,7 @@
         <v>3.2589999999999999</v>
       </c>
       <c r="AR111">
-        <v>-1.923014749</v>
+        <v>-1.9298952490000001</v>
       </c>
       <c r="AS111">
         <v>-1.96</v>
@@ -18636,7 +18639,7 @@
         <v>-1.85</v>
       </c>
       <c r="AU111">
-        <v>-1.8924931899999999</v>
+        <v>-1.9017115899999999</v>
       </c>
       <c r="AV111">
         <v>-1.91</v>
@@ -18645,7 +18648,7 @@
         <v>-1.67</v>
       </c>
       <c r="AX111">
-        <v>-1.7224999999999999</v>
+        <v>-1.7422498</v>
       </c>
       <c r="AY111">
         <v>-1.06</v>
@@ -18654,7 +18657,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA111">
-        <v>-1.8174025069999999</v>
+        <v>-1.8335004070000001</v>
       </c>
       <c r="BB111">
         <v>-1.03</v>
@@ -18783,7 +18786,7 @@
         <v>3.548</v>
       </c>
       <c r="AR112">
-        <v>-1.8732529040000001</v>
+        <v>-1.8804064039999999</v>
       </c>
       <c r="AS112">
         <v>-1.74</v>
@@ -18792,7 +18795,7 @@
         <v>-1.56</v>
       </c>
       <c r="AU112">
-        <v>-1.825308044</v>
+        <v>-1.835243644</v>
       </c>
       <c r="AV112">
         <v>-1.36</v>
@@ -18801,7 +18804,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AX112">
-        <v>-0.79190000000000005</v>
+        <v>-0.82272200000000018</v>
       </c>
       <c r="AY112">
         <v>-1.3</v>
@@ -18810,7 +18813,7 @@
         <v>-1.36</v>
       </c>
       <c r="BA112">
-        <v>-1.7532514690000001</v>
+        <v>-1.7665285690000001</v>
       </c>
       <c r="BB112">
         <v>-1.54</v>
@@ -18939,7 +18942,7 @@
         <v>3.472</v>
       </c>
       <c r="AR113">
-        <v>-1.893052307</v>
+        <v>-1.900016607</v>
       </c>
       <c r="AS113">
         <v>-1.88</v>
@@ -18948,7 +18951,7 @@
         <v>-1.75</v>
       </c>
       <c r="AU113">
-        <v>-1.850789429</v>
+        <v>-1.860433529</v>
       </c>
       <c r="AV113">
         <v>-1.64</v>
@@ -18957,7 +18960,7 @@
         <v>-1.38</v>
       </c>
       <c r="AX113">
-        <v>-0.81150000000000011</v>
+        <v>-0.83636640000000018</v>
       </c>
       <c r="AY113">
         <v>-1.38</v>
@@ -18966,7 +18969,7 @@
         <v>-1.46</v>
       </c>
       <c r="BA113">
-        <v>-1.805553202</v>
+        <v>-1.8180769020000001</v>
       </c>
       <c r="BB113">
         <v>-1.57</v>
@@ -19095,7 +19098,7 @@
         <v>3.4550000000000001</v>
       </c>
       <c r="AR114">
-        <v>-1.8950467390000001</v>
+        <v>-1.903570539</v>
       </c>
       <c r="AS114">
         <v>-1.89</v>
@@ -19104,7 +19107,7 @@
         <v>-1.82</v>
       </c>
       <c r="AU114">
-        <v>-1.851656835</v>
+        <v>-1.863666635</v>
       </c>
       <c r="AV114">
         <v>-1.7</v>
@@ -19113,7 +19116,7 @@
         <v>-1.57</v>
       </c>
       <c r="AX114">
-        <v>-0.79909999999999992</v>
+        <v>-0.82847050000000011</v>
       </c>
       <c r="AY114">
         <v>-1.36</v>
@@ -19122,7 +19125,7 @@
         <v>-1.43</v>
       </c>
       <c r="BA114">
-        <v>-1.785959415</v>
+        <v>-1.802972515</v>
       </c>
       <c r="BB114">
         <v>-1.47</v>
@@ -19251,7 +19254,7 @@
         <v>2.6309999999999998</v>
       </c>
       <c r="AR115">
-        <v>-1.911281242</v>
+        <v>-1.920955242</v>
       </c>
       <c r="AS115">
         <v>-1.91</v>
@@ -19260,7 +19263,7 @@
         <v>-1.88</v>
       </c>
       <c r="AU115">
-        <v>-1.8823037410000001</v>
+        <v>-1.8953846409999999</v>
       </c>
       <c r="AV115">
         <v>-1.85</v>
@@ -19269,7 +19272,7 @@
         <v>-1.84</v>
       </c>
       <c r="AX115">
-        <v>-1.2252000000000001</v>
+        <v>-1.2634588</v>
       </c>
       <c r="AY115">
         <v>-1</v>
@@ -19278,7 +19281,7 @@
         <v>-1.01</v>
       </c>
       <c r="BA115">
-        <v>-1.4434124429999999</v>
+        <v>-1.4576116429999999</v>
       </c>
       <c r="BB115">
         <v>-0.83</v>
@@ -19407,7 +19410,7 @@
         <v>3.35</v>
       </c>
       <c r="AR116">
-        <v>-1.9112909060000001</v>
+        <v>-1.919670306</v>
       </c>
       <c r="AS116">
         <v>-1.95</v>
@@ -19416,7 +19419,7 @@
         <v>-1.71</v>
       </c>
       <c r="AU116">
-        <v>-1.880200579</v>
+        <v>-1.8918933790000001</v>
       </c>
       <c r="AV116">
         <v>-1.88</v>
@@ -19425,7 +19428,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AX116">
-        <v>-1.4495</v>
+        <v>-1.4704227999999999</v>
       </c>
       <c r="AY116">
         <v>-1.28</v>
@@ -19434,7 +19437,7 @@
         <v>-1.34</v>
       </c>
       <c r="BA116">
-        <v>-1.667052161</v>
+        <v>-1.679222561</v>
       </c>
       <c r="BB116">
         <v>-1.17</v>
@@ -19563,7 +19566,7 @@
         <v>2.3580000000000001</v>
       </c>
       <c r="AR117">
-        <v>-1.9154927340000001</v>
+        <v>-1.925682034</v>
       </c>
       <c r="AS117">
         <v>-1.81</v>
@@ -19572,7 +19575,7 @@
         <v>-1.9</v>
       </c>
       <c r="AU117">
-        <v>-1.881028723</v>
+        <v>-1.895488823</v>
       </c>
       <c r="AV117">
         <v>-1.72</v>
@@ -19581,7 +19584,7 @@
         <v>-1.86</v>
       </c>
       <c r="AX117">
-        <v>-1.6716</v>
+        <v>-1.7096015</v>
       </c>
       <c r="AY117">
         <v>-1.64</v>
@@ -19590,7 +19593,7 @@
         <v>-1.7</v>
       </c>
       <c r="BA117">
-        <v>-1.8058336500000001</v>
+        <v>-1.8287578499999999</v>
       </c>
       <c r="BB117">
         <v>-1.79</v>
@@ -19719,7 +19722,7 @@
         <v>2.72</v>
       </c>
       <c r="AR118">
-        <v>-1.868614481</v>
+        <v>-1.880734881</v>
       </c>
       <c r="AS118">
         <v>-1.66</v>
@@ -19728,7 +19731,7 @@
         <v>-1.78</v>
       </c>
       <c r="AU118">
-        <v>-1.818471223</v>
+        <v>-1.8366342229999999</v>
       </c>
       <c r="AV118">
         <v>-1.51</v>
@@ -19737,7 +19740,7 @@
         <v>-1.67</v>
       </c>
       <c r="AX118">
-        <v>-1.5341</v>
+        <v>-1.5875976000000001</v>
       </c>
       <c r="AY118">
         <v>-1.21</v>
@@ -19746,7 +19749,7 @@
         <v>-1.65</v>
       </c>
       <c r="BA118">
-        <v>-1.7168828060000001</v>
+        <v>-1.746028106</v>
       </c>
       <c r="BB118">
         <v>-1.51</v>
@@ -19875,7 +19878,7 @@
         <v>2.4580000000000002</v>
       </c>
       <c r="AR119">
-        <v>-1.4494011069999999</v>
+        <v>-1.4657642070000001</v>
       </c>
       <c r="AS119">
         <v>-1.37</v>
@@ -19884,7 +19887,7 @@
         <v>-1.39</v>
       </c>
       <c r="AU119">
-        <v>-1.3955296399999999</v>
+        <v>-1.4193576400000001</v>
       </c>
       <c r="AV119">
         <v>-1.27</v>
@@ -19893,7 +19896,7 @@
         <v>-1.26</v>
       </c>
       <c r="AX119">
-        <v>-1.1015999999999999</v>
+        <v>-1.1726128</v>
       </c>
       <c r="AY119">
         <v>-0.86</v>
@@ -19902,7 +19905,7 @@
         <v>-0.83</v>
       </c>
       <c r="BA119">
-        <v>-1.1930000000000001</v>
+        <v>-1.2369112</v>
       </c>
       <c r="BB119">
         <v>-0.77</v>
@@ -20031,7 +20034,7 @@
         <v>2.6539999999999999</v>
       </c>
       <c r="AR120">
-        <v>-1.802274991</v>
+        <v>-1.8149816910000001</v>
       </c>
       <c r="AS120">
         <v>-1.67</v>
@@ -20040,7 +20043,7 @@
         <v>-1.83</v>
       </c>
       <c r="AU120">
-        <v>-1.7463950260000001</v>
+        <v>-1.764726926</v>
       </c>
       <c r="AV120">
         <v>-1.59</v>
@@ -20049,7 +20052,7 @@
         <v>-1.79</v>
       </c>
       <c r="AX120">
-        <v>-1.4379999999999999</v>
+        <v>-1.4962797000000001</v>
       </c>
       <c r="AY120">
         <v>-0.99</v>
@@ -20058,7 +20061,7 @@
         <v>-1.03</v>
       </c>
       <c r="BA120">
-        <v>-1.6107500779999999</v>
+        <v>-1.641637778</v>
       </c>
       <c r="BB120">
         <v>-0.92</v>
@@ -20187,7 +20190,7 @@
         <v>3.4329999999999998</v>
       </c>
       <c r="AR121">
-        <v>-1.904010832</v>
+        <v>-1.914725832</v>
       </c>
       <c r="AS121">
         <v>-1.88</v>
@@ -20196,7 +20199,7 @@
         <v>-1.89</v>
       </c>
       <c r="AU121">
-        <v>-1.855214436</v>
+        <v>-1.8715161360000001</v>
       </c>
       <c r="AV121">
         <v>-1.8</v>
@@ -20205,7 +20208,7 @@
         <v>-1.82</v>
       </c>
       <c r="AX121">
-        <v>-1.5623</v>
+        <v>-1.6122787000000001</v>
       </c>
       <c r="AY121">
         <v>-1.42</v>
@@ -20214,7 +20217,7 @@
         <v>-1.42</v>
       </c>
       <c r="BA121">
-        <v>-1.764622666</v>
+        <v>-1.8070099660000001</v>
       </c>
       <c r="BB121">
         <v>-1.58</v>
@@ -20316,7 +20319,7 @@
         <v>4.4110000000000003E-2</v>
       </c>
       <c r="AG122" s="5">
-        <v>0.10981</v>
+        <v>0.10979</v>
       </c>
       <c r="AI122" s="6">
         <v>3.2490000000000001</v>
@@ -20343,7 +20346,7 @@
         <v>1.647</v>
       </c>
       <c r="AR122">
-        <v>-1.6438158970000001</v>
+        <v>-1.671455197</v>
       </c>
       <c r="AS122">
         <v>-1.6</v>
@@ -20352,7 +20355,7 @@
         <v>-1.62</v>
       </c>
       <c r="AU122">
-        <v>-1.4968599680000001</v>
+        <v>-1.539737868</v>
       </c>
       <c r="AV122">
         <v>-1.46</v>
@@ -20361,7 +20364,7 @@
         <v>-1.48</v>
       </c>
       <c r="AX122">
-        <v>-0.82559999999999989</v>
+        <v>-0.94469329999999974</v>
       </c>
       <c r="AY122">
         <v>-1.0900000000000001</v>
@@ -20370,7 +20373,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BA122">
-        <v>-1.1674</v>
+        <v>-1.2525071000000001</v>
       </c>
       <c r="BB122">
         <v>-1.08</v>
@@ -20472,7 +20475,7 @@
         <v>0.17146</v>
       </c>
       <c r="AG123" s="5">
-        <v>0.10100000000000001</v>
+        <v>0.10102999999999999</v>
       </c>
       <c r="AI123" s="6">
         <v>2.024</v>
@@ -20499,7 +20502,7 @@
         <v>5.1749999999999998</v>
       </c>
       <c r="AR123">
-        <v>-1.931547243</v>
+        <v>-1.936967543</v>
       </c>
       <c r="AS123">
         <v>-0.99</v>
@@ -20508,7 +20511,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU123">
-        <v>-1.4902921229999999</v>
+        <v>-1.5377629230000001</v>
       </c>
       <c r="AV123">
         <v>-0.66</v>
@@ -20517,7 +20520,7 @@
         <v>-0.79</v>
       </c>
       <c r="AX123">
-        <v>-0.85460000000000003</v>
+        <v>-1.0124773</v>
       </c>
       <c r="AY123">
         <v>-1.1100000000000001</v>
@@ -20526,7 +20529,7 @@
         <v>-0.93</v>
       </c>
       <c r="BA123">
-        <v>-1.5354000000000001</v>
+        <v>-1.6219387000000001</v>
       </c>
       <c r="BB123">
         <v>-1.18</v>
@@ -20655,7 +20658,7 @@
         <v>3.7389999999999999</v>
       </c>
       <c r="AR124">
-        <v>-1.564334624</v>
+        <v>-1.598878824</v>
       </c>
       <c r="AS124">
         <v>-0.96</v>
@@ -20664,7 +20667,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU124">
-        <v>-1.4378894129999999</v>
+        <v>-1.488200513</v>
       </c>
       <c r="AV124">
         <v>-0.99</v>
@@ -20673,7 +20676,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX124">
-        <v>-0.86769999999999992</v>
+        <v>-0.98107600000000006</v>
       </c>
       <c r="AY124">
         <v>-0.55000000000000004</v>
@@ -20682,7 +20685,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA124">
-        <v>-1.2710999999999999</v>
+        <v>-1.3517573000000001</v>
       </c>
       <c r="BB124">
         <v>-1.04</v>
@@ -20811,7 +20814,7 @@
         <v>2.2570000000000001</v>
       </c>
       <c r="AR125">
-        <v>-1.9481658930000001</v>
+        <v>-1.955926493</v>
       </c>
       <c r="AS125">
         <v>-1.65</v>
@@ -20820,7 +20823,7 @@
         <v>-1.79</v>
       </c>
       <c r="AU125">
-        <v>-1.93073139</v>
+        <v>-1.9409257900000001</v>
       </c>
       <c r="AV125">
         <v>-1.52</v>
@@ -20829,7 +20832,7 @@
         <v>-1.68</v>
       </c>
       <c r="AX125">
-        <v>-1.8469</v>
+        <v>-1.8656028</v>
       </c>
       <c r="AY125">
         <v>-1.27</v>
@@ -20838,7 +20841,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA125">
-        <v>-1.898643401</v>
+        <v>-1.9128307010000001</v>
       </c>
       <c r="BB125">
         <v>-1.53</v>
@@ -20967,7 +20970,7 @@
         <v>2.3679999999999999</v>
       </c>
       <c r="AR126">
-        <v>-1.9401698949999999</v>
+        <v>-1.946933695</v>
       </c>
       <c r="AS126">
         <v>-1.63</v>
@@ -20976,7 +20979,7 @@
         <v>-1.75</v>
       </c>
       <c r="AU126">
-        <v>-1.9193389999999999</v>
+        <v>-1.9281178000000001</v>
       </c>
       <c r="AV126">
         <v>-1.49</v>
@@ -20985,7 +20988,7 @@
         <v>-1.62</v>
       </c>
       <c r="AX126">
-        <v>-1.8061</v>
+        <v>-1.8228622000000001</v>
       </c>
       <c r="AY126">
         <v>-1.18</v>
@@ -20994,7 +20997,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA126">
-        <v>-1.871344873</v>
+        <v>-1.883843473</v>
       </c>
       <c r="BB126">
         <v>-1.49</v>
@@ -21123,7 +21126,7 @@
         <v>2.657</v>
       </c>
       <c r="AR127">
-        <v>-1.9381432830000001</v>
+        <v>-1.9485338830000001</v>
       </c>
       <c r="AS127">
         <v>-1.69</v>
@@ -21132,7 +21135,7 @@
         <v>-1.72</v>
       </c>
       <c r="AU127">
-        <v>-1.917542072</v>
+        <v>-1.931122872</v>
       </c>
       <c r="AV127">
         <v>-1.56</v>
@@ -21141,7 +21144,7 @@
         <v>-1.59</v>
       </c>
       <c r="AX127">
-        <v>-1.7950999999999999</v>
+        <v>-1.8223404000000001</v>
       </c>
       <c r="AY127">
         <v>-1.0900000000000001</v>
@@ -21150,7 +21153,7 @@
         <v>-0.95</v>
       </c>
       <c r="BA127">
-        <v>-1.8725258330000001</v>
+        <v>-1.8912378329999999</v>
       </c>
       <c r="BB127">
         <v>-1.37</v>
@@ -21279,7 +21282,7 @@
         <v>2.415</v>
       </c>
       <c r="AR128">
-        <v>-1.9227037069999999</v>
+        <v>-1.9302438070000001</v>
       </c>
       <c r="AS128">
         <v>-1.58</v>
@@ -21288,7 +21291,7 @@
         <v>-1.76</v>
       </c>
       <c r="AU128">
-        <v>-1.8916259689999999</v>
+        <v>-1.901850169</v>
       </c>
       <c r="AV128">
         <v>-1.44</v>
@@ -21297,7 +21300,7 @@
         <v>-1.67</v>
       </c>
       <c r="AX128">
-        <v>-1.7419</v>
+        <v>-1.7667056000000001</v>
       </c>
       <c r="AY128">
         <v>-1.0900000000000001</v>
@@ -21306,7 +21309,7 @@
         <v>-1.01</v>
       </c>
       <c r="BA128">
-        <v>-1.881910427</v>
+        <v>-1.893611827</v>
       </c>
       <c r="BB128">
         <v>-1.3</v>
@@ -21435,7 +21438,7 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="AR129">
-        <v>-1.9436004600000001</v>
+        <v>-1.9512651599999999</v>
       </c>
       <c r="AS129">
         <v>-1.57</v>
@@ -21444,7 +21447,7 @@
         <v>-1.7</v>
       </c>
       <c r="AU129">
-        <v>-1.9236605680000001</v>
+        <v>-1.9337069680000001</v>
       </c>
       <c r="AV129">
         <v>-1.43</v>
@@ -21453,7 +21456,7 @@
         <v>-1.57</v>
       </c>
       <c r="AX129">
-        <v>-1.8403</v>
+        <v>-1.8580616000000001</v>
       </c>
       <c r="AY129">
         <v>-1.07</v>
@@ -21462,7 +21465,7 @@
         <v>-1.04</v>
       </c>
       <c r="BA129">
-        <v>-1.9083114670000001</v>
+        <v>-1.9204604670000001</v>
       </c>
       <c r="BB129">
         <v>-1.24</v>
@@ -21591,7 +21594,7 @@
         <v>2.4830000000000001</v>
       </c>
       <c r="AR130">
-        <v>-1.939445788</v>
+        <v>-1.947110688</v>
       </c>
       <c r="AS130">
         <v>-1.59</v>
@@ -21600,7 +21603,7 @@
         <v>-1.74</v>
       </c>
       <c r="AU130">
-        <v>-1.9173649129999999</v>
+        <v>-1.9275863129999999</v>
       </c>
       <c r="AV130">
         <v>-1.45</v>
@@ -21609,7 +21612,7 @@
         <v>-1.63</v>
       </c>
       <c r="AX130">
-        <v>-1.8278000000000001</v>
+        <v>-1.8467445</v>
       </c>
       <c r="AY130">
         <v>-1.1000000000000001</v>
@@ -21618,7 +21621,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BA130">
-        <v>-1.9014208539999999</v>
+        <v>-1.913562854</v>
       </c>
       <c r="BB130">
         <v>-1.28</v>
@@ -21747,7 +21750,7 @@
         <v>2.484</v>
       </c>
       <c r="AR131">
-        <v>-1.7789242030000001</v>
+        <v>-1.7895636029999999</v>
       </c>
       <c r="AS131">
         <v>-1.56</v>
@@ -21756,7 +21759,7 @@
         <v>-1.73</v>
       </c>
       <c r="AU131">
-        <v>-1.7159371940000001</v>
+        <v>-1.7340185939999999</v>
       </c>
       <c r="AV131">
         <v>-1.35</v>
@@ -21765,7 +21768,7 @@
         <v>-1.67</v>
       </c>
       <c r="AX131">
-        <v>-0.92399999999999993</v>
+        <v>-1.0709154000000001</v>
       </c>
       <c r="AY131">
         <v>-1.34</v>
@@ -21774,7 +21777,7 @@
         <v>-1.28</v>
       </c>
       <c r="BA131">
-        <v>-1.2970999999999999</v>
+        <v>-1.3598763</v>
       </c>
       <c r="BB131">
         <v>-1.49</v>
@@ -21903,7 +21906,7 @@
         <v>2.4740000000000002</v>
       </c>
       <c r="AR132">
-        <v>-1.8077872230000001</v>
+        <v>-1.8259950229999999</v>
       </c>
       <c r="AS132">
         <v>-1.65</v>
@@ -21912,7 +21915,7 @@
         <v>-1.82</v>
       </c>
       <c r="AU132">
-        <v>-1.7465053150000001</v>
+        <v>-1.775954915</v>
       </c>
       <c r="AV132">
         <v>-1.48</v>
@@ -21921,7 +21924,7 @@
         <v>-1.77</v>
       </c>
       <c r="AX132">
-        <v>-1.3951</v>
+        <v>-1.5077871</v>
       </c>
       <c r="AY132">
         <v>-1.29</v>
@@ -21930,7 +21933,7 @@
         <v>-1.22</v>
       </c>
       <c r="BA132">
-        <v>-1.625910755</v>
+        <v>-1.681033955</v>
       </c>
       <c r="BB132">
         <v>-1.18</v>
@@ -22059,7 +22062,7 @@
         <v>2.5790000000000002</v>
       </c>
       <c r="AR133">
-        <v>-1.896470876</v>
+        <v>-1.9105877760000001</v>
       </c>
       <c r="AS133">
         <v>-1.91</v>
@@ -22068,7 +22071,7 @@
         <v>-1.91</v>
       </c>
       <c r="AU133">
-        <v>-0.93965242425530804</v>
+        <v>-0.96202752425530802</v>
       </c>
       <c r="AV133">
         <v>-1.81</v>
@@ -22077,7 +22080,7 @@
         <v>-1.83</v>
       </c>
       <c r="AX133">
-        <v>-0.83640000000000003</v>
+        <v>-0.95254149999999993</v>
       </c>
       <c r="AY133">
         <v>-1.06</v>
@@ -22086,7 +22089,7 @@
         <v>-1.07</v>
       </c>
       <c r="BA133">
-        <v>-0.89459999999999995</v>
+        <v>-0.93780890000000028</v>
       </c>
       <c r="BB133">
         <v>-1.56</v>
@@ -22215,7 +22218,7 @@
         <v>2.4780000000000002</v>
       </c>
       <c r="AR134">
-        <v>-1.2710999999999999</v>
+        <v>-1.2948341999999999</v>
       </c>
       <c r="AS134">
         <v>-0.51</v>
@@ -22224,7 +22227,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU134">
-        <v>-1.2970999999999999</v>
+        <v>-1.3321483999999999</v>
       </c>
       <c r="AV134">
         <v>-0.69</v>
@@ -22233,7 +22236,7 @@
         <v>-0.97</v>
       </c>
       <c r="AX134">
-        <v>-1.1498999999999999</v>
+        <v>-1.2572147</v>
       </c>
       <c r="AY134">
         <v>-0.8</v>
@@ -22242,7 +22245,7 @@
         <v>-0.88</v>
       </c>
       <c r="BA134">
-        <v>-1.2248000000000001</v>
+        <v>-1.2941758999999999</v>
       </c>
       <c r="BB134">
         <v>-0.93</v>
@@ -22371,7 +22374,7 @@
         <v>2.6440000000000001</v>
       </c>
       <c r="AR135">
-        <v>-0.99019070600901404</v>
+        <v>-1.010383406009014</v>
       </c>
       <c r="AS135">
         <v>-1.65</v>
@@ -22380,7 +22383,7 @@
         <v>-1.67</v>
       </c>
       <c r="AU135">
-        <v>-0.96373584155382597</v>
+        <v>-0.99435074155382575</v>
       </c>
       <c r="AV135">
         <v>-1.56</v>
@@ -22389,7 +22392,7 @@
         <v>-1.59</v>
       </c>
       <c r="AX135">
-        <v>-0.89440000000000008</v>
+        <v>-1.0222361</v>
       </c>
       <c r="AY135">
         <v>-1.07</v>
@@ -22398,7 +22401,7 @@
         <v>-1.08</v>
       </c>
       <c r="BA135">
-        <v>-0.91210000000000002</v>
+        <v>-0.97278870000000017</v>
       </c>
       <c r="BB135">
         <v>-1.49</v>
@@ -22527,7 +22530,7 @@
         <v>2.198</v>
       </c>
       <c r="AR136">
-        <v>-1.94005564</v>
+        <v>-1.9593166399999999</v>
       </c>
       <c r="AS136">
         <v>-1.91</v>
@@ -22536,7 +22539,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU136">
-        <v>-1.913260586</v>
+        <v>-1.941697386</v>
       </c>
       <c r="AV136">
         <v>-1.87</v>
@@ -22545,7 +22548,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX136">
-        <v>-1.3255999999999999</v>
+        <v>-1.4543912999999999</v>
       </c>
       <c r="AY136">
         <v>-1.37</v>
@@ -22554,7 +22557,7 @@
         <v>-1.27</v>
       </c>
       <c r="BA136">
-        <v>-1.550358718</v>
+        <v>-1.620844618</v>
       </c>
       <c r="BB136">
         <v>-1.01</v>
@@ -22683,7 +22686,7 @@
         <v>3.0289999999999999</v>
       </c>
       <c r="AR137">
-        <v>-1.924678624</v>
+        <v>-1.9475314239999999</v>
       </c>
       <c r="AS137">
         <v>-0.99</v>
@@ -22692,7 +22695,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU137">
-        <v>-1.8938081200000001</v>
+        <v>-1.9261930199999999</v>
       </c>
       <c r="AV137">
         <v>-0.98</v>
@@ -22701,7 +22704,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX137">
-        <v>-1.6448</v>
+        <v>-1.7274176000000001</v>
       </c>
       <c r="AY137">
         <v>-0.46</v>
@@ -22710,7 +22713,7 @@
         <v>-0.9</v>
       </c>
       <c r="BA137">
-        <v>-1.793522499</v>
+        <v>-1.8444360989999999</v>
       </c>
       <c r="BB137">
         <v>-0.97</v>
@@ -22839,7 +22842,7 @@
         <v>3.3730000000000002</v>
       </c>
       <c r="AR138">
-        <v>-1.9070394610000001</v>
+        <v>-1.9141872609999999</v>
       </c>
       <c r="AS138">
         <v>-1.55</v>
@@ -22848,7 +22851,7 @@
         <v>-1.41</v>
       </c>
       <c r="AU138">
-        <v>-1.8693167850000001</v>
+        <v>-1.878544685</v>
       </c>
       <c r="AV138">
         <v>-1.4</v>
@@ -22857,7 +22860,7 @@
         <v>-1.28</v>
       </c>
       <c r="AX138">
-        <v>-1.601</v>
+        <v>-1.6332886</v>
       </c>
       <c r="AY138">
         <v>-0.94</v>
@@ -22866,7 +22869,7 @@
         <v>-0.89</v>
       </c>
       <c r="BA138">
-        <v>-1.774016526</v>
+        <v>-1.7904235260000001</v>
       </c>
       <c r="BB138">
         <v>-1.0900000000000001</v>
@@ -22995,7 +22998,7 @@
         <v>3.4660000000000002</v>
       </c>
       <c r="AR139">
-        <v>-1.90665722</v>
+        <v>-1.9139934199999999</v>
       </c>
       <c r="AS139">
         <v>-1.47</v>
@@ -23004,7 +23007,7 @@
         <v>-1.29</v>
       </c>
       <c r="AU139">
-        <v>-1.8686388469999999</v>
+        <v>-1.878144847</v>
       </c>
       <c r="AV139">
         <v>-1.32</v>
@@ -23013,7 +23016,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AX139">
-        <v>-1.5828</v>
+        <v>-1.6167841999999999</v>
       </c>
       <c r="AY139">
         <v>-0.89</v>
@@ -23022,7 +23025,7 @@
         <v>-0.94</v>
       </c>
       <c r="BA139">
-        <v>-1.7761552279999999</v>
+        <v>-1.792677028</v>
       </c>
       <c r="BB139">
         <v>-0.99</v>
@@ -23151,7 +23154,7 @@
         <v>3.198</v>
       </c>
       <c r="AR140">
-        <v>-1.888652891</v>
+        <v>-1.8974728910000001</v>
       </c>
       <c r="AS140">
         <v>-1.61</v>
@@ -23160,7 +23163,7 @@
         <v>-1.58</v>
       </c>
       <c r="AU140">
-        <v>-1.8421434779999999</v>
+        <v>-1.854222678</v>
       </c>
       <c r="AV140">
         <v>-1.49</v>
@@ -23169,7 +23172,7 @@
         <v>-1.49</v>
       </c>
       <c r="AX140">
-        <v>-1.5673999999999999</v>
+        <v>-1.6123769999999999</v>
       </c>
       <c r="AY140">
         <v>-1.08</v>
@@ -23178,7 +23181,7 @@
         <v>-1.08</v>
       </c>
       <c r="BA140">
-        <v>-1.733752347</v>
+        <v>-1.7571283470000001</v>
       </c>
       <c r="BB140">
         <v>-1.3</v>
@@ -23307,7 +23310,7 @@
         <v>3.4009999999999998</v>
       </c>
       <c r="AR141">
-        <v>-1.8993074969999999</v>
+        <v>-1.9075972969999999</v>
       </c>
       <c r="AS141">
         <v>-1.57</v>
@@ -23316,7 +23319,7 @@
         <v>-1.4</v>
       </c>
       <c r="AU141">
-        <v>-1.8564425769999999</v>
+        <v>-1.8676678769999999</v>
       </c>
       <c r="AV141">
         <v>-1.4</v>
@@ -23325,7 +23328,7 @@
         <v>-1.26</v>
       </c>
       <c r="AX141">
-        <v>-1.5410999999999999</v>
+        <v>-1.5863233000000001</v>
       </c>
       <c r="AY141">
         <v>-0.85</v>
@@ -23334,7 +23337,7 @@
         <v>-0.88</v>
       </c>
       <c r="BA141">
-        <v>-1.735661422</v>
+        <v>-1.757858522</v>
       </c>
       <c r="BB141">
         <v>-1.02</v>
@@ -23463,7 +23466,7 @@
         <v>3.0790000000000002</v>
       </c>
       <c r="AR142">
-        <v>-1.869865675</v>
+        <v>-1.881820375</v>
       </c>
       <c r="AS142">
         <v>-1.64</v>
@@ -23472,7 +23475,7 @@
         <v>-1.67</v>
       </c>
       <c r="AU142">
-        <v>-1.8180401450000001</v>
+        <v>-1.8348616449999999</v>
       </c>
       <c r="AV142">
         <v>-1.53</v>
@@ -23481,7 +23484,7 @@
         <v>-1.58</v>
       </c>
       <c r="AX142">
-        <v>-1.5517000000000001</v>
+        <v>-1.6092727</v>
       </c>
       <c r="AY142">
         <v>-1.18</v>
@@ -23490,7 +23493,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA142">
-        <v>-1.7159430280000001</v>
+        <v>-1.7471604279999999</v>
       </c>
       <c r="BB142">
         <v>-1.42</v>
@@ -23619,7 +23622,7 @@
         <v>3.6789999999999998</v>
       </c>
       <c r="AR143">
-        <v>-1.899415211</v>
+        <v>-1.9104866110000001</v>
       </c>
       <c r="AS143">
         <v>-1.19</v>
@@ -23628,7 +23631,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU143">
-        <v>-1.858387966</v>
+        <v>-1.874288366</v>
       </c>
       <c r="AV143">
         <v>-0.98</v>
@@ -23637,7 +23640,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AX143">
-        <v>-1.5123</v>
+        <v>-1.5693109999999999</v>
       </c>
       <c r="AY143">
         <v>-1.23</v>
@@ -23646,7 +23649,7 @@
         <v>-1.27</v>
       </c>
       <c r="BA143">
-        <v>-1.7208000000000001</v>
+        <v>-1.7530726999999999</v>
       </c>
       <c r="BB143">
         <v>-1.24</v>
@@ -23775,7 +23778,7 @@
         <v>3.6640000000000001</v>
       </c>
       <c r="AR144">
-        <v>-1.9035920319999999</v>
+        <v>-1.914609032</v>
       </c>
       <c r="AS144">
         <v>-1.2</v>
@@ -23784,7 +23787,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU144">
-        <v>-1.8639392509999999</v>
+        <v>-1.879648151</v>
       </c>
       <c r="AV144">
         <v>-1</v>
@@ -23793,7 +23796,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AX144">
-        <v>-1.5229999999999999</v>
+        <v>-1.5786032999999999</v>
       </c>
       <c r="AY144">
         <v>-1.23</v>
@@ -23802,7 +23805,7 @@
         <v>-1.28</v>
       </c>
       <c r="BA144">
-        <v>-1.7264999999999999</v>
+        <v>-1.7581032999999999</v>
       </c>
       <c r="BB144">
         <v>-1.25</v>
@@ -23931,7 +23934,7 @@
         <v>3.774</v>
       </c>
       <c r="AR145">
-        <v>-1.909783054</v>
+        <v>-1.9189271539999999</v>
       </c>
       <c r="AS145">
         <v>-1.1499999999999999</v>
@@ -23940,7 +23943,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AU145">
-        <v>-1.872695467</v>
+        <v>-1.8854497670000001</v>
       </c>
       <c r="AV145">
         <v>-0.97</v>
@@ -23949,7 +23952,7 @@
         <v>-1.21</v>
       </c>
       <c r="AX145">
-        <v>-1.4893000000000001</v>
+        <v>-1.5375884</v>
       </c>
       <c r="AY145">
         <v>-1.31</v>
@@ -23958,7 +23961,7 @@
         <v>-1.37</v>
       </c>
       <c r="BA145">
-        <v>-1.7544999999999999</v>
+        <v>-1.7801113</v>
       </c>
       <c r="BB145">
         <v>-1.35</v>
@@ -24087,7 +24090,7 @@
         <v>3.742</v>
       </c>
       <c r="AR146">
-        <v>-1.9117108359999999</v>
+        <v>-1.920815336</v>
       </c>
       <c r="AS146">
         <v>-1.19</v>
@@ -24096,7 +24099,7 @@
         <v>-1.04</v>
       </c>
       <c r="AU146">
-        <v>-1.875609723</v>
+        <v>-1.888195423</v>
       </c>
       <c r="AV146">
         <v>-0.99</v>
@@ -24105,7 +24108,7 @@
         <v>-1.17</v>
       </c>
       <c r="AX146">
-        <v>-1.5045999999999999</v>
+        <v>-1.550319</v>
       </c>
       <c r="AY146">
         <v>-1.31</v>
@@ -24114,7 +24117,7 @@
         <v>-1.37</v>
       </c>
       <c r="BA146">
-        <v>-1.7632000000000001</v>
+        <v>-1.7875369000000001</v>
       </c>
       <c r="BB146">
         <v>-1.35</v>
@@ -24243,7 +24246,7 @@
         <v>3.5609999999999999</v>
       </c>
       <c r="AR147">
-        <v>-1.906950564</v>
+        <v>-1.9143868639999999</v>
       </c>
       <c r="AS147">
         <v>-1.38</v>
@@ -24252,7 +24255,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AU147">
-        <v>-1.869065258</v>
+        <v>-1.8786874579999999</v>
       </c>
       <c r="AV147">
         <v>-1.23</v>
@@ -24261,7 +24264,7 @@
         <v>-1.03</v>
       </c>
       <c r="AX147">
-        <v>-1.5644</v>
+        <v>-1.5977749999999999</v>
       </c>
       <c r="AY147">
         <v>-0.99</v>
@@ -24270,7 +24273,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA147">
-        <v>-1.784188833</v>
+        <v>-1.799909633</v>
       </c>
       <c r="BB147">
         <v>-0.98</v>
@@ -24399,7 +24402,7 @@
         <v>3.4049999999999998</v>
       </c>
       <c r="AR148">
-        <v>-1.9142687839999999</v>
+        <v>-1.9216522840000001</v>
       </c>
       <c r="AS148">
         <v>-1.55</v>
@@ -24408,7 +24411,7 @@
         <v>-1.43</v>
       </c>
       <c r="AU148">
-        <v>-1.880730781</v>
+        <v>-1.8902506809999999</v>
       </c>
       <c r="AV148">
         <v>-1.4</v>
@@ -24417,7 +24420,7 @@
         <v>-1.27</v>
       </c>
       <c r="AX148">
-        <v>-1.6302000000000001</v>
+        <v>-1.6570391</v>
       </c>
       <c r="AY148">
         <v>-0.91</v>
@@ -24426,7 +24429,7 @@
         <v>-0.95</v>
       </c>
       <c r="BA148">
-        <v>-1.8034505860000001</v>
+        <v>-1.8178419859999999</v>
       </c>
       <c r="BB148">
         <v>-1.01</v>
@@ -24555,7 +24558,7 @@
         <v>3.48</v>
       </c>
       <c r="AR149">
-        <v>-1.9020453239999999</v>
+        <v>-1.910331124</v>
       </c>
       <c r="AS149">
         <v>-1.63</v>
@@ -24564,7 +24567,7 @@
         <v>-1.44</v>
       </c>
       <c r="AU149">
-        <v>-1.8620328370000001</v>
+        <v>-1.872969237</v>
       </c>
       <c r="AV149">
         <v>-1.48</v>
@@ -24573,7 +24576,7 @@
         <v>-1.3</v>
       </c>
       <c r="AX149">
-        <v>-1.5694999999999999</v>
+        <v>-1.6063932000000001</v>
       </c>
       <c r="AY149">
         <v>-0.94</v>
@@ -24582,7 +24585,7 @@
         <v>-0.88</v>
       </c>
       <c r="BA149">
-        <v>-1.7720598599999999</v>
+        <v>-1.7904518599999999</v>
       </c>
       <c r="BB149">
         <v>-1.1200000000000001</v>
@@ -24711,7 +24714,7 @@
         <v>3.625</v>
       </c>
       <c r="AR150">
-        <v>-1.9131993469999999</v>
+        <v>-1.924509147</v>
       </c>
       <c r="AS150">
         <v>-1.4</v>
@@ -24720,7 +24723,7 @@
         <v>-1.31</v>
       </c>
       <c r="AU150">
-        <v>-1.8774947559999999</v>
+        <v>-1.8929344560000001</v>
       </c>
       <c r="AV150">
         <v>-1.23</v>
@@ -24729,7 +24732,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AX150">
-        <v>-0.9406000000000001</v>
+        <v>-0.9829420000000002</v>
       </c>
       <c r="AY150">
         <v>-1.1499999999999999</v>
@@ -24738,7 +24741,7 @@
         <v>-1.22</v>
       </c>
       <c r="BA150">
-        <v>-1.807837811</v>
+        <v>-1.8302673110000001</v>
       </c>
       <c r="BB150">
         <v>-1.1599999999999999</v>
@@ -24867,7 +24870,7 @@
         <v>1.998</v>
       </c>
       <c r="AR151">
-        <v>-1.849070736</v>
+        <v>-1.8576512359999999</v>
       </c>
       <c r="AS151">
         <v>-1.83</v>
@@ -24876,7 +24879,7 @@
         <v>-1.84</v>
       </c>
       <c r="AU151">
-        <v>-1.819118725</v>
+        <v>-1.8299269250000001</v>
       </c>
       <c r="AV151">
         <v>-1.79</v>
@@ -24885,7 +24888,7 @@
         <v>-1.81</v>
       </c>
       <c r="AX151">
-        <v>-1.7000999999999999</v>
+        <v>-1.7242876</v>
       </c>
       <c r="AY151">
         <v>-1.72</v>
@@ -24894,7 +24897,7 @@
         <v>-1.73</v>
       </c>
       <c r="BA151">
-        <v>-1.7514650940000001</v>
+        <v>-1.7676872939999999</v>
       </c>
       <c r="BB151">
         <v>-1.74</v>
@@ -25023,7 +25026,7 @@
         <v>2.165</v>
       </c>
       <c r="AR152">
-        <v>-1.867039879</v>
+        <v>-1.871144379</v>
       </c>
       <c r="AS152">
         <v>-1.9</v>
@@ -25032,7 +25035,7 @@
         <v>-1.9</v>
       </c>
       <c r="AU152">
-        <v>-1.815352673</v>
+        <v>-1.820696573</v>
       </c>
       <c r="AV152">
         <v>-1.86</v>
@@ -25041,7 +25044,7 @@
         <v>-1.85</v>
       </c>
       <c r="AX152">
-        <v>-1.5822000000000001</v>
+        <v>-1.6003395</v>
       </c>
       <c r="AY152">
         <v>-1.66</v>
@@ -25050,7 +25053,7 @@
         <v>-1.66</v>
       </c>
       <c r="BA152">
-        <v>-1.680150912</v>
+        <v>-1.691144312</v>
       </c>
       <c r="BB152">
         <v>-1.72</v>
@@ -25179,7 +25182,7 @@
         <v>1.859</v>
       </c>
       <c r="AR153">
-        <v>-1.860193247</v>
+        <v>-1.8678739470000001</v>
       </c>
       <c r="AS153">
         <v>-1.84</v>
@@ -25188,7 +25191,7 @@
         <v>-1.85</v>
       </c>
       <c r="AU153">
-        <v>-1.8333117249999999</v>
+        <v>-1.8429549249999999</v>
       </c>
       <c r="AV153">
         <v>-1.8</v>
@@ -25197,7 +25200,7 @@
         <v>-1.83</v>
       </c>
       <c r="AX153">
-        <v>-1.7205999999999999</v>
+        <v>-1.7421333999999999</v>
       </c>
       <c r="AY153">
         <v>-1.73</v>
@@ -25206,7 +25209,7 @@
         <v>-1.74</v>
       </c>
       <c r="BA153">
-        <v>-1.7646239690000001</v>
+        <v>-1.779095069</v>
       </c>
       <c r="BB153">
         <v>-1.75</v>
@@ -25335,7 +25338,7 @@
         <v>2.2240000000000002</v>
       </c>
       <c r="AR154">
-        <v>-1.8400591289999999</v>
+        <v>-1.847891929</v>
       </c>
       <c r="AS154">
         <v>-1.82</v>
@@ -25344,7 +25347,7 @@
         <v>-1.83</v>
       </c>
       <c r="AU154">
-        <v>-1.8017685539999999</v>
+        <v>-1.8119294539999999</v>
       </c>
       <c r="AV154">
         <v>-1.77</v>
@@ -25353,7 +25356,7 @@
         <v>-1.79</v>
       </c>
       <c r="AX154">
-        <v>-1.6555</v>
+        <v>-1.6805199</v>
       </c>
       <c r="AY154">
         <v>-1.66</v>
@@ -25362,7 +25365,7 @@
         <v>-1.67</v>
       </c>
       <c r="BA154">
-        <v>-1.7191024100000001</v>
+        <v>-1.7354314099999999</v>
       </c>
       <c r="BB154">
         <v>-1.7</v>
@@ -25491,7 +25494,7 @@
         <v>2.4</v>
       </c>
       <c r="AR155">
-        <v>-1.880703609</v>
+        <v>-1.8843729090000001</v>
       </c>
       <c r="AS155">
         <v>-1.92</v>
@@ -25500,7 +25503,7 @@
         <v>-1.91</v>
       </c>
       <c r="AU155">
-        <v>-1.8261242449999999</v>
+        <v>-1.830796345</v>
       </c>
       <c r="AV155">
         <v>-1.88</v>
@@ -25509,7 +25512,7 @@
         <v>-1.87</v>
       </c>
       <c r="AX155">
-        <v>-1.5825</v>
+        <v>-1.6019337</v>
       </c>
       <c r="AY155">
         <v>-1.64</v>
@@ -25518,7 +25521,7 @@
         <v>-1.63</v>
       </c>
       <c r="BA155">
-        <v>-1.695640356</v>
+        <v>-1.706074756</v>
       </c>
       <c r="BB155">
         <v>-1.72</v>
@@ -25647,7 +25650,7 @@
         <v>2.2120000000000002</v>
       </c>
       <c r="AR156">
-        <v>-1.8305245450000001</v>
+        <v>-1.8379617450000001</v>
       </c>
       <c r="AS156">
         <v>-1.77</v>
@@ -25656,7 +25659,7 @@
         <v>-1.8</v>
       </c>
       <c r="AU156">
-        <v>-1.787147866</v>
+        <v>-1.796967266</v>
       </c>
       <c r="AV156">
         <v>-1.7</v>
@@ -25665,7 +25668,7 @@
         <v>-1.75</v>
       </c>
       <c r="AX156">
-        <v>-1.6312</v>
+        <v>-1.6567118999999999</v>
       </c>
       <c r="AY156">
         <v>-1.6</v>
@@ -25674,7 +25677,7 @@
         <v>-1.62</v>
       </c>
       <c r="BA156">
-        <v>-1.6914191750000001</v>
+        <v>-1.707742775</v>
       </c>
       <c r="BB156">
         <v>-1.65</v>
@@ -25803,7 +25806,7 @@
         <v>2.8410000000000002</v>
       </c>
       <c r="AR157">
-        <v>-1.8994937039999999</v>
+        <v>-1.9040146040000001</v>
       </c>
       <c r="AS157">
         <v>-1.92</v>
@@ -25812,7 +25815,7 @@
         <v>-1.88</v>
       </c>
       <c r="AU157">
-        <v>-1.8593491280000001</v>
+        <v>-1.8650490280000001</v>
       </c>
       <c r="AV157">
         <v>-1.88</v>
@@ -25821,7 +25824,7 @@
         <v>-1.84</v>
       </c>
       <c r="AX157">
-        <v>-1.6177999999999999</v>
+        <v>-1.6412598</v>
       </c>
       <c r="AY157">
         <v>-1.49</v>
@@ -25830,7 +25833,7 @@
         <v>-1.48</v>
       </c>
       <c r="BA157">
-        <v>-1.7495933400000001</v>
+        <v>-1.7615009399999999</v>
       </c>
       <c r="BB157">
         <v>-1.67</v>
@@ -25959,7 +25962,7 @@
         <v>3.4849999999999999</v>
       </c>
       <c r="AR158">
-        <v>-1.9025503189999999</v>
+        <v>-1.913751719</v>
       </c>
       <c r="AS158">
         <v>-1.48</v>
@@ -25968,7 +25971,7 @@
         <v>-1.49</v>
       </c>
       <c r="AU158">
-        <v>-1.8627529599999999</v>
+        <v>-1.87740796</v>
       </c>
       <c r="AV158">
         <v>-1.36</v>
@@ -25977,7 +25980,7 @@
         <v>-1.37</v>
       </c>
       <c r="AX158">
-        <v>-1.5570999999999999</v>
+        <v>-1.5980615</v>
       </c>
       <c r="AY158">
         <v>-0.97</v>
@@ -25986,7 +25989,7 @@
         <v>-0.94</v>
       </c>
       <c r="BA158">
-        <v>-1.7656527500000001</v>
+        <v>-1.7872487500000001</v>
       </c>
       <c r="BB158">
         <v>-1.1299999999999999</v>
@@ -26115,7 +26118,7 @@
         <v>2.4510000000000001</v>
       </c>
       <c r="AR159">
-        <v>-1.8663648580000001</v>
+        <v>-1.872412258</v>
       </c>
       <c r="AS159">
         <v>-1.64</v>
@@ -26124,7 +26127,7 @@
         <v>-1.66</v>
       </c>
       <c r="AU159">
-        <v>-1.827144203</v>
+        <v>-1.835144103</v>
       </c>
       <c r="AV159">
         <v>-1.56</v>
@@ -26133,7 +26136,7 @@
         <v>-1.63</v>
       </c>
       <c r="AX159">
-        <v>-1.6779999999999999</v>
+        <v>-1.7017949000000001</v>
       </c>
       <c r="AY159">
         <v>-1.55</v>
@@ -26142,7 +26145,7 @@
         <v>-1.57</v>
       </c>
       <c r="BA159">
-        <v>-1.1413</v>
+        <v>-1.1563203</v>
       </c>
       <c r="BB159">
         <v>-1.62</v>
@@ -26271,7 +26274,7 @@
         <v>2.1579999999999999</v>
       </c>
       <c r="AR160">
-        <v>-1.8652959929999999</v>
+        <v>-1.8713415929999999</v>
       </c>
       <c r="AS160">
         <v>-1.67</v>
@@ -26280,7 +26283,7 @@
         <v>-1.74</v>
       </c>
       <c r="AU160">
-        <v>-1.8284632430000001</v>
+        <v>-1.836295043</v>
       </c>
       <c r="AV160">
         <v>-1.59</v>
@@ -26289,7 +26292,7 @@
         <v>-1.7</v>
       </c>
       <c r="AX160">
-        <v>-0.9819</v>
+        <v>-1.0032715999999999</v>
       </c>
       <c r="AY160">
         <v>-1.59</v>
@@ -26298,7 +26301,7 @@
         <v>-1.62</v>
       </c>
       <c r="BA160">
-        <v>-1.1456</v>
+        <v>-1.1593576999999999</v>
       </c>
       <c r="BB160">
         <v>-1.64</v>
@@ -26427,7 +26430,7 @@
         <v>2.6840000000000002</v>
       </c>
       <c r="AR161">
-        <v>-1.873914944</v>
+        <v>-1.8797759439999999</v>
       </c>
       <c r="AS161">
         <v>-1.64</v>
@@ -26436,7 +26439,7 @@
         <v>-1.59</v>
       </c>
       <c r="AU161">
-        <v>-1.828571213</v>
+        <v>-1.8365066130000001</v>
       </c>
       <c r="AV161">
         <v>-1.53</v>
@@ -26445,7 +26448,7 @@
         <v>-1.55</v>
       </c>
       <c r="AX161">
-        <v>-1.6344000000000001</v>
+        <v>-1.6616015</v>
       </c>
       <c r="AY161">
         <v>-1.41</v>
@@ -26454,7 +26457,7 @@
         <v>-1.42</v>
       </c>
       <c r="BA161">
-        <v>-1.712641868</v>
+        <v>-1.7287511680000001</v>
       </c>
       <c r="BB161">
         <v>-1.53</v>
@@ -26583,7 +26586,7 @@
         <v>2.6360000000000001</v>
       </c>
       <c r="AR162">
-        <v>-1.8780015889999999</v>
+        <v>-1.8842578889999999</v>
       </c>
       <c r="AS162">
         <v>-1.63</v>
@@ -26592,7 +26595,7 @@
         <v>-1.6</v>
       </c>
       <c r="AU162">
-        <v>-1.833347469</v>
+        <v>-1.8417138689999999</v>
       </c>
       <c r="AV162">
         <v>-1.51</v>
@@ -26601,7 +26604,7 @@
         <v>-1.55</v>
       </c>
       <c r="AX162">
-        <v>-1.6344000000000001</v>
+        <v>-1.6624293999999999</v>
       </c>
       <c r="AY162">
         <v>-1.38</v>
@@ -26610,7 +26613,7 @@
         <v>-1.4</v>
       </c>
       <c r="BA162">
-        <v>-1.7142370060000001</v>
+        <v>-1.730819506</v>
       </c>
       <c r="BB162">
         <v>-1.51</v>
@@ -26631,7 +26634,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B742B78-CE28-4524-AE34-EC41C6D94660}">
   <dimension ref="A1:BE38"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -26884,7 +26887,7 @@
       <c r="AP3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -26893,7 +26896,7 @@
       <c r="AT3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AV3" s="2" t="s">
@@ -26902,7 +26905,7 @@
       <c r="AW3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AY3" s="2" t="s">
@@ -26911,7 +26914,7 @@
       <c r="AZ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="BB3" s="2" t="s">
@@ -27028,7 +27031,7 @@
       <c r="AL4" s="5">
         <v>1.708</v>
       </c>
-      <c r="AM4" s="11">
+      <c r="AM4">
         <v>4.3730000000000002</v>
       </c>
       <c r="AN4" s="5" t="s">
@@ -27041,7 +27044,7 @@
         <v>2.024</v>
       </c>
       <c r="AR4">
-        <v>-1.943599598</v>
+        <v>-1.952076498</v>
       </c>
       <c r="AS4">
         <v>-1.97</v>
@@ -27050,7 +27053,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU4">
-        <v>-1.9187402140000001</v>
+        <v>-1.9306364140000001</v>
       </c>
       <c r="AV4">
         <v>-1.95</v>
@@ -27059,7 +27062,7 @@
         <v>-1.96</v>
       </c>
       <c r="AX4">
-        <v>-1.7777000000000001</v>
+        <v>-1.8048725000000001</v>
       </c>
       <c r="AY4">
         <v>-1.91</v>
@@ -27068,7 +27071,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA4">
-        <v>-0.96393915900000005</v>
+        <v>-0.98395675900000024</v>
       </c>
       <c r="BB4">
         <v>-1.92</v>
@@ -27184,7 +27187,7 @@
       <c r="AL5" s="5">
         <v>1.8480000000000001</v>
       </c>
-      <c r="AM5" s="11">
+      <c r="AM5">
         <v>4.8289999999999997</v>
       </c>
       <c r="AN5" s="5" t="s">
@@ -27197,7 +27200,7 @@
         <v>2.23</v>
       </c>
       <c r="AR5">
-        <v>-1.9359191849999999</v>
+        <v>-1.9459501850000001</v>
       </c>
       <c r="AS5">
         <v>-1.97</v>
@@ -27206,7 +27209,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU5">
-        <v>-1.909452079</v>
+        <v>-1.9233387790000001</v>
       </c>
       <c r="AV5">
         <v>-1.96</v>
@@ -27215,7 +27218,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX5">
-        <v>-1.7619</v>
+        <v>-1.7911398999999999</v>
       </c>
       <c r="AY5">
         <v>-1.89</v>
@@ -27224,7 +27227,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA5">
-        <v>-1.8458042530000001</v>
+        <v>-1.869182353</v>
       </c>
       <c r="BB5">
         <v>-1.91</v>
@@ -27292,7 +27295,7 @@
       <c r="T6" s="5">
         <v>0.94531000000000009</v>
       </c>
-      <c r="U6" s="16">
+      <c r="U6" s="5">
         <v>1.00101</v>
       </c>
       <c r="V6" s="5">
@@ -27340,7 +27343,7 @@
       <c r="AL6" s="5">
         <v>1.778</v>
       </c>
-      <c r="AM6" s="11">
+      <c r="AM6">
         <v>4.9409999999999998</v>
       </c>
       <c r="AN6" s="5" t="s">
@@ -27353,7 +27356,7 @@
         <v>2.2690000000000001</v>
       </c>
       <c r="AR6">
-        <v>-1.9404846659999999</v>
+        <v>-1.9504044659999999</v>
       </c>
       <c r="AS6">
         <v>-1.94</v>
@@ -27362,7 +27365,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU6">
-        <v>-1.9143773770000001</v>
+        <v>-1.928459777</v>
       </c>
       <c r="AV6">
         <v>-1.93</v>
@@ -27371,7 +27374,7 @@
         <v>-1.93</v>
       </c>
       <c r="AX6">
-        <v>-0.94080000000000008</v>
+        <v>-0.97334700000000018</v>
       </c>
       <c r="AY6">
         <v>-1.88</v>
@@ -27380,7 +27383,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA6">
-        <v>-0.96023211600000002</v>
+        <v>-0.98563211599999989</v>
       </c>
       <c r="BB6">
         <v>-1.9</v>
@@ -27496,7 +27499,7 @@
       <c r="AL7" s="5">
         <v>1.796</v>
       </c>
-      <c r="AM7" s="11">
+      <c r="AM7">
         <v>4.7709999999999999</v>
       </c>
       <c r="AN7" s="5" t="s">
@@ -27509,7 +27512,7 @@
         <v>2.1880000000000002</v>
       </c>
       <c r="AR7">
-        <v>-1.938960657</v>
+        <v>-1.9489855570000001</v>
       </c>
       <c r="AS7">
         <v>-1.97</v>
@@ -27518,7 +27521,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU7">
-        <v>-1.913266109</v>
+        <v>-1.9271825090000001</v>
       </c>
       <c r="AV7">
         <v>-1.96</v>
@@ -27527,7 +27530,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX7">
-        <v>-1.7712000000000001</v>
+        <v>-1.8008128000000001</v>
       </c>
       <c r="AY7">
         <v>-1.9</v>
@@ -27536,7 +27539,7 @@
         <v>-1.89</v>
       </c>
       <c r="BA7">
-        <v>-1.852018776</v>
+        <v>-1.8759010759999999</v>
       </c>
       <c r="BB7">
         <v>-1.91</v>
@@ -27652,7 +27655,7 @@
       <c r="AL8" s="5">
         <v>1.629</v>
       </c>
-      <c r="AM8" s="11">
+      <c r="AM8">
         <v>4.4189999999999996</v>
       </c>
       <c r="AN8" s="5" t="s">
@@ -27665,7 +27668,7 @@
         <v>1.946</v>
       </c>
       <c r="AR8">
-        <v>-1.942988765</v>
+        <v>-1.954103465</v>
       </c>
       <c r="AS8">
         <v>-1.97</v>
@@ -27674,7 +27677,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU8">
-        <v>-1.9179545760000001</v>
+        <v>-1.9338693760000001</v>
       </c>
       <c r="AV8">
         <v>-1.95</v>
@@ -27683,7 +27686,7 @@
         <v>-1.96</v>
       </c>
       <c r="AX8">
-        <v>-0.91480000000000006</v>
+        <v>-0.95450200000000018</v>
       </c>
       <c r="AY8">
         <v>-1.92</v>
@@ -27692,7 +27695,7 @@
         <v>-1.91</v>
       </c>
       <c r="BA8">
-        <v>-1.8613114310000001</v>
+        <v>-1.8880952310000001</v>
       </c>
       <c r="BB8">
         <v>-1.93</v>
@@ -27808,7 +27811,7 @@
       <c r="AL9" s="5">
         <v>1.6279999999999999</v>
       </c>
-      <c r="AM9" s="11">
+      <c r="AM9">
         <v>4.6520000000000001</v>
       </c>
       <c r="AN9" s="5" t="s">
@@ -27821,7 +27824,7 @@
         <v>2.4670000000000001</v>
       </c>
       <c r="AR9">
-        <v>-1.9255350280000001</v>
+        <v>-1.935045028</v>
       </c>
       <c r="AS9">
         <v>-0.99</v>
@@ -27830,7 +27833,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU9">
-        <v>-1.8933406209999999</v>
+        <v>-1.905899521</v>
       </c>
       <c r="AV9">
         <v>-0.99</v>
@@ -27839,7 +27842,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX9">
-        <v>-0.91989999999999994</v>
+        <v>-0.94451510000000005</v>
       </c>
       <c r="AY9">
         <v>-1.39</v>
@@ -27848,7 +27851,7 @@
         <v>-1.47</v>
       </c>
       <c r="BA9">
-        <v>-1.0094142420000001</v>
+        <v>-1.026057942</v>
       </c>
       <c r="BB9">
         <v>-0.97</v>
@@ -27964,7 +27967,7 @@
       <c r="AL10" s="5">
         <v>1.1020000000000001</v>
       </c>
-      <c r="AM10" s="11">
+      <c r="AM10">
         <v>4.3099999999999996</v>
       </c>
       <c r="AN10" s="5" t="s">
@@ -27977,7 +27980,7 @@
         <v>2.1579999999999999</v>
       </c>
       <c r="AR10">
-        <v>-1.899143193</v>
+        <v>-1.9140066929999999</v>
       </c>
       <c r="AS10">
         <v>-1</v>
@@ -27986,7 +27989,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU10">
-        <v>-1.8721808879999999</v>
+        <v>-1.8942652879999999</v>
       </c>
       <c r="AV10">
         <v>-1</v>
@@ -27995,7 +27998,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX10">
-        <v>-1.6782999999999999</v>
+        <v>-1.7402139000000001</v>
       </c>
       <c r="AY10">
         <v>-0.99</v>
@@ -28004,7 +28007,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA10">
-        <v>-1.5963720269999999</v>
+        <v>-1.636496427</v>
       </c>
       <c r="BB10">
         <v>-1.04</v>
@@ -28056,14 +28059,14 @@
       <c r="N11" s="5">
         <v>0.24238999999999999</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="12">
         <v>-2.8369999999999999E-2</v>
       </c>
       <c r="P11" s="5">
         <v>0.17704</v>
       </c>
       <c r="Q11" s="5">
-        <v>3.9660000000000001E-2</v>
+        <v>3.9780000000000003E-2</v>
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5">
@@ -28072,7 +28075,7 @@
       <c r="T11" s="5">
         <v>0.7593399999999999</v>
       </c>
-      <c r="U11" s="16">
+      <c r="U11" s="5">
         <v>0.61880999999999997</v>
       </c>
       <c r="V11" s="5">
@@ -28120,7 +28123,7 @@
       <c r="AL11" s="5">
         <v>1.653</v>
       </c>
-      <c r="AM11" s="12" t="s">
+      <c r="AM11" s="10" t="s">
         <v>267</v>
       </c>
       <c r="AN11" s="5" t="s">
@@ -28133,7 +28136,7 @@
         <v>2.2360000000000002</v>
       </c>
       <c r="AR11">
-        <v>-0.97703702699999995</v>
+        <v>-0.98337002700000009</v>
       </c>
       <c r="AS11">
         <v>-1.98</v>
@@ -28142,7 +28145,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU11">
-        <v>-0.966146014</v>
+        <v>-0.97809891399999982</v>
       </c>
       <c r="AV11">
         <v>-1.88</v>
@@ -28151,7 +28154,7 @@
         <v>-1.91</v>
       </c>
       <c r="AX11">
-        <v>-0.95039999999999991</v>
+        <v>-0.97960859999999994</v>
       </c>
       <c r="AY11">
         <v>-1.86</v>
@@ -28160,7 +28163,7 @@
         <v>-1.86</v>
       </c>
       <c r="BA11">
-        <v>-0.95717434899999998</v>
+        <v>-0.98143464899999988</v>
       </c>
       <c r="BB11">
         <v>-1.91</v>
@@ -28255,13 +28258,13 @@
       <c r="AD12" s="5">
         <v>0.71404000000000001</v>
       </c>
-      <c r="AE12" s="15">
+      <c r="AE12" s="13">
         <v>0.31489</v>
       </c>
       <c r="AF12" s="5">
         <v>0.65507000000000004</v>
       </c>
-      <c r="AG12" s="15">
+      <c r="AG12" s="13">
         <v>0.24240999999999999</v>
       </c>
       <c r="AI12" s="5">
@@ -28276,20 +28279,20 @@
       <c r="AL12" s="5">
         <v>1.4710000000000001</v>
       </c>
-      <c r="AM12" s="12" t="s">
+      <c r="AM12" s="10" t="s">
         <v>268</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="AO12" s="15">
+      <c r="AO12" s="13">
         <v>5.2729999999999997</v>
       </c>
-      <c r="AP12" s="15">
+      <c r="AP12" s="13">
         <v>4.968</v>
       </c>
       <c r="AR12">
-        <v>-1.706968874</v>
+        <v>-1.719942874</v>
       </c>
       <c r="AS12">
         <v>-0.99</v>
@@ -28298,7 +28301,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU12">
-        <v>-1.002698517</v>
+        <v>-1.0205297170000001</v>
       </c>
       <c r="AV12">
         <v>-1</v>
@@ -28307,7 +28310,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX12">
-        <v>-1.0839000000000001</v>
+        <v>-1.1190503000000001</v>
       </c>
       <c r="AY12">
         <v>-1.48</v>
@@ -28316,7 +28319,7 @@
         <v>-1.49</v>
       </c>
       <c r="BA12">
-        <v>-1.003946502</v>
+        <v>-1.0274177019999999</v>
       </c>
       <c r="BB12">
         <v>-1.62</v>
@@ -28432,7 +28435,7 @@
       <c r="AL13" s="5">
         <v>1.7529999999999999</v>
       </c>
-      <c r="AM13" s="12" t="s">
+      <c r="AM13" s="10" t="s">
         <v>269</v>
       </c>
       <c r="AN13" s="5" t="s">
@@ -28445,7 +28448,7 @@
         <v>2.1120000000000001</v>
       </c>
       <c r="AR13">
-        <v>-1.9388149960000001</v>
+        <v>-1.9504397959999999</v>
       </c>
       <c r="AS13">
         <v>-1.97</v>
@@ -28454,7 +28457,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU13">
-        <v>-1.9121746669999999</v>
+        <v>-1.9293892669999999</v>
       </c>
       <c r="AV13">
         <v>-1.94</v>
@@ -28463,7 +28466,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX13">
-        <v>-0.89999999999999991</v>
+        <v>-0.94715289999999985</v>
       </c>
       <c r="AY13">
         <v>-1.91</v>
@@ -28472,7 +28475,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA13">
-        <v>-0.940915838</v>
+        <v>-0.97250883799999999</v>
       </c>
       <c r="BB13">
         <v>-1.93</v>
@@ -28588,7 +28591,7 @@
       <c r="AL14" s="5">
         <v>1.7050000000000001</v>
       </c>
-      <c r="AM14" s="12" t="s">
+      <c r="AM14" s="10" t="s">
         <v>270</v>
       </c>
       <c r="AN14" s="5" t="s">
@@ -28601,7 +28604,7 @@
         <v>2.1349999999999998</v>
       </c>
       <c r="AR14">
-        <v>-1.9408847579999999</v>
+        <v>-1.952070558</v>
       </c>
       <c r="AS14">
         <v>-1.95</v>
@@ -28610,7 +28613,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU14">
-        <v>-1.9135521929999999</v>
+        <v>-1.930201193</v>
       </c>
       <c r="AV14">
         <v>-1.91</v>
@@ -28619,7 +28622,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX14">
-        <v>-0.89500000000000002</v>
+        <v>-0.94207730000000023</v>
       </c>
       <c r="AY14">
         <v>-1.91</v>
@@ -28628,7 +28631,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA14">
-        <v>-0.93952430799999997</v>
+        <v>-0.97086100800000019</v>
       </c>
       <c r="BB14">
         <v>-1.93</v>
@@ -28744,7 +28747,7 @@
       <c r="AL15" s="5">
         <v>1.7150000000000001</v>
       </c>
-      <c r="AM15" s="12" t="s">
+      <c r="AM15" s="10" t="s">
         <v>271</v>
       </c>
       <c r="AN15" s="5" t="s">
@@ -28757,7 +28760,7 @@
         <v>2.125</v>
       </c>
       <c r="AR15">
-        <v>-1.9418871280000001</v>
+        <v>-1.953041528</v>
       </c>
       <c r="AS15">
         <v>-1.97</v>
@@ -28766,7 +28769,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU15">
-        <v>-1.915516362</v>
+        <v>-1.931902362</v>
       </c>
       <c r="AV15">
         <v>-1.96</v>
@@ -28775,7 +28778,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX15">
-        <v>-0.90359999999999996</v>
+        <v>-0.94740249999999993</v>
       </c>
       <c r="AY15">
         <v>-1.91</v>
@@ -28784,7 +28787,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA15">
-        <v>-0.94388623599999999</v>
+        <v>-0.97367813600000019</v>
       </c>
       <c r="BB15">
         <v>-1.93</v>
@@ -28821,7 +28824,7 @@
       <c r="H16" s="5">
         <v>0.20780000000000001</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="13">
         <v>8.1193570000000007E-2</v>
       </c>
       <c r="K16" s="6">
@@ -28900,7 +28903,7 @@
       <c r="AL16" s="5">
         <v>1.712</v>
       </c>
-      <c r="AM16" s="12" t="s">
+      <c r="AM16" s="10" t="s">
         <v>272</v>
       </c>
       <c r="AN16" s="5" t="s">
@@ -28913,7 +28916,7 @@
         <v>2.13</v>
       </c>
       <c r="AR16">
-        <v>-1.9418096970000001</v>
+        <v>-1.952889697</v>
       </c>
       <c r="AS16">
         <v>-1.97</v>
@@ -28922,7 +28925,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU16">
-        <v>-1.9154219299999999</v>
+        <v>-1.93169623</v>
       </c>
       <c r="AV16">
         <v>-1.96</v>
@@ -28931,7 +28934,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX16">
-        <v>-0.90379999999999994</v>
+        <v>-0.94721080000000013</v>
       </c>
       <c r="AY16">
         <v>-1.91</v>
@@ -28940,7 +28943,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA16">
-        <v>-0.94364012200000003</v>
+        <v>-0.97324742200000003</v>
       </c>
       <c r="BB16">
         <v>-1.93</v>
@@ -29056,7 +29059,7 @@
       <c r="AL17" s="5">
         <v>1.7330000000000001</v>
       </c>
-      <c r="AM17" s="12" t="s">
+      <c r="AM17" s="10" t="s">
         <v>273</v>
       </c>
       <c r="AN17" s="5" t="s">
@@ -29069,7 +29072,7 @@
         <v>2.1440000000000001</v>
       </c>
       <c r="AR17">
-        <v>-1.940915508</v>
+        <v>-1.952125508</v>
       </c>
       <c r="AS17">
         <v>-1.97</v>
@@ -29078,7 +29081,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU17">
-        <v>-1.9142706620000001</v>
+        <v>-1.9307605619999999</v>
       </c>
       <c r="AV17">
         <v>-1.96</v>
@@ -29087,7 +29090,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX17">
-        <v>-0.90399999999999991</v>
+        <v>-0.94850009999999996</v>
       </c>
       <c r="AY17">
         <v>-1.91</v>
@@ -29096,7 +29099,7 @@
         <v>-1.9</v>
       </c>
       <c r="BA17">
-        <v>-0.94350360499999997</v>
+        <v>-0.9735979050000001</v>
       </c>
       <c r="BB17">
         <v>-1.93</v>
@@ -29212,7 +29215,7 @@
       <c r="AL18" s="5">
         <v>1.508</v>
       </c>
-      <c r="AM18" s="12" t="s">
+      <c r="AM18" s="10" t="s">
         <v>274</v>
       </c>
       <c r="AN18" s="5" t="s">
@@ -29225,7 +29228,7 @@
         <v>1.863</v>
       </c>
       <c r="AR18">
-        <v>-1.9498888379999999</v>
+        <v>-1.9603728380000001</v>
       </c>
       <c r="AS18">
         <v>-1.93</v>
@@ -29234,7 +29237,7 @@
         <v>-1.97</v>
       </c>
       <c r="AU18">
-        <v>-1.9268832149999999</v>
+        <v>-1.942443315</v>
       </c>
       <c r="AV18">
         <v>-1.88</v>
@@ -29243,7 +29246,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX18">
-        <v>-0.9153</v>
+        <v>-0.95866859999999998</v>
       </c>
       <c r="AY18">
         <v>-1.91</v>
@@ -29252,7 +29255,7 @@
         <v>-1.91</v>
       </c>
       <c r="BA18">
-        <v>-0.94599755600000002</v>
+        <v>-0.97500225600000023</v>
       </c>
       <c r="BB18">
         <v>-1.93</v>
@@ -29368,7 +29371,7 @@
       <c r="AL19" s="5">
         <v>1.5409999999999999</v>
       </c>
-      <c r="AM19" s="12" t="s">
+      <c r="AM19" s="10" t="s">
         <v>275</v>
       </c>
       <c r="AN19" s="5" t="s">
@@ -29381,7 +29384,7 @@
         <v>2.1549999999999998</v>
       </c>
       <c r="AR19">
-        <v>-1.9222715960000001</v>
+        <v>-1.9342796959999999</v>
       </c>
       <c r="AS19">
         <v>-1.95</v>
@@ -29390,7 +29393,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU19">
-        <v>-1.88531424</v>
+        <v>-1.90289284</v>
       </c>
       <c r="AV19">
         <v>-1.94</v>
@@ -29399,7 +29402,7 @@
         <v>-1.93</v>
       </c>
       <c r="AX19">
-        <v>-1.0228999999999999</v>
+        <v>-1.0649960999999999</v>
       </c>
       <c r="AY19">
         <v>-1.67</v>
@@ -29408,7 +29411,7 @@
         <v>-1.68</v>
       </c>
       <c r="BA19">
-        <v>-1.073640017</v>
+        <v>-1.102960717</v>
       </c>
       <c r="BB19">
         <v>-1.72</v>
@@ -29524,7 +29527,7 @@
       <c r="AL20" s="5">
         <v>1.6539999999999999</v>
       </c>
-      <c r="AM20" s="12" t="s">
+      <c r="AM20" s="10" t="s">
         <v>276</v>
       </c>
       <c r="AN20" s="5" t="s">
@@ -29537,7 +29540,7 @@
         <v>2.1080000000000001</v>
       </c>
       <c r="AR20">
-        <v>-1.95295222</v>
+        <v>-1.9607074200000001</v>
       </c>
       <c r="AS20">
         <v>-1</v>
@@ -29546,7 +29549,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU20">
-        <v>-1.8869177509999999</v>
+        <v>-1.898820851</v>
       </c>
       <c r="AV20">
         <v>-1.07</v>
@@ -29555,7 +29558,7 @@
         <v>-1.24</v>
       </c>
       <c r="AX20">
-        <v>-0.93009999999999993</v>
+        <v>-0.97755489999999989</v>
       </c>
       <c r="AY20">
         <v>-1.89</v>
@@ -29564,7 +29567,7 @@
         <v>-1.89</v>
       </c>
       <c r="BA20">
-        <v>-0.95446510600000001</v>
+        <v>-1.0030365059999999</v>
       </c>
       <c r="BB20">
         <v>-1</v>
@@ -29680,7 +29683,7 @@
       <c r="AL21" s="5">
         <v>1.075</v>
       </c>
-      <c r="AM21" s="12" t="s">
+      <c r="AM21" s="10" t="s">
         <v>277</v>
       </c>
       <c r="AN21" s="5" t="s">
@@ -29693,7 +29696,7 @@
         <v>1.546</v>
       </c>
       <c r="AR21">
-        <v>-1.9623348430000001</v>
+        <v>-1.970494443</v>
       </c>
       <c r="AS21">
         <v>-1.98</v>
@@ -29702,7 +29705,7 @@
         <v>-1.98</v>
       </c>
       <c r="AU21">
-        <v>-1.944261268</v>
+        <v>-1.9563550679999999</v>
       </c>
       <c r="AV21">
         <v>-1.96</v>
@@ -29711,7 +29714,7 @@
         <v>-1.97</v>
       </c>
       <c r="AX21">
-        <v>-1.8277000000000001</v>
+        <v>-1.8579939999999999</v>
       </c>
       <c r="AY21">
         <v>-1.93</v>
@@ -29720,7 +29723,7 @@
         <v>-1.92</v>
       </c>
       <c r="BA21">
-        <v>-1.8899597130000001</v>
+        <v>-1.9097361129999999</v>
       </c>
       <c r="BB21">
         <v>-1.93</v>
@@ -29836,7 +29839,7 @@
       <c r="AL22" s="5">
         <v>1.7509999999999999</v>
       </c>
-      <c r="AM22" s="12" t="s">
+      <c r="AM22" s="10" t="s">
         <v>278</v>
       </c>
       <c r="AN22" s="5" t="s">
@@ -29849,7 +29852,7 @@
         <v>2.1680000000000001</v>
       </c>
       <c r="AR22">
-        <v>-1.939942378</v>
+        <v>-1.9493761780000001</v>
       </c>
       <c r="AS22">
         <v>-1.97</v>
@@ -29858,7 +29861,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU22">
-        <v>-1.911053761</v>
+        <v>-1.924342561</v>
       </c>
       <c r="AV22">
         <v>-1.96</v>
@@ -29867,7 +29870,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX22">
-        <v>-0.93890000000000007</v>
+        <v>-0.96819840000000013</v>
       </c>
       <c r="AY22">
         <v>-1.88</v>
@@ -29876,7 +29879,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA22">
-        <v>-1.8481566570000001</v>
+        <v>-1.8701261570000001</v>
       </c>
       <c r="BB22">
         <v>-1.91</v>
@@ -29977,7 +29980,7 @@
       <c r="AF23" s="5">
         <v>0.52712999999999999</v>
       </c>
-      <c r="AG23" s="14">
+      <c r="AG23" s="12">
         <v>0.36473</v>
       </c>
       <c r="AI23" s="5">
@@ -29992,7 +29995,7 @@
       <c r="AL23" s="5">
         <v>1.6890000000000001</v>
       </c>
-      <c r="AM23" s="12" t="s">
+      <c r="AM23" s="10" t="s">
         <v>279</v>
       </c>
       <c r="AN23" s="5" t="s">
@@ -30005,7 +30008,7 @@
         <v>2.0859999999999999</v>
       </c>
       <c r="AR23">
-        <v>-1.9433176270000001</v>
+        <v>-1.9521063270000001</v>
       </c>
       <c r="AS23">
         <v>-1.97</v>
@@ -30014,7 +30017,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU23">
-        <v>-1.9158687649999999</v>
+        <v>-1.9282296649999999</v>
       </c>
       <c r="AV23">
         <v>-1.96</v>
@@ -30023,7 +30026,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX23">
-        <v>-0.9426000000000001</v>
+        <v>-0.97084610000000016</v>
       </c>
       <c r="AY23">
         <v>-1.87</v>
@@ -30032,7 +30035,7 @@
         <v>-1.87</v>
       </c>
       <c r="BA23">
-        <v>-1.856233281</v>
+        <v>-1.8770016810000001</v>
       </c>
       <c r="BB23">
         <v>-1.91</v>
@@ -30148,7 +30151,7 @@
       <c r="AL24" s="5">
         <v>1.75</v>
       </c>
-      <c r="AM24" s="12" t="s">
+      <c r="AM24" s="10" t="s">
         <v>266</v>
       </c>
       <c r="AN24" s="5" t="s">
@@ -30161,7 +30164,7 @@
         <v>2.173</v>
       </c>
       <c r="AR24">
-        <v>-1.939672045</v>
+        <v>-1.949160145</v>
       </c>
       <c r="AS24">
         <v>-1.97</v>
@@ -30170,7 +30173,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU24">
-        <v>-1.9106566460000001</v>
+        <v>-1.924078046</v>
       </c>
       <c r="AV24">
         <v>-1.96</v>
@@ -30179,7 +30182,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX24">
-        <v>-0.94500000000000006</v>
+        <v>-0.97534200000000015</v>
       </c>
       <c r="AY24">
         <v>-1.88</v>
@@ -30188,7 +30191,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA24">
-        <v>-1.847942609</v>
+        <v>-1.870386109</v>
       </c>
       <c r="BB24">
         <v>-1.91</v>
@@ -30304,7 +30307,7 @@
       <c r="AL25" s="5">
         <v>1.746</v>
       </c>
-      <c r="AM25" s="12" t="s">
+      <c r="AM25" s="10" t="s">
         <v>280</v>
       </c>
       <c r="AN25" s="5" t="s">
@@ -30317,7 +30320,7 @@
         <v>2.1659999999999999</v>
       </c>
       <c r="AR25">
-        <v>-1.939606199</v>
+        <v>-1.9490477989999999</v>
       </c>
       <c r="AS25">
         <v>-1.97</v>
@@ -30326,7 +30329,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU25">
-        <v>-1.9104473369999999</v>
+        <v>-1.9238068370000001</v>
       </c>
       <c r="AV25">
         <v>-1.96</v>
@@ -30335,7 +30338,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX25">
-        <v>-0.94550000000000001</v>
+        <v>-0.97531649999999992</v>
       </c>
       <c r="AY25">
         <v>-1.88</v>
@@ -30344,7 +30347,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA25">
-        <v>-1.847224524</v>
+        <v>-1.869500924</v>
       </c>
       <c r="BB25">
         <v>-1.91</v>
@@ -30460,7 +30463,7 @@
       <c r="AL26" s="5">
         <v>1.7490000000000001</v>
       </c>
-      <c r="AM26" s="12" t="s">
+      <c r="AM26" s="10" t="s">
         <v>281</v>
       </c>
       <c r="AN26" s="5" t="s">
@@ -30473,7 +30476,7 @@
         <v>2.17</v>
       </c>
       <c r="AR26">
-        <v>-1.7880764060000001</v>
+        <v>-1.797580806</v>
       </c>
       <c r="AS26">
         <v>-1</v>
@@ -30482,7 +30485,7 @@
         <v>-1</v>
       </c>
       <c r="AU26">
-        <v>-1.9100599540000001</v>
+        <v>-1.923475354</v>
       </c>
       <c r="AV26">
         <v>-1</v>
@@ -30491,7 +30494,7 @@
         <v>-1.18</v>
       </c>
       <c r="AX26">
-        <v>-1.7613000000000001</v>
+        <v>-1.7910016</v>
       </c>
       <c r="AY26">
         <v>-1.88</v>
@@ -30500,7 +30503,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA26">
-        <v>-1.846435356</v>
+        <v>-1.868709956</v>
       </c>
       <c r="BB26">
         <v>-1.91</v>
@@ -30616,7 +30619,7 @@
       <c r="AL27" s="6">
         <v>1.502</v>
       </c>
-      <c r="AM27" s="12" t="s">
+      <c r="AM27" s="10" t="s">
         <v>282</v>
       </c>
       <c r="AN27" s="6" t="s">
@@ -30629,7 +30632,7 @@
         <v>2.1720000000000002</v>
       </c>
       <c r="AR27">
-        <v>-1.8819792909999999</v>
+        <v>-1.8914405910000001</v>
       </c>
       <c r="AS27">
         <v>-0.69</v>
@@ -30638,7 +30641,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU27">
-        <v>-1.903794038</v>
+        <v>-1.9172450379999999</v>
       </c>
       <c r="AV27">
         <v>-1</v>
@@ -30647,7 +30650,7 @@
         <v>-1.02</v>
       </c>
       <c r="AX27">
-        <v>-1.7619</v>
+        <v>-1.7914897000000001</v>
       </c>
       <c r="AY27">
         <v>-1.88</v>
@@ -30656,7 +30659,7 @@
         <v>-1.88</v>
       </c>
       <c r="BA27">
-        <v>-1.84659511</v>
+        <v>-1.8688855099999999</v>
       </c>
       <c r="BB27">
         <v>-1.91</v>
@@ -30772,7 +30775,7 @@
       <c r="AL28" s="6">
         <v>1.742</v>
       </c>
-      <c r="AM28" s="12" t="s">
+      <c r="AM28" s="10" t="s">
         <v>283</v>
       </c>
       <c r="AN28" s="6" t="s">
@@ -30785,7 +30788,7 @@
         <v>2.0590000000000002</v>
       </c>
       <c r="AR28">
-        <v>-1.946775637</v>
+        <v>-1.957836237</v>
       </c>
       <c r="AS28">
         <v>-1.97</v>
@@ -30794,7 +30797,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU28">
-        <v>-1.921803025</v>
+        <v>-1.937935425</v>
       </c>
       <c r="AV28">
         <v>-1.97</v>
@@ -30803,7 +30806,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX28">
-        <v>-0.90860000000000007</v>
+        <v>-0.9509242</v>
       </c>
       <c r="AY28">
         <v>-1.82</v>
@@ -30812,7 +30815,7 @@
         <v>-1.83</v>
       </c>
       <c r="BA28">
-        <v>-0.94600406000000004</v>
+        <v>-0.97632685999999991</v>
       </c>
       <c r="BB28">
         <v>-1.91</v>
@@ -30880,7 +30883,7 @@
       <c r="T29" s="6">
         <v>1.1661700000000002</v>
       </c>
-      <c r="U29" s="17">
+      <c r="U29" s="6">
         <v>1.095</v>
       </c>
       <c r="V29" s="6">
@@ -30928,7 +30931,7 @@
       <c r="AL29" s="6">
         <v>1.6639999999999999</v>
       </c>
-      <c r="AM29" s="12" t="s">
+      <c r="AM29" s="10" t="s">
         <v>284</v>
       </c>
       <c r="AN29" s="6" t="s">
@@ -30941,7 +30944,7 @@
         <v>2.056</v>
       </c>
       <c r="AR29">
-        <v>-1.92110728</v>
+        <v>-1.9350786799999999</v>
       </c>
       <c r="AS29">
         <v>-1.94</v>
@@ -30950,7 +30953,7 @@
         <v>-1.94</v>
       </c>
       <c r="AU29">
-        <v>-1.889076942</v>
+        <v>-1.908290442</v>
       </c>
       <c r="AV29">
         <v>-1.93</v>
@@ -30959,7 +30962,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX29">
-        <v>-0.92999999999999994</v>
+        <v>-0.98605750000000003</v>
       </c>
       <c r="AY29">
         <v>-1.82</v>
@@ -30968,7 +30971,7 @@
         <v>-1.82</v>
       </c>
       <c r="BA29">
-        <v>-0.96681749299999997</v>
+        <v>-0.99886099299999986</v>
       </c>
       <c r="BB29">
         <v>-1.88</v>
@@ -31084,7 +31087,7 @@
       <c r="AL30" s="6">
         <v>1.605</v>
       </c>
-      <c r="AM30" s="12" t="s">
+      <c r="AM30" s="10" t="s">
         <v>285</v>
       </c>
       <c r="AN30" s="6" t="s">
@@ -31097,7 +31100,7 @@
         <v>2.04</v>
       </c>
       <c r="AR30">
-        <v>-1.924668885</v>
+        <v>-1.938358185</v>
       </c>
       <c r="AS30">
         <v>-1.95</v>
@@ -31106,7 +31109,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU30">
-        <v>-1.892831369</v>
+        <v>-1.9117715689999999</v>
       </c>
       <c r="AV30">
         <v>-1.94</v>
@@ -31115,7 +31118,7 @@
         <v>-1.93</v>
       </c>
       <c r="AX30">
-        <v>-0.92660000000000009</v>
+        <v>-0.98258780000000012</v>
       </c>
       <c r="AY30">
         <v>-1.81</v>
@@ -31124,7 +31127,7 @@
         <v>-1.81</v>
       </c>
       <c r="BA30">
-        <v>-0.96490590899999995</v>
+        <v>-0.99767540900000018</v>
       </c>
       <c r="BB30">
         <v>-1.88</v>
@@ -31240,7 +31243,7 @@
       <c r="AL31" s="6">
         <v>1.56</v>
       </c>
-      <c r="AM31" s="12" t="s">
+      <c r="AM31" s="10" t="s">
         <v>286</v>
       </c>
       <c r="AN31" s="6" t="s">
@@ -31253,7 +31256,7 @@
         <v>2.0230000000000001</v>
       </c>
       <c r="AR31">
-        <v>-1.9304848349999999</v>
+        <v>-1.943078935</v>
       </c>
       <c r="AS31">
         <v>-1.96</v>
@@ -31262,7 +31265,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU31">
-        <v>-1.9000426079999999</v>
+        <v>-1.9172705080000001</v>
       </c>
       <c r="AV31">
         <v>-1.95</v>
@@ -31271,7 +31274,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX31">
-        <v>-0.93169999999999997</v>
+        <v>-0.97974679999999981</v>
       </c>
       <c r="AY31">
         <v>-1.87</v>
@@ -31280,7 +31283,7 @@
         <v>-1.86</v>
       </c>
       <c r="BA31">
-        <v>-0.96318946699999997</v>
+        <v>-0.99166246699999983</v>
       </c>
       <c r="BB31">
         <v>-1.9</v>
@@ -31396,7 +31399,7 @@
       <c r="AL32" s="6">
         <v>1.577</v>
       </c>
-      <c r="AM32" s="12" t="s">
+      <c r="AM32" s="10" t="s">
         <v>287</v>
       </c>
       <c r="AN32" s="6" t="s">
@@ -31409,7 +31412,7 @@
         <v>2.0179999999999998</v>
       </c>
       <c r="AR32">
-        <v>-1.9283548079999999</v>
+        <v>-1.941384408</v>
       </c>
       <c r="AS32">
         <v>-1.95</v>
@@ -31418,7 +31421,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU32">
-        <v>-1.8976796229999999</v>
+        <v>-1.9156255230000001</v>
       </c>
       <c r="AV32">
         <v>-1.94</v>
@@ -31427,7 +31430,7 @@
         <v>-1.93</v>
       </c>
       <c r="AX32">
-        <v>-0.93270000000000008</v>
+        <v>-0.98617759999999999</v>
       </c>
       <c r="AY32">
         <v>-1.84</v>
@@ -31436,7 +31439,7 @@
         <v>-1.84</v>
       </c>
       <c r="BA32">
-        <v>-0.96782719100000003</v>
+        <v>-0.99887239099999992</v>
       </c>
       <c r="BB32">
         <v>-1.89</v>
@@ -31552,7 +31555,7 @@
       <c r="AL33" s="6">
         <v>1.5740000000000001</v>
       </c>
-      <c r="AM33" s="12" t="s">
+      <c r="AM33" s="10" t="s">
         <v>288</v>
       </c>
       <c r="AN33" s="6" t="s">
@@ -31565,7 +31568,7 @@
         <v>2.0510000000000002</v>
       </c>
       <c r="AR33">
-        <v>-1.9564889329999999</v>
+        <v>-1.969968333</v>
       </c>
       <c r="AS33">
         <v>-1.07</v>
@@ -31574,7 +31577,7 @@
         <v>-1.93</v>
       </c>
       <c r="AU33">
-        <v>-1.892267959</v>
+        <v>-1.9109735590000001</v>
       </c>
       <c r="AV33">
         <v>-1.93</v>
@@ -31583,7 +31586,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX33">
-        <v>-0.91870000000000007</v>
+        <v>-0.97398209999999996</v>
       </c>
       <c r="AY33">
         <v>-1.79</v>
@@ -31592,7 +31595,7 @@
         <v>-1.79</v>
       </c>
       <c r="BA33">
-        <v>-0.96045274800000002</v>
+        <v>-0.9932029480000002</v>
       </c>
       <c r="BB33">
         <v>-1.86</v>
@@ -31708,7 +31711,7 @@
       <c r="AL34" s="6">
         <v>1.6819999999999999</v>
       </c>
-      <c r="AM34" s="12" t="s">
+      <c r="AM34" s="10" t="s">
         <v>289</v>
       </c>
       <c r="AN34" s="6" t="s">
@@ -31721,7 +31724,7 @@
         <v>2.1110000000000002</v>
       </c>
       <c r="AR34">
-        <v>-1.918407615</v>
+        <v>-1.9325626149999999</v>
       </c>
       <c r="AS34">
         <v>-1.95</v>
@@ -31730,7 +31733,7 @@
         <v>-1.94</v>
       </c>
       <c r="AU34">
-        <v>-1.8857401869999999</v>
+        <v>-1.905326987</v>
       </c>
       <c r="AV34">
         <v>-1.93</v>
@@ -31739,7 +31742,7 @@
         <v>-1.92</v>
       </c>
       <c r="AX34">
-        <v>-0.92179999999999995</v>
+        <v>-0.98050510000000002</v>
       </c>
       <c r="AY34">
         <v>-1.83</v>
@@ -31748,7 +31751,7 @@
         <v>-1.82</v>
       </c>
       <c r="BA34">
-        <v>-1.9183922550000001</v>
+        <v>-1.952180255</v>
       </c>
       <c r="BB34">
         <v>-1.88</v>
@@ -31864,7 +31867,7 @@
       <c r="AL35" s="6">
         <v>1.3240000000000001</v>
       </c>
-      <c r="AM35" s="12" t="s">
+      <c r="AM35" s="10" t="s">
         <v>290</v>
       </c>
       <c r="AN35" s="6" t="s">
@@ -31877,7 +31880,7 @@
         <v>1.6679999999999999</v>
       </c>
       <c r="AR35">
-        <v>-1.94089124</v>
+        <v>-1.9536493399999999</v>
       </c>
       <c r="AS35">
         <v>-1.96</v>
@@ -31886,7 +31889,7 @@
         <v>-1.96</v>
       </c>
       <c r="AU35">
-        <v>-1.918431794</v>
+        <v>-1.9356663940000001</v>
       </c>
       <c r="AV35">
         <v>-1.95</v>
@@ -31895,7 +31898,7 @@
         <v>-1.95</v>
       </c>
       <c r="AX35">
-        <v>-0.94900000000000007</v>
+        <v>-0.99888800000000022</v>
       </c>
       <c r="AY35">
         <v>-1.87</v>
@@ -31904,7 +31907,7 @@
         <v>-1.87</v>
       </c>
       <c r="BA35">
-        <v>-1.854405386</v>
+        <v>-1.886815186</v>
       </c>
       <c r="BB35">
         <v>-1.9</v>
@@ -32020,7 +32023,7 @@
       <c r="AL36" s="6">
         <v>1.228</v>
       </c>
-      <c r="AM36" s="10">
+      <c r="AM36" s="1">
         <v>3.798</v>
       </c>
       <c r="AN36" s="6" t="s">
@@ -32033,7 +32036,7 @@
         <v>1.5620000000000001</v>
       </c>
       <c r="AR36">
-        <v>-1.941368384</v>
+        <v>-1.9540978840000001</v>
       </c>
       <c r="AS36">
         <v>-1.96</v>
@@ -32042,7 +32045,7 @@
         <v>-1.95</v>
       </c>
       <c r="AU36">
-        <v>-1.921148614</v>
+        <v>-1.9384737139999999</v>
       </c>
       <c r="AV36">
         <v>-1.94</v>
@@ -32051,7 +32054,7 @@
         <v>-1.94</v>
       </c>
       <c r="AX36">
-        <v>-0.9403999999999999</v>
+        <v>-0.98924950000000011</v>
       </c>
       <c r="AY36">
         <v>-1.86</v>
@@ -32060,7 +32063,7 @@
         <v>-1.86</v>
       </c>
       <c r="BA36">
-        <v>-1.8564291429999999</v>
+        <v>-1.8905978429999999</v>
       </c>
       <c r="BB36">
         <v>-1.89</v>
@@ -32128,7 +32131,7 @@
       <c r="T37" s="6">
         <v>1.20804</v>
       </c>
-      <c r="U37" s="17">
+      <c r="U37" s="6">
         <v>0.85680000000000001</v>
       </c>
       <c r="V37" s="6">
@@ -32155,13 +32158,13 @@
       <c r="AD37" s="5">
         <v>0.72779000000000005</v>
       </c>
-      <c r="AE37" s="14">
+      <c r="AE37" s="12">
         <v>0.30620999999999998</v>
       </c>
       <c r="AF37" s="5">
         <v>0.67503999999999997</v>
       </c>
-      <c r="AG37" s="14">
+      <c r="AG37" s="12">
         <v>0.51602999999999999</v>
       </c>
       <c r="AI37" s="5">
@@ -32176,10 +32179,10 @@
       <c r="AL37" s="6">
         <v>3.1349999999999998</v>
       </c>
-      <c r="AM37" s="15">
+      <c r="AM37" s="13">
         <v>6.0750000000000002</v>
       </c>
-      <c r="AN37" s="15">
+      <c r="AN37" s="13">
         <v>6.3170000000000002</v>
       </c>
       <c r="AO37" s="5">
@@ -32189,7 +32192,7 @@
         <v>0.97099999999999997</v>
       </c>
       <c r="AR37">
-        <v>-1.9031037790000001</v>
+        <v>-1.917919379</v>
       </c>
       <c r="AS37">
         <v>-0.98</v>
@@ -32198,7 +32201,7 @@
         <v>-0.98</v>
       </c>
       <c r="AU37">
-        <v>-1.1387377780000001</v>
+        <v>-1.163580278</v>
       </c>
       <c r="AV37">
         <v>-1.02</v>
@@ -32207,7 +32210,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX37">
-        <v>-0.92910000000000004</v>
+        <v>-0.97632980000000025</v>
       </c>
       <c r="AY37">
         <v>-1.44</v>
@@ -32216,7 +32219,7 @@
         <v>-1.47</v>
       </c>
       <c r="BA37">
-        <v>-1.0283189159999999</v>
+        <v>-1.0614065159999999</v>
       </c>
       <c r="BB37">
         <v>-1.46</v>
@@ -32296,7 +32299,7 @@
       <c r="X38" s="6">
         <v>0.16058</v>
       </c>
-      <c r="Y38" s="15">
+      <c r="Y38" s="13">
         <v>0.39323000000000002</v>
       </c>
       <c r="AA38" s="6">
@@ -32335,7 +32338,7 @@
       <c r="AM38" s="6">
         <v>4.3780000000000001</v>
       </c>
-      <c r="AN38" s="15">
+      <c r="AN38" s="13">
         <v>2.262</v>
       </c>
       <c r="AO38" s="5">
@@ -32345,7 +32348,7 @@
         <v>1.998</v>
       </c>
       <c r="AR38">
-        <v>-0.98089999999999999</v>
+        <v>-0.99511660000000024</v>
       </c>
       <c r="AS38">
         <v>-1.68</v>
@@ -32354,7 +32357,7 @@
         <v>-1.78</v>
       </c>
       <c r="AU38">
-        <v>-1.857725061</v>
+        <v>-1.8770806609999999</v>
       </c>
       <c r="AV38">
         <v>-1.78</v>
@@ -32363,7 +32366,7 @@
         <v>-1.83</v>
       </c>
       <c r="AX38">
-        <v>-1.0315000000000001</v>
+        <v>-1.1374107</v>
       </c>
       <c r="AY38">
         <v>-0.9</v>
@@ -32372,7 +32375,7 @@
         <v>-0.87</v>
       </c>
       <c r="BA38">
-        <v>-0.95509999999999995</v>
+        <v>-0.98609860000000005</v>
       </c>
       <c r="BB38">
         <v>-1.81</v>
@@ -32393,7 +32396,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3022EA92-DD80-4549-8700-EFF920438755}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -32648,7 +32651,7 @@
       <c r="AP3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -32657,7 +32660,7 @@
       <c r="AT3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AV3" s="2" t="s">
@@ -32666,7 +32669,7 @@
       <c r="AW3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AY3" s="2" t="s">
@@ -32675,7 +32678,7 @@
       <c r="AZ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="BB3" s="2" t="s">
@@ -32805,7 +32808,7 @@
         <v>3.702</v>
       </c>
       <c r="AR4">
-        <v>-1.87674962837977</v>
+        <v>-1.89754182837977</v>
       </c>
       <c r="AS4">
         <v>-1.25</v>
@@ -32814,7 +32817,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AU4">
-        <v>-1.8227530017415601</v>
+        <v>-1.8524833017415601</v>
       </c>
       <c r="AV4">
         <v>-1.1200000000000001</v>
@@ -32823,7 +32826,7 @@
         <v>-1.01</v>
       </c>
       <c r="AX4">
-        <v>-0.87109999999999999</v>
+        <v>-0.97456460000000011</v>
       </c>
       <c r="AY4">
         <v>-1.1000000000000001</v>
@@ -32832,7 +32835,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BA4">
-        <v>-1.6747987672475999</v>
+        <v>-1.7261831672476</v>
       </c>
       <c r="BB4">
         <v>-0.98</v>
@@ -32961,7 +32964,7 @@
         <v>3.5179999999999998</v>
       </c>
       <c r="AR5">
-        <v>-1.8494242265937499</v>
+        <v>-1.87326502659375</v>
       </c>
       <c r="AS5">
         <v>-1.47</v>
@@ -32970,7 +32973,7 @@
         <v>-1.52</v>
       </c>
       <c r="AU5">
-        <v>-1.7956893354791901</v>
+        <v>-1.82837403547919</v>
       </c>
       <c r="AV5">
         <v>-1.39</v>
@@ -32979,7 +32982,7 @@
         <v>-1.43</v>
       </c>
       <c r="AX5">
-        <v>-0.8296</v>
+        <v>-0.92324190000000028</v>
       </c>
       <c r="AY5">
         <v>-0.95</v>
@@ -32988,7 +32991,7 @@
         <v>-0.98</v>
       </c>
       <c r="BA5">
-        <v>-0.89209801194549998</v>
+        <v>-0.94121361194549991</v>
       </c>
       <c r="BB5">
         <v>-1.22</v>
@@ -33117,7 +33120,7 @@
         <v>3.6669999999999998</v>
       </c>
       <c r="AR6">
-        <v>-1.8472596047491601</v>
+        <v>-1.8718621047491599</v>
       </c>
       <c r="AS6">
         <v>-1.29</v>
@@ -33126,7 +33129,7 @@
         <v>-1.26</v>
       </c>
       <c r="AU6">
-        <v>-1.78397001623844</v>
+        <v>-1.8198588162384399</v>
       </c>
       <c r="AV6">
         <v>-1.1299999999999999</v>
@@ -33135,7 +33138,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AX6">
-        <v>-0.84789999999999999</v>
+        <v>-0.97559230000000019</v>
       </c>
       <c r="AY6">
         <v>-1.06</v>
@@ -33144,7 +33147,7 @@
         <v>-1.07</v>
       </c>
       <c r="BA6">
-        <v>-0.84602602159310003</v>
+        <v>-0.91164732159310002</v>
       </c>
       <c r="BB6">
         <v>-0.91</v>
@@ -33273,7 +33276,7 @@
         <v>3.6539999999999999</v>
       </c>
       <c r="AR7">
-        <v>-1.8407082166075901</v>
+        <v>-1.8660777166075899</v>
       </c>
       <c r="AS7">
         <v>-1.32</v>
@@ -33282,7 +33285,7 @@
         <v>-1.29</v>
       </c>
       <c r="AU7">
-        <v>-0.94806739470996004</v>
+        <v>-0.9856152947099599</v>
       </c>
       <c r="AV7">
         <v>-1.1399999999999999</v>
@@ -33291,7 +33294,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AX7">
-        <v>-0.8378000000000001</v>
+        <v>-0.97673990000000011</v>
       </c>
       <c r="AY7">
         <v>-1.05</v>
@@ -33300,7 +33303,7 @@
         <v>-1.05</v>
       </c>
       <c r="BA7">
-        <v>-0.84001054168022005</v>
+        <v>-0.9110192416802203</v>
       </c>
       <c r="BB7">
         <v>-0.9</v>
@@ -33325,7 +33328,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4837044-DD50-48A8-AC77-D1678C65813F}">
   <dimension ref="A1:BI51"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -33578,7 +33581,7 @@
       <c r="AP3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -33587,7 +33590,7 @@
       <c r="AT3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AV3" s="2" t="s">
@@ -33596,7 +33599,7 @@
       <c r="AW3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="AY3" s="2" t="s">
@@ -33605,7 +33608,7 @@
       <c r="AZ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="BB3" s="2" t="s">
@@ -33741,7 +33744,7 @@
         <v>3.9729999999999999</v>
       </c>
       <c r="AR4">
-        <v>-1.8435358597960001</v>
+        <v>-1.855538359796</v>
       </c>
       <c r="AS4" s="9">
         <v>-1.1000000000000001</v>
@@ -33750,7 +33753,7 @@
         <v>-0.97</v>
       </c>
       <c r="AU4" s="1">
-        <v>-1.76809183487342</v>
+        <v>-1.78888123487342</v>
       </c>
       <c r="AV4">
         <v>-0.95</v>
@@ -33759,7 +33762,7 @@
         <v>-1.01</v>
       </c>
       <c r="AX4">
-        <v>-1.3642000000000001</v>
+        <v>-1.4393479000000002</v>
       </c>
       <c r="AY4">
         <v>-1.04</v>
@@ -33768,7 +33771,7 @@
         <v>-1.07</v>
       </c>
       <c r="BA4" s="1">
-        <v>-1.63487671537907</v>
+        <v>-1.6768799153790699</v>
       </c>
       <c r="BB4">
         <v>-0.97</v>
@@ -33904,7 +33907,7 @@
         <v>4.2679999999999998</v>
       </c>
       <c r="AR5">
-        <v>-1.8609688177363</v>
+        <v>-1.8741535177363</v>
       </c>
       <c r="AS5" s="9">
         <v>-1.49</v>
@@ -33913,7 +33916,7 @@
         <v>-1.45</v>
       </c>
       <c r="AU5" s="1">
-        <v>-1.7850107604199601</v>
+        <v>-1.80658656041996</v>
       </c>
       <c r="AV5">
         <v>-1.33</v>
@@ -33922,7 +33925,7 @@
         <v>-1.24</v>
       </c>
       <c r="AX5">
-        <v>-1.2950999999999999</v>
+        <v>-1.3551789999999999</v>
       </c>
       <c r="AY5">
         <v>-1.0900000000000001</v>
@@ -33931,7 +33934,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BA5" s="1">
-        <v>-1.6138600946881601</v>
+        <v>-1.6569302946881599</v>
       </c>
       <c r="BB5">
         <v>-0.97</v>
@@ -34067,7 +34070,7 @@
         <v>5.782</v>
       </c>
       <c r="AR6">
-        <v>-1.8296312402488399</v>
+        <v>-1.84442774024884</v>
       </c>
       <c r="AS6" s="9">
         <v>-1.3</v>
@@ -34076,7 +34079,7 @@
         <v>-1.24</v>
       </c>
       <c r="AU6" s="1">
-        <v>-1.7047893334215101</v>
+        <v>-1.7287137334215099</v>
       </c>
       <c r="AV6">
         <v>-1.1499999999999999</v>
@@ -34085,7 +34088,7 @@
         <v>-1.08</v>
       </c>
       <c r="AX6">
-        <v>-1.0017</v>
+        <v>-1.0805103000000003</v>
       </c>
       <c r="AY6">
         <v>-1.06</v>
@@ -34094,7 +34097,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BA6" s="1">
-        <v>-0.91239999999999999</v>
+        <v>-0.96715949999999973</v>
       </c>
       <c r="BB6">
         <v>-1.01</v>
@@ -34231,7 +34234,7 @@
         <v>4.0919999999999996</v>
       </c>
       <c r="AR7">
-        <v>-1.88544004848229</v>
+        <v>-1.8949272484822901</v>
       </c>
       <c r="AS7" s="9">
         <v>-1.1599999999999999</v>
@@ -34240,7 +34243,7 @@
         <v>-0.99</v>
       </c>
       <c r="AU7" s="1">
-        <v>-1.82976079814663</v>
+        <v>-1.8441384981466298</v>
       </c>
       <c r="AV7">
         <v>-1.04</v>
@@ -34249,7 +34252,7 @@
         <v>-1.07</v>
       </c>
       <c r="AX7">
-        <v>-1.4259999999999999</v>
+        <v>-1.4717203000000001</v>
       </c>
       <c r="AY7">
         <v>-1.1000000000000001</v>
@@ -34258,7 +34261,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BA7" s="1">
-        <v>-1.7128694366977799</v>
+        <v>-1.7396574366977797</v>
       </c>
       <c r="BB7">
         <v>-1.08</v>
@@ -34394,7 +34397,7 @@
         <v>5.1950000000000003</v>
       </c>
       <c r="AR8">
-        <v>-1.8685876818046401</v>
+        <v>-1.8761800818046401</v>
       </c>
       <c r="AS8" s="9">
         <v>-1.42</v>
@@ -34403,7 +34406,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU8" s="1">
-        <v>-1.7847169498091899</v>
+        <v>-1.7964899498091897</v>
       </c>
       <c r="AV8">
         <v>-1.1299999999999999</v>
@@ -34412,7 +34415,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AX8">
-        <v>-0.98439999999999994</v>
+        <v>-1.1300206999999998</v>
       </c>
       <c r="AY8">
         <v>-1.24</v>
@@ -34421,7 +34424,7 @@
         <v>-1.26</v>
       </c>
       <c r="BA8" s="1">
-        <v>-1.3475354492489799</v>
+        <v>-1.43894904924898</v>
       </c>
       <c r="BB8">
         <v>-1.24</v>
@@ -34499,7 +34502,7 @@
       <c r="U9" s="6">
         <v>0.30275000000000002</v>
       </c>
-      <c r="V9" s="17">
+      <c r="V9" s="6">
         <v>0.12741886999999999</v>
       </c>
       <c r="W9" s="6">
@@ -34557,7 +34560,7 @@
         <v>5.1310000000000002</v>
       </c>
       <c r="AR9">
-        <v>-1.7679074609854299</v>
+        <v>-1.7889276609854301</v>
       </c>
       <c r="AS9" s="9">
         <v>-1.28</v>
@@ -34566,7 +34569,7 @@
         <v>-1.28</v>
       </c>
       <c r="AU9" s="1">
-        <v>-1.59975779553024</v>
+        <v>-1.6450539955302401</v>
       </c>
       <c r="AV9">
         <v>-0.97</v>
@@ -34575,7 +34578,7 @@
         <v>-1.02</v>
       </c>
       <c r="AX9">
-        <v>-1.1207</v>
+        <v>-1.5116265</v>
       </c>
       <c r="AY9">
         <v>-1.18</v>
@@ -34584,7 +34587,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA9" s="1">
-        <v>-1.1862999999999999</v>
+        <v>-1.4611973</v>
       </c>
       <c r="BB9">
         <v>-0.95</v>
@@ -34720,7 +34723,7 @@
         <v>3.9470000000000001</v>
       </c>
       <c r="AR10">
-        <v>-1.8903961620752701</v>
+        <v>-1.9075592620752699</v>
       </c>
       <c r="AS10" s="9">
         <v>-1.31</v>
@@ -34729,7 +34732,7 @@
         <v>-1.24</v>
       </c>
       <c r="AU10" s="1">
-        <v>-1.8386294708687101</v>
+        <v>-1.8645781708687099</v>
       </c>
       <c r="AV10">
         <v>-1.1499999999999999</v>
@@ -34738,7 +34741,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AX10">
-        <v>-1.4851000000000001</v>
+        <v>-1.5660381000000001</v>
       </c>
       <c r="AY10">
         <v>-1</v>
@@ -34747,7 +34750,7 @@
         <v>-1.03</v>
       </c>
       <c r="BA10" s="1">
-        <v>-1.7200569565942401</v>
+        <v>-1.7689601565942399</v>
       </c>
       <c r="BB10">
         <v>-1</v>
@@ -34883,7 +34886,7 @@
         <v>5.6289999999999996</v>
       </c>
       <c r="AR11">
-        <v>-1.81607774866691</v>
+        <v>-1.83271434866691</v>
       </c>
       <c r="AS11" s="9">
         <v>-1.1599999999999999</v>
@@ -34892,7 +34895,7 @@
         <v>-1.02</v>
       </c>
       <c r="AU11" s="1">
-        <v>-1.6460979816135399</v>
+        <v>-1.6855592816135401</v>
       </c>
       <c r="AV11">
         <v>-0.96</v>
@@ -34901,7 +34904,7 @@
         <v>-1.01</v>
       </c>
       <c r="AX11">
-        <v>-0.9588000000000001</v>
+        <v>-1.1828915000000002</v>
       </c>
       <c r="AY11">
         <v>-1.23</v>
@@ -34910,7 +34913,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA11" s="1">
-        <v>-1.207778561824</v>
+        <v>-1.3592952618240002</v>
       </c>
       <c r="BB11">
         <v>-1.18</v>
@@ -35046,7 +35049,7 @@
         <v>4.4059999999999997</v>
       </c>
       <c r="AR12">
-        <v>-1.8633293412893801</v>
+        <v>-1.87766604128938</v>
       </c>
       <c r="AS12" s="9">
         <v>-1.27</v>
@@ -35055,7 +35058,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AU12" s="1">
-        <v>-1.78674705411766</v>
+        <v>-1.8107495541176599</v>
       </c>
       <c r="AV12">
         <v>-1.1200000000000001</v>
@@ -35064,7 +35067,7 @@
         <v>-1</v>
       </c>
       <c r="AX12">
-        <v>-1.4866999999999999</v>
+        <v>-1.5594828999999999</v>
       </c>
       <c r="AY12">
         <v>-1.08</v>
@@ -35073,7 +35076,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BA12" s="1">
-        <v>-1.6231338062338501</v>
+        <v>-1.67297800623385</v>
       </c>
       <c r="BB12">
         <v>-0.99</v>
@@ -35209,7 +35212,7 @@
         <v>5.8390000000000004</v>
       </c>
       <c r="AR13">
-        <v>-1.8281240502542599</v>
+        <v>-1.8443607502542598</v>
       </c>
       <c r="AS13" s="9">
         <v>-1.17</v>
@@ -35218,7 +35221,7 @@
         <v>-1.03</v>
       </c>
       <c r="AU13" s="1">
-        <v>-1.6590807600598101</v>
+        <v>-1.6926505600598101</v>
       </c>
       <c r="AV13">
         <v>-0.94</v>
@@ -35227,7 +35230,7 @@
         <v>-1</v>
       </c>
       <c r="AX13">
-        <v>-0.50679999999999992</v>
+        <v>-0.7061312999999998</v>
       </c>
       <c r="AY13">
         <v>-1.19</v>
@@ -35236,7 +35239,7 @@
         <v>-1.19</v>
       </c>
       <c r="BA13" s="1">
-        <v>-1.0891071354370401</v>
+        <v>-1.2133760354370402</v>
       </c>
       <c r="BB13">
         <v>-1.1399999999999999</v>
@@ -35372,7 +35375,7 @@
         <v>4.6269999999999998</v>
       </c>
       <c r="AR14">
-        <v>-1.8540080839950099</v>
+        <v>-1.8702599839950098</v>
       </c>
       <c r="AS14" s="9">
         <v>-1.21</v>
@@ -35381,7 +35384,7 @@
         <v>-1.05</v>
       </c>
       <c r="AU14" s="1">
-        <v>-1.76143184594532</v>
+        <v>-1.79177224594532</v>
       </c>
       <c r="AV14">
         <v>-1.02</v>
@@ -35390,7 +35393,7 @@
         <v>-0.94</v>
       </c>
       <c r="AX14">
-        <v>-1.1845000000000001</v>
+        <v>-1.2908504000000003</v>
       </c>
       <c r="AY14">
         <v>-1.1299999999999999</v>
@@ -35399,7 +35402,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BA14" s="1">
-        <v>-1.5618963756814599</v>
+        <v>-1.6336704756814597</v>
       </c>
       <c r="BB14">
         <v>-1.06</v>
@@ -35535,7 +35538,7 @@
         <v>3.8170000000000002</v>
       </c>
       <c r="AR15">
-        <v>-1.8905077733823901</v>
+        <v>-1.9023727733823899</v>
       </c>
       <c r="AS15" s="9">
         <v>-1.39</v>
@@ -35544,7 +35547,7 @@
         <v>-1.28</v>
       </c>
       <c r="AU15" s="1">
-        <v>-1.8373535861521999</v>
+        <v>-1.8550598861521999</v>
       </c>
       <c r="AV15">
         <v>-1.17</v>
@@ -35553,7 +35556,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AX15">
-        <v>-1.5408999999999999</v>
+        <v>-1.5989573000000001</v>
       </c>
       <c r="AY15">
         <v>-1.1399999999999999</v>
@@ -35562,7 +35565,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA15" s="1">
-        <v>-1.67397141748641</v>
+        <v>-1.7092388174864099</v>
       </c>
       <c r="BB15">
         <v>-1.1200000000000001</v>
@@ -35698,7 +35701,7 @@
         <v>4.157</v>
       </c>
       <c r="AR16">
-        <v>-1.88431332535137</v>
+        <v>-1.9004125253513702</v>
       </c>
       <c r="AS16" s="9">
         <v>-1.27</v>
@@ -35707,7 +35710,7 @@
         <v>-1.17</v>
       </c>
       <c r="AU16" s="1">
-        <v>-1.81806692464118</v>
+        <v>-1.84385162464118</v>
       </c>
       <c r="AV16">
         <v>-1.07</v>
@@ -35716,7 +35719,7 @@
         <v>-1</v>
       </c>
       <c r="AX16">
-        <v>-1.3358000000000001</v>
+        <v>-1.4372027000000001</v>
       </c>
       <c r="AY16">
         <v>-1.1100000000000001</v>
@@ -35725,7 +35728,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BA16" s="1">
-        <v>-1.62310177204807</v>
+        <v>-1.68432537204807</v>
       </c>
       <c r="BB16">
         <v>-1.1200000000000001</v>
@@ -35861,7 +35864,7 @@
         <v>4.2789999999999999</v>
       </c>
       <c r="AR17">
-        <v>-1.8961883001456601</v>
+        <v>-1.9082111001456601</v>
       </c>
       <c r="AS17" s="9">
         <v>-1.38</v>
@@ -35870,7 +35873,7 @@
         <v>-1.2</v>
       </c>
       <c r="AU17" s="1">
-        <v>-1.8431414380514299</v>
+        <v>-1.86131983805143</v>
       </c>
       <c r="AV17">
         <v>-1.1599999999999999</v>
@@ -35879,7 +35882,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX17">
-        <v>-1.2141999999999999</v>
+        <v>-1.3390689</v>
       </c>
       <c r="AY17">
         <v>-1.19</v>
@@ -35888,7 +35891,7 @@
         <v>-1.21</v>
       </c>
       <c r="BA17" s="1">
-        <v>-1.57180944148716</v>
+        <v>-1.6423028414871601</v>
       </c>
       <c r="BB17">
         <v>-1.36</v>
@@ -36024,7 +36027,7 @@
         <v>4.2770000000000001</v>
       </c>
       <c r="AR18">
-        <v>-1.8564982694386001</v>
+        <v>-1.8747999694385999</v>
       </c>
       <c r="AS18" s="9">
         <v>-1.41</v>
@@ -36033,7 +36036,7 @@
         <v>-1.31</v>
       </c>
       <c r="AU18" s="1">
-        <v>-1.77886976813183</v>
+        <v>-1.8092113681318298</v>
       </c>
       <c r="AV18">
         <v>-1.1000000000000001</v>
@@ -36042,7 +36045,7 @@
         <v>-1.04</v>
       </c>
       <c r="AX18">
-        <v>-1.2353000000000001</v>
+        <v>-1.3647507999999999</v>
       </c>
       <c r="AY18">
         <v>-1.18</v>
@@ -36051,7 +36054,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA18" s="1">
-        <v>-1.51356737535924</v>
+        <v>-1.5973022753592401</v>
       </c>
       <c r="BB18">
         <v>-1.1499999999999999</v>
@@ -36187,7 +36190,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="AR19">
-        <v>-1.89223293887018</v>
+        <v>-1.8974267388701798</v>
       </c>
       <c r="AS19" s="9">
         <v>-1.44</v>
@@ -36196,7 +36199,7 @@
         <v>-1.75</v>
       </c>
       <c r="AU19" s="1">
-        <v>-1.8369163293426201</v>
+        <v>-1.8438390293426201</v>
       </c>
       <c r="AV19">
         <v>-1.54</v>
@@ -36205,7 +36208,7 @@
         <v>-1.73</v>
       </c>
       <c r="AX19">
-        <v>-0.87230000000000008</v>
+        <v>-0.91831219999999991</v>
       </c>
       <c r="AY19">
         <v>-1.41</v>
@@ -36214,7 +36217,7 @@
         <v>-1.47</v>
       </c>
       <c r="BA19" s="1">
-        <v>-1.69083707709819</v>
+        <v>-1.7010761770981901</v>
       </c>
       <c r="BB19">
         <v>-1.62</v>
@@ -36350,7 +36353,7 @@
         <v>5.0599999999999996</v>
       </c>
       <c r="AR20">
-        <v>-1.8635636102669899</v>
+        <v>-1.8765153102669898</v>
       </c>
       <c r="AS20" s="9">
         <v>-1.18</v>
@@ -36359,7 +36362,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU20" s="1">
-        <v>-1.7764820782591599</v>
+        <v>-1.7968902782591598</v>
       </c>
       <c r="AV20">
         <v>-1.05</v>
@@ -36368,7 +36371,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX20">
-        <v>-1.0960000000000001</v>
+        <v>-1.1587787000000001</v>
       </c>
       <c r="AY20">
         <v>-1.26</v>
@@ -36377,7 +36380,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA20" s="1">
-        <v>-1.5814881321704199</v>
+        <v>-1.6233139321704197</v>
       </c>
       <c r="BB20">
         <v>-1.22</v>
@@ -36513,7 +36516,7 @@
         <v>5.2930000000000001</v>
       </c>
       <c r="AR21">
-        <v>-1.8486406947681999</v>
+        <v>-1.8626005947682001</v>
       </c>
       <c r="AS21" s="9">
         <v>-1.23</v>
@@ -36522,7 +36525,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AU21" s="1">
-        <v>-1.73175491586875</v>
+        <v>-1.76000211586875</v>
       </c>
       <c r="AV21">
         <v>-1</v>
@@ -36531,7 +36534,7 @@
         <v>-0.96</v>
       </c>
       <c r="AX21">
-        <v>-1.2273000000000001</v>
+        <v>-1.3718064000000001</v>
       </c>
       <c r="AY21">
         <v>-1.1599999999999999</v>
@@ -36540,7 +36543,7 @@
         <v>-1.18</v>
       </c>
       <c r="BA21" s="1">
-        <v>-1.41290509025948</v>
+        <v>-1.5127869902594802</v>
       </c>
       <c r="BB21">
         <v>-1.1299999999999999</v>
@@ -36676,7 +36679,7 @@
         <v>4.5940000000000003</v>
       </c>
       <c r="AR22">
-        <v>-1.8713482546523901</v>
+        <v>-1.8818727546523899</v>
       </c>
       <c r="AS22" s="9">
         <v>-1.17</v>
@@ -36685,7 +36688,7 @@
         <v>-1.04</v>
       </c>
       <c r="AU22" s="1">
-        <v>-1.78808872011805</v>
+        <v>-1.8076104201180498</v>
       </c>
       <c r="AV22">
         <v>-0.95</v>
@@ -36694,7 +36697,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AX22">
-        <v>-1.2968</v>
+        <v>-1.3891343999999999</v>
       </c>
       <c r="AY22">
         <v>-1.26</v>
@@ -36703,7 +36706,7 @@
         <v>-1.31</v>
       </c>
       <c r="BA22" s="1">
-        <v>-1.5660886608507301</v>
+        <v>-1.6269834608507299</v>
       </c>
       <c r="BB22">
         <v>-1.23</v>
@@ -36839,7 +36842,7 @@
         <v>4.41</v>
       </c>
       <c r="AR23">
-        <v>-1.8878037792144799</v>
+        <v>-1.9014871792144801</v>
       </c>
       <c r="AS23" s="9">
         <v>-1.4</v>
@@ -36848,7 +36851,7 @@
         <v>-1.42</v>
       </c>
       <c r="AU23" s="1">
-        <v>-1.82059391820303</v>
+        <v>-1.84155421820303</v>
       </c>
       <c r="AV23">
         <v>-1.21</v>
@@ -36857,16 +36860,16 @@
         <v>-1.23</v>
       </c>
       <c r="AX23">
-        <v>-1.5508</v>
-      </c>
-      <c r="AY23" s="13">
+        <v>-1.6236336</v>
+      </c>
+      <c r="AY23" s="11">
         <v>-1.41</v>
       </c>
       <c r="AZ23">
         <v>-1.58</v>
       </c>
       <c r="BA23" s="1">
-        <v>-1.67364610828699</v>
+        <v>-1.7227532082869901</v>
       </c>
       <c r="BB23">
         <v>-1.44</v>
@@ -36922,7 +36925,7 @@
       <c r="M24" s="6">
         <v>-0.22427424111503499</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="13">
         <v>0.3196</v>
       </c>
       <c r="O24" s="6">
@@ -37002,7 +37005,7 @@
         <v>4.3390000000000004</v>
       </c>
       <c r="AR24">
-        <v>-1.8300991870407699</v>
+        <v>-1.8558120870407697</v>
       </c>
       <c r="AS24" s="9">
         <v>-1.17</v>
@@ -37011,16 +37014,16 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AU24" s="1">
-        <v>-1.7420897212870401</v>
-      </c>
-      <c r="AV24" s="13">
+        <v>-1.7861849212870402</v>
+      </c>
+      <c r="AV24" s="11">
         <v>-0.89</v>
       </c>
       <c r="AW24">
         <v>-0.9</v>
       </c>
       <c r="AX24">
-        <v>-1.4129</v>
+        <v>-1.5543008</v>
       </c>
       <c r="AY24">
         <v>-1.18</v>
@@ -37029,7 +37032,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA24" s="1">
-        <v>-1.5494790230003399</v>
+        <v>-1.6490740230003398</v>
       </c>
       <c r="BB24">
         <v>-1.18</v>
@@ -37165,7 +37168,7 @@
         <v>4.5309999999999997</v>
       </c>
       <c r="AR25">
-        <v>-1.8856678274715899</v>
+        <v>-1.8970463274715901</v>
       </c>
       <c r="AS25" s="9">
         <v>-1.1100000000000001</v>
@@ -37174,7 +37177,7 @@
         <v>-1.03</v>
       </c>
       <c r="AU25" s="1">
-        <v>-1.82310360018234</v>
+        <v>-1.8407354001823402</v>
       </c>
       <c r="AV25">
         <v>-0.98</v>
@@ -37183,7 +37186,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AX25">
-        <v>-1.8129999999999999</v>
+        <v>-1.8752728999999999</v>
       </c>
       <c r="AY25">
         <v>-1.18</v>
@@ -37192,7 +37195,7 @@
         <v>-1.23</v>
       </c>
       <c r="BA25" s="1">
-        <v>-1.6727496735851399</v>
+        <v>-1.71200317358514</v>
       </c>
       <c r="BB25">
         <v>-1.17</v>
@@ -37328,7 +37331,7 @@
         <v>5.0019999999999998</v>
       </c>
       <c r="AR26">
-        <v>-1.87513508923756</v>
+        <v>-1.8868674892375601</v>
       </c>
       <c r="AS26" s="9">
         <v>-1.1100000000000001</v>
@@ -37337,7 +37340,7 @@
         <v>-1.01</v>
       </c>
       <c r="AU26" s="1">
-        <v>-1.802151714661</v>
+        <v>-1.819073214661</v>
       </c>
       <c r="AV26">
         <v>-1</v>
@@ -37346,7 +37349,7 @@
         <v>-1.08</v>
       </c>
       <c r="AX26">
-        <v>-1.0886</v>
+        <v>-1.1366149000000001</v>
       </c>
       <c r="AY26">
         <v>-1.23</v>
@@ -37355,7 +37358,7 @@
         <v>-1.3</v>
       </c>
       <c r="BA26" s="1">
-        <v>-1.9003212509633201</v>
+        <v>-1.9310260509633201</v>
       </c>
       <c r="BB26">
         <v>-1.23</v>
@@ -37491,7 +37494,7 @@
         <v>4.782</v>
       </c>
       <c r="AR27">
-        <v>-1.87783234626217</v>
+        <v>-1.8892750462621699</v>
       </c>
       <c r="AS27" s="9">
         <v>-1.1299999999999999</v>
@@ -37500,7 +37503,7 @@
         <v>-1.02</v>
       </c>
       <c r="AU27" s="1">
-        <v>-1.7992766840091201</v>
+        <v>-1.81893808400912</v>
       </c>
       <c r="AV27">
         <v>-0.96</v>
@@ -37509,7 +37512,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AX27">
-        <v>-1.7333000000000001</v>
+        <v>-1.824454</v>
       </c>
       <c r="AY27">
         <v>-1.22</v>
@@ -37518,7 +37521,7 @@
         <v>-1.25</v>
       </c>
       <c r="BA27" s="1">
-        <v>-1.58014583352817</v>
+        <v>-1.6377554335281701</v>
       </c>
       <c r="BB27">
         <v>-1.2</v>
@@ -37654,7 +37657,7 @@
         <v>4.4379999999999997</v>
       </c>
       <c r="AR28">
-        <v>-1.8886352113107301</v>
+        <v>-1.9058375113107302</v>
       </c>
       <c r="AS28" s="9">
         <v>-1.29</v>
@@ -37663,7 +37666,7 @@
         <v>-1.22</v>
       </c>
       <c r="AU28" s="1">
-        <v>-1.83372433308405</v>
+        <v>-1.8585464330840502</v>
       </c>
       <c r="AV28">
         <v>-1.1399999999999999</v>
@@ -37672,7 +37675,7 @@
         <v>-1.08</v>
       </c>
       <c r="AX28">
-        <v>-1.8174999999999999</v>
+        <v>-1.8847701999999997</v>
       </c>
       <c r="AY28">
         <v>-1.06</v>
@@ -37681,7 +37684,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BA28" s="1">
-        <v>-1.6773924059423899</v>
+        <v>-1.7179616059423901</v>
       </c>
       <c r="BB28">
         <v>-1.1100000000000001</v>
@@ -37817,7 +37820,7 @@
         <v>4.3540000000000001</v>
       </c>
       <c r="AR29">
-        <v>-1.8892776162615501</v>
+        <v>-1.89799081626155</v>
       </c>
       <c r="AS29" s="9">
         <v>-1.17</v>
@@ -37826,7 +37829,7 @@
         <v>-1.05</v>
       </c>
       <c r="AU29" s="1">
-        <v>-1.8285016857135701</v>
+        <v>-1.8417256857135702</v>
       </c>
       <c r="AV29">
         <v>-0.99</v>
@@ -37835,7 +37838,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AX29">
-        <v>-1.7601</v>
+        <v>-1.8015796000000002</v>
       </c>
       <c r="AY29">
         <v>-1.27</v>
@@ -37844,7 +37847,7 @@
         <v>-1.35</v>
       </c>
       <c r="BA29" s="1">
-        <v>-1.6674148965375699</v>
+        <v>-1.6944925965375699</v>
       </c>
       <c r="BB29">
         <v>-1.27</v>
@@ -37980,7 +37983,7 @@
         <v>5.91</v>
       </c>
       <c r="AR30">
-        <v>-1.8519835737321499</v>
+        <v>-1.8631554737321498</v>
       </c>
       <c r="AS30" s="9">
         <v>-1.24</v>
@@ -37989,7 +37992,7 @@
         <v>-1.02</v>
       </c>
       <c r="AU30" s="1">
-        <v>-1.71866395477026</v>
+        <v>-1.73724805477026</v>
       </c>
       <c r="AV30">
         <v>-1.04</v>
@@ -37998,7 +38001,7 @@
         <v>-1.07</v>
       </c>
       <c r="AX30">
-        <v>-0.78570000000000007</v>
+        <v>-1.0188273000000001</v>
       </c>
       <c r="AY30">
         <v>-1.25</v>
@@ -38007,7 +38010,7 @@
         <v>-1.25</v>
       </c>
       <c r="BA30" s="1">
-        <v>-1.1636426977545</v>
+        <v>-1.3180863977544999</v>
       </c>
       <c r="BB30">
         <v>-1.2</v>
@@ -38143,7 +38146,7 @@
         <v>5.1449999999999996</v>
       </c>
       <c r="AR31">
-        <v>-1.8800873963609801</v>
+        <v>-1.8870905963609803</v>
       </c>
       <c r="AS31" s="9">
         <v>-1.35</v>
@@ -38152,7 +38155,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AU31" s="1">
-        <v>-1.8034763425312801</v>
+        <v>-1.8135778425312803</v>
       </c>
       <c r="AV31">
         <v>-1.1599999999999999</v>
@@ -38161,7 +38164,7 @@
         <v>-1.03</v>
       </c>
       <c r="AX31">
-        <v>-0.85529999999999995</v>
+        <v>-0.93999810000000017</v>
       </c>
       <c r="AY31">
         <v>-1.3</v>
@@ -38169,8 +38172,8 @@
       <c r="AZ31">
         <v>-1.36</v>
       </c>
-      <c r="BA31" s="13">
-        <v>-0.83338181759864993</v>
+      <c r="BA31" s="11">
+        <v>-0.88140591759864995</v>
       </c>
       <c r="BB31">
         <v>-1.33</v>
@@ -38248,13 +38251,13 @@
       <c r="U32" s="6">
         <v>1.2295499999999999</v>
       </c>
-      <c r="V32" s="15">
+      <c r="V32" s="13">
         <v>-0.12889999999999999</v>
       </c>
       <c r="W32" s="6">
         <v>-0.59506000000000003</v>
       </c>
-      <c r="X32" s="15">
+      <c r="X32" s="13">
         <v>-0.19051000000000001</v>
       </c>
       <c r="Y32">
@@ -38306,7 +38309,7 @@
         <v>5.2569999999999997</v>
       </c>
       <c r="AR32">
-        <v>-1.86973416305269</v>
+        <v>-1.8805566630526902</v>
       </c>
       <c r="AS32" s="9">
         <v>-1.0900000000000001</v>
@@ -38315,7 +38318,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AU32" s="1">
-        <v>-1.75073786639744</v>
+        <v>-1.7741420663974399</v>
       </c>
       <c r="AV32">
         <v>-1.05</v>
@@ -38324,16 +38327,16 @@
         <v>-1.19</v>
       </c>
       <c r="AX32">
-        <v>-0.81010000000000004</v>
-      </c>
-      <c r="AY32" s="13">
+        <v>-0.92943690000000001</v>
+      </c>
+      <c r="AY32" s="11">
         <v>-1.29</v>
       </c>
-      <c r="AZ32" s="13">
+      <c r="AZ32" s="11">
         <v>-1.32</v>
       </c>
       <c r="BA32" s="1">
-        <v>-1.4200581010194899</v>
+        <v>-1.5330219010194901</v>
       </c>
       <c r="BB32">
         <v>-1.26</v>
@@ -38389,7 +38392,7 @@
       <c r="M33" s="6">
         <v>-0.57673901628125401</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="13">
         <v>0.24329999999999999</v>
       </c>
       <c r="O33" s="6">
@@ -38417,8 +38420,8 @@
       <c r="W33" s="6">
         <v>-0.64137</v>
       </c>
-      <c r="X33" s="6">
-        <v>-0.15511</v>
+      <c r="X33" s="13">
+        <v>-0.15523000000000001</v>
       </c>
       <c r="Y33">
         <v>-0.20094000000000001</v>
@@ -38469,7 +38472,7 @@
         <v>6.085</v>
       </c>
       <c r="AR33">
-        <v>-1.8452264609998199</v>
+        <v>-1.8567780609998201</v>
       </c>
       <c r="AS33" s="9">
         <v>-1.1200000000000001</v>
@@ -38478,16 +38481,16 @@
         <v>-0.98</v>
       </c>
       <c r="AU33" s="1">
-        <v>-1.70297546347597</v>
-      </c>
-      <c r="AV33" s="13">
+        <v>-1.7205679634759701</v>
+      </c>
+      <c r="AV33" s="11">
         <v>-0.97</v>
       </c>
       <c r="AW33">
         <v>-1.1000000000000001</v>
       </c>
       <c r="AX33">
-        <v>-0.81570000000000009</v>
+        <v>-0.92999959999999993</v>
       </c>
       <c r="AY33">
         <v>-1.26</v>
@@ -38496,7 +38499,7 @@
         <v>-1.31</v>
       </c>
       <c r="BA33" s="1">
-        <v>-1.6228</v>
+        <v>-1.6807584999999998</v>
       </c>
       <c r="BB33">
         <v>-1.23</v>
@@ -38632,7 +38635,7 @@
         <v>4.9279999999999999</v>
       </c>
       <c r="AR34">
-        <v>-1.8160427185706201</v>
+        <v>-1.8386511185706202</v>
       </c>
       <c r="AS34" s="9">
         <v>-1.17</v>
@@ -38641,7 +38644,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="AU34" s="1">
-        <v>-1.6802571425350701</v>
+        <v>-1.72753594253507</v>
       </c>
       <c r="AV34">
         <v>-0.95</v>
@@ -38650,7 +38653,7 @@
         <v>-0.94</v>
       </c>
       <c r="AX34">
-        <v>-1.3613</v>
+        <v>-1.5742354999999999</v>
       </c>
       <c r="AY34">
         <v>-1.27</v>
@@ -38659,7 +38662,7 @@
         <v>-1.3</v>
       </c>
       <c r="BA34" s="1">
-        <v>-1.3557110218625099</v>
+        <v>-1.4966107218625098</v>
       </c>
       <c r="BB34">
         <v>-1.26</v>
@@ -38795,7 +38798,7 @@
         <v>5.1459999999999999</v>
       </c>
       <c r="AR35">
-        <v>-1.88342345935235</v>
+        <v>-1.89002815935235</v>
       </c>
       <c r="AS35" s="9">
         <v>-1.1299999999999999</v>
@@ -38804,7 +38807,7 @@
         <v>-1.26</v>
       </c>
       <c r="AU35" s="1">
-        <v>-1.81046289455542</v>
+        <v>-1.8201122945554198</v>
       </c>
       <c r="AV35">
         <v>-1.05</v>
@@ -38813,7 +38816,7 @@
         <v>-1.37</v>
       </c>
       <c r="AX35">
-        <v>-1.0547</v>
+        <v>-1.1297719000000002</v>
       </c>
       <c r="AY35">
         <v>-1.27</v>
@@ -38822,7 +38825,7 @@
         <v>-1.32</v>
       </c>
       <c r="BA35" s="1">
-        <v>-1.3963418175986499</v>
+        <v>-1.4293905175986501</v>
       </c>
       <c r="BB35">
         <v>-1.36</v>
@@ -38900,13 +38903,13 @@
       <c r="U36" s="6">
         <v>-0.92978000000000005</v>
       </c>
-      <c r="V36" s="15">
+      <c r="V36" s="13">
         <v>-6.6409999999999997E-2</v>
       </c>
       <c r="W36" s="6">
         <v>-0.62870000000000004</v>
       </c>
-      <c r="X36" s="15">
+      <c r="X36" s="13">
         <v>-0.13780000000000001</v>
       </c>
       <c r="Y36">
@@ -38958,7 +38961,7 @@
         <v>5.1130000000000004</v>
       </c>
       <c r="AR36">
-        <v>-1.8826895929456899</v>
+        <v>-1.8891181929456899</v>
       </c>
       <c r="AS36" s="9">
         <v>-1.1200000000000001</v>
@@ -38967,7 +38970,7 @@
         <v>-1.29</v>
       </c>
       <c r="AU36" s="1">
-        <v>-1.7997608731623</v>
+        <v>-1.8104337731622999</v>
       </c>
       <c r="AV36">
         <v>-1.1000000000000001</v>
@@ -38976,16 +38979,16 @@
         <v>-1.39</v>
       </c>
       <c r="AX36">
-        <v>-0.80160000000000009</v>
-      </c>
-      <c r="AY36" s="13">
+        <v>-0.9438070999999999</v>
+      </c>
+      <c r="AY36" s="11">
         <v>-1.32</v>
       </c>
-      <c r="AZ36" s="13">
+      <c r="AZ36" s="11">
         <v>-1.35</v>
       </c>
       <c r="BA36" s="1">
-        <v>-1.39139107300034</v>
+        <v>-1.4758973730003402</v>
       </c>
       <c r="BB36">
         <v>-1.33</v>
@@ -39121,7 +39124,7 @@
         <v>5.7220000000000004</v>
       </c>
       <c r="AR37">
-        <v>-1.8405628097181399</v>
+        <v>-1.8572982097181399</v>
       </c>
       <c r="AS37" s="9">
         <v>-1.1200000000000001</v>
@@ -39130,7 +39133,7 @@
         <v>-0.95</v>
       </c>
       <c r="AU37" s="1">
-        <v>-1.71254836917178</v>
+        <v>-1.7447074691717799</v>
       </c>
       <c r="AV37">
         <v>-0.94</v>
@@ -39139,7 +39142,7 @@
         <v>-1.07</v>
       </c>
       <c r="AX37">
-        <v>-1.0251999999999999</v>
+        <v>-1.1727542</v>
       </c>
       <c r="AY37">
         <v>-1.37</v>
@@ -39148,7 +39151,7 @@
         <v>-1.45</v>
       </c>
       <c r="BA37" s="1">
-        <v>-1.5975600100696601</v>
+        <v>-1.6993119100696601</v>
       </c>
       <c r="BB37">
         <v>-1.34</v>
@@ -39210,7 +39213,7 @@
       <c r="O38" s="6">
         <v>-0.21840000000000001</v>
       </c>
-      <c r="P38" s="15">
+      <c r="P38" s="13">
         <v>-2.3999999999999998E-3</v>
       </c>
       <c r="Q38" s="6">
@@ -39284,7 +39287,7 @@
         <v>4.6959999999999997</v>
       </c>
       <c r="AR38">
-        <v>-1.89173507981542</v>
+        <v>-1.9038919798154199</v>
       </c>
       <c r="AS38" s="9">
         <v>-1.32</v>
@@ -39293,16 +39296,16 @@
         <v>-1.07</v>
       </c>
       <c r="AU38" s="1">
-        <v>-1.8311736959617</v>
+        <v>-1.8502098959616999</v>
       </c>
       <c r="AV38">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="AW38" s="13">
+      <c r="AW38" s="11">
         <v>-0.97</v>
       </c>
       <c r="AX38">
-        <v>-1.5481</v>
+        <v>-1.6592743999999999</v>
       </c>
       <c r="AY38">
         <v>-1.21</v>
@@ -39311,7 +39314,7 @@
         <v>-1.25</v>
       </c>
       <c r="BA38" s="1">
-        <v>-1.5336764005872201</v>
+        <v>-1.5851809005872202</v>
       </c>
       <c r="BB38">
         <v>-1.25</v>
@@ -39389,16 +39392,16 @@
       <c r="U39" s="6">
         <v>-0.33368999999999999</v>
       </c>
-      <c r="V39" s="15">
+      <c r="V39" s="13">
         <v>7.6380000000000003E-2</v>
       </c>
       <c r="W39" s="6">
         <v>-0.22835</v>
       </c>
-      <c r="X39" s="15">
+      <c r="X39" s="13">
         <v>3.5699999999999998E-3</v>
       </c>
-      <c r="Y39" s="13">
+      <c r="Y39" s="11">
         <v>3.517E-2</v>
       </c>
       <c r="AA39" s="6">
@@ -39447,7 +39450,7 @@
         <v>5.2220000000000004</v>
       </c>
       <c r="AR39">
-        <v>-1.3514739459343801</v>
+        <v>-1.4228731459343802</v>
       </c>
       <c r="AS39" s="9">
         <v>-1.21</v>
@@ -39456,7 +39459,7 @@
         <v>-1.18</v>
       </c>
       <c r="AU39" s="1">
-        <v>-1.1554</v>
+        <v>-1.2803994000000001</v>
       </c>
       <c r="AV39">
         <v>-1.21</v>
@@ -39465,16 +39468,16 @@
         <v>-1.25</v>
       </c>
       <c r="AX39">
-        <v>-0.91900000000000004</v>
-      </c>
-      <c r="AY39" s="13">
+        <v>-1.2457872999999999</v>
+      </c>
+      <c r="AY39" s="11">
         <v>-1.33</v>
       </c>
-      <c r="AZ39" s="13">
+      <c r="AZ39" s="11">
         <v>-1.34</v>
       </c>
       <c r="BA39" s="1">
-        <v>-1.00104149966598</v>
+        <v>-1.22773369966598</v>
       </c>
       <c r="BB39">
         <v>-1.32</v>
@@ -39610,7 +39613,7 @@
         <v>4.9210000000000003</v>
       </c>
       <c r="AR40">
-        <v>-1.88364571071631</v>
+        <v>-1.9005327107163101</v>
       </c>
       <c r="AS40" s="9">
         <v>-1.21</v>
@@ -39619,7 +39622,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AU40" s="1">
-        <v>-1.82106901791464</v>
+        <v>-1.8445232179146402</v>
       </c>
       <c r="AV40">
         <v>-1.07</v>
@@ -39628,7 +39631,7 @@
         <v>-0.98</v>
       </c>
       <c r="AX40">
-        <v>-0.90300000000000002</v>
+        <v>-0.95845620000000009</v>
       </c>
       <c r="AY40">
         <v>-1.1299999999999999</v>
@@ -39637,7 +39640,7 @@
         <v>-1.2</v>
       </c>
       <c r="BA40" s="1">
-        <v>-1.9576271117464199</v>
+        <v>-1.98986941174642</v>
       </c>
       <c r="BB40">
         <v>-1.22</v>
@@ -39715,13 +39718,13 @@
       <c r="U41" s="6">
         <v>0.60577999999999999</v>
       </c>
-      <c r="V41" s="15">
+      <c r="V41" s="13">
         <v>-6.5300000000000002E-3</v>
       </c>
       <c r="W41" s="6">
         <v>-0.51549999999999996</v>
       </c>
-      <c r="X41" s="15">
+      <c r="X41" s="13">
         <v>-6.5339999999999995E-2</v>
       </c>
       <c r="Y41">
@@ -39773,7 +39776,7 @@
         <v>5.319</v>
       </c>
       <c r="AR41">
-        <v>-1.83878967949506</v>
+        <v>-1.85418457949506</v>
       </c>
       <c r="AS41" s="9">
         <v>-1.31</v>
@@ -39782,7 +39785,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AU41" s="1">
-        <v>-1.56474683486223</v>
+        <v>-1.60726393486223</v>
       </c>
       <c r="AV41">
         <v>-0.96</v>
@@ -39791,16 +39794,16 @@
         <v>-1.02</v>
       </c>
       <c r="AX41">
-        <v>-0.85820000000000007</v>
-      </c>
-      <c r="AY41" s="13">
+        <v>-1.0091977999999999</v>
+      </c>
+      <c r="AY41" s="11">
         <v>-1.29</v>
       </c>
-      <c r="AZ41" s="13">
+      <c r="AZ41" s="11">
         <v>-1.32</v>
       </c>
       <c r="BA41" s="1">
-        <v>-0.98804249768075203</v>
+        <v>-1.0873718976807518</v>
       </c>
       <c r="BB41">
         <v>-1.33</v>
@@ -39936,7 +39939,7 @@
         <v>3.9489999999999998</v>
       </c>
       <c r="AR42">
-        <v>-1.8622634806593701</v>
+        <v>-1.8802794806593699</v>
       </c>
       <c r="AS42" s="9">
         <v>-1.43</v>
@@ -39945,7 +39948,7 @@
         <v>-1.35</v>
       </c>
       <c r="AU42" s="1">
-        <v>-1.7984559835073199</v>
+        <v>-1.8261231835073197</v>
       </c>
       <c r="AV42">
         <v>-1.1200000000000001</v>
@@ -39954,7 +39957,7 @@
         <v>-1.08</v>
       </c>
       <c r="AX42">
-        <v>-1.7485999999999999</v>
+        <v>-1.8235916999999999</v>
       </c>
       <c r="AY42">
         <v>-1.34</v>
@@ -39963,7 +39966,7 @@
         <v>-1.44</v>
       </c>
       <c r="BA42" s="1">
-        <v>-1.61142881398718</v>
+        <v>-1.66508621398718</v>
       </c>
       <c r="BB42">
         <v>-1.28</v>
@@ -40099,7 +40102,7 @@
         <v>4.9109999999999996</v>
       </c>
       <c r="AR43">
-        <v>-1.87557143711816</v>
+        <v>-1.8922467371181602</v>
       </c>
       <c r="AS43" s="9">
         <v>-1.17</v>
@@ -40108,7 +40111,7 @@
         <v>-1</v>
       </c>
       <c r="AU43" s="1">
-        <v>-1.7721762360444999</v>
+        <v>-1.8041234360444998</v>
       </c>
       <c r="AV43">
         <v>-0.96</v>
@@ -40117,7 +40120,7 @@
         <v>-1.05</v>
       </c>
       <c r="AX43">
-        <v>-1.5775999999999999</v>
+        <v>-1.7681329999999997</v>
       </c>
       <c r="AY43">
         <v>-1.29</v>
@@ -40126,7 +40129,7 @@
         <v>-1.31</v>
       </c>
       <c r="BA43" s="1">
-        <v>-1.4483394403587799</v>
+        <v>-1.57550344035878</v>
       </c>
       <c r="BB43">
         <v>-1.3</v>
@@ -40262,7 +40265,7 @@
         <v>4.5359999999999996</v>
       </c>
       <c r="AR44">
-        <v>-1.8859335431180899</v>
+        <v>-1.9018459431180899</v>
       </c>
       <c r="AS44" s="9">
         <v>-1.5</v>
@@ -40271,7 +40274,7 @@
         <v>-1.35</v>
       </c>
       <c r="AU44" s="1">
-        <v>-1.82085518626163</v>
+        <v>-1.8460378862616298</v>
       </c>
       <c r="AV44">
         <v>-1.22</v>
@@ -40280,7 +40283,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AX44">
-        <v>-1.6311</v>
+        <v>-1.7346452000000001</v>
       </c>
       <c r="AY44">
         <v>-1.24</v>
@@ -40289,7 +40292,7 @@
         <v>-1.29</v>
       </c>
       <c r="BA44" s="1">
-        <v>-1.79011349318722</v>
+        <v>-1.8533701931872202</v>
       </c>
       <c r="BB44">
         <v>-1.25</v>
@@ -40425,7 +40428,7 @@
         <v>4.5869999999999997</v>
       </c>
       <c r="AR45">
-        <v>-1.8848019379177099</v>
+        <v>-1.9010157379177099</v>
       </c>
       <c r="AS45" s="9">
         <v>-1.27</v>
@@ -40434,7 +40437,7 @@
         <v>-1.18</v>
       </c>
       <c r="AU45" s="1">
-        <v>-1.8201967178260501</v>
+        <v>-1.8439956178260501</v>
       </c>
       <c r="AV45">
         <v>-1.1000000000000001</v>
@@ -40443,7 +40446,7 @@
         <v>-1.02</v>
       </c>
       <c r="AX45">
-        <v>-1.6717</v>
+        <v>-1.7341744000000001</v>
       </c>
       <c r="AY45">
         <v>-1.19</v>
@@ -40452,7 +40455,7 @@
         <v>-1.27</v>
       </c>
       <c r="BA45" s="1">
-        <v>-1.6136803602933301</v>
+        <v>-1.6543292602933299</v>
       </c>
       <c r="BB45">
         <v>-1.26</v>
@@ -40487,13 +40490,13 @@
       <c r="E46" s="6">
         <v>-2.8604166392080101E-2</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="11">
         <v>-8.8739999999999999E-2</v>
       </c>
       <c r="G46" s="6">
         <v>-3.5819999999999998E-2</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="11">
         <v>-0.12614</v>
       </c>
       <c r="I46" s="6">
@@ -40530,13 +40533,13 @@
       <c r="U46" s="6">
         <v>-4.99E-2</v>
       </c>
-      <c r="V46" s="15">
+      <c r="V46" s="13">
         <v>0.45222000000000001</v>
       </c>
       <c r="W46" s="6">
         <v>-0.25359999999999999</v>
       </c>
-      <c r="X46" s="15">
+      <c r="X46" s="13">
         <v>0.40239000000000003</v>
       </c>
       <c r="Y46">
@@ -40588,16 +40591,16 @@
         <v>1.98</v>
       </c>
       <c r="AR46">
-        <v>-1.9410286965421899</v>
-      </c>
-      <c r="AS46" s="18">
+        <v>-1.9526276965421898</v>
+      </c>
+      <c r="AS46" s="14">
         <v>-1</v>
       </c>
       <c r="AT46">
         <v>-1</v>
       </c>
       <c r="AU46" s="1">
-        <v>-1.9118251864473299</v>
+        <v>-1.9697654864473297</v>
       </c>
       <c r="AV46">
         <v>-1</v>
@@ -40606,16 +40609,16 @@
         <v>-1</v>
       </c>
       <c r="AX46">
-        <v>-1.6778</v>
-      </c>
-      <c r="AY46" s="13">
+        <v>-1.8207342999999998</v>
+      </c>
+      <c r="AY46" s="11">
         <v>-1.01</v>
       </c>
-      <c r="AZ46" s="13">
+      <c r="AZ46" s="11">
         <v>-1.01</v>
       </c>
       <c r="BA46" s="1">
-        <v>-1.86135507799483</v>
+        <v>-1.8895285779948299</v>
       </c>
       <c r="BB46">
         <v>-1.1200000000000001</v>
@@ -40629,7 +40632,7 @@
       <c r="BF46">
         <v>-9.7430000000000606E-3</v>
       </c>
-      <c r="BH46" s="13">
+      <c r="BH46" s="11">
         <v>91.870999999999995</v>
       </c>
       <c r="BI46" s="5"/>
@@ -40751,7 +40754,7 @@
         <v>3.3210000000000002</v>
       </c>
       <c r="AR47">
-        <v>-1.89483744657353</v>
+        <v>-1.9017996465735298</v>
       </c>
       <c r="AS47" s="9">
         <v>-1.67</v>
@@ -40760,7 +40763,7 @@
         <v>-1.65</v>
       </c>
       <c r="AU47" s="1">
-        <v>-1.8510921991698099</v>
+        <v>-1.86059249916981</v>
       </c>
       <c r="AV47">
         <v>-1.5</v>
@@ -40769,7 +40772,7 @@
         <v>-1.54</v>
       </c>
       <c r="AX47">
-        <v>-1.6677999999999999</v>
+        <v>-1.6847071</v>
       </c>
       <c r="AY47">
         <v>-1.5</v>
@@ -40778,7 +40781,7 @@
         <v>-1.42</v>
       </c>
       <c r="BA47" s="1">
-        <v>-1.7784865034269199</v>
+        <v>-1.7911004034269198</v>
       </c>
       <c r="BB47">
         <v>-1.49</v>
@@ -40914,7 +40917,7 @@
         <v>3.6920000000000002</v>
       </c>
       <c r="AR48">
-        <v>-1.90370944061379</v>
+        <v>-1.9159485406137899</v>
       </c>
       <c r="AS48" s="9">
         <v>-1.1200000000000001</v>
@@ -40923,7 +40926,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AU48" s="1">
-        <v>-1.8600820524217101</v>
+        <v>-1.8780606524217103</v>
       </c>
       <c r="AV48">
         <v>-1.02</v>
@@ -40932,7 +40935,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AX48">
-        <v>-1.8837999999999999</v>
+        <v>-1.9283041999999999</v>
       </c>
       <c r="AY48">
         <v>-1.1200000000000001</v>
@@ -40941,7 +40944,7 @@
         <v>-1.19</v>
       </c>
       <c r="BA48" s="1">
-        <v>-1.7697917683929301</v>
+        <v>-1.80030046839293</v>
       </c>
       <c r="BB48">
         <v>-1.1000000000000001</v>
@@ -40973,7 +40976,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5563FF0C-5BB8-4FAA-8AF4-94C243B80F11}">
   <dimension ref="A1:AK63"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -41803,7 +41806,7 @@
         <v>1.6970799999999999</v>
       </c>
       <c r="U11">
-        <v>1.63636</v>
+        <v>1.4366000000000001</v>
       </c>
       <c r="V11">
         <v>1.5765899999999999</v>
@@ -41818,7 +41821,7 @@
         <v>1.72082</v>
       </c>
       <c r="AA11">
-        <v>1.63636</v>
+        <v>1.4366000000000001</v>
       </c>
       <c r="AB11">
         <v>1.5262199999999999</v>
@@ -42736,7 +42739,7 @@
         <v>1.24682</v>
       </c>
       <c r="U25">
-        <v>1.4366000000000001</v>
+        <v>1.2368399999999999</v>
       </c>
       <c r="V25">
         <v>1.1994</v>
@@ -42751,7 +42754,7 @@
         <v>1.1541399999999999</v>
       </c>
       <c r="AA25">
-        <v>1.4366000000000001</v>
+        <v>1.2368399999999999</v>
       </c>
       <c r="AB25">
         <v>1.38422</v>
@@ -43746,7 +43749,7 @@
       <c r="S39">
         <v>-0.45025999999999999</v>
       </c>
-      <c r="U39" s="13">
+      <c r="U39" s="11">
         <v>-0.19975999999999999</v>
       </c>
       <c r="V39">
@@ -43761,7 +43764,7 @@
       <c r="Y39">
         <v>-0.56667999999999996</v>
       </c>
-      <c r="AA39" s="13">
+      <c r="AA39" s="11">
         <v>-0.19975999999999999</v>
       </c>
       <c r="AB39">
@@ -45567,7 +45570,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4750BC-1188-421B-BE5C-F526F345B7FA}">
   <dimension ref="A1:AH12"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="C1" t="s">

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F53CDA-4CE5-4A0D-8274-C1185BE13507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE921BF-A5BD-41A4-AAF5-D596067F88DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE921BF-A5BD-41A4-AAF5-D596067F88DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD551F9-550C-42BA-B6B4-04FA02A85169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="324">
   <si>
     <t>B3LYP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1529,10 +1529,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE162"/>
+  <dimension ref="A1:BF162"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
@@ -1581,7 +1581,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1665,7 +1665,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1818,10 +1818,13 @@
         <v>2</v>
       </c>
       <c r="BE3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1976,8 +1979,11 @@
       <c r="BE4">
         <v>0</v>
       </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -2132,8 +2138,11 @@
       <c r="BE5">
         <v>0</v>
       </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -2286,10 +2295,13 @@
         <v>-1.93</v>
       </c>
       <c r="BE6">
+        <v>95.186000000000007</v>
+      </c>
+      <c r="BF6">
         <v>96.572000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -2444,8 +2456,11 @@
       <c r="BE7">
         <v>0</v>
       </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -2598,10 +2613,13 @@
         <v>-1.53</v>
       </c>
       <c r="BE8">
+        <v>94.39</v>
+      </c>
+      <c r="BF8">
         <v>95.897000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -2756,8 +2774,11 @@
       <c r="BE9">
         <v>0</v>
       </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -2910,10 +2931,13 @@
         <v>-1.93</v>
       </c>
       <c r="BE10">
+        <v>95.040999999999997</v>
+      </c>
+      <c r="BF10">
         <v>96.397999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
@@ -3066,10 +3090,13 @@
         <v>-1.7</v>
       </c>
       <c r="BE11">
+        <v>95.754999999999995</v>
+      </c>
+      <c r="BF11">
         <v>96.918999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -3222,10 +3249,13 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BE12">
+        <v>87.540999999999997</v>
+      </c>
+      <c r="BF12">
         <v>84.253</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
@@ -3378,10 +3408,13 @@
         <v>-1.75</v>
       </c>
       <c r="BE13">
+        <v>95.561999999999998</v>
+      </c>
+      <c r="BF13">
         <v>96.626999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -3534,10 +3567,13 @@
         <v>-0.99</v>
       </c>
       <c r="BE14">
+        <v>96.055999999999997</v>
+      </c>
+      <c r="BF14">
         <v>97.194999999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>21</v>
       </c>
@@ -3690,10 +3726,13 @@
         <v>-1.32</v>
       </c>
       <c r="BE15">
+        <v>92.221999999999994</v>
+      </c>
+      <c r="BF15">
         <v>93.626999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -3846,10 +3885,13 @@
         <v>-1.43</v>
       </c>
       <c r="BE16">
+        <v>93.965999999999994</v>
+      </c>
+      <c r="BF16">
         <v>95.197000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -4002,10 +4044,13 @@
         <v>-0.82</v>
       </c>
       <c r="BE17">
+        <v>92.007999999999996</v>
+      </c>
+      <c r="BF17">
         <v>91.387</v>
       </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
@@ -4158,10 +4203,13 @@
         <v>-1.41</v>
       </c>
       <c r="BE18">
+        <v>94.042000000000002</v>
+      </c>
+      <c r="BF18">
         <v>95.245999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
@@ -4314,10 +4362,13 @@
         <v>-0.69</v>
       </c>
       <c r="BE19">
+        <v>92.716999999999999</v>
+      </c>
+      <c r="BF19">
         <v>92.700999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
@@ -4470,10 +4521,13 @@
         <v>-0.99</v>
       </c>
       <c r="BE20">
+        <v>96.096999999999994</v>
+      </c>
+      <c r="BF20">
         <v>97.316999999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
@@ -4628,8 +4682,11 @@
       <c r="BE21">
         <v>0</v>
       </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -4784,8 +4841,11 @@
       <c r="BE22">
         <v>0</v>
       </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -4940,8 +5000,11 @@
       <c r="BE23">
         <v>0</v>
       </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
@@ -5096,8 +5159,11 @@
       <c r="BE24">
         <v>0</v>
       </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -5252,8 +5318,11 @@
       <c r="BE25">
         <v>0</v>
       </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -5408,8 +5477,11 @@
       <c r="BE26">
         <v>0</v>
       </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>33</v>
       </c>
@@ -5562,10 +5634,13 @@
         <v>-1.39</v>
       </c>
       <c r="BE27">
+        <v>95.412000000000006</v>
+      </c>
+      <c r="BF27">
         <v>96.733000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>34</v>
       </c>
@@ -5718,10 +5793,13 @@
         <v>-1.38</v>
       </c>
       <c r="BE28">
+        <v>95.4</v>
+      </c>
+      <c r="BF28">
         <v>96.722999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
@@ -5874,10 +5952,13 @@
         <v>-1.2</v>
       </c>
       <c r="BE29">
+        <v>95.355999999999995</v>
+      </c>
+      <c r="BF29">
         <v>96.653999999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>36</v>
       </c>
@@ -6030,10 +6111,13 @@
         <v>-1.3</v>
       </c>
       <c r="BE30">
+        <v>95.281999999999996</v>
+      </c>
+      <c r="BF30">
         <v>96.588999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
@@ -6186,10 +6270,13 @@
         <v>-1.06</v>
       </c>
       <c r="BE31">
+        <v>94.88</v>
+      </c>
+      <c r="BF31">
         <v>96.195999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
@@ -6342,10 +6429,13 @@
         <v>-1.01</v>
       </c>
       <c r="BE32">
+        <v>95.78</v>
+      </c>
+      <c r="BF32">
         <v>97.028000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
@@ -6498,10 +6588,13 @@
         <v>-1.2</v>
       </c>
       <c r="BE33">
+        <v>95.61</v>
+      </c>
+      <c r="BF33">
         <v>96.915000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -6654,10 +6747,13 @@
         <v>-1.07</v>
       </c>
       <c r="BE34">
+        <v>95.730999999999995</v>
+      </c>
+      <c r="BF34">
         <v>96.963999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -6810,10 +6906,13 @@
         <v>-1.08</v>
       </c>
       <c r="BE35">
+        <v>95.834000000000003</v>
+      </c>
+      <c r="BF35">
         <v>97.061000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
@@ -6966,10 +7065,13 @@
         <v>-1.4</v>
       </c>
       <c r="BE36">
+        <v>95.344999999999999</v>
+      </c>
+      <c r="BF36">
         <v>96.682000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>43</v>
       </c>
@@ -7122,10 +7224,13 @@
         <v>-1.4</v>
       </c>
       <c r="BE37">
+        <v>95.429000000000002</v>
+      </c>
+      <c r="BF37">
         <v>96.75</v>
       </c>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
@@ -7278,10 +7383,13 @@
         <v>-1.08</v>
       </c>
       <c r="BE38">
+        <v>95.052000000000007</v>
+      </c>
+      <c r="BF38">
         <v>96.406999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>45</v>
       </c>
@@ -7434,10 +7542,13 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BE39">
+        <v>94.39</v>
+      </c>
+      <c r="BF39">
         <v>95.704999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -7590,10 +7701,13 @@
         <v>-1.4</v>
       </c>
       <c r="BE40">
+        <v>95.405000000000001</v>
+      </c>
+      <c r="BF40">
         <v>96.744</v>
       </c>
     </row>
-    <row r="41" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>47</v>
       </c>
@@ -7746,10 +7860,13 @@
         <v>-0.9</v>
       </c>
       <c r="BE41">
+        <v>93.025999999999996</v>
+      </c>
+      <c r="BF41">
         <v>94.322999999999993</v>
       </c>
     </row>
-    <row r="42" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>48</v>
       </c>
@@ -7902,10 +8019,13 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="BE42">
+        <v>95.766000000000005</v>
+      </c>
+      <c r="BF42">
         <v>97.058999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>49</v>
       </c>
@@ -8058,10 +8178,13 @@
         <v>-0.98</v>
       </c>
       <c r="BE43">
+        <v>95.18</v>
+      </c>
+      <c r="BF43">
         <v>96.501000000000005</v>
       </c>
     </row>
-    <row r="44" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>50</v>
       </c>
@@ -8214,10 +8337,13 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BE44">
+        <v>93.963999999999999</v>
+      </c>
+      <c r="BF44">
         <v>95.263000000000005</v>
       </c>
     </row>
-    <row r="45" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>51</v>
       </c>
@@ -8370,10 +8496,13 @@
         <v>-1.21</v>
       </c>
       <c r="BE45">
+        <v>94.438999999999993</v>
+      </c>
+      <c r="BF45">
         <v>95.725999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>52</v>
       </c>
@@ -8526,10 +8655,13 @@
         <v>-1</v>
       </c>
       <c r="BE46">
+        <v>95.736999999999995</v>
+      </c>
+      <c r="BF46">
         <v>97.012</v>
       </c>
     </row>
-    <row r="47" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>53</v>
       </c>
@@ -8682,10 +8814,13 @@
         <v>-0.98</v>
       </c>
       <c r="BE47">
+        <v>95.429000000000002</v>
+      </c>
+      <c r="BF47">
         <v>96.704999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>54</v>
       </c>
@@ -8838,10 +8973,13 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="BE48">
+        <v>94.179000000000002</v>
+      </c>
+      <c r="BF48">
         <v>95.501000000000005</v>
       </c>
     </row>
-    <row r="49" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
@@ -8994,10 +9132,13 @@
         <v>-1.03</v>
       </c>
       <c r="BE49">
+        <v>95.611000000000004</v>
+      </c>
+      <c r="BF49">
         <v>96.917000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>56</v>
       </c>
@@ -9150,10 +9291,13 @@
         <v>-1.01</v>
       </c>
       <c r="BE50">
+        <v>95.165999999999997</v>
+      </c>
+      <c r="BF50">
         <v>96.474000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>57</v>
       </c>
@@ -9306,10 +9450,13 @@
         <v>-1.4</v>
       </c>
       <c r="BE51">
+        <v>95.462999999999994</v>
+      </c>
+      <c r="BF51">
         <v>96.813000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>58</v>
       </c>
@@ -9462,10 +9609,13 @@
         <v>-1.07</v>
       </c>
       <c r="BE52">
+        <v>95.406999999999996</v>
+      </c>
+      <c r="BF52">
         <v>96.751999999999995</v>
       </c>
     </row>
-    <row r="53" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>59</v>
       </c>
@@ -9618,10 +9768,13 @@
         <v>-1.67</v>
       </c>
       <c r="BE53">
+        <v>95.314999999999998</v>
+      </c>
+      <c r="BF53">
         <v>96.716999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>60</v>
       </c>
@@ -9774,10 +9927,13 @@
         <v>-1.61</v>
       </c>
       <c r="BE54">
+        <v>95.475999999999999</v>
+      </c>
+      <c r="BF54">
         <v>96.856999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
@@ -9930,10 +10086,13 @@
         <v>-1.65</v>
       </c>
       <c r="BE55">
+        <v>95.316999999999993</v>
+      </c>
+      <c r="BF55">
         <v>96.703000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>62</v>
       </c>
@@ -10086,10 +10245,13 @@
         <v>-1.56</v>
       </c>
       <c r="BE56">
+        <v>95.438999999999993</v>
+      </c>
+      <c r="BF56">
         <v>96.798000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>63</v>
       </c>
@@ -10242,10 +10404,13 @@
         <v>-1.44</v>
       </c>
       <c r="BE57">
+        <v>95.096999999999994</v>
+      </c>
+      <c r="BF57">
         <v>96.554000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
@@ -10398,10 +10563,13 @@
         <v>-1.34</v>
       </c>
       <c r="BE58">
+        <v>95.024000000000001</v>
+      </c>
+      <c r="BF58">
         <v>96.466999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>65</v>
       </c>
@@ -10554,10 +10722,13 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BE59">
+        <v>94.668000000000006</v>
+      </c>
+      <c r="BF59">
         <v>96.075999999999993</v>
       </c>
     </row>
-    <row r="60" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>66</v>
       </c>
@@ -10710,10 +10881,13 @@
         <v>-1.08</v>
       </c>
       <c r="BE60">
+        <v>93.22</v>
+      </c>
+      <c r="BF60">
         <v>94.683000000000007</v>
       </c>
     </row>
-    <row r="61" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>67</v>
       </c>
@@ -10866,10 +11040,13 @@
         <v>-1.2</v>
       </c>
       <c r="BE61">
+        <v>92.861000000000004</v>
+      </c>
+      <c r="BF61">
         <v>94.331999999999994</v>
       </c>
     </row>
-    <row r="62" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>68</v>
       </c>
@@ -11022,10 +11199,13 @@
         <v>-0.97</v>
       </c>
       <c r="BE62">
+        <v>93.867999999999995</v>
+      </c>
+      <c r="BF62">
         <v>95.331999999999994</v>
       </c>
     </row>
-    <row r="63" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>69</v>
       </c>
@@ -11178,10 +11358,13 @@
         <v>-0.96</v>
       </c>
       <c r="BE63">
+        <v>93.861000000000004</v>
+      </c>
+      <c r="BF63">
         <v>95.32</v>
       </c>
     </row>
-    <row r="64" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>70</v>
       </c>
@@ -11334,10 +11517,13 @@
         <v>-1.22</v>
       </c>
       <c r="BE64">
+        <v>94.77</v>
+      </c>
+      <c r="BF64">
         <v>96.227000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>71</v>
       </c>
@@ -11490,10 +11676,13 @@
         <v>-1.54</v>
       </c>
       <c r="BE65">
+        <v>90.094999999999999</v>
+      </c>
+      <c r="BF65">
         <v>91.584999999999994</v>
       </c>
     </row>
-    <row r="66" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>72</v>
       </c>
@@ -11646,10 +11835,13 @@
         <v>-1.65</v>
       </c>
       <c r="BE66">
+        <v>89.960999999999999</v>
+      </c>
+      <c r="BF66">
         <v>91.77</v>
       </c>
     </row>
-    <row r="67" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>73</v>
       </c>
@@ -11802,10 +11994,13 @@
         <v>-1.23</v>
       </c>
       <c r="BE67">
+        <v>91.387</v>
+      </c>
+      <c r="BF67">
         <v>92.745999999999995</v>
       </c>
     </row>
-    <row r="68" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>74</v>
       </c>
@@ -11958,10 +12153,13 @@
         <v>-1.2</v>
       </c>
       <c r="BE68">
+        <v>91.498000000000005</v>
+      </c>
+      <c r="BF68">
         <v>92.820999999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>75</v>
       </c>
@@ -12114,10 +12312,13 @@
         <v>-1.31</v>
       </c>
       <c r="BE69">
+        <v>94.936999999999998</v>
+      </c>
+      <c r="BF69">
         <v>96.444999999999993</v>
       </c>
     </row>
-    <row r="70" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>76</v>
       </c>
@@ -12270,10 +12471,13 @@
         <v>-0.91</v>
       </c>
       <c r="BE70">
+        <v>95.575000000000003</v>
+      </c>
+      <c r="BF70">
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>77</v>
       </c>
@@ -12426,10 +12630,13 @@
         <v>-1.38</v>
       </c>
       <c r="BE71">
+        <v>80.56</v>
+      </c>
+      <c r="BF71">
         <v>81.06</v>
       </c>
     </row>
-    <row r="72" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>78</v>
       </c>
@@ -12582,10 +12789,13 @@
         <v>-1.23</v>
       </c>
       <c r="BE72">
+        <v>95.397000000000006</v>
+      </c>
+      <c r="BF72">
         <v>96.841999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>79</v>
       </c>
@@ -12738,10 +12948,13 @@
         <v>-1.29</v>
       </c>
       <c r="BE73">
+        <v>95.349000000000004</v>
+      </c>
+      <c r="BF73">
         <v>96.784000000000006</v>
       </c>
     </row>
-    <row r="74" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
@@ -12894,10 +13107,13 @@
         <v>-1.58</v>
       </c>
       <c r="BE74">
+        <v>95.400999999999996</v>
+      </c>
+      <c r="BF74">
         <v>96.372</v>
       </c>
     </row>
-    <row r="75" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>81</v>
       </c>
@@ -13050,10 +13266,13 @@
         <v>-1.38</v>
       </c>
       <c r="BE75">
+        <v>95.498999999999995</v>
+      </c>
+      <c r="BF75">
         <v>96.534000000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>82</v>
       </c>
@@ -13208,8 +13427,11 @@
       <c r="BE76">
         <v>0</v>
       </c>
+      <c r="BF76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>83</v>
       </c>
@@ -13362,10 +13584,13 @@
         <v>-1.33</v>
       </c>
       <c r="BE77">
+        <v>73.734999999999999</v>
+      </c>
+      <c r="BF77">
         <v>63.398000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>84</v>
       </c>
@@ -13518,10 +13743,13 @@
         <v>-1.54</v>
       </c>
       <c r="BE78">
+        <v>90.22</v>
+      </c>
+      <c r="BF78">
         <v>89.105000000000004</v>
       </c>
     </row>
-    <row r="79" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>85</v>
       </c>
@@ -13674,10 +13902,13 @@
         <v>-1.54</v>
       </c>
       <c r="BE79">
+        <v>82.977999999999994</v>
+      </c>
+      <c r="BF79">
         <v>80.531999999999996</v>
       </c>
     </row>
-    <row r="80" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>86</v>
       </c>
@@ -13832,8 +14063,11 @@
       <c r="BE80">
         <v>0</v>
       </c>
+      <c r="BF80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>87</v>
       </c>
@@ -13986,10 +14220,13 @@
         <v>-1.45</v>
       </c>
       <c r="BE81">
+        <v>96.394999999999996</v>
+      </c>
+      <c r="BF81">
         <v>97.462000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>88</v>
       </c>
@@ -14142,10 +14379,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE82">
+        <v>96.448999999999998</v>
+      </c>
+      <c r="BF82">
         <v>97.465000000000003</v>
       </c>
     </row>
-    <row r="83" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>89</v>
       </c>
@@ -14300,8 +14540,11 @@
       <c r="BE83">
         <v>0</v>
       </c>
+      <c r="BF83">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>90</v>
       </c>
@@ -14456,8 +14699,11 @@
       <c r="BE84">
         <v>0</v>
       </c>
+      <c r="BF84">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>91</v>
       </c>
@@ -14610,10 +14856,13 @@
         <v>-1.28</v>
       </c>
       <c r="BE85">
+        <v>75.397999999999996</v>
+      </c>
+      <c r="BF85">
         <v>66.903999999999996</v>
       </c>
     </row>
-    <row r="86" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>92</v>
       </c>
@@ -14766,10 +15015,13 @@
         <v>-1.74</v>
       </c>
       <c r="BE86">
+        <v>96.355000000000004</v>
+      </c>
+      <c r="BF86">
         <v>97.394999999999996</v>
       </c>
     </row>
-    <row r="87" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>93</v>
       </c>
@@ -14922,10 +15174,13 @@
         <v>-1.66</v>
       </c>
       <c r="BE87">
+        <v>92.302999999999997</v>
+      </c>
+      <c r="BF87">
         <v>93.507999999999996</v>
       </c>
     </row>
-    <row r="88" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>94</v>
       </c>
@@ -15078,10 +15333,13 @@
         <v>-1.6</v>
       </c>
       <c r="BE88">
+        <v>88.492999999999995</v>
+      </c>
+      <c r="BF88">
         <v>88.881</v>
       </c>
     </row>
-    <row r="89" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>95</v>
       </c>
@@ -15234,10 +15492,13 @@
         <v>-1.63</v>
       </c>
       <c r="BE89">
+        <v>96.91</v>
+      </c>
+      <c r="BF89">
         <v>97.944999999999993</v>
       </c>
     </row>
-    <row r="90" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>96</v>
       </c>
@@ -15390,10 +15651,13 @@
         <v>-1.8</v>
       </c>
       <c r="BE90">
+        <v>95.441999999999993</v>
+      </c>
+      <c r="BF90">
         <v>96.581999999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>97</v>
       </c>
@@ -15546,10 +15810,13 @@
         <v>-1.65</v>
       </c>
       <c r="BE91">
+        <v>96.813999999999993</v>
+      </c>
+      <c r="BF91">
         <v>97.831000000000003</v>
       </c>
     </row>
-    <row r="92" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>98</v>
       </c>
@@ -15702,10 +15969,13 @@
         <v>-1.82</v>
       </c>
       <c r="BE92">
+        <v>95.808999999999997</v>
+      </c>
+      <c r="BF92">
         <v>96.953000000000003</v>
       </c>
     </row>
-    <row r="93" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>99</v>
       </c>
@@ -15858,10 +16128,13 @@
         <v>-1.66</v>
       </c>
       <c r="BE93">
+        <v>96.756</v>
+      </c>
+      <c r="BF93">
         <v>97.789000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>100</v>
       </c>
@@ -16014,10 +16287,13 @@
         <v>-0.96</v>
       </c>
       <c r="BE94">
+        <v>97.21</v>
+      </c>
+      <c r="BF94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>101</v>
       </c>
@@ -16170,10 +16446,13 @@
         <v>-1.51</v>
       </c>
       <c r="BE95">
+        <v>96.212000000000003</v>
+      </c>
+      <c r="BF95">
         <v>97.328000000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>102</v>
       </c>
@@ -16326,10 +16605,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE96">
+        <v>96.492000000000004</v>
+      </c>
+      <c r="BF96">
         <v>97.51</v>
       </c>
     </row>
-    <row r="97" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>103</v>
       </c>
@@ -16484,8 +16766,11 @@
       <c r="BE97">
         <v>0</v>
       </c>
+      <c r="BF97">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>104</v>
       </c>
@@ -16638,10 +16923,13 @@
         <v>-1.51</v>
       </c>
       <c r="BE98">
+        <v>95.522999999999996</v>
+      </c>
+      <c r="BF98">
         <v>96.671999999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>105</v>
       </c>
@@ -16796,8 +17084,11 @@
       <c r="BE99">
         <v>0</v>
       </c>
+      <c r="BF99">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>106</v>
       </c>
@@ -16950,10 +17241,13 @@
         <v>-1.73</v>
       </c>
       <c r="BE100">
+        <v>93.927999999999997</v>
+      </c>
+      <c r="BF100">
         <v>95.256</v>
       </c>
     </row>
-    <row r="101" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>107</v>
       </c>
@@ -17106,10 +17400,13 @@
         <v>-0.89</v>
       </c>
       <c r="BE101">
+        <v>7.98</v>
+      </c>
+      <c r="BF101">
         <v>2.4279999999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>108</v>
       </c>
@@ -17262,10 +17559,13 @@
         <v>-0.84</v>
       </c>
       <c r="BE102">
+        <v>4.0750000000000002</v>
+      </c>
+      <c r="BF102">
         <v>1.6479999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>109</v>
       </c>
@@ -17418,10 +17718,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE103">
+        <v>94.873000000000005</v>
+      </c>
+      <c r="BF103">
         <v>95.875</v>
       </c>
     </row>
-    <row r="104" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>110</v>
       </c>
@@ -17574,10 +17877,13 @@
         <v>-0.78</v>
       </c>
       <c r="BE104">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="BF104">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>111</v>
       </c>
@@ -17730,10 +18036,13 @@
         <v>-1.17</v>
       </c>
       <c r="BE105">
+        <v>95.843999999999994</v>
+      </c>
+      <c r="BF105">
         <v>97.052999999999997</v>
       </c>
     </row>
-    <row r="106" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>112</v>
       </c>
@@ -17886,10 +18195,13 @@
         <v>-1.28</v>
       </c>
       <c r="BE106">
+        <v>95.5</v>
+      </c>
+      <c r="BF106">
         <v>96.798000000000002</v>
       </c>
     </row>
-    <row r="107" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>113</v>
       </c>
@@ -18042,10 +18354,13 @@
         <v>-1.29</v>
       </c>
       <c r="BE107">
+        <v>95.507999999999996</v>
+      </c>
+      <c r="BF107">
         <v>96.819000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>114</v>
       </c>
@@ -18198,10 +18513,13 @@
         <v>-1.86</v>
       </c>
       <c r="BE108">
+        <v>95.212000000000003</v>
+      </c>
+      <c r="BF108">
         <v>96.742000000000004</v>
       </c>
     </row>
-    <row r="109" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>115</v>
       </c>
@@ -18354,10 +18672,13 @@
         <v>-1.8</v>
       </c>
       <c r="BE109">
+        <v>95.355000000000004</v>
+      </c>
+      <c r="BF109">
         <v>96.802000000000007</v>
       </c>
     </row>
-    <row r="110" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>116</v>
       </c>
@@ -18510,10 +18831,13 @@
         <v>-0.98</v>
       </c>
       <c r="BE110">
+        <v>95.784000000000006</v>
+      </c>
+      <c r="BF110">
         <v>96.98</v>
       </c>
     </row>
-    <row r="111" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>117</v>
       </c>
@@ -18666,10 +18990,13 @@
         <v>-1.22</v>
       </c>
       <c r="BE111">
+        <v>95.688999999999993</v>
+      </c>
+      <c r="BF111">
         <v>96.988</v>
       </c>
     </row>
-    <row r="112" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>118</v>
       </c>
@@ -18822,10 +19149,13 @@
         <v>-1.63</v>
       </c>
       <c r="BE112">
+        <v>94.212999999999994</v>
+      </c>
+      <c r="BF112">
         <v>95.173000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>119</v>
       </c>
@@ -18978,10 +19308,13 @@
         <v>-1.67</v>
       </c>
       <c r="BE113">
+        <v>94.79</v>
+      </c>
+      <c r="BF113">
         <v>95.935000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>120</v>
       </c>
@@ -19134,10 +19467,13 @@
         <v>-1.57</v>
       </c>
       <c r="BE114">
+        <v>94.727999999999994</v>
+      </c>
+      <c r="BF114">
         <v>95.968000000000004</v>
       </c>
     </row>
-    <row r="115" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>121</v>
       </c>
@@ -19290,10 +19626,13 @@
         <v>-0.88</v>
       </c>
       <c r="BE115">
+        <v>92.593000000000004</v>
+      </c>
+      <c r="BF115">
         <v>93.992999999999995</v>
       </c>
     </row>
-    <row r="116" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>122</v>
       </c>
@@ -19446,10 +19785,13 @@
         <v>-1.32</v>
       </c>
       <c r="BE116">
+        <v>94.594999999999999</v>
+      </c>
+      <c r="BF116">
         <v>96.143000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>123</v>
       </c>
@@ -19602,10 +19944,13 @@
         <v>-1.83</v>
       </c>
       <c r="BE117">
+        <v>95.283000000000001</v>
+      </c>
+      <c r="BF117">
         <v>96.18</v>
       </c>
     </row>
-    <row r="118" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>124</v>
       </c>
@@ -19758,10 +20103,13 @@
         <v>-1.65</v>
       </c>
       <c r="BE118">
+        <v>93.215000000000003</v>
+      </c>
+      <c r="BF118">
         <v>93.736000000000004</v>
       </c>
     </row>
-    <row r="119" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>125</v>
       </c>
@@ -19914,10 +20262,13 @@
         <v>-0.7</v>
       </c>
       <c r="BE119">
+        <v>72.897000000000006</v>
+      </c>
+      <c r="BF119">
         <v>67.337999999999994</v>
       </c>
     </row>
-    <row r="120" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>126</v>
       </c>
@@ -20070,10 +20421,13 @@
         <v>-0.86</v>
       </c>
       <c r="BE120">
+        <v>90.834000000000003</v>
+      </c>
+      <c r="BF120">
         <v>90.715000000000003</v>
       </c>
     </row>
-    <row r="121" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>127</v>
       </c>
@@ -20226,10 +20580,13 @@
         <v>-1.59</v>
       </c>
       <c r="BE121">
+        <v>95.358000000000004</v>
+      </c>
+      <c r="BF121">
         <v>96.53</v>
       </c>
     </row>
-    <row r="122" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>128</v>
       </c>
@@ -20382,10 +20739,13 @@
         <v>-1.08</v>
       </c>
       <c r="BE122">
+        <v>93.709000000000003</v>
+      </c>
+      <c r="BF122">
         <v>94.429000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>129</v>
       </c>
@@ -20538,10 +20898,13 @@
         <v>-0.73</v>
       </c>
       <c r="BE123">
+        <v>93.816999999999993</v>
+      </c>
+      <c r="BF123">
         <v>66.159000000000006</v>
       </c>
     </row>
-    <row r="124" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>130</v>
       </c>
@@ -20694,10 +21057,13 @@
         <v>-1.07</v>
       </c>
       <c r="BE124">
+        <v>2.2919999999999998</v>
+      </c>
+      <c r="BF124">
         <v>1.821</v>
       </c>
     </row>
-    <row r="125" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>131</v>
       </c>
@@ -20850,10 +21216,13 @@
         <v>-1.59</v>
       </c>
       <c r="BE125">
+        <v>96.418000000000006</v>
+      </c>
+      <c r="BF125">
         <v>97.268000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>132</v>
       </c>
@@ -21006,10 +21375,13 @@
         <v>-1.53</v>
       </c>
       <c r="BE126">
+        <v>95.768000000000001</v>
+      </c>
+      <c r="BF126">
         <v>96.617999999999995</v>
       </c>
     </row>
-    <row r="127" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>133</v>
       </c>
@@ -21162,10 +21534,13 @@
         <v>-1.27</v>
       </c>
       <c r="BE127">
+        <v>95.625</v>
+      </c>
+      <c r="BF127">
         <v>96.738</v>
       </c>
     </row>
-    <row r="128" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>134</v>
       </c>
@@ -21318,10 +21693,13 @@
         <v>-1.28</v>
       </c>
       <c r="BE128">
+        <v>94.819000000000003</v>
+      </c>
+      <c r="BF128">
         <v>95.841999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>135</v>
       </c>
@@ -21474,10 +21852,13 @@
         <v>-1.04</v>
       </c>
       <c r="BE129">
+        <v>96.161000000000001</v>
+      </c>
+      <c r="BF129">
         <v>97.171999999999997</v>
       </c>
     </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>136</v>
       </c>
@@ -21630,10 +22011,13 @@
         <v>-1.06</v>
       </c>
       <c r="BE130">
+        <v>96.031999999999996</v>
+      </c>
+      <c r="BF130">
         <v>97.1</v>
       </c>
     </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>137</v>
       </c>
@@ -21786,10 +22170,13 @@
         <v>-1.41</v>
       </c>
       <c r="BE131">
+        <v>90.013999999999996</v>
+      </c>
+      <c r="BF131">
         <v>89.52</v>
       </c>
     </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>138</v>
       </c>
@@ -21942,10 +22329,13 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BE132">
+        <v>91.733000000000004</v>
+      </c>
+      <c r="BF132">
         <v>92.106999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>139</v>
       </c>
@@ -22098,10 +22488,13 @@
         <v>-1.56</v>
       </c>
       <c r="BE133">
+        <v>96.221000000000004</v>
+      </c>
+      <c r="BF133">
         <v>97.141000000000005</v>
       </c>
     </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>140</v>
       </c>
@@ -22254,10 +22647,13 @@
         <v>-0.96</v>
       </c>
       <c r="BE134">
+        <v>45.207999999999998</v>
+      </c>
+      <c r="BF134">
         <v>21.042000000000002</v>
       </c>
     </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>141</v>
       </c>
@@ -22410,10 +22806,13 @@
         <v>-1.48</v>
       </c>
       <c r="BE135">
+        <v>90.156999999999996</v>
+      </c>
+      <c r="BF135">
         <v>89.100999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>142</v>
       </c>
@@ -22566,10 +22965,13 @@
         <v>-0.82</v>
       </c>
       <c r="BE136">
+        <v>96.311000000000007</v>
+      </c>
+      <c r="BF136">
         <v>97.44</v>
       </c>
     </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>143</v>
       </c>
@@ -22722,10 +23124,13 @@
         <v>-0.97</v>
       </c>
       <c r="BE137">
+        <v>8.7769999999999992</v>
+      </c>
+      <c r="BF137">
         <v>1.8660000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>144</v>
       </c>
@@ -22878,10 +23283,13 @@
         <v>-1.02</v>
       </c>
       <c r="BE138">
+        <v>94.375</v>
+      </c>
+      <c r="BF138">
         <v>95.756</v>
       </c>
     </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>145</v>
       </c>
@@ -23034,10 +23442,13 @@
         <v>-0.93</v>
       </c>
       <c r="BE139">
+        <v>94.41</v>
+      </c>
+      <c r="BF139">
         <v>95.820999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>146</v>
       </c>
@@ -23190,10 +23601,13 @@
         <v>-1.3</v>
       </c>
       <c r="BE140">
+        <v>93.412999999999997</v>
+      </c>
+      <c r="BF140">
         <v>94.78</v>
       </c>
     </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>147</v>
       </c>
@@ -23346,10 +23760,13 @@
         <v>-0.96</v>
       </c>
       <c r="BE141">
+        <v>94.073999999999998</v>
+      </c>
+      <c r="BF141">
         <v>95.516999999999996</v>
       </c>
     </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>148</v>
       </c>
@@ -23502,10 +23919,13 @@
         <v>-1.45</v>
       </c>
       <c r="BE142">
+        <v>92.603999999999999</v>
+      </c>
+      <c r="BF142">
         <v>93.954999999999998</v>
       </c>
     </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>149</v>
       </c>
@@ -23658,10 +24078,13 @@
         <v>-1.31</v>
       </c>
       <c r="BE143">
+        <v>94.984999999999999</v>
+      </c>
+      <c r="BF143">
         <v>96.305999999999997</v>
       </c>
     </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>150</v>
       </c>
@@ -23814,10 +24237,13 @@
         <v>-1.31</v>
       </c>
       <c r="BE144">
+        <v>95.081000000000003</v>
+      </c>
+      <c r="BF144">
         <v>96.408000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>151</v>
       </c>
@@ -23970,10 +24396,13 @@
         <v>-1.44</v>
       </c>
       <c r="BE145">
+        <v>95.302000000000007</v>
+      </c>
+      <c r="BF145">
         <v>96.652000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>152</v>
       </c>
@@ -24126,10 +24555,13 @@
         <v>-1.44</v>
       </c>
       <c r="BE146">
+        <v>95.335999999999999</v>
+      </c>
+      <c r="BF146">
         <v>96.685000000000002</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>153</v>
       </c>
@@ -24282,10 +24714,13 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BE147">
+        <v>94.497</v>
+      </c>
+      <c r="BF147">
         <v>95.933999999999997</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>154</v>
       </c>
@@ -24438,10 +24873,13 @@
         <v>-0.95</v>
       </c>
       <c r="BE148">
+        <v>94.805000000000007</v>
+      </c>
+      <c r="BF148">
         <v>96.182000000000002</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>155</v>
       </c>
@@ -24594,10 +25032,13 @@
         <v>-1.02</v>
       </c>
       <c r="BE149">
+        <v>94.033000000000001</v>
+      </c>
+      <c r="BF149">
         <v>95.596000000000004</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>156</v>
       </c>
@@ -24750,10 +25191,13 @@
         <v>-1.27</v>
       </c>
       <c r="BE150">
+        <v>95.272999999999996</v>
+      </c>
+      <c r="BF150">
         <v>96.653999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>157</v>
       </c>
@@ -24906,10 +25350,13 @@
         <v>-1.75</v>
       </c>
       <c r="BE151">
+        <v>89.010999999999996</v>
+      </c>
+      <c r="BF151">
         <v>90.561000000000007</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>158</v>
       </c>
@@ -25062,10 +25509,13 @@
         <v>-1.71</v>
       </c>
       <c r="BE152">
+        <v>90.837999999999994</v>
+      </c>
+      <c r="BF152">
         <v>91.84</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>159</v>
       </c>
@@ -25218,10 +25668,13 @@
         <v>-1.77</v>
       </c>
       <c r="BE153">
+        <v>89.316000000000003</v>
+      </c>
+      <c r="BF153">
         <v>90.891999999999996</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>160</v>
       </c>
@@ -25374,10 +25827,13 @@
         <v>-1.71</v>
       </c>
       <c r="BE154">
+        <v>88.902000000000001</v>
+      </c>
+      <c r="BF154">
         <v>90.254000000000005</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>161</v>
       </c>
@@ -25530,10 +25986,13 @@
         <v>-1.71</v>
       </c>
       <c r="BE155">
+        <v>91.968999999999994</v>
+      </c>
+      <c r="BF155">
         <v>92.998999999999995</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>162</v>
       </c>
@@ -25686,10 +26145,13 @@
         <v>-1.67</v>
       </c>
       <c r="BE156">
+        <v>88.513999999999996</v>
+      </c>
+      <c r="BF156">
         <v>89.594999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>163</v>
       </c>
@@ -25842,10 +26304,13 @@
         <v>-1.65</v>
       </c>
       <c r="BE157">
+        <v>93.188999999999993</v>
+      </c>
+      <c r="BF157">
         <v>94.56</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>164</v>
       </c>
@@ -25998,10 +26463,13 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BE158">
+        <v>94.254000000000005</v>
+      </c>
+      <c r="BF158">
         <v>95.703000000000003</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>165</v>
       </c>
@@ -26154,10 +26622,13 @@
         <v>-1.64</v>
       </c>
       <c r="BE159">
+        <v>91.233999999999995</v>
+      </c>
+      <c r="BF159">
         <v>92.411000000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>166</v>
       </c>
@@ -26310,10 +26781,13 @@
         <v>-1.68</v>
       </c>
       <c r="BE160">
+        <v>90.834999999999994</v>
+      </c>
+      <c r="BF160">
         <v>91.911000000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>167</v>
       </c>
@@ -26466,10 +26940,13 @@
         <v>-1.55</v>
       </c>
       <c r="BE161">
+        <v>91.92</v>
+      </c>
+      <c r="BF161">
         <v>93.141000000000005</v>
       </c>
     </row>
-    <row r="162" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>168</v>
       </c>
@@ -26622,6 +27099,9 @@
         <v>-1.54</v>
       </c>
       <c r="BE162">
+        <v>92.1</v>
+      </c>
+      <c r="BF162">
         <v>93.332999999999998</v>
       </c>
     </row>
@@ -26633,10 +27113,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B742B78-CE28-4524-AE34-EC41C6D94660}">
-  <dimension ref="A1:BE38"/>
+  <dimension ref="A1:BF38"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
@@ -26686,7 +27166,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -26771,7 +27251,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -26924,10 +27404,13 @@
         <v>2</v>
       </c>
       <c r="BE3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>175</v>
       </c>
@@ -27080,10 +27563,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE4">
+        <v>95.992000000000004</v>
+      </c>
+      <c r="BF4">
         <v>97.021000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>176</v>
       </c>
@@ -27236,10 +27722,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE5">
+        <v>95.234999999999999</v>
+      </c>
+      <c r="BF5">
         <v>96.370999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>177</v>
       </c>
@@ -27392,10 +27881,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE6">
+        <v>95.926000000000002</v>
+      </c>
+      <c r="BF6">
         <v>96.917000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>178</v>
       </c>
@@ -27548,10 +28040,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE7">
+        <v>95.478999999999999</v>
+      </c>
+      <c r="BF7">
         <v>96.588999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>179</v>
       </c>
@@ -27704,10 +28199,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE8">
+        <v>96.04</v>
+      </c>
+      <c r="BF8">
         <v>97.070999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>180</v>
       </c>
@@ -27860,10 +28358,13 @@
         <v>-0.98</v>
       </c>
       <c r="BE9">
+        <v>94.055000000000007</v>
+      </c>
+      <c r="BF9">
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>181</v>
       </c>
@@ -28016,10 +28517,13 @@
         <v>-1.06</v>
       </c>
       <c r="BE10">
+        <v>94.503</v>
+      </c>
+      <c r="BF10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>182</v>
       </c>
@@ -28172,10 +28676,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE11">
+        <v>96.795000000000002</v>
+      </c>
+      <c r="BF11">
         <v>97.811000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>183</v>
       </c>
@@ -28328,10 +28835,13 @@
         <v>-1.64</v>
       </c>
       <c r="BE12">
+        <v>95.066000000000003</v>
+      </c>
+      <c r="BF12">
         <v>95.668000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>184</v>
       </c>
@@ -28484,10 +28994,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE13">
+        <v>96.078000000000003</v>
+      </c>
+      <c r="BF13">
         <v>97.138000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>185</v>
       </c>
@@ -28640,10 +29153,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE14">
+        <v>96.162000000000006</v>
+      </c>
+      <c r="BF14">
         <v>97.245999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>186</v>
       </c>
@@ -28796,10 +29312,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE15">
+        <v>96.129000000000005</v>
+      </c>
+      <c r="BF15">
         <v>97.195999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>187</v>
       </c>
@@ -28952,10 +29471,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE16">
+        <v>96.161000000000001</v>
+      </c>
+      <c r="BF16">
         <v>97.215000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>188</v>
       </c>
@@ -29108,10 +29630,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE17">
+        <v>96.147999999999996</v>
+      </c>
+      <c r="BF17">
         <v>97.206000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>189</v>
       </c>
@@ -29264,10 +29789,13 @@
         <v>-1.92</v>
       </c>
       <c r="BE18">
+        <v>96.519000000000005</v>
+      </c>
+      <c r="BF18">
         <v>97.492999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>190</v>
       </c>
@@ -29420,10 +29948,13 @@
         <v>-1.72</v>
       </c>
       <c r="BE19">
+        <v>95.227000000000004</v>
+      </c>
+      <c r="BF19">
         <v>96.179000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>191</v>
       </c>
@@ -29576,10 +30107,13 @@
         <v>-1.04</v>
       </c>
       <c r="BE20">
+        <v>96.498000000000005</v>
+      </c>
+      <c r="BF20">
         <v>97.486999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>192</v>
       </c>
@@ -29732,10 +30266,13 @@
         <v>-1.93</v>
       </c>
       <c r="BE21">
+        <v>96.751000000000005</v>
+      </c>
+      <c r="BF21">
         <v>97.632999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>193</v>
       </c>
@@ -29888,10 +30425,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE22">
+        <v>95.466999999999999</v>
+      </c>
+      <c r="BF22">
         <v>96.602999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>194</v>
       </c>
@@ -30044,10 +30584,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE23">
+        <v>95.804000000000002</v>
+      </c>
+      <c r="BF23">
         <v>96.899000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>195</v>
       </c>
@@ -30200,10 +30743,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE24">
+        <v>95.465999999999994</v>
+      </c>
+      <c r="BF24">
         <v>96.6</v>
       </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>196</v>
       </c>
@@ -30356,10 +30902,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE25">
+        <v>95.465000000000003</v>
+      </c>
+      <c r="BF25">
         <v>96.600999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>197</v>
       </c>
@@ -30512,10 +31061,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE26">
+        <v>89.622</v>
+      </c>
+      <c r="BF26">
         <v>0.78300000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>198</v>
       </c>
@@ -30668,10 +31220,13 @@
         <v>-1.9</v>
       </c>
       <c r="BE27">
+        <v>1.33</v>
+      </c>
+      <c r="BF27">
         <v>0.63600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>199</v>
       </c>
@@ -30824,10 +31379,13 @@
         <v>-1.91</v>
       </c>
       <c r="BE28">
+        <v>96.352999999999994</v>
+      </c>
+      <c r="BF28">
         <v>97.435000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>200</v>
       </c>
@@ -30980,10 +31538,13 @@
         <v>-1.88</v>
       </c>
       <c r="BE29">
+        <v>94.665999999999997</v>
+      </c>
+      <c r="BF29">
         <v>95.814999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>201</v>
       </c>
@@ -31136,10 +31697,13 @@
         <v>-1.87</v>
       </c>
       <c r="BE30">
+        <v>94.814999999999998</v>
+      </c>
+      <c r="BF30">
         <v>95.97</v>
       </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>202</v>
       </c>
@@ -31292,10 +31856,13 @@
         <v>-1.89</v>
       </c>
       <c r="BE31">
+        <v>95.037000000000006</v>
+      </c>
+      <c r="BF31">
         <v>96.215000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>203</v>
       </c>
@@ -31448,10 +32015,13 @@
         <v>-1.88</v>
       </c>
       <c r="BE32">
+        <v>94.876000000000005</v>
+      </c>
+      <c r="BF32">
         <v>96.087000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>204</v>
       </c>
@@ -31604,10 +32174,13 @@
         <v>-1.86</v>
       </c>
       <c r="BE33">
+        <v>94.805999999999997</v>
+      </c>
+      <c r="BF33">
         <v>95.817999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>205</v>
       </c>
@@ -31760,10 +32333,13 @@
         <v>-1.87</v>
       </c>
       <c r="BE34">
+        <v>94.29</v>
+      </c>
+      <c r="BF34">
         <v>95.55</v>
       </c>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>206</v>
       </c>
@@ -31916,10 +32492,13 @@
         <v>-1.89</v>
       </c>
       <c r="BE35">
+        <v>95.171999999999997</v>
+      </c>
+      <c r="BF35">
         <v>96.301000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>207</v>
       </c>
@@ -32072,10 +32651,13 @@
         <v>-1.88</v>
       </c>
       <c r="BE36">
+        <v>94.966999999999999</v>
+      </c>
+      <c r="BF36">
         <v>96.007000000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>208</v>
       </c>
@@ -32228,10 +32810,13 @@
         <v>-1.18</v>
       </c>
       <c r="BE37">
+        <v>94.631</v>
+      </c>
+      <c r="BF37">
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>209</v>
       </c>
@@ -32384,6 +32969,9 @@
         <v>-1.82</v>
       </c>
       <c r="BE38">
+        <v>92.373000000000005</v>
+      </c>
+      <c r="BF38">
         <v>91.456000000000003</v>
       </c>
     </row>
@@ -32395,10 +32983,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3022EA92-DD80-4549-8700-EFF920438755}">
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF14"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
@@ -32449,7 +33037,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -32534,7 +33122,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -32688,10 +33276,13 @@
         <v>2</v>
       </c>
       <c r="BE3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>213</v>
       </c>
@@ -32844,10 +33435,13 @@
         <v>-1.04</v>
       </c>
       <c r="BE4">
+        <v>91.816999999999993</v>
+      </c>
+      <c r="BF4">
         <v>94.513999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>214</v>
       </c>
@@ -33000,10 +33594,13 @@
         <v>-1.27</v>
       </c>
       <c r="BE5">
+        <v>92.909000000000006</v>
+      </c>
+      <c r="BF5">
         <v>94.582999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>215</v>
       </c>
@@ -33156,10 +33753,13 @@
         <v>-0.91</v>
       </c>
       <c r="BE6">
+        <v>92.811999999999998</v>
+      </c>
+      <c r="BF6">
         <v>94.822000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>216</v>
       </c>
@@ -33312,12 +33912,35 @@
         <v>-0.9</v>
       </c>
       <c r="BE7">
+        <v>91.491</v>
+      </c>
+      <c r="BF7">
         <v>93.644999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
+    </row>
+    <row r="11" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="AR11" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="AR12" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="AR13" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="AR14" s="8" t="s">
+        <v>216</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -33624,6 +34247,9 @@
         <v>221</v>
       </c>
       <c r="BH3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI3" s="2" t="s">
         <v>263</v>
       </c>
     </row>
@@ -33785,10 +34411,13 @@
       <c r="BF4">
         <v>-0.22168099999999999</v>
       </c>
+      <c r="BG4" s="5"/>
       <c r="BH4">
+        <v>92.754999999999995</v>
+      </c>
+      <c r="BI4">
         <v>94.090999999999994</v>
       </c>
-      <c r="BI4" s="5"/>
     </row>
     <row r="5" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -33948,10 +34577,13 @@
       <c r="BF5">
         <v>-0.10931</v>
       </c>
+      <c r="BG5" s="5"/>
       <c r="BH5">
+        <v>93.537000000000006</v>
+      </c>
+      <c r="BI5">
         <v>94.944999999999993</v>
       </c>
-      <c r="BI5" s="5"/>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -34111,11 +34743,13 @@
       <c r="BF6">
         <v>-0.13537299999999999</v>
       </c>
-      <c r="BG6" s="1"/>
+      <c r="BG6" s="5"/>
       <c r="BH6">
+        <v>92.8</v>
+      </c>
+      <c r="BI6">
         <v>94.497</v>
       </c>
-      <c r="BI6" s="5"/>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -34275,10 +34909,13 @@
       <c r="BF7">
         <v>-0.199318</v>
       </c>
+      <c r="BG7" s="5"/>
       <c r="BH7">
+        <v>94.103999999999999</v>
+      </c>
+      <c r="BI7">
         <v>95.581999999999994</v>
       </c>
-      <c r="BI7" s="5"/>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -34438,10 +35075,13 @@
       <c r="BF8">
         <v>-0.14741799999999999</v>
       </c>
+      <c r="BG8" s="5"/>
       <c r="BH8">
+        <v>93.581000000000003</v>
+      </c>
+      <c r="BI8">
         <v>95.251999999999995</v>
       </c>
-      <c r="BI8" s="5"/>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -34601,10 +35241,13 @@
       <c r="BF9">
         <v>-0.109267</v>
       </c>
+      <c r="BG9" s="5"/>
       <c r="BH9">
+        <v>91.147999999999996</v>
+      </c>
+      <c r="BI9">
         <v>92.575000000000003</v>
       </c>
-      <c r="BI9" s="5"/>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -34764,10 +35407,13 @@
       <c r="BF10">
         <v>-8.6100999999999997E-2</v>
       </c>
+      <c r="BG10" s="5"/>
       <c r="BH10">
+        <v>94.742999999999995</v>
+      </c>
+      <c r="BI10">
         <v>96.075000000000003</v>
       </c>
-      <c r="BI10" s="5"/>
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -34927,10 +35573,13 @@
       <c r="BF11">
         <v>-0.14046700000000001</v>
       </c>
+      <c r="BG11" s="5"/>
       <c r="BH11">
+        <v>93.025000000000006</v>
+      </c>
+      <c r="BI11">
         <v>94.704999999999998</v>
       </c>
-      <c r="BI11" s="5"/>
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -35090,10 +35739,13 @@
       <c r="BF12">
         <v>-0.14418900000000001</v>
       </c>
+      <c r="BG12" s="5"/>
       <c r="BH12">
+        <v>93.649000000000001</v>
+      </c>
+      <c r="BI12">
         <v>95.164000000000001</v>
       </c>
-      <c r="BI12" s="5"/>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -35253,10 +35905,13 @@
       <c r="BF13">
         <v>-9.5584000000000002E-2</v>
       </c>
+      <c r="BG13" s="5"/>
       <c r="BH13">
+        <v>93.787000000000006</v>
+      </c>
+      <c r="BI13">
         <v>95.367999999999995</v>
       </c>
-      <c r="BI13" s="5"/>
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -35416,10 +36071,13 @@
       <c r="BF14">
         <v>-0.14058499999999999</v>
       </c>
+      <c r="BG14" s="5"/>
       <c r="BH14">
+        <v>93.977000000000004</v>
+      </c>
+      <c r="BI14">
         <v>95.495999999999995</v>
       </c>
-      <c r="BI14" s="5"/>
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -35579,10 +36237,13 @@
       <c r="BF15">
         <v>-9.5748000000000097E-2</v>
       </c>
+      <c r="BG15" s="5"/>
       <c r="BH15">
+        <v>94.674999999999997</v>
+      </c>
+      <c r="BI15">
         <v>95.834999999999994</v>
       </c>
-      <c r="BI15" s="5"/>
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -35742,10 +36403,13 @@
       <c r="BF16">
         <v>-9.5870999999999998E-2</v>
       </c>
+      <c r="BG16" s="5"/>
       <c r="BH16">
+        <v>95.049000000000007</v>
+      </c>
+      <c r="BI16">
         <v>96.375</v>
       </c>
-      <c r="BI16" s="5"/>
     </row>
     <row r="17" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -35905,10 +36569,13 @@
       <c r="BF17">
         <v>-0.101919</v>
       </c>
+      <c r="BG17" s="5"/>
       <c r="BH17">
+        <v>94.81</v>
+      </c>
+      <c r="BI17">
         <v>96.097999999999999</v>
       </c>
-      <c r="BI17" s="5"/>
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -36068,10 +36735,13 @@
       <c r="BF18">
         <v>-9.6645999999999996E-2</v>
       </c>
+      <c r="BG18" s="5"/>
       <c r="BH18">
+        <v>93.918000000000006</v>
+      </c>
+      <c r="BI18">
         <v>95.159000000000006</v>
       </c>
-      <c r="BI18" s="5"/>
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -36231,10 +36901,13 @@
       <c r="BF19">
         <v>-0.31610500000000002</v>
       </c>
+      <c r="BG19" s="5"/>
       <c r="BH19">
+        <v>94.661000000000001</v>
+      </c>
+      <c r="BI19">
         <v>96.212999999999994</v>
       </c>
-      <c r="BI19" s="5"/>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -36394,10 +37067,13 @@
       <c r="BF20">
         <v>-0.16564899999999999</v>
       </c>
+      <c r="BG20" s="5"/>
       <c r="BH20">
+        <v>93.882000000000005</v>
+      </c>
+      <c r="BI20">
         <v>95.498999999999995</v>
       </c>
-      <c r="BI20" s="5"/>
     </row>
     <row r="21" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -36557,10 +37233,13 @@
       <c r="BF21">
         <v>-0.14147700000000007</v>
       </c>
+      <c r="BG21" s="5"/>
       <c r="BH21">
+        <v>93.552000000000007</v>
+      </c>
+      <c r="BI21">
         <v>95.215000000000003</v>
       </c>
-      <c r="BI21" s="5"/>
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -36720,10 +37399,13 @@
       <c r="BF22">
         <v>-0.158168</v>
       </c>
+      <c r="BG22" s="5"/>
       <c r="BH22">
+        <v>94.257999999999996</v>
+      </c>
+      <c r="BI22">
         <v>95.728999999999999</v>
       </c>
-      <c r="BI22" s="5"/>
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -36883,10 +37565,13 @@
       <c r="BF23">
         <v>-6.6350000000000006E-2</v>
       </c>
+      <c r="BG23" s="5"/>
       <c r="BH23">
+        <v>94.894999999999996</v>
+      </c>
+      <c r="BI23">
         <v>96.3</v>
       </c>
-      <c r="BI23" s="5"/>
     </row>
     <row r="24" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -37046,10 +37731,13 @@
       <c r="BF24">
         <v>-8.7050000000000002E-2</v>
       </c>
+      <c r="BG24" s="5"/>
       <c r="BH24">
+        <v>94.106999999999999</v>
+      </c>
+      <c r="BI24">
         <v>95.245999999999995</v>
       </c>
-      <c r="BI24" s="5"/>
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -37209,10 +37897,13 @@
       <c r="BF25">
         <v>-0.18790899999999999</v>
       </c>
+      <c r="BG25" s="5"/>
       <c r="BH25">
+        <v>94.352000000000004</v>
+      </c>
+      <c r="BI25">
         <v>95.906000000000006</v>
       </c>
-      <c r="BI25" s="5"/>
     </row>
     <row r="26" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -37372,10 +38063,13 @@
       <c r="BF26">
         <v>-0.190189</v>
       </c>
+      <c r="BG26" s="5"/>
       <c r="BH26">
+        <v>94.001000000000005</v>
+      </c>
+      <c r="BI26">
         <v>95.638000000000005</v>
       </c>
-      <c r="BI26" s="5"/>
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -37535,10 +38229,13 @@
       <c r="BF27">
         <v>-0.17302200000000001</v>
       </c>
+      <c r="BG27" s="5"/>
       <c r="BH27">
+        <v>94.399000000000001</v>
+      </c>
+      <c r="BI27">
         <v>95.947000000000003</v>
       </c>
-      <c r="BI27" s="5"/>
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -37698,10 +38395,13 @@
       <c r="BF28">
         <v>-8.7182999999999997E-2</v>
       </c>
+      <c r="BG28" s="5"/>
       <c r="BH28">
+        <v>94.626000000000005</v>
+      </c>
+      <c r="BI28">
         <v>96.048000000000002</v>
       </c>
-      <c r="BI28" s="5"/>
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -37861,10 +38561,13 @@
       <c r="BF29">
         <v>-0.169603</v>
       </c>
+      <c r="BG29" s="5"/>
       <c r="BH29">
+        <v>94.536000000000001</v>
+      </c>
+      <c r="BI29">
         <v>95.977999999999994</v>
       </c>
-      <c r="BI29" s="5"/>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -38024,10 +38727,13 @@
       <c r="BF30">
         <v>-0.14256199999999999</v>
       </c>
+      <c r="BG30" s="5"/>
       <c r="BH30">
+        <v>93.653000000000006</v>
+      </c>
+      <c r="BI30">
         <v>95.373000000000005</v>
       </c>
-      <c r="BI30" s="5"/>
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A31">
@@ -38187,10 +38893,13 @@
       <c r="BF31">
         <v>-0.15307799999999999</v>
       </c>
+      <c r="BG31" s="5"/>
       <c r="BH31">
+        <v>93.757000000000005</v>
+      </c>
+      <c r="BI31">
         <v>95.462000000000003</v>
       </c>
-      <c r="BI31" s="5"/>
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -38350,10 +39059,13 @@
       <c r="BF32">
         <v>-0.174233</v>
       </c>
+      <c r="BG32" s="5"/>
       <c r="BH32">
+        <v>94.227999999999994</v>
+      </c>
+      <c r="BI32">
         <v>95.822000000000003</v>
       </c>
-      <c r="BI32" s="5"/>
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A33">
@@ -38513,10 +39225,13 @@
       <c r="BF33">
         <v>-0.17144300000000001</v>
       </c>
+      <c r="BG33" s="5"/>
       <c r="BH33">
+        <v>93.165999999999997</v>
+      </c>
+      <c r="BI33">
         <v>94.881</v>
       </c>
-      <c r="BI33" s="5"/>
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A34">
@@ -38676,10 +39391,13 @@
       <c r="BF34">
         <v>-6.9732999999999906E-2</v>
       </c>
+      <c r="BG34" s="5"/>
       <c r="BH34">
+        <v>94.459000000000003</v>
+      </c>
+      <c r="BI34">
         <v>95.819000000000003</v>
       </c>
-      <c r="BI34" s="5"/>
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A35">
@@ -38839,10 +39557,13 @@
       <c r="BF35">
         <v>-0.165411</v>
       </c>
+      <c r="BG35" s="5"/>
       <c r="BH35">
+        <v>94.343000000000004</v>
+      </c>
+      <c r="BI35">
         <v>95.948999999999998</v>
       </c>
-      <c r="BI35" s="5"/>
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A36">
@@ -39002,10 +39723,13 @@
       <c r="BF36">
         <v>-0.16719000000000001</v>
       </c>
+      <c r="BG36" s="5"/>
       <c r="BH36">
+        <v>94.346999999999994</v>
+      </c>
+      <c r="BI36">
         <v>95.947000000000003</v>
       </c>
-      <c r="BI36" s="5"/>
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A37">
@@ -39165,10 +39889,13 @@
       <c r="BF37">
         <v>-0.15587699999999999</v>
       </c>
+      <c r="BG37" s="5"/>
       <c r="BH37">
+        <v>93.724999999999994</v>
+      </c>
+      <c r="BI37">
         <v>95.423000000000002</v>
       </c>
-      <c r="BI37" s="5"/>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A38">
@@ -39328,10 +40055,13 @@
       <c r="BF38">
         <v>-0.11014699999999999</v>
       </c>
+      <c r="BG38" s="5"/>
       <c r="BH38">
+        <v>94.912999999999997</v>
+      </c>
+      <c r="BI38">
         <v>96.340999999999994</v>
       </c>
-      <c r="BI38" s="5"/>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A39">
@@ -39491,10 +40221,13 @@
       <c r="BF39">
         <v>-7.5556000000000095E-2</v>
       </c>
+      <c r="BG39" s="5"/>
       <c r="BH39">
+        <v>91.662999999999997</v>
+      </c>
+      <c r="BI39">
         <v>91.718000000000004</v>
       </c>
-      <c r="BI39" s="5"/>
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A40">
@@ -39654,10 +40387,13 @@
       <c r="BF40">
         <v>-0.102496</v>
       </c>
+      <c r="BG40" s="5"/>
       <c r="BH40">
+        <v>94.57</v>
+      </c>
+      <c r="BI40">
         <v>96.075999999999993</v>
       </c>
-      <c r="BI40" s="5"/>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A41">
@@ -39817,10 +40553,13 @@
       <c r="BF41">
         <v>-7.1001999999999996E-2</v>
       </c>
+      <c r="BG41" s="5"/>
       <c r="BH41">
+        <v>94.206999999999994</v>
+      </c>
+      <c r="BI41">
         <v>95.734999999999999</v>
       </c>
-      <c r="BI41" s="5"/>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A42">
@@ -39980,10 +40719,13 @@
       <c r="BF42">
         <v>-8.7143999999999999E-2</v>
       </c>
+      <c r="BG42" s="5"/>
       <c r="BH42">
+        <v>94.165999999999997</v>
+      </c>
+      <c r="BI42">
         <v>95.257000000000005</v>
       </c>
-      <c r="BI42" s="5"/>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A43">
@@ -40143,10 +40885,13 @@
       <c r="BF43">
         <v>-0.11899899999999999</v>
       </c>
+      <c r="BG43" s="5"/>
       <c r="BH43">
+        <v>94.77</v>
+      </c>
+      <c r="BI43">
         <v>96.204999999999998</v>
       </c>
-      <c r="BI43" s="5"/>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A44">
@@ -40306,10 +41051,13 @@
       <c r="BF44">
         <v>-8.5280999999999996E-2</v>
       </c>
+      <c r="BG44" s="5"/>
       <c r="BH44">
+        <v>94.866</v>
+      </c>
+      <c r="BI44">
         <v>96.299000000000007</v>
       </c>
-      <c r="BI44" s="5"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A45">
@@ -40469,10 +41217,13 @@
       <c r="BF45">
         <v>-9.6089999999999995E-2</v>
       </c>
+      <c r="BG45" s="5"/>
       <c r="BH45">
+        <v>94.795000000000002</v>
+      </c>
+      <c r="BI45">
         <v>96.197000000000003</v>
       </c>
-      <c r="BI45" s="5"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A46">
@@ -40632,10 +41383,13 @@
       <c r="BF46">
         <v>-9.7430000000000606E-3</v>
       </c>
-      <c r="BH46" s="11">
+      <c r="BG46" s="5"/>
+      <c r="BH46">
+        <v>92.765000000000001</v>
+      </c>
+      <c r="BI46" s="11">
         <v>91.870999999999995</v>
       </c>
-      <c r="BI46" s="5"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A47">
@@ -40795,10 +41549,13 @@
       <c r="BF47">
         <v>-9.0204000000000104E-2</v>
       </c>
+      <c r="BG47" s="5"/>
       <c r="BH47">
+        <v>93.501000000000005</v>
+      </c>
+      <c r="BI47">
         <v>95.031999999999996</v>
       </c>
-      <c r="BI47" s="5"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A48">
@@ -40958,12 +41715,18 @@
       <c r="BF48">
         <v>-0.15165200000000001</v>
       </c>
+      <c r="BG48" s="5"/>
       <c r="BH48">
+        <v>94.902000000000001</v>
+      </c>
+      <c r="BI48">
         <v>96.32</v>
       </c>
-      <c r="BI48" s="5"/>
     </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:61" x14ac:dyDescent="0.3">
+      <c r="BI50" s="5"/>
+    </row>
+    <row r="51" spans="4:61" x14ac:dyDescent="0.3">
       <c r="D51" s="6"/>
     </row>
   </sheetData>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD551F9-550C-42BA-B6B4-04FA02A85169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90438349-B179-438A-B8E7-CBEBBD27F7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="325">
   <si>
     <t>B3LYP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1126,6 +1126,10 @@
     <t>BLYP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>XSF-TDA MC method 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -44658,7 +44662,7 @@
         <v>235</v>
       </c>
       <c r="U43" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="AA43" t="s">
         <v>237</v>
@@ -44806,7 +44810,7 @@
         <v>2.3978199999999998</v>
       </c>
       <c r="W45">
-        <v>2.1368999999999998</v>
+        <v>2.1583000000000001</v>
       </c>
       <c r="X45">
         <v>2.5021800000000001</v>
@@ -44972,7 +44976,7 @@
         <v>5.8060400000000003</v>
       </c>
       <c r="W47">
-        <v>5.5211699999999997</v>
+        <v>5.5481999999999996</v>
       </c>
       <c r="X47">
         <v>5.9889200000000002</v>
@@ -45055,7 +45059,7 @@
         <v>5.5797600000000003</v>
       </c>
       <c r="W48">
-        <v>5.3731999999999998</v>
+        <v>5.4187000000000003</v>
       </c>
       <c r="X48">
         <v>5.4642799999999996</v>
@@ -45138,7 +45142,7 @@
         <v>7.0912699999999997</v>
       </c>
       <c r="W49">
-        <v>6.8147900000000003</v>
+        <v>6.8692000000000002</v>
       </c>
       <c r="X49">
         <v>6.7583200000000003</v>
@@ -45221,7 +45225,7 @@
         <v>6.3299799999999999</v>
       </c>
       <c r="W50">
-        <v>6.13063</v>
+        <v>6.2507000000000001</v>
       </c>
       <c r="X50">
         <v>5.9907300000000001</v>
@@ -45304,7 +45308,7 @@
         <v>5.7540300000000002</v>
       </c>
       <c r="W51">
-        <v>5.5481100000000003</v>
+        <v>5.5949</v>
       </c>
       <c r="X51">
         <v>5.6759199999999996</v>
@@ -45387,7 +45391,7 @@
         <v>6.7022500000000003</v>
       </c>
       <c r="W52">
-        <v>6.4280999999999997</v>
+        <v>6.4606000000000003</v>
       </c>
       <c r="X52">
         <v>6.5784200000000004</v>
@@ -45470,7 +45474,7 @@
         <v>6.1490200000000002</v>
       </c>
       <c r="W53">
-        <v>5.9583199999999996</v>
+        <v>6.0041000000000002</v>
       </c>
       <c r="X53">
         <v>6.1745000000000001</v>
@@ -45553,7 +45557,7 @@
         <v>6.7804700000000002</v>
       </c>
       <c r="W54">
-        <v>6.3649500000000003</v>
+        <v>6.4303999999999997</v>
       </c>
       <c r="X54">
         <v>6.2287699999999999</v>
@@ -45636,7 +45640,7 @@
         <v>6.5928300000000002</v>
       </c>
       <c r="W55">
-        <v>6.2497400000000001</v>
+        <v>6.3666999999999998</v>
       </c>
       <c r="X55">
         <v>6.4047700000000001</v>
@@ -45719,7 +45723,7 @@
         <v>4.1699000000000002</v>
       </c>
       <c r="W56">
-        <v>3.7253500000000002</v>
+        <v>3.7770999999999999</v>
       </c>
       <c r="X56">
         <v>4.4186699999999997</v>
@@ -45802,7 +45806,7 @@
         <v>6.3880600000000003</v>
       </c>
       <c r="W57">
-        <v>6.0160299999999998</v>
+        <v>6.1273999999999997</v>
       </c>
       <c r="X57">
         <v>5.9365800000000002</v>
@@ -45885,7 +45889,7 @@
         <v>5.1495600000000001</v>
       </c>
       <c r="W58">
-        <v>4.8972600000000002</v>
+        <v>4.9584999999999999</v>
       </c>
       <c r="X58">
         <v>5.0733699999999997</v>
@@ -45968,7 +45972,7 @@
         <v>8.0660299999999996</v>
       </c>
       <c r="W59">
-        <v>7.4599000000000002</v>
+        <v>7.5627000000000004</v>
       </c>
       <c r="X59">
         <v>7.6174099999999996</v>
@@ -46051,7 +46055,7 @@
         <v>4.5793900000000001</v>
       </c>
       <c r="W60">
-        <v>4.4085700000000001</v>
+        <v>4.476</v>
       </c>
       <c r="X60">
         <v>4.0423099999999996</v>
@@ -46134,7 +46138,7 @@
         <v>4.75387</v>
       </c>
       <c r="W61">
-        <v>4.5613799999999998</v>
+        <v>4.6933999999999996</v>
       </c>
       <c r="X61">
         <v>4.4014300000000004</v>
@@ -46217,7 +46221,7 @@
         <v>6.3852599999999997</v>
       </c>
       <c r="W62">
-        <v>6.0843800000000003</v>
+        <v>6.1222000000000003</v>
       </c>
       <c r="X62">
         <v>6.5764199999999997</v>
@@ -46300,7 +46304,7 @@
         <v>4.8411200000000001</v>
       </c>
       <c r="W63">
-        <v>4.6242000000000001</v>
+        <v>4.6684000000000001</v>
       </c>
       <c r="X63">
         <v>4.7813800000000004</v>

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90438349-B179-438A-B8E7-CBEBBD27F7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6048A4-AE44-43AD-89B8-9244196807D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1224,7 +1224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1251,6 +1251,9 @@
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -44726,7 +44729,7 @@
       <c r="V44" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="W44" s="1" t="s">
+      <c r="W44" s="16" t="s">
         <v>226</v>
       </c>
       <c r="X44" s="1" t="s">

--- a/TADF_all.xlsx
+++ b/TADF_all.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gits\XSF-TDA-calculated-TADF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6048A4-AE44-43AD-89B8-9244196807D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00BDC2F-088B-4A92-A1BF-8C9BE8168AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAH159" sheetId="1" r:id="rId1"/>
     <sheet name="MR-TADF-35" sheetId="2" r:id="rId2"/>
     <sheet name="Heptazine-4" sheetId="3" r:id="rId3"/>
     <sheet name="INVEST-45" sheetId="4" r:id="rId4"/>
-    <sheet name="Fig3c" sheetId="5" r:id="rId5"/>
-    <sheet name="Fig3a" sheetId="6" r:id="rId6"/>
+    <sheet name="Fig3a" sheetId="6" r:id="rId5"/>
+    <sheet name="Fig3c" sheetId="5" r:id="rId6"/>
+    <sheet name="QUEST-19" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1224,7 +1225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1251,9 +1252,6 @@
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -21064,7 +21062,7 @@
         <v>-1.07</v>
       </c>
       <c r="BE124">
-        <v>2.2919999999999998</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="BF124">
         <v>1.821</v>
@@ -41744,8 +41742,1078 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4750BC-1188-421B-BE5C-F526F345B7FA}">
+  <dimension ref="A1:AH12"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>233</v>
+      </c>
+      <c r="X1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>0.2</v>
+      </c>
+      <c r="F2">
+        <v>0.3</v>
+      </c>
+      <c r="G2">
+        <v>0.4</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.1</v>
+      </c>
+      <c r="L2">
+        <v>0.2</v>
+      </c>
+      <c r="M2">
+        <v>0.3</v>
+      </c>
+      <c r="N2">
+        <v>0.4</v>
+      </c>
+      <c r="O2">
+        <v>0.5</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0.1</v>
+      </c>
+      <c r="S2">
+        <v>0.2</v>
+      </c>
+      <c r="T2">
+        <v>0.3</v>
+      </c>
+      <c r="U2">
+        <v>0.4</v>
+      </c>
+      <c r="V2">
+        <v>0.5</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0.1</v>
+      </c>
+      <c r="Z2">
+        <v>0.2</v>
+      </c>
+      <c r="AA2">
+        <v>0.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.4</v>
+      </c>
+      <c r="AC2">
+        <v>0.5</v>
+      </c>
+      <c r="AD2">
+        <v>0.6</v>
+      </c>
+      <c r="AE2">
+        <v>0.7</v>
+      </c>
+      <c r="AF2">
+        <v>0.8</v>
+      </c>
+      <c r="AG2">
+        <v>0.9</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-0.219</v>
+      </c>
+      <c r="C3">
+        <v>-5.3695317466150333E-2</v>
+      </c>
+      <c r="D3">
+        <v>-8.4102878702926778E-2</v>
+      </c>
+      <c r="E3">
+        <v>-0.11633440672357941</v>
+      </c>
+      <c r="F3">
+        <v>-0.15028698889018019</v>
+      </c>
+      <c r="G3">
+        <v>-0.18586431067123349</v>
+      </c>
+      <c r="H3">
+        <v>-0.22297630634159291</v>
+      </c>
+      <c r="J3">
+        <v>-8.1221728988329633E-2</v>
+      </c>
+      <c r="K3">
+        <v>-0.1168439462624653</v>
+      </c>
+      <c r="L3">
+        <v>-0.1543783903576694</v>
+      </c>
+      <c r="M3">
+        <v>-0.19370979611356831</v>
+      </c>
+      <c r="N3">
+        <v>-0.23473102971272899</v>
+      </c>
+      <c r="O3">
+        <v>-0.27734256639983113</v>
+      </c>
+      <c r="Q3">
+        <v>-0.27408865700000001</v>
+      </c>
+      <c r="R3">
+        <v>-0.33523172800000001</v>
+      </c>
+      <c r="S3">
+        <v>-0.398866673</v>
+      </c>
+      <c r="T3">
+        <v>-0.46480048400000001</v>
+      </c>
+      <c r="U3">
+        <v>-0.53285906599999999</v>
+      </c>
+      <c r="V3">
+        <v>-0.60288523199999999</v>
+      </c>
+      <c r="X3">
+        <v>2.682E-2</v>
+      </c>
+      <c r="Y3">
+        <v>1.2760000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>-2.4599999999999999E-3</v>
+      </c>
+      <c r="AA3">
+        <v>-1.8780000000000002E-2</v>
+      </c>
+      <c r="AB3">
+        <v>-3.6170000000000001E-2</v>
+      </c>
+      <c r="AC3">
+        <v>-5.4579999999999997E-2</v>
+      </c>
+      <c r="AD3">
+        <v>-7.3980000000000004E-2</v>
+      </c>
+      <c r="AE3">
+        <v>-9.4320000000000001E-2</v>
+      </c>
+      <c r="AF3">
+        <v>-0.11557000000000001</v>
+      </c>
+      <c r="AG3">
+        <v>-0.13769000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>-0.16064999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="C4">
+        <v>-3.1462667469395918E-2</v>
+      </c>
+      <c r="D4">
+        <v>-5.7451959499349288E-2</v>
+      </c>
+      <c r="E4">
+        <v>-8.5006908621180446E-2</v>
+      </c>
+      <c r="F4">
+        <v>-0.1140423230292225</v>
+      </c>
+      <c r="G4">
+        <v>-0.14447911975026531</v>
+      </c>
+      <c r="H4">
+        <v>-0.17624296741757189</v>
+      </c>
+      <c r="J4">
+        <v>-5.1558887936486449E-2</v>
+      </c>
+      <c r="K4">
+        <v>-8.2066392931280693E-2</v>
+      </c>
+      <c r="L4">
+        <v>-0.1142090426485647</v>
+      </c>
+      <c r="M4">
+        <v>-0.1478924968137027</v>
+      </c>
+      <c r="N4">
+        <v>-0.1830289005774553</v>
+      </c>
+      <c r="O4">
+        <v>-0.21953647554575689</v>
+      </c>
+      <c r="Q4">
+        <v>-0.20636560900000001</v>
+      </c>
+      <c r="R4">
+        <v>-0.25783493899999999</v>
+      </c>
+      <c r="S4">
+        <v>-0.31149030100000002</v>
+      </c>
+      <c r="T4">
+        <v>-0.367171892</v>
+      </c>
+      <c r="U4">
+        <v>-0.42473488999999998</v>
+      </c>
+      <c r="V4">
+        <v>-0.48404794800000001</v>
+      </c>
+      <c r="X4">
+        <v>3.4810000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.2460000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>9.1199999999999996E-3</v>
+      </c>
+      <c r="AA4">
+        <v>-5.1700000000000001E-3</v>
+      </c>
+      <c r="AB4">
+        <v>-2.0369999999999999E-2</v>
+      </c>
+      <c r="AC4">
+        <v>-3.6450000000000003E-2</v>
+      </c>
+      <c r="AD4">
+        <v>-5.3379999999999997E-2</v>
+      </c>
+      <c r="AE4">
+        <v>-7.1110000000000007E-2</v>
+      </c>
+      <c r="AF4">
+        <v>-8.9630000000000001E-2</v>
+      </c>
+      <c r="AG4">
+        <v>-0.10891000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>-0.12889999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-0.10100000000000001</v>
+      </c>
+      <c r="C5">
+        <v>6.392647431346832E-3</v>
+      </c>
+      <c r="D5">
+        <v>-2.042892695471232E-2</v>
+      </c>
+      <c r="E5">
+        <v>-4.8838594915497607E-2</v>
+      </c>
+      <c r="F5">
+        <v>-7.8751659338270288E-2</v>
+      </c>
+      <c r="G5">
+        <v>-0.1100886063337147</v>
+      </c>
+      <c r="H5">
+        <v>-0.14277484495396939</v>
+      </c>
+      <c r="J5">
+        <v>-4.657382802000465E-3</v>
+      </c>
+      <c r="K5">
+        <v>-3.6149245480160679E-2</v>
+      </c>
+      <c r="L5">
+        <v>-6.9295718372846801E-2</v>
+      </c>
+      <c r="M5">
+        <v>-0.10400277538607799</v>
+      </c>
+      <c r="N5">
+        <v>-0.1401827194620858</v>
+      </c>
+      <c r="O5">
+        <v>-0.17775379440728689</v>
+      </c>
+      <c r="Q5">
+        <v>-9.6803934999999994E-2</v>
+      </c>
+      <c r="R5">
+        <v>-0.15100649899999999</v>
+      </c>
+      <c r="S5">
+        <v>-0.20737256000000001</v>
+      </c>
+      <c r="T5">
+        <v>-0.26574688899999999</v>
+      </c>
+      <c r="U5">
+        <v>-0.32598851299999998</v>
+      </c>
+      <c r="V5">
+        <v>-0.38796929299999999</v>
+      </c>
+      <c r="X5">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="Y5">
+        <v>3.7139999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.367E-2</v>
+      </c>
+      <c r="AA5">
+        <v>9.2300000000000004E-3</v>
+      </c>
+      <c r="AB5">
+        <v>-6.1500000000000001E-3</v>
+      </c>
+      <c r="AC5">
+        <v>-2.2419999999999999E-2</v>
+      </c>
+      <c r="AD5">
+        <v>-3.9550000000000002E-2</v>
+      </c>
+      <c r="AE5">
+        <v>-5.7520000000000002E-2</v>
+      </c>
+      <c r="AF5">
+        <v>-7.6280000000000001E-2</v>
+      </c>
+      <c r="AG5">
+        <v>-9.5820000000000002E-2</v>
+      </c>
+      <c r="AH5">
+        <v>-0.11611</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-0.11899999999999999</v>
+      </c>
+      <c r="C6">
+        <v>1.8855847345124029E-2</v>
+      </c>
+      <c r="D6">
+        <v>-8.5659206541532657E-3</v>
+      </c>
+      <c r="E6">
+        <v>-3.7617608193249517E-2</v>
+      </c>
+      <c r="F6">
+        <v>-6.8213368704139188E-2</v>
+      </c>
+      <c r="G6">
+        <v>-0.100272485440766</v>
+      </c>
+      <c r="H6">
+        <v>-0.1337191250826063</v>
+      </c>
+      <c r="J6">
+        <v>1.3737276567256561E-2</v>
+      </c>
+      <c r="K6">
+        <v>-1.8407061019353101E-2</v>
+      </c>
+      <c r="L6">
+        <v>-5.2251599137904843E-2</v>
+      </c>
+      <c r="M6">
+        <v>-8.7700722041839735E-2</v>
+      </c>
+      <c r="N6">
+        <v>-0.1246651516473347</v>
+      </c>
+      <c r="O6">
+        <v>-0.16306155922403159</v>
+      </c>
+      <c r="Q6">
+        <v>-5.5137939999999998E-3</v>
+      </c>
+      <c r="R6">
+        <v>-6.1069144999999998E-2</v>
+      </c>
+      <c r="S6">
+        <v>-0.118833578</v>
+      </c>
+      <c r="T6">
+        <v>-0.17864759099999999</v>
+      </c>
+      <c r="U6">
+        <v>-0.24036676700000001</v>
+      </c>
+      <c r="V6">
+        <v>-0.30386011299999999</v>
+      </c>
+      <c r="X6">
+        <v>5.5320000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>4.265E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.894E-2</v>
+      </c>
+      <c r="AA6">
+        <v>1.423E-2</v>
+      </c>
+      <c r="AB6">
+        <v>-1.4400000000000001E-3</v>
+      </c>
+      <c r="AC6">
+        <v>-1.804E-2</v>
+      </c>
+      <c r="AD6">
+        <v>-3.5520000000000003E-2</v>
+      </c>
+      <c r="AE6">
+        <v>-5.3870000000000001E-2</v>
+      </c>
+      <c r="AF6">
+        <v>-7.3039999999999994E-2</v>
+      </c>
+      <c r="AG6">
+        <v>-9.2999999999999999E-2</v>
+      </c>
+      <c r="AH6">
+        <v>-0.11373999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-0.10299999999999999</v>
+      </c>
+      <c r="C7">
+        <v>2.2675964678355962E-2</v>
+      </c>
+      <c r="D7">
+        <v>-5.4979017709457711E-3</v>
+      </c>
+      <c r="E7">
+        <v>-3.5306226326697152E-2</v>
+      </c>
+      <c r="F7">
+        <v>-6.6661778532552618E-2</v>
+      </c>
+      <c r="G7">
+        <v>-9.9482604507277889E-2</v>
+      </c>
+      <c r="H7">
+        <v>-0.13369177152301939</v>
+      </c>
+      <c r="J7">
+        <v>1.8822699744775E-2</v>
+      </c>
+      <c r="K7">
+        <v>-1.421465783355901E-2</v>
+      </c>
+      <c r="L7">
+        <v>-4.8950947252423438E-2</v>
+      </c>
+      <c r="M7">
+        <v>-8.5289465095391412E-2</v>
+      </c>
+      <c r="N7">
+        <v>-0.1231399656008607</v>
+      </c>
+      <c r="O7">
+        <v>-0.16241827088485161</v>
+      </c>
+      <c r="Q7">
+        <v>2.8673549999999998E-3</v>
+      </c>
+      <c r="R7">
+        <v>-5.4679327E-2</v>
+      </c>
+      <c r="S7">
+        <v>-0.114407702</v>
+      </c>
+      <c r="T7">
+        <v>-0.176156009</v>
+      </c>
+      <c r="U7">
+        <v>-0.23977792000000001</v>
+      </c>
+      <c r="V7">
+        <v>-0.30514089999999999</v>
+      </c>
+      <c r="X7">
+        <v>5.2929999999999998E-2</v>
+      </c>
+      <c r="Y7">
+        <v>3.9949999999999999E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.5940000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>1.091E-2</v>
+      </c>
+      <c r="AB7">
+        <v>-5.0800000000000003E-3</v>
+      </c>
+      <c r="AC7">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="AD7">
+        <v>-3.9820000000000001E-2</v>
+      </c>
+      <c r="AE7">
+        <v>-5.8500000000000003E-2</v>
+      </c>
+      <c r="AF7">
+        <v>-7.8009999999999996E-2</v>
+      </c>
+      <c r="AG7">
+        <v>-9.8320000000000005E-2</v>
+      </c>
+      <c r="AH7">
+        <v>-0.11940000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>-7.0999999999999994E-2</v>
+      </c>
+      <c r="C8">
+        <v>1.5592835887828759E-2</v>
+      </c>
+      <c r="D8">
+        <v>-1.0409235665267091E-2</v>
+      </c>
+      <c r="E8">
+        <v>-3.7952279368353478E-2</v>
+      </c>
+      <c r="F8">
+        <v>-6.6955553268395349E-2</v>
+      </c>
+      <c r="G8">
+        <v>-9.7343052517346942E-2</v>
+      </c>
+      <c r="H8">
+        <v>-0.1290434580088165</v>
+      </c>
+      <c r="J8">
+        <v>4.7672386310944398E-3</v>
+      </c>
+      <c r="K8">
+        <v>-2.5699218815081179E-2</v>
+      </c>
+      <c r="L8">
+        <v>-5.7773463700363813E-2</v>
+      </c>
+      <c r="M8">
+        <v>-9.1365616827648641E-2</v>
+      </c>
+      <c r="N8">
+        <v>-0.1263918154273341</v>
+      </c>
+      <c r="O8">
+        <v>-0.16277384319369759</v>
+      </c>
+      <c r="Q8">
+        <v>-0.106780098</v>
+      </c>
+      <c r="R8">
+        <v>-0.15863750300000001</v>
+      </c>
+      <c r="S8">
+        <v>-0.21262815700000001</v>
+      </c>
+      <c r="T8">
+        <v>-0.26860271400000002</v>
+      </c>
+      <c r="U8">
+        <v>-0.32642531299999999</v>
+      </c>
+      <c r="V8">
+        <v>-0.38597228</v>
+      </c>
+      <c r="X8">
+        <v>6.2460000000000002E-2</v>
+      </c>
+      <c r="Y8">
+        <v>5.0209999999999998E-2</v>
+      </c>
+      <c r="Z8">
+        <v>3.6970000000000003E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>7.7200000000000003E-3</v>
+      </c>
+      <c r="AC8">
+        <v>-8.2299999999999995E-3</v>
+      </c>
+      <c r="AD8">
+        <v>-2.5020000000000001E-2</v>
+      </c>
+      <c r="AE8">
+        <v>-4.2619999999999998E-2</v>
+      </c>
+      <c r="AF8">
+        <v>-6.0990000000000003E-2</v>
+      </c>
+      <c r="AG8">
+        <v>-8.0119999999999997E-2</v>
+      </c>
+      <c r="AH8">
+        <v>-9.9970000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-4.2000000000000003E-2</v>
+      </c>
+      <c r="C9">
+        <v>3.1888112739289307E-2</v>
+      </c>
+      <c r="D9">
+        <v>5.9341618138347291E-3</v>
+      </c>
+      <c r="E9">
+        <v>-2.1563130386763239E-2</v>
+      </c>
+      <c r="F9">
+        <v>-5.0523097903328151E-2</v>
+      </c>
+      <c r="G9">
+        <v>-8.0869813795292081E-2</v>
+      </c>
+      <c r="H9">
+        <v>-0.112532059471306</v>
+      </c>
+      <c r="J9">
+        <v>2.2583175002177051E-2</v>
+      </c>
+      <c r="K9">
+        <v>-7.8050654854916173E-3</v>
+      </c>
+      <c r="L9">
+        <v>-3.9801838131088729E-2</v>
+      </c>
+      <c r="M9">
+        <v>-7.3317450055239833E-2</v>
+      </c>
+      <c r="N9">
+        <v>-0.1082682472183325</v>
+      </c>
+      <c r="O9">
+        <v>-0.14457623501814859</v>
+      </c>
+      <c r="Q9">
+        <v>-9.3796044999999995E-2</v>
+      </c>
+      <c r="R9">
+        <v>-0.14568030500000001</v>
+      </c>
+      <c r="S9">
+        <v>-0.199692861</v>
+      </c>
+      <c r="T9">
+        <v>-0.255684315</v>
+      </c>
+      <c r="U9">
+        <v>-0.31351889399999999</v>
+      </c>
+      <c r="V9">
+        <v>-0.37307309300000002</v>
+      </c>
+      <c r="X9">
+        <v>7.7649999999999997E-2</v>
+      </c>
+      <c r="Y9">
+        <v>6.5449999999999994E-2</v>
+      </c>
+      <c r="Z9">
+        <v>5.2269999999999997E-2</v>
+      </c>
+      <c r="AA9">
+        <v>3.814E-2</v>
+      </c>
+      <c r="AB9">
+        <v>2.3109999999999999E-2</v>
+      </c>
+      <c r="AC9">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="AD9">
+        <v>-9.5499999999999995E-3</v>
+      </c>
+      <c r="AE9">
+        <v>-2.7109999999999999E-2</v>
+      </c>
+      <c r="AF9">
+        <v>-4.5449999999999997E-2</v>
+      </c>
+      <c r="AG9">
+        <v>-6.4549999999999996E-2</v>
+      </c>
+      <c r="AH9">
+        <v>-8.4370000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-2.9000000000000001E-2</v>
+      </c>
+      <c r="C10">
+        <v>3.2329776261994542E-2</v>
+      </c>
+      <c r="D10">
+        <v>6.79428298235959E-3</v>
+      </c>
+      <c r="E10">
+        <v>-2.02987107648963E-2</v>
+      </c>
+      <c r="F10">
+        <v>-4.8867466581410397E-2</v>
+      </c>
+      <c r="G10">
+        <v>-7.883603005744548E-2</v>
+      </c>
+      <c r="H10">
+        <v>-0.11013292056451771</v>
+      </c>
+      <c r="J10">
+        <v>2.1079103380963068E-2</v>
+      </c>
+      <c r="K10">
+        <v>-8.7560876359118103E-3</v>
+      </c>
+      <c r="L10">
+        <v>-4.0216667593618333E-2</v>
+      </c>
+      <c r="M10">
+        <v>-7.3212472293816694E-2</v>
+      </c>
+      <c r="N10">
+        <v>-0.1076594125027476</v>
+      </c>
+      <c r="O10">
+        <v>-0.14347909064678041</v>
+      </c>
+      <c r="Q10">
+        <v>-0.120186082</v>
+      </c>
+      <c r="R10">
+        <v>-0.170671076</v>
+      </c>
+      <c r="S10">
+        <v>-0.22333318099999999</v>
+      </c>
+      <c r="T10">
+        <v>-0.27802027099999999</v>
+      </c>
+      <c r="U10">
+        <v>-0.33459407600000002</v>
+      </c>
+      <c r="V10">
+        <v>-0.39292883299999998</v>
+      </c>
+      <c r="X10">
+        <v>8.5290000000000005E-2</v>
+      </c>
+      <c r="Y10">
+        <v>7.3230000000000003E-2</v>
+      </c>
+      <c r="Z10">
+        <v>6.0179999999999997E-2</v>
+      </c>
+      <c r="AA10">
+        <v>4.6190000000000002E-2</v>
+      </c>
+      <c r="AB10">
+        <v>3.1280000000000002E-2</v>
+      </c>
+      <c r="AC10">
+        <v>1.55E-2</v>
+      </c>
+      <c r="AD10">
+        <v>-1.14E-3</v>
+      </c>
+      <c r="AE10">
+        <v>-1.8589999999999999E-2</v>
+      </c>
+      <c r="AF10">
+        <v>-3.6830000000000002E-2</v>
+      </c>
+      <c r="AG10">
+        <v>-5.5820000000000002E-2</v>
+      </c>
+      <c r="AH10">
+        <v>-7.5550000000000006E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-0.19900000000000001</v>
+      </c>
+      <c r="C11">
+        <v>-3.2959371646610551E-2</v>
+      </c>
+      <c r="D11">
+        <v>-6.1272270547884457E-2</v>
+      </c>
+      <c r="E11">
+        <v>-9.1157421525328491E-2</v>
+      </c>
+      <c r="F11">
+        <v>-0.12252535152473989</v>
+      </c>
+      <c r="G11">
+        <v>-0.1552915189198798</v>
+      </c>
+      <c r="H11">
+        <v>-0.18937775058770059</v>
+      </c>
+      <c r="J11">
+        <v>-4.894262749152916E-2</v>
+      </c>
+      <c r="K11">
+        <v>-8.2307098975137744E-2</v>
+      </c>
+      <c r="L11">
+        <v>-0.1172873529920645</v>
+      </c>
+      <c r="M11">
+        <v>-0.15378532387720131</v>
+      </c>
+      <c r="N11">
+        <v>-0.1917099606251845</v>
+      </c>
+      <c r="O11">
+        <v>-0.2309767555804062</v>
+      </c>
+      <c r="Q11">
+        <v>-0.101662419</v>
+      </c>
+      <c r="R11">
+        <v>-0.15666648399999999</v>
+      </c>
+      <c r="S11">
+        <v>-0.213700058</v>
+      </c>
+      <c r="T11">
+        <v>-0.27261286600000001</v>
+      </c>
+      <c r="U11">
+        <v>-0.333268658</v>
+      </c>
+      <c r="V11">
+        <v>-0.39554379499999998</v>
+      </c>
+      <c r="X11">
+        <v>-8.8500000000000002E-3</v>
+      </c>
+      <c r="Y11">
+        <v>-5.1799999999999997E-3</v>
+      </c>
+      <c r="Z11">
+        <v>-2.1729999999999999E-2</v>
+      </c>
+      <c r="AA11">
+        <v>-4.147E-2</v>
+      </c>
+      <c r="AB11">
+        <v>-6.2089999999999999E-2</v>
+      </c>
+      <c r="AC11">
+        <v>-8.3449999999999996E-2</v>
+      </c>
+      <c r="AD11">
+        <v>-0.10549</v>
+      </c>
+      <c r="AE11">
+        <v>-0.12816</v>
+      </c>
+      <c r="AF11">
+        <v>-0.15145</v>
+      </c>
+      <c r="AG11">
+        <v>-0.17532</v>
+      </c>
+      <c r="AH11">
+        <v>-0.19975999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-0.30499999999999999</v>
+      </c>
+      <c r="C12">
+        <v>-0.12267649568150581</v>
+      </c>
+      <c r="D12">
+        <v>-0.1526386350437948</v>
+      </c>
+      <c r="E12">
+        <v>-0.18434143875100781</v>
+      </c>
+      <c r="F12">
+        <v>-0.21767820517851541</v>
+      </c>
+      <c r="G12">
+        <v>-0.25255019501554887</v>
+      </c>
+      <c r="H12">
+        <v>-0.28886440115855472</v>
+      </c>
+      <c r="J12">
+        <v>-0.1616918408863468</v>
+      </c>
+      <c r="K12">
+        <v>-0.1970203499165803</v>
+      </c>
+      <c r="L12">
+        <v>-0.2341469362622812</v>
+      </c>
+      <c r="M12">
+        <v>-0.27295414540999602</v>
+      </c>
+      <c r="N12">
+        <v>-0.31333359043364523</v>
+      </c>
+      <c r="O12">
+        <v>-0.35518528603498473</v>
+      </c>
+      <c r="Q12">
+        <v>-0.34264759700000003</v>
+      </c>
+      <c r="R12">
+        <v>-0.401169045</v>
+      </c>
+      <c r="S12">
+        <v>-0.46199827900000001</v>
+      </c>
+      <c r="T12">
+        <v>-0.52494490400000005</v>
+      </c>
+      <c r="U12">
+        <v>-0.58983831499999995</v>
+      </c>
+      <c r="V12">
+        <v>-0.65652546499999997</v>
+      </c>
+      <c r="X12">
+        <v>-0.19067999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>-0.19116</v>
+      </c>
+      <c r="Z12">
+        <v>-0.19273999999999999</v>
+      </c>
+      <c r="AA12">
+        <v>-0.19544</v>
+      </c>
+      <c r="AB12">
+        <v>-0.19922999999999999</v>
+      </c>
+      <c r="AC12">
+        <v>-0.20411000000000001</v>
+      </c>
+      <c r="AD12">
+        <v>-0.21007000000000001</v>
+      </c>
+      <c r="AE12">
+        <v>-0.21711</v>
+      </c>
+      <c r="AF12">
+        <v>-0.22523000000000001</v>
+      </c>
+      <c r="AG12">
+        <v>-0.2344</v>
+      </c>
+      <c r="AH12">
+        <v>-0.24462</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5563FF0C-5BB8-4FAA-8AF4-94C243B80F11}">
-  <dimension ref="A1:AK63"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -44647,1689 +45715,43 @@
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C43" s="1" t="s">
-        <v>229</v>
-      </c>
+      <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="I43" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="O43" t="s">
-        <v>235</v>
-      </c>
-      <c r="U43" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>237</v>
-      </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="W44" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="AA44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC44" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AD44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>238</v>
-      </c>
-      <c r="B45">
-        <v>2.0960000000000001</v>
-      </c>
-      <c r="C45">
-        <v>2.1288800000000001</v>
-      </c>
-      <c r="D45">
-        <v>2.1560000000000001</v>
-      </c>
-      <c r="E45">
-        <v>1.83477</v>
-      </c>
-      <c r="F45">
-        <v>2.2327599999999999</v>
-      </c>
-      <c r="G45">
-        <v>2.3058000000000001</v>
-      </c>
-      <c r="I45">
-        <v>2.3583500000000002</v>
-      </c>
-      <c r="J45">
-        <v>2.3411300000000002</v>
-      </c>
-      <c r="K45">
-        <v>2.10588</v>
-      </c>
-      <c r="L45">
-        <v>2.4064000000000001</v>
-      </c>
-      <c r="M45">
-        <v>2.4380500000000001</v>
-      </c>
-      <c r="O45">
-        <v>2.1633599999999999</v>
-      </c>
-      <c r="P45">
-        <v>2.21014</v>
-      </c>
-      <c r="Q45">
-        <v>1.87835</v>
-      </c>
-      <c r="R45">
-        <v>2.3258100000000002</v>
-      </c>
-      <c r="S45">
-        <v>2.3741300000000001</v>
-      </c>
-      <c r="U45">
-        <v>2.3952900000000001</v>
-      </c>
-      <c r="V45">
-        <v>2.3978199999999998</v>
-      </c>
-      <c r="W45">
-        <v>2.1583000000000001</v>
-      </c>
-      <c r="X45">
-        <v>2.5021800000000001</v>
-      </c>
-      <c r="Y45">
-        <v>2.5086900000000001</v>
-      </c>
-      <c r="AA45">
-        <v>2.3952900000000001</v>
-      </c>
-      <c r="AB45">
-        <v>2.3805800000000001</v>
-      </c>
-      <c r="AC45">
-        <v>2.1368999999999998</v>
-      </c>
-      <c r="AD45">
-        <v>2.4618500000000001</v>
-      </c>
-      <c r="AE45">
-        <v>2.47959</v>
-      </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46">
-        <v>6.0119999999999996</v>
-      </c>
-      <c r="C46">
-        <v>5.0999600000000003</v>
-      </c>
-      <c r="D46">
-        <v>5.2027099999999997</v>
-      </c>
-      <c r="E46">
-        <v>4.9863200000000001</v>
-      </c>
-      <c r="F46">
-        <v>5.2807500000000003</v>
-      </c>
-      <c r="G46">
-        <v>5.2485299999999997</v>
-      </c>
-      <c r="I46">
-        <v>5.3336100000000002</v>
-      </c>
-      <c r="J46">
-        <v>5.4356900000000001</v>
-      </c>
-      <c r="K46">
-        <v>5.3049900000000001</v>
-      </c>
-      <c r="L46">
-        <v>5.57402</v>
-      </c>
-      <c r="M46">
-        <v>5.4936199999999999</v>
-      </c>
-      <c r="O46">
-        <v>5.5749599999999999</v>
-      </c>
-      <c r="P46">
-        <v>7.1021400000000003</v>
-      </c>
-      <c r="Q46">
-        <v>7.2969200000000001</v>
-      </c>
-      <c r="R46">
-        <v>5.5322199999999997</v>
-      </c>
-      <c r="S46">
-        <v>5.4358199999999997</v>
-      </c>
-      <c r="U46">
-        <v>5.4409799999999997</v>
-      </c>
-      <c r="V46">
-        <v>5.59009</v>
-      </c>
-      <c r="W46">
-        <v>5.4838399999999998</v>
-      </c>
-      <c r="X46">
-        <v>5.8223799999999999</v>
-      </c>
-      <c r="Y46">
-        <v>5.6810400000000003</v>
-      </c>
-      <c r="AA46">
-        <v>5.4409799999999997</v>
-      </c>
-      <c r="AB46">
-        <v>5.5586700000000002</v>
-      </c>
-      <c r="AC46">
-        <v>5.4427500000000002</v>
-      </c>
-      <c r="AD46">
-        <v>5.7377900000000004</v>
-      </c>
-      <c r="AE46">
-        <v>5.6229899999999997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>240</v>
-      </c>
-      <c r="B47">
-        <v>5.3730000000000002</v>
-      </c>
-      <c r="C47">
-        <v>5.42476</v>
-      </c>
-      <c r="D47">
-        <v>5.5299300000000002</v>
-      </c>
-      <c r="E47">
-        <v>5.2299499999999997</v>
-      </c>
-      <c r="F47">
-        <v>5.68865</v>
-      </c>
-      <c r="G47">
-        <v>5.5966399999999998</v>
-      </c>
-      <c r="I47">
-        <v>5.6723800000000004</v>
-      </c>
-      <c r="J47">
-        <v>5.7133599999999998</v>
-      </c>
-      <c r="K47">
-        <v>5.4531900000000002</v>
-      </c>
-      <c r="L47">
-        <v>5.8290199999999999</v>
-      </c>
-      <c r="M47">
-        <v>5.7266599999999999</v>
-      </c>
-      <c r="O47">
-        <v>5.4827700000000004</v>
-      </c>
-      <c r="P47">
-        <v>5.6185999999999998</v>
-      </c>
-      <c r="Q47">
-        <v>5.3190600000000003</v>
-      </c>
-      <c r="R47">
-        <v>5.8436300000000001</v>
-      </c>
-      <c r="S47">
-        <v>5.7100200000000001</v>
-      </c>
-      <c r="U47">
-        <v>5.7337600000000002</v>
-      </c>
-      <c r="V47">
-        <v>5.8060400000000003</v>
-      </c>
-      <c r="W47">
-        <v>5.5481999999999996</v>
-      </c>
-      <c r="X47">
-        <v>5.9889200000000002</v>
-      </c>
-      <c r="Y47">
-        <v>5.8438999999999997</v>
-      </c>
-      <c r="AA47">
-        <v>5.7337600000000002</v>
-      </c>
-      <c r="AB47">
-        <v>5.78383</v>
-      </c>
-      <c r="AC47">
-        <v>5.5211699999999997</v>
-      </c>
-      <c r="AD47">
-        <v>5.93126</v>
-      </c>
-      <c r="AE47">
-        <v>5.8051300000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>241</v>
-      </c>
-      <c r="B48">
-        <v>5.2960000000000003</v>
-      </c>
-      <c r="C48">
-        <v>5.1177900000000003</v>
-      </c>
-      <c r="D48">
-        <v>5.0582799999999999</v>
-      </c>
-      <c r="E48">
-        <v>4.78505</v>
-      </c>
-      <c r="F48">
-        <v>4.9172099999999999</v>
-      </c>
-      <c r="G48">
-        <v>5.1114699999999997</v>
-      </c>
-      <c r="I48">
-        <v>5.5449299999999999</v>
-      </c>
-      <c r="J48">
-        <v>5.3917700000000002</v>
-      </c>
-      <c r="K48">
-        <v>5.1818799999999996</v>
-      </c>
-      <c r="L48">
-        <v>5.19536</v>
-      </c>
-      <c r="M48">
-        <v>5.3744300000000003</v>
-      </c>
-      <c r="O48">
-        <v>5.2696500000000004</v>
-      </c>
-      <c r="P48">
-        <v>5.2480900000000004</v>
-      </c>
-      <c r="Q48">
-        <v>5.0234100000000002</v>
-      </c>
-      <c r="R48">
-        <v>5.1870599999999998</v>
-      </c>
-      <c r="S48">
-        <v>5.3065899999999999</v>
-      </c>
-      <c r="U48">
-        <v>5.6937899999999999</v>
-      </c>
-      <c r="V48">
-        <v>5.5797600000000003</v>
-      </c>
-      <c r="W48">
-        <v>5.4187000000000003</v>
-      </c>
-      <c r="X48">
-        <v>5.4642799999999996</v>
-      </c>
-      <c r="Y48">
-        <v>5.5703100000000001</v>
-      </c>
-      <c r="AA48">
-        <v>5.6937899999999999</v>
-      </c>
-      <c r="AB48">
-        <v>5.54481</v>
-      </c>
-      <c r="AC48">
-        <v>5.3731999999999998</v>
-      </c>
-      <c r="AD48">
-        <v>5.36897</v>
-      </c>
-      <c r="AE48">
-        <v>5.5080900000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>242</v>
-      </c>
-      <c r="B49">
-        <v>6.9279999999999999</v>
-      </c>
-      <c r="C49">
-        <v>6.8207399999999998</v>
-      </c>
-      <c r="D49">
-        <v>6.5551399999999997</v>
-      </c>
-      <c r="E49">
-        <v>6.2331300000000001</v>
-      </c>
-      <c r="F49">
-        <v>6.1615000000000002</v>
-      </c>
-      <c r="G49">
-        <v>6.5285799999999998</v>
-      </c>
-      <c r="I49">
-        <v>7.2242800000000003</v>
-      </c>
-      <c r="J49">
-        <v>6.8806799999999999</v>
-      </c>
-      <c r="K49">
-        <v>6.6109400000000003</v>
-      </c>
-      <c r="L49">
-        <v>6.4442199999999996</v>
-      </c>
-      <c r="M49">
-        <v>6.79779</v>
-      </c>
-      <c r="O49">
-        <v>6.9882299999999997</v>
-      </c>
-      <c r="P49">
-        <v>6.7681699999999996</v>
-      </c>
-      <c r="Q49">
-        <v>6.4938000000000002</v>
-      </c>
-      <c r="R49">
-        <v>6.4780100000000003</v>
-      </c>
-      <c r="S49">
-        <v>6.7493400000000001</v>
-      </c>
-      <c r="U49">
-        <v>7.38863</v>
-      </c>
-      <c r="V49">
-        <v>7.0912699999999997</v>
-      </c>
-      <c r="W49">
-        <v>6.8692000000000002</v>
-      </c>
-      <c r="X49">
-        <v>6.7583200000000003</v>
-      </c>
-      <c r="Y49">
-        <v>7.0183200000000001</v>
-      </c>
-      <c r="AA49">
-        <v>7.38863</v>
-      </c>
-      <c r="AB49">
-        <v>7.0489800000000002</v>
-      </c>
-      <c r="AC49">
-        <v>6.8147900000000003</v>
-      </c>
-      <c r="AD49">
-        <v>6.6386900000000004</v>
-      </c>
-      <c r="AE49">
-        <v>6.9428299999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>243</v>
-      </c>
-      <c r="B50">
-        <v>6.2389999999999999</v>
-      </c>
-      <c r="C50">
-        <v>6.0460099999999999</v>
-      </c>
-      <c r="D50">
-        <v>5.9287999999999998</v>
-      </c>
-      <c r="E50">
-        <v>5.7895700000000003</v>
-      </c>
-      <c r="F50">
-        <v>5.3358699999999999</v>
-      </c>
-      <c r="G50">
-        <v>5.8660500000000004</v>
-      </c>
-      <c r="I50">
-        <v>6.2227399999999999</v>
-      </c>
-      <c r="J50">
-        <v>6.0352300000000003</v>
-      </c>
-      <c r="K50">
-        <v>5.9087100000000001</v>
-      </c>
-      <c r="L50">
-        <v>5.4293699999999996</v>
-      </c>
-      <c r="M50">
-        <v>5.9614200000000004</v>
-      </c>
-      <c r="O50">
-        <v>6.1902799999999996</v>
-      </c>
-      <c r="P50">
-        <v>6.2183900000000003</v>
-      </c>
-      <c r="Q50">
-        <v>6.1255499999999996</v>
-      </c>
-      <c r="R50">
-        <v>5.8932599999999997</v>
-      </c>
-      <c r="S50">
-        <v>6.2211600000000002</v>
-      </c>
-      <c r="U50">
-        <v>6.3699300000000001</v>
-      </c>
-      <c r="V50">
-        <v>6.3299799999999999</v>
-      </c>
-      <c r="W50">
-        <v>6.2507000000000001</v>
-      </c>
-      <c r="X50">
-        <v>5.9907300000000001</v>
-      </c>
-      <c r="Y50">
-        <v>6.32186</v>
-      </c>
-      <c r="AA50">
-        <v>6.3699300000000001</v>
-      </c>
-      <c r="AB50">
-        <v>6.2410899999999998</v>
-      </c>
-      <c r="AC50">
-        <v>6.13063</v>
-      </c>
-      <c r="AD50">
-        <v>5.6795900000000001</v>
-      </c>
-      <c r="AE50">
-        <v>6.1419899999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>244</v>
-      </c>
-      <c r="B51">
-        <v>5.1840000000000002</v>
-      </c>
-      <c r="C51">
-        <v>5.2764199999999999</v>
-      </c>
-      <c r="D51">
-        <v>5.2597399999999999</v>
-      </c>
-      <c r="E51">
-        <v>4.9944800000000003</v>
-      </c>
-      <c r="F51">
-        <v>5.1749400000000003</v>
-      </c>
-      <c r="G51">
-        <v>5.35419</v>
-      </c>
-      <c r="I51">
-        <v>5.7049899999999996</v>
-      </c>
-      <c r="J51">
-        <v>5.5930099999999996</v>
-      </c>
-      <c r="K51">
-        <v>5.3915600000000001</v>
-      </c>
-      <c r="L51">
-        <v>5.4554</v>
-      </c>
-      <c r="M51">
-        <v>5.60825</v>
-      </c>
-      <c r="O51">
-        <v>6.3269200000000003</v>
-      </c>
-      <c r="P51">
-        <v>5.4227299999999996</v>
-      </c>
-      <c r="Q51">
-        <v>5.19909</v>
-      </c>
-      <c r="R51">
-        <v>5.3959900000000003</v>
-      </c>
-      <c r="S51">
-        <v>5.5216200000000004</v>
-      </c>
-      <c r="U51">
-        <v>6.7516699999999998</v>
-      </c>
-      <c r="V51">
-        <v>5.7540300000000002</v>
-      </c>
-      <c r="W51">
-        <v>5.5949</v>
-      </c>
-      <c r="X51">
-        <v>5.6759199999999996</v>
-      </c>
-      <c r="Y51">
-        <v>5.77658</v>
-      </c>
-      <c r="AA51">
-        <v>6.7516699999999998</v>
-      </c>
-      <c r="AB51">
-        <v>5.7176099999999996</v>
-      </c>
-      <c r="AC51">
-        <v>5.5481100000000003</v>
-      </c>
-      <c r="AD51">
-        <v>5.5807900000000004</v>
-      </c>
-      <c r="AE51">
-        <v>5.7126700000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>245</v>
-      </c>
-      <c r="B52">
-        <v>6.4</v>
-      </c>
-      <c r="C52">
-        <v>6.46997</v>
-      </c>
-      <c r="D52">
-        <v>6.4458900000000003</v>
-      </c>
-      <c r="E52">
-        <v>6.1179100000000002</v>
-      </c>
-      <c r="F52">
-        <v>6.2541799999999999</v>
-      </c>
-      <c r="G52">
-        <v>6.4096799999999998</v>
-      </c>
-      <c r="I52">
-        <v>6.6135099999999998</v>
-      </c>
-      <c r="J52">
-        <v>6.5665399999999998</v>
-      </c>
-      <c r="K52">
-        <v>6.2806300000000004</v>
-      </c>
-      <c r="L52">
-        <v>6.3670400000000003</v>
-      </c>
-      <c r="M52">
-        <v>6.5027799999999996</v>
-      </c>
-      <c r="O52">
-        <v>6.9500900000000003</v>
-      </c>
-      <c r="P52">
-        <v>6.5792900000000003</v>
-      </c>
-      <c r="Q52">
-        <v>6.2947100000000002</v>
-      </c>
-      <c r="R52">
-        <v>6.4631699999999999</v>
-      </c>
-      <c r="S52">
-        <v>6.5611600000000001</v>
-      </c>
-      <c r="U52">
-        <v>7.0972</v>
-      </c>
-      <c r="V52">
-        <v>6.7022500000000003</v>
-      </c>
-      <c r="W52">
-        <v>6.4606000000000003</v>
-      </c>
-      <c r="X52">
-        <v>6.5784200000000004</v>
-      </c>
-      <c r="Y52">
-        <v>6.6565399999999997</v>
-      </c>
-      <c r="AA52">
-        <v>7.0972</v>
-      </c>
-      <c r="AB52">
-        <v>6.6766699999999997</v>
-      </c>
-      <c r="AC52">
-        <v>6.4280999999999997</v>
-      </c>
-      <c r="AD52">
-        <v>6.5014099999999999</v>
-      </c>
-      <c r="AE52">
-        <v>6.6062700000000003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>246</v>
-      </c>
-      <c r="B53">
-        <v>5.9450000000000003</v>
-      </c>
-      <c r="C53">
-        <v>5.8789899999999999</v>
-      </c>
-      <c r="D53">
-        <v>5.9235300000000004</v>
-      </c>
-      <c r="E53">
-        <v>5.7336900000000002</v>
-      </c>
-      <c r="F53">
-        <v>5.8350200000000001</v>
-      </c>
-      <c r="G53">
-        <v>5.9850099999999999</v>
-      </c>
-      <c r="I53">
-        <v>5.9996</v>
-      </c>
-      <c r="J53">
-        <v>6.01227</v>
-      </c>
-      <c r="K53">
-        <v>5.8405699999999996</v>
-      </c>
-      <c r="L53">
-        <v>5.8994200000000001</v>
-      </c>
-      <c r="M53">
-        <v>6.0483200000000004</v>
-      </c>
-      <c r="O53">
-        <v>5.9531099999999997</v>
-      </c>
-      <c r="P53">
-        <v>6.0579700000000001</v>
-      </c>
-      <c r="Q53">
-        <v>5.8936599999999997</v>
-      </c>
-      <c r="R53">
-        <v>6.1089000000000002</v>
-      </c>
-      <c r="S53">
-        <v>6.1697499999999996</v>
-      </c>
-      <c r="U53">
-        <v>6.0764199999999997</v>
-      </c>
-      <c r="V53">
-        <v>6.1490200000000002</v>
-      </c>
-      <c r="W53">
-        <v>6.0041000000000002</v>
-      </c>
-      <c r="X53">
-        <v>6.1745000000000001</v>
-      </c>
-      <c r="Y53">
-        <v>6.2346399999999997</v>
-      </c>
-      <c r="AA53">
-        <v>6.0764199999999997</v>
-      </c>
-      <c r="AB53">
-        <v>6.1163600000000002</v>
-      </c>
-      <c r="AC53">
-        <v>5.9583199999999996</v>
-      </c>
-      <c r="AD53">
-        <v>6.0423</v>
-      </c>
-      <c r="AE53">
-        <v>6.1617100000000002</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>247</v>
-      </c>
-      <c r="B54">
-        <v>6.923</v>
-      </c>
-      <c r="C54">
-        <v>6.8431600000000001</v>
-      </c>
-      <c r="D54">
-        <v>6.3953800000000003</v>
-      </c>
-      <c r="E54">
-        <v>5.9561999999999999</v>
-      </c>
-      <c r="F54">
-        <v>5.7942299999999998</v>
-      </c>
-      <c r="G54">
-        <v>6.2489100000000004</v>
-      </c>
-      <c r="I54">
-        <v>7.0754999999999999</v>
-      </c>
-      <c r="J54">
-        <v>6.5908100000000003</v>
-      </c>
-      <c r="K54">
-        <v>6.2039099999999996</v>
-      </c>
-      <c r="L54">
-        <v>5.9678800000000001</v>
-      </c>
-      <c r="M54">
-        <v>6.4067299999999996</v>
-      </c>
-      <c r="O54">
-        <v>6.9969700000000001</v>
-      </c>
-      <c r="P54">
-        <v>6.5853000000000002</v>
-      </c>
-      <c r="Q54">
-        <v>6.1830499999999997</v>
-      </c>
-      <c r="R54">
-        <v>6.0551500000000003</v>
-      </c>
-      <c r="S54">
-        <v>6.4477700000000002</v>
-      </c>
-      <c r="U54">
-        <v>7.2289199999999996</v>
-      </c>
-      <c r="V54">
-        <v>6.7804700000000002</v>
-      </c>
-      <c r="W54">
-        <v>6.4303999999999997</v>
-      </c>
-      <c r="X54">
-        <v>6.2287699999999999</v>
-      </c>
-      <c r="Y54">
-        <v>6.6062799999999999</v>
-      </c>
-      <c r="AA54">
-        <v>7.2289199999999996</v>
-      </c>
-      <c r="AB54">
-        <v>6.7287499999999998</v>
-      </c>
-      <c r="AC54">
-        <v>6.3649500000000003</v>
-      </c>
-      <c r="AD54">
-        <v>6.0811299999999999</v>
-      </c>
-      <c r="AE54">
-        <v>6.5136700000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>248</v>
-      </c>
-      <c r="B55">
-        <v>6.3890000000000002</v>
-      </c>
-      <c r="C55">
-        <v>6.3773099999999996</v>
-      </c>
-      <c r="D55">
-        <v>6.1761799999999996</v>
-      </c>
-      <c r="E55">
-        <v>5.8795799999999998</v>
-      </c>
-      <c r="F55">
-        <v>5.8297100000000004</v>
-      </c>
-      <c r="G55">
-        <v>6.1966299999999999</v>
-      </c>
-      <c r="I55">
-        <v>6.5934999999999997</v>
-      </c>
-      <c r="J55">
-        <v>6.3505700000000003</v>
-      </c>
-      <c r="K55">
-        <v>6.0795599999999999</v>
-      </c>
-      <c r="L55">
-        <v>5.9840099999999996</v>
-      </c>
-      <c r="M55">
-        <v>6.3427600000000002</v>
-      </c>
-      <c r="O55">
-        <v>6.5215699999999996</v>
-      </c>
-      <c r="P55">
-        <v>6.4155600000000002</v>
-      </c>
-      <c r="Q55">
-        <v>6.1639900000000001</v>
-      </c>
-      <c r="R55">
-        <v>6.2499799999999999</v>
-      </c>
-      <c r="S55">
-        <v>6.4754300000000002</v>
-      </c>
-      <c r="U55">
-        <v>6.7416099999999997</v>
-      </c>
-      <c r="V55">
-        <v>6.5928300000000002</v>
-      </c>
-      <c r="W55">
-        <v>6.3666999999999998</v>
-      </c>
-      <c r="X55">
-        <v>6.4047700000000001</v>
-      </c>
-      <c r="Y55">
-        <v>6.6254200000000001</v>
-      </c>
-      <c r="AA55">
-        <v>6.7416099999999997</v>
-      </c>
-      <c r="AB55">
-        <v>6.5083000000000002</v>
-      </c>
-      <c r="AC55">
-        <v>6.2497400000000001</v>
-      </c>
-      <c r="AD55">
-        <v>6.1386200000000004</v>
-      </c>
-      <c r="AE55">
-        <v>6.4661400000000002</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>249</v>
-      </c>
-      <c r="B56">
-        <v>3.8559999999999999</v>
-      </c>
-      <c r="C56">
-        <v>3.65008</v>
-      </c>
-      <c r="D56">
-        <v>3.6656599999999999</v>
-      </c>
-      <c r="E56">
-        <v>3.16778</v>
-      </c>
-      <c r="F56">
-        <v>3.9047200000000002</v>
-      </c>
-      <c r="G56">
-        <v>3.9011900000000002</v>
-      </c>
-      <c r="I56">
-        <v>4.13537</v>
-      </c>
-      <c r="J56">
-        <v>4.0565499999999997</v>
-      </c>
-      <c r="K56">
-        <v>3.6601599999999999</v>
-      </c>
-      <c r="L56">
-        <v>4.2520300000000004</v>
-      </c>
-      <c r="M56">
-        <v>4.1984899999999996</v>
-      </c>
-      <c r="O56">
-        <v>3.7237399999999998</v>
-      </c>
-      <c r="P56">
-        <v>3.7788499999999998</v>
-      </c>
-      <c r="Q56">
-        <v>3.27759</v>
-      </c>
-      <c r="R56">
-        <v>4.0714600000000001</v>
-      </c>
-      <c r="S56">
-        <v>4.0248100000000004</v>
-      </c>
-      <c r="U56">
-        <v>4.2098800000000001</v>
-      </c>
-      <c r="V56">
-        <v>4.1699000000000002</v>
-      </c>
-      <c r="W56">
-        <v>3.7770999999999999</v>
-      </c>
-      <c r="X56">
-        <v>4.4186699999999997</v>
-      </c>
-      <c r="Y56">
-        <v>4.3245500000000003</v>
-      </c>
-      <c r="AA56">
-        <v>4.2098800000000001</v>
-      </c>
-      <c r="AB56">
-        <v>4.1312300000000004</v>
-      </c>
-      <c r="AC56">
-        <v>3.7253500000000002</v>
-      </c>
-      <c r="AD56">
-        <v>4.32592</v>
-      </c>
-      <c r="AE56">
-        <v>4.2601699999999996</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>250</v>
-      </c>
-      <c r="B57">
-        <v>6.3250000000000002</v>
-      </c>
-      <c r="C57">
-        <v>6.3114999999999997</v>
-      </c>
-      <c r="D57">
-        <v>6.1025299999999998</v>
-      </c>
-      <c r="E57">
-        <v>5.7821199999999999</v>
-      </c>
-      <c r="F57">
-        <v>5.4802499999999998</v>
-      </c>
-      <c r="G57">
-        <v>6.00875</v>
-      </c>
-      <c r="I57">
-        <v>6.3975799999999996</v>
-      </c>
-      <c r="J57">
-        <v>6.1673400000000003</v>
-      </c>
-      <c r="K57">
-        <v>5.8662900000000002</v>
-      </c>
-      <c r="L57">
-        <v>5.5288300000000001</v>
-      </c>
-      <c r="M57">
-        <v>6.0600199999999997</v>
-      </c>
-      <c r="O57">
-        <v>6.4305899999999996</v>
-      </c>
-      <c r="P57">
-        <v>6.3204200000000004</v>
-      </c>
-      <c r="Q57">
-        <v>6.0387700000000004</v>
-      </c>
-      <c r="R57">
-        <v>5.8859399999999997</v>
-      </c>
-      <c r="S57">
-        <v>6.28444</v>
-      </c>
-      <c r="U57">
-        <v>6.51952</v>
-      </c>
-      <c r="V57">
-        <v>6.3880600000000003</v>
-      </c>
-      <c r="W57">
-        <v>6.1273999999999997</v>
-      </c>
-      <c r="X57">
-        <v>5.9365800000000002</v>
-      </c>
-      <c r="Y57">
-        <v>6.3382500000000004</v>
-      </c>
-      <c r="AA57">
-        <v>6.51952</v>
-      </c>
-      <c r="AB57">
-        <v>6.3092699999999997</v>
-      </c>
-      <c r="AC57">
-        <v>6.0160299999999998</v>
-      </c>
-      <c r="AD57">
-        <v>5.6403800000000004</v>
-      </c>
-      <c r="AE57">
-        <v>6.1726900000000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>251</v>
-      </c>
-      <c r="B58">
-        <v>5.1379999999999999</v>
-      </c>
-      <c r="C58">
-        <v>4.9756</v>
-      </c>
-      <c r="D58">
-        <v>4.9244300000000001</v>
-      </c>
-      <c r="E58">
-        <v>4.6650999999999998</v>
-      </c>
-      <c r="F58">
-        <v>4.7640900000000004</v>
-      </c>
-      <c r="G58">
-        <v>4.8620999999999999</v>
-      </c>
-      <c r="I58">
-        <v>5.0815999999999999</v>
-      </c>
-      <c r="J58">
-        <v>5.0096400000000001</v>
-      </c>
-      <c r="K58">
-        <v>4.77121</v>
-      </c>
-      <c r="L58">
-        <v>4.83596</v>
-      </c>
-      <c r="M58">
-        <v>4.9297700000000004</v>
-      </c>
-      <c r="O58">
-        <v>5.06128</v>
-      </c>
-      <c r="P58">
-        <v>5.0608199999999997</v>
-      </c>
-      <c r="Q58">
-        <v>4.8481500000000004</v>
-      </c>
-      <c r="R58">
-        <v>4.99824</v>
-      </c>
-      <c r="S58">
-        <v>5.0404099999999996</v>
-      </c>
-      <c r="U58">
-        <v>5.1705500000000004</v>
-      </c>
-      <c r="V58">
-        <v>5.1495600000000001</v>
-      </c>
-      <c r="W58">
-        <v>4.9584999999999999</v>
-      </c>
-      <c r="X58">
-        <v>5.0733699999999997</v>
-      </c>
-      <c r="Y58">
-        <v>5.1110699999999998</v>
-      </c>
-      <c r="AA58">
-        <v>5.1705500000000004</v>
-      </c>
-      <c r="AB58">
-        <v>5.1063599999999996</v>
-      </c>
-      <c r="AC58">
-        <v>4.8972600000000002</v>
-      </c>
-      <c r="AD58">
-        <v>4.9312399999999998</v>
-      </c>
-      <c r="AE58">
-        <v>5.0147700000000004</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>252</v>
-      </c>
-      <c r="B59">
-        <v>7.34</v>
-      </c>
-      <c r="C59">
-        <v>8.2261299999999995</v>
-      </c>
-      <c r="D59">
-        <v>7.8620799999999997</v>
-      </c>
-      <c r="E59">
-        <v>7.2978800000000001</v>
-      </c>
-      <c r="F59">
-        <v>7.3174700000000001</v>
-      </c>
-      <c r="G59">
-        <v>7.79901</v>
-      </c>
-      <c r="I59">
-        <v>8.2709200000000003</v>
-      </c>
-      <c r="J59">
-        <v>7.8924899999999996</v>
-      </c>
-      <c r="K59">
-        <v>7.3615700000000004</v>
-      </c>
-      <c r="L59">
-        <v>7.3345799999999999</v>
-      </c>
-      <c r="M59">
-        <v>7.8239200000000002</v>
-      </c>
-      <c r="O59">
-        <v>8.3429599999999997</v>
-      </c>
-      <c r="P59">
-        <v>8.0356799999999993</v>
-      </c>
-      <c r="Q59">
-        <v>7.49641</v>
-      </c>
-      <c r="R59">
-        <v>7.6011199999999999</v>
-      </c>
-      <c r="S59">
-        <v>8.0024200000000008</v>
-      </c>
-      <c r="U59">
-        <v>8.3879999999999999</v>
-      </c>
-      <c r="V59">
-        <v>8.0660299999999996</v>
-      </c>
-      <c r="W59">
-        <v>7.5627000000000004</v>
-      </c>
-      <c r="X59">
-        <v>7.6174099999999996</v>
-      </c>
-      <c r="Y59">
-        <v>8.0273000000000003</v>
-      </c>
-      <c r="AA59">
-        <v>8.3879999999999999</v>
-      </c>
-      <c r="AB59">
-        <v>7.98787</v>
-      </c>
-      <c r="AC59">
-        <v>7.4599000000000002</v>
-      </c>
-      <c r="AD59">
-        <v>7.3895099999999996</v>
-      </c>
-      <c r="AE59">
-        <v>7.8849999999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>253</v>
-      </c>
-      <c r="B60">
-        <v>4.34</v>
-      </c>
-      <c r="C60">
-        <v>4.33392</v>
-      </c>
-      <c r="D60">
-        <v>4.1085000000000003</v>
-      </c>
-      <c r="E60">
-        <v>3.9306899999999998</v>
-      </c>
-      <c r="F60">
-        <v>3.3314699999999999</v>
-      </c>
-      <c r="G60">
-        <v>3.9678100000000001</v>
-      </c>
-      <c r="I60">
-        <v>4.4246999999999996</v>
-      </c>
-      <c r="J60">
-        <v>4.2845800000000001</v>
-      </c>
-      <c r="K60">
-        <v>4.13706</v>
-      </c>
-      <c r="L60">
-        <v>3.5188600000000001</v>
-      </c>
-      <c r="M60">
-        <v>4.1363200000000004</v>
-      </c>
-      <c r="O60">
-        <v>4.4861199999999997</v>
-      </c>
-      <c r="P60">
-        <v>4.4010699999999998</v>
-      </c>
-      <c r="Q60">
-        <v>4.2675599999999996</v>
-      </c>
-      <c r="R60">
-        <v>3.8538700000000001</v>
-      </c>
-      <c r="S60">
-        <v>4.2905800000000003</v>
-      </c>
-      <c r="U60">
-        <v>4.58019</v>
-      </c>
-      <c r="V60">
-        <v>4.5793900000000001</v>
-      </c>
-      <c r="W60">
-        <v>4.476</v>
-      </c>
-      <c r="X60">
-        <v>4.0423099999999996</v>
-      </c>
-      <c r="Y60">
-        <v>4.4622000000000002</v>
-      </c>
-      <c r="AA60">
-        <v>4.58019</v>
-      </c>
-      <c r="AB60">
-        <v>4.5279299999999996</v>
-      </c>
-      <c r="AC60">
-        <v>4.4085700000000001</v>
-      </c>
-      <c r="AD60">
-        <v>3.88185</v>
-      </c>
-      <c r="AE60">
-        <v>4.3680300000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>254</v>
-      </c>
-      <c r="B61">
-        <v>4.617</v>
-      </c>
-      <c r="C61">
-        <v>4.6782700000000004</v>
-      </c>
-      <c r="D61">
-        <v>4.2742100000000001</v>
-      </c>
-      <c r="E61">
-        <v>4.1455000000000002</v>
-      </c>
-      <c r="F61">
-        <v>3.5605000000000002</v>
-      </c>
-      <c r="G61">
-        <v>4.2126999999999999</v>
-      </c>
-      <c r="I61">
-        <v>4.8129299999999997</v>
-      </c>
-      <c r="J61">
-        <v>4.3867900000000004</v>
-      </c>
-      <c r="K61">
-        <v>4.26668</v>
-      </c>
-      <c r="L61">
-        <v>3.6653500000000001</v>
-      </c>
-      <c r="M61">
-        <v>4.3151999999999999</v>
-      </c>
-      <c r="O61">
-        <v>4.8655400000000002</v>
-      </c>
-      <c r="P61">
-        <v>4.6350699999999998</v>
-      </c>
-      <c r="Q61">
-        <v>4.5657899999999998</v>
-      </c>
-      <c r="R61">
-        <v>4.2923400000000003</v>
-      </c>
-      <c r="S61">
-        <v>4.6544499999999998</v>
-      </c>
-      <c r="U61">
-        <v>5.00718</v>
-      </c>
-      <c r="V61">
-        <v>4.75387</v>
-      </c>
-      <c r="W61">
-        <v>4.6933999999999996</v>
-      </c>
-      <c r="X61">
-        <v>4.4014300000000004</v>
-      </c>
-      <c r="Y61">
-        <v>4.7637</v>
-      </c>
-      <c r="AA61">
-        <v>5.00718</v>
-      </c>
-      <c r="AB61">
-        <v>4.6569000000000003</v>
-      </c>
-      <c r="AC61">
-        <v>4.5613799999999998</v>
-      </c>
-      <c r="AD61">
-        <v>4.0550699999999997</v>
-      </c>
-      <c r="AE61">
-        <v>4.5705900000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>255</v>
-      </c>
-      <c r="B62">
-        <v>6.1479999999999997</v>
-      </c>
-      <c r="C62">
-        <v>5.9503599999999999</v>
-      </c>
-      <c r="D62">
-        <v>6.0391399999999997</v>
-      </c>
-      <c r="E62">
-        <v>5.6969399999999997</v>
-      </c>
-      <c r="F62">
-        <v>6.1851200000000004</v>
-      </c>
-      <c r="G62">
-        <v>6.2167300000000001</v>
-      </c>
-      <c r="I62">
-        <v>6.2520199999999999</v>
-      </c>
-      <c r="J62">
-        <v>6.2794600000000003</v>
-      </c>
-      <c r="K62">
-        <v>5.9990199999999998</v>
-      </c>
-      <c r="L62">
-        <v>6.4059799999999996</v>
-      </c>
-      <c r="M62">
-        <v>6.4038899999999996</v>
-      </c>
-      <c r="O62">
-        <v>6.5945499999999999</v>
-      </c>
-      <c r="P62">
-        <v>6.1420899999999996</v>
-      </c>
-      <c r="Q62">
-        <v>5.8146300000000002</v>
-      </c>
-      <c r="R62">
-        <v>6.3517000000000001</v>
-      </c>
-      <c r="S62">
-        <v>6.3398700000000003</v>
-      </c>
-      <c r="U62">
-        <v>6.9</v>
-      </c>
-      <c r="V62">
-        <v>6.3852599999999997</v>
-      </c>
-      <c r="W62">
-        <v>6.1222000000000003</v>
-      </c>
-      <c r="X62">
-        <v>6.5764199999999997</v>
-      </c>
-      <c r="Y62">
-        <v>6.5309799999999996</v>
-      </c>
-      <c r="AA62">
-        <v>6.9</v>
-      </c>
-      <c r="AB62">
-        <v>6.3571200000000001</v>
-      </c>
-      <c r="AC62">
-        <v>6.0843800000000003</v>
-      </c>
-      <c r="AD62">
-        <v>6.5034900000000002</v>
-      </c>
-      <c r="AE62">
-        <v>6.4808599999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>256</v>
-      </c>
-      <c r="B63">
-        <v>4.5609999999999999</v>
-      </c>
-      <c r="C63">
-        <v>4.3763500000000004</v>
-      </c>
-      <c r="D63">
-        <v>4.3522100000000004</v>
-      </c>
-      <c r="E63">
-        <v>4.0474600000000001</v>
-      </c>
-      <c r="F63">
-        <v>4.2801799999999997</v>
-      </c>
-      <c r="G63">
-        <v>4.4260799999999998</v>
-      </c>
-      <c r="I63">
-        <v>4.7791100000000002</v>
-      </c>
-      <c r="J63">
-        <v>4.6658200000000001</v>
-      </c>
-      <c r="K63">
-        <v>4.4412099999999999</v>
-      </c>
-      <c r="L63">
-        <v>4.5373999999999999</v>
-      </c>
-      <c r="M63">
-        <v>4.6617899999999999</v>
-      </c>
-      <c r="O63">
-        <v>4.5198400000000003</v>
-      </c>
-      <c r="P63">
-        <v>4.5292899999999996</v>
-      </c>
-      <c r="Q63">
-        <v>4.2757899999999998</v>
-      </c>
-      <c r="R63">
-        <v>4.52494</v>
-      </c>
-      <c r="S63">
-        <v>4.60839</v>
-      </c>
-      <c r="U63">
-        <v>4.9196099999999996</v>
-      </c>
-      <c r="V63">
-        <v>4.8411200000000001</v>
-      </c>
-      <c r="W63">
-        <v>4.6684000000000001</v>
-      </c>
-      <c r="X63">
-        <v>4.7813800000000004</v>
-      </c>
-      <c r="Y63">
-        <v>4.8449799999999996</v>
-      </c>
-      <c r="AA63">
-        <v>4.9196099999999996</v>
-      </c>
-      <c r="AB63">
-        <v>4.8072900000000001</v>
-      </c>
-      <c r="AC63">
-        <v>4.6242000000000001</v>
-      </c>
-      <c r="AD63">
-        <v>4.6915399999999998</v>
-      </c>
-      <c r="AE63">
-        <v>4.7850999999999999</v>
-      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -46337,1068 +45759,1694 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4750BC-1188-421B-BE5C-F526F345B7FA}">
-  <dimension ref="A1:AH12"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39933782-880B-4133-AE6A-8BEFCB6DEA02}">
+  <dimension ref="A1:AE21"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>233</v>
-      </c>
-      <c r="X1" t="s">
-        <v>323</v>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="O1" t="s">
+        <v>235</v>
+      </c>
+      <c r="U1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>222</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0.1</v>
-      </c>
-      <c r="E2">
-        <v>0.2</v>
-      </c>
-      <c r="F2">
-        <v>0.3</v>
-      </c>
-      <c r="G2">
-        <v>0.4</v>
-      </c>
-      <c r="H2">
-        <v>0.5</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0.1</v>
-      </c>
-      <c r="L2">
-        <v>0.2</v>
-      </c>
-      <c r="M2">
-        <v>0.3</v>
-      </c>
-      <c r="N2">
-        <v>0.4</v>
-      </c>
-      <c r="O2">
-        <v>0.5</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0.1</v>
-      </c>
-      <c r="S2">
-        <v>0.2</v>
-      </c>
-      <c r="T2">
-        <v>0.3</v>
-      </c>
-      <c r="U2">
-        <v>0.4</v>
-      </c>
-      <c r="V2">
-        <v>0.5</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0.1</v>
-      </c>
-      <c r="Z2">
-        <v>0.2</v>
-      </c>
-      <c r="AA2">
-        <v>0.3</v>
-      </c>
-      <c r="AB2">
-        <v>0.4</v>
-      </c>
-      <c r="AC2">
-        <v>0.5</v>
-      </c>
-      <c r="AD2">
-        <v>0.6</v>
-      </c>
-      <c r="AE2">
-        <v>0.7</v>
-      </c>
-      <c r="AF2">
-        <v>0.8</v>
-      </c>
-      <c r="AG2">
-        <v>0.9</v>
-      </c>
-      <c r="AH2">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>-0.219</v>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3">
+        <v>2.0960000000000001</v>
       </c>
       <c r="C3">
-        <v>-5.3695317466150333E-2</v>
+        <v>2.1288800000000001</v>
       </c>
       <c r="D3">
-        <v>-8.4102878702926778E-2</v>
+        <v>2.1560000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.11633440672357941</v>
+        <v>1.83477</v>
       </c>
       <c r="F3">
-        <v>-0.15028698889018019</v>
+        <v>2.2327599999999999</v>
       </c>
       <c r="G3">
-        <v>-0.18586431067123349</v>
-      </c>
-      <c r="H3">
-        <v>-0.22297630634159291</v>
+        <v>2.3058000000000001</v>
+      </c>
+      <c r="I3">
+        <v>2.3583500000000002</v>
       </c>
       <c r="J3">
-        <v>-8.1221728988329633E-2</v>
+        <v>2.3411300000000002</v>
       </c>
       <c r="K3">
-        <v>-0.1168439462624653</v>
+        <v>2.10588</v>
       </c>
       <c r="L3">
-        <v>-0.1543783903576694</v>
+        <v>2.4064000000000001</v>
       </c>
       <c r="M3">
-        <v>-0.19370979611356831</v>
-      </c>
-      <c r="N3">
-        <v>-0.23473102971272899</v>
+        <v>2.4380500000000001</v>
       </c>
       <c r="O3">
-        <v>-0.27734256639983113</v>
+        <v>2.1633599999999999</v>
+      </c>
+      <c r="P3">
+        <v>2.21014</v>
       </c>
       <c r="Q3">
-        <v>-0.27408865700000001</v>
+        <v>1.87835</v>
       </c>
       <c r="R3">
-        <v>-0.33523172800000001</v>
+        <v>2.3258100000000002</v>
       </c>
       <c r="S3">
-        <v>-0.398866673</v>
-      </c>
-      <c r="T3">
-        <v>-0.46480048400000001</v>
+        <v>2.3741300000000001</v>
       </c>
       <c r="U3">
-        <v>-0.53285906599999999</v>
+        <v>2.3952900000000001</v>
       </c>
       <c r="V3">
-        <v>-0.60288523199999999</v>
+        <v>2.3978199999999998</v>
+      </c>
+      <c r="W3">
+        <v>2.1583000000000001</v>
       </c>
       <c r="X3">
-        <v>2.682E-2</v>
+        <v>2.5021800000000001</v>
       </c>
       <c r="Y3">
-        <v>1.2760000000000001E-2</v>
-      </c>
-      <c r="Z3">
-        <v>-2.4599999999999999E-3</v>
+        <v>2.5086900000000001</v>
       </c>
       <c r="AA3">
-        <v>-1.8780000000000002E-2</v>
+        <v>2.3952900000000001</v>
       </c>
       <c r="AB3">
-        <v>-3.6170000000000001E-2</v>
+        <v>2.3805800000000001</v>
       </c>
       <c r="AC3">
-        <v>-5.4579999999999997E-2</v>
+        <v>2.1368999999999998</v>
       </c>
       <c r="AD3">
-        <v>-7.3980000000000004E-2</v>
+        <v>2.4618500000000001</v>
       </c>
       <c r="AE3">
-        <v>-9.4320000000000001E-2</v>
-      </c>
-      <c r="AF3">
-        <v>-0.11557000000000001</v>
-      </c>
-      <c r="AG3">
-        <v>-0.13769000000000001</v>
-      </c>
-      <c r="AH3">
-        <v>-0.16064999999999999</v>
+        <v>2.47959</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>-0.13100000000000001</v>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4">
+        <v>6.0119999999999996</v>
       </c>
       <c r="C4">
-        <v>-3.1462667469395918E-2</v>
+        <v>5.0999600000000003</v>
       </c>
       <c r="D4">
-        <v>-5.7451959499349288E-2</v>
+        <v>5.2027099999999997</v>
       </c>
       <c r="E4">
-        <v>-8.5006908621180446E-2</v>
+        <v>4.9863200000000001</v>
       </c>
       <c r="F4">
-        <v>-0.1140423230292225</v>
+        <v>5.2807500000000003</v>
       </c>
       <c r="G4">
-        <v>-0.14447911975026531</v>
-      </c>
-      <c r="H4">
-        <v>-0.17624296741757189</v>
+        <v>5.2485299999999997</v>
+      </c>
+      <c r="I4">
+        <v>5.3336100000000002</v>
       </c>
       <c r="J4">
-        <v>-5.1558887936486449E-2</v>
+        <v>5.4356900000000001</v>
       </c>
       <c r="K4">
-        <v>-8.2066392931280693E-2</v>
+        <v>5.3049900000000001</v>
       </c>
       <c r="L4">
-        <v>-0.1142090426485647</v>
+        <v>5.57402</v>
       </c>
       <c r="M4">
-        <v>-0.1478924968137027</v>
-      </c>
-      <c r="N4">
-        <v>-0.1830289005774553</v>
+        <v>5.4936199999999999</v>
       </c>
       <c r="O4">
-        <v>-0.21953647554575689</v>
+        <v>5.5749599999999999</v>
+      </c>
+      <c r="P4">
+        <v>7.1021400000000003</v>
       </c>
       <c r="Q4">
-        <v>-0.20636560900000001</v>
+        <v>7.2969200000000001</v>
       </c>
       <c r="R4">
-        <v>-0.25783493899999999</v>
+        <v>5.5322199999999997</v>
       </c>
       <c r="S4">
-        <v>-0.31149030100000002</v>
-      </c>
-      <c r="T4">
-        <v>-0.367171892</v>
+        <v>5.4358199999999997</v>
       </c>
       <c r="U4">
-        <v>-0.42473488999999998</v>
+        <v>5.4409799999999997</v>
       </c>
       <c r="V4">
-        <v>-0.48404794800000001</v>
+        <v>5.59009</v>
+      </c>
+      <c r="W4">
+        <v>5.4838399999999998</v>
       </c>
       <c r="X4">
-        <v>3.4810000000000001E-2</v>
+        <v>5.8223799999999999</v>
       </c>
       <c r="Y4">
-        <v>2.2460000000000001E-2</v>
-      </c>
-      <c r="Z4">
-        <v>9.1199999999999996E-3</v>
+        <v>5.6810400000000003</v>
       </c>
       <c r="AA4">
-        <v>-5.1700000000000001E-3</v>
+        <v>5.4409799999999997</v>
       </c>
       <c r="AB4">
-        <v>-2.0369999999999999E-2</v>
+        <v>5.5586700000000002</v>
       </c>
       <c r="AC4">
-        <v>-3.6450000000000003E-2</v>
+        <v>5.4427500000000002</v>
       </c>
       <c r="AD4">
-        <v>-5.3379999999999997E-2</v>
+        <v>5.7377900000000004</v>
       </c>
       <c r="AE4">
-        <v>-7.1110000000000007E-2</v>
-      </c>
-      <c r="AF4">
-        <v>-8.9630000000000001E-2</v>
-      </c>
-      <c r="AG4">
-        <v>-0.10891000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>-0.12889999999999999</v>
+        <v>5.6229899999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>-0.10100000000000001</v>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5">
+        <v>5.3730000000000002</v>
       </c>
       <c r="C5">
-        <v>6.392647431346832E-3</v>
+        <v>5.42476</v>
       </c>
       <c r="D5">
-        <v>-2.042892695471232E-2</v>
+        <v>5.5299300000000002</v>
       </c>
       <c r="E5">
-        <v>-4.8838594915497607E-2</v>
+        <v>5.2299499999999997</v>
       </c>
       <c r="F5">
-        <v>-7.8751659338270288E-2</v>
+        <v>5.68865</v>
       </c>
       <c r="G5">
-        <v>-0.1100886063337147</v>
-      </c>
-      <c r="H5">
-        <v>-0.14277484495396939</v>
+        <v>5.5966399999999998</v>
+      </c>
+      <c r="I5">
+        <v>5.6723800000000004</v>
       </c>
       <c r="J5">
-        <v>-4.657382802000465E-3</v>
+        <v>5.7133599999999998</v>
       </c>
       <c r="K5">
-        <v>-3.6149245480160679E-2</v>
+        <v>5.4531900000000002</v>
       </c>
       <c r="L5">
-        <v>-6.9295718372846801E-2</v>
+        <v>5.8290199999999999</v>
       </c>
       <c r="M5">
-        <v>-0.10400277538607799</v>
-      </c>
-      <c r="N5">
-        <v>-0.1401827194620858</v>
+        <v>5.7266599999999999</v>
       </c>
       <c r="O5">
-        <v>-0.17775379440728689</v>
+        <v>5.4827700000000004</v>
+      </c>
+      <c r="P5">
+        <v>5.6185999999999998</v>
       </c>
       <c r="Q5">
-        <v>-9.6803934999999994E-2</v>
+        <v>5.3190600000000003</v>
       </c>
       <c r="R5">
-        <v>-0.15100649899999999</v>
+        <v>5.8436300000000001</v>
       </c>
       <c r="S5">
-        <v>-0.20737256000000001</v>
-      </c>
-      <c r="T5">
-        <v>-0.26574688899999999</v>
+        <v>5.7100200000000001</v>
       </c>
       <c r="U5">
-        <v>-0.32598851299999998</v>
+        <v>5.7337600000000002</v>
       </c>
       <c r="V5">
-        <v>-0.38796929299999999</v>
+        <v>5.8060400000000003</v>
+      </c>
+      <c r="W5">
+        <v>5.5481999999999996</v>
       </c>
       <c r="X5">
-        <v>4.9599999999999998E-2</v>
+        <v>5.9889200000000002</v>
       </c>
       <c r="Y5">
-        <v>3.7139999999999999E-2</v>
-      </c>
-      <c r="Z5">
-        <v>2.367E-2</v>
+        <v>5.8438999999999997</v>
       </c>
       <c r="AA5">
-        <v>9.2300000000000004E-3</v>
+        <v>5.7337600000000002</v>
       </c>
       <c r="AB5">
-        <v>-6.1500000000000001E-3</v>
+        <v>5.78383</v>
       </c>
       <c r="AC5">
-        <v>-2.2419999999999999E-2</v>
+        <v>5.5211699999999997</v>
       </c>
       <c r="AD5">
-        <v>-3.9550000000000002E-2</v>
+        <v>5.93126</v>
       </c>
       <c r="AE5">
-        <v>-5.7520000000000002E-2</v>
-      </c>
-      <c r="AF5">
-        <v>-7.6280000000000001E-2</v>
-      </c>
-      <c r="AG5">
-        <v>-9.5820000000000002E-2</v>
-      </c>
-      <c r="AH5">
-        <v>-0.11611</v>
+        <v>5.8051300000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>-0.11899999999999999</v>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6">
+        <v>5.2960000000000003</v>
       </c>
       <c r="C6">
-        <v>1.8855847345124029E-2</v>
+        <v>5.1177900000000003</v>
       </c>
       <c r="D6">
-        <v>-8.5659206541532657E-3</v>
+        <v>5.0582799999999999</v>
       </c>
       <c r="E6">
-        <v>-3.7617608193249517E-2</v>
+        <v>4.78505</v>
       </c>
       <c r="F6">
-        <v>-6.8213368704139188E-2</v>
+        <v>4.9172099999999999</v>
       </c>
       <c r="G6">
-        <v>-0.100272485440766</v>
-      </c>
-      <c r="H6">
-        <v>-0.1337191250826063</v>
+        <v>5.1114699999999997</v>
+      </c>
+      <c r="I6">
+        <v>5.5449299999999999</v>
       </c>
       <c r="J6">
-        <v>1.3737276567256561E-2</v>
+        <v>5.3917700000000002</v>
       </c>
       <c r="K6">
-        <v>-1.8407061019353101E-2</v>
+        <v>5.1818799999999996</v>
       </c>
       <c r="L6">
-        <v>-5.2251599137904843E-2</v>
+        <v>5.19536</v>
       </c>
       <c r="M6">
-        <v>-8.7700722041839735E-2</v>
-      </c>
-      <c r="N6">
-        <v>-0.1246651516473347</v>
+        <v>5.3744300000000003</v>
       </c>
       <c r="O6">
-        <v>-0.16306155922403159</v>
+        <v>5.2696500000000004</v>
+      </c>
+      <c r="P6">
+        <v>5.2480900000000004</v>
       </c>
       <c r="Q6">
-        <v>-5.5137939999999998E-3</v>
+        <v>5.0234100000000002</v>
       </c>
       <c r="R6">
-        <v>-6.1069144999999998E-2</v>
+        <v>5.1870599999999998</v>
       </c>
       <c r="S6">
-        <v>-0.118833578</v>
-      </c>
-      <c r="T6">
-        <v>-0.17864759099999999</v>
+        <v>5.3065899999999999</v>
       </c>
       <c r="U6">
-        <v>-0.24036676700000001</v>
+        <v>5.6937899999999999</v>
       </c>
       <c r="V6">
-        <v>-0.30386011299999999</v>
+        <v>5.5797600000000003</v>
+      </c>
+      <c r="W6">
+        <v>5.4187000000000003</v>
       </c>
       <c r="X6">
-        <v>5.5320000000000001E-2</v>
+        <v>5.4642799999999996</v>
       </c>
       <c r="Y6">
-        <v>4.265E-2</v>
-      </c>
-      <c r="Z6">
-        <v>2.894E-2</v>
+        <v>5.5703100000000001</v>
       </c>
       <c r="AA6">
-        <v>1.423E-2</v>
+        <v>5.6937899999999999</v>
       </c>
       <c r="AB6">
-        <v>-1.4400000000000001E-3</v>
+        <v>5.54481</v>
       </c>
       <c r="AC6">
-        <v>-1.804E-2</v>
+        <v>5.3731999999999998</v>
       </c>
       <c r="AD6">
-        <v>-3.5520000000000003E-2</v>
+        <v>5.36897</v>
       </c>
       <c r="AE6">
-        <v>-5.3870000000000001E-2</v>
-      </c>
-      <c r="AF6">
-        <v>-7.3039999999999994E-2</v>
-      </c>
-      <c r="AG6">
-        <v>-9.2999999999999999E-2</v>
-      </c>
-      <c r="AH6">
-        <v>-0.11373999999999999</v>
+        <v>5.5080900000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
-        <v>-0.10299999999999999</v>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7">
+        <v>6.9279999999999999</v>
       </c>
       <c r="C7">
-        <v>2.2675964678355962E-2</v>
+        <v>6.8207399999999998</v>
       </c>
       <c r="D7">
-        <v>-5.4979017709457711E-3</v>
+        <v>6.5551399999999997</v>
       </c>
       <c r="E7">
-        <v>-3.5306226326697152E-2</v>
+        <v>6.2331300000000001</v>
       </c>
       <c r="F7">
-        <v>-6.6661778532552618E-2</v>
+        <v>6.1615000000000002</v>
       </c>
       <c r="G7">
-        <v>-9.9482604507277889E-2</v>
-      </c>
-      <c r="H7">
-        <v>-0.13369177152301939</v>
+        <v>6.5285799999999998</v>
+      </c>
+      <c r="I7">
+        <v>7.2242800000000003</v>
       </c>
       <c r="J7">
-        <v>1.8822699744775E-2</v>
+        <v>6.8806799999999999</v>
       </c>
       <c r="K7">
-        <v>-1.421465783355901E-2</v>
+        <v>6.6109400000000003</v>
       </c>
       <c r="L7">
-        <v>-4.8950947252423438E-2</v>
+        <v>6.4442199999999996</v>
       </c>
       <c r="M7">
-        <v>-8.5289465095391412E-2</v>
-      </c>
-      <c r="N7">
-        <v>-0.1231399656008607</v>
+        <v>6.79779</v>
       </c>
       <c r="O7">
-        <v>-0.16241827088485161</v>
+        <v>6.9882299999999997</v>
+      </c>
+      <c r="P7">
+        <v>6.7681699999999996</v>
       </c>
       <c r="Q7">
-        <v>2.8673549999999998E-3</v>
+        <v>6.4938000000000002</v>
       </c>
       <c r="R7">
-        <v>-5.4679327E-2</v>
+        <v>6.4780100000000003</v>
       </c>
       <c r="S7">
-        <v>-0.114407702</v>
-      </c>
-      <c r="T7">
-        <v>-0.176156009</v>
+        <v>6.7493400000000001</v>
       </c>
       <c r="U7">
-        <v>-0.23977792000000001</v>
+        <v>7.38863</v>
       </c>
       <c r="V7">
-        <v>-0.30514089999999999</v>
+        <v>7.0912699999999997</v>
+      </c>
+      <c r="W7">
+        <v>6.8692000000000002</v>
       </c>
       <c r="X7">
-        <v>5.2929999999999998E-2</v>
+        <v>6.7583200000000003</v>
       </c>
       <c r="Y7">
-        <v>3.9949999999999999E-2</v>
-      </c>
-      <c r="Z7">
-        <v>2.5940000000000001E-2</v>
+        <v>7.0183200000000001</v>
       </c>
       <c r="AA7">
-        <v>1.091E-2</v>
+        <v>7.38863</v>
       </c>
       <c r="AB7">
-        <v>-5.0800000000000003E-3</v>
+        <v>7.0489800000000002</v>
       </c>
       <c r="AC7">
-        <v>-2.1999999999999999E-2</v>
+        <v>6.8147900000000003</v>
       </c>
       <c r="AD7">
-        <v>-3.9820000000000001E-2</v>
+        <v>6.6386900000000004</v>
       </c>
       <c r="AE7">
-        <v>-5.8500000000000003E-2</v>
-      </c>
-      <c r="AF7">
-        <v>-7.8009999999999996E-2</v>
-      </c>
-      <c r="AG7">
-        <v>-9.8320000000000005E-2</v>
-      </c>
-      <c r="AH7">
-        <v>-0.11940000000000001</v>
+        <v>6.9428299999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>-7.0999999999999994E-2</v>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8">
+        <v>6.2389999999999999</v>
       </c>
       <c r="C8">
-        <v>1.5592835887828759E-2</v>
+        <v>6.0460099999999999</v>
       </c>
       <c r="D8">
-        <v>-1.0409235665267091E-2</v>
+        <v>5.9287999999999998</v>
       </c>
       <c r="E8">
-        <v>-3.7952279368353478E-2</v>
+        <v>5.7895700000000003</v>
       </c>
       <c r="F8">
-        <v>-6.6955553268395349E-2</v>
+        <v>5.3358699999999999</v>
       </c>
       <c r="G8">
-        <v>-9.7343052517346942E-2</v>
-      </c>
-      <c r="H8">
-        <v>-0.1290434580088165</v>
+        <v>5.8660500000000004</v>
+      </c>
+      <c r="I8">
+        <v>6.2227399999999999</v>
       </c>
       <c r="J8">
-        <v>4.7672386310944398E-3</v>
+        <v>6.0352300000000003</v>
       </c>
       <c r="K8">
-        <v>-2.5699218815081179E-2</v>
+        <v>5.9087100000000001</v>
       </c>
       <c r="L8">
-        <v>-5.7773463700363813E-2</v>
+        <v>5.4293699999999996</v>
       </c>
       <c r="M8">
-        <v>-9.1365616827648641E-2</v>
-      </c>
-      <c r="N8">
-        <v>-0.1263918154273341</v>
+        <v>5.9614200000000004</v>
       </c>
       <c r="O8">
-        <v>-0.16277384319369759</v>
+        <v>6.1902799999999996</v>
+      </c>
+      <c r="P8">
+        <v>6.2183900000000003</v>
       </c>
       <c r="Q8">
-        <v>-0.106780098</v>
+        <v>6.1255499999999996</v>
       </c>
       <c r="R8">
-        <v>-0.15863750300000001</v>
+        <v>5.8932599999999997</v>
       </c>
       <c r="S8">
-        <v>-0.21262815700000001</v>
-      </c>
-      <c r="T8">
-        <v>-0.26860271400000002</v>
+        <v>6.2211600000000002</v>
       </c>
       <c r="U8">
-        <v>-0.32642531299999999</v>
+        <v>6.3699300000000001</v>
       </c>
       <c r="V8">
-        <v>-0.38597228</v>
+        <v>6.3299799999999999</v>
+      </c>
+      <c r="W8">
+        <v>6.2507000000000001</v>
       </c>
       <c r="X8">
-        <v>6.2460000000000002E-2</v>
+        <v>5.9907300000000001</v>
       </c>
       <c r="Y8">
-        <v>5.0209999999999998E-2</v>
-      </c>
-      <c r="Z8">
-        <v>3.6970000000000003E-2</v>
+        <v>6.32186</v>
       </c>
       <c r="AA8">
-        <v>2.2800000000000001E-2</v>
+        <v>6.3699300000000001</v>
       </c>
       <c r="AB8">
-        <v>7.7200000000000003E-3</v>
+        <v>6.2410899999999998</v>
       </c>
       <c r="AC8">
-        <v>-8.2299999999999995E-3</v>
+        <v>6.13063</v>
       </c>
       <c r="AD8">
-        <v>-2.5020000000000001E-2</v>
+        <v>5.6795900000000001</v>
       </c>
       <c r="AE8">
-        <v>-4.2619999999999998E-2</v>
-      </c>
-      <c r="AF8">
-        <v>-6.0990000000000003E-2</v>
-      </c>
-      <c r="AG8">
-        <v>-8.0119999999999997E-2</v>
-      </c>
-      <c r="AH8">
-        <v>-9.9970000000000003E-2</v>
+        <v>6.1419899999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>-4.2000000000000003E-2</v>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9">
+        <v>5.1840000000000002</v>
       </c>
       <c r="C9">
-        <v>3.1888112739289307E-2</v>
+        <v>5.2764199999999999</v>
       </c>
       <c r="D9">
-        <v>5.9341618138347291E-3</v>
+        <v>5.2597399999999999</v>
       </c>
       <c r="E9">
-        <v>-2.1563130386763239E-2</v>
+        <v>4.9944800000000003</v>
       </c>
       <c r="F9">
-        <v>-5.0523097903328151E-2</v>
+        <v>5.1749400000000003</v>
       </c>
       <c r="G9">
-        <v>-8.0869813795292081E-2</v>
-      </c>
-      <c r="H9">
-        <v>-0.112532059471306</v>
+        <v>5.35419</v>
+      </c>
+      <c r="I9">
+        <v>5.7049899999999996</v>
       </c>
       <c r="J9">
-        <v>2.2583175002177051E-2</v>
+        <v>5.5930099999999996</v>
       </c>
       <c r="K9">
-        <v>-7.8050654854916173E-3</v>
+        <v>5.3915600000000001</v>
       </c>
       <c r="L9">
-        <v>-3.9801838131088729E-2</v>
+        <v>5.4554</v>
       </c>
       <c r="M9">
-        <v>-7.3317450055239833E-2</v>
-      </c>
-      <c r="N9">
-        <v>-0.1082682472183325</v>
+        <v>5.60825</v>
       </c>
       <c r="O9">
-        <v>-0.14457623501814859</v>
+        <v>6.3269200000000003</v>
+      </c>
+      <c r="P9">
+        <v>5.4227299999999996</v>
       </c>
       <c r="Q9">
-        <v>-9.3796044999999995E-2</v>
+        <v>5.19909</v>
       </c>
       <c r="R9">
-        <v>-0.14568030500000001</v>
+        <v>5.3959900000000003</v>
       </c>
       <c r="S9">
-        <v>-0.199692861</v>
-      </c>
-      <c r="T9">
-        <v>-0.255684315</v>
+        <v>5.5216200000000004</v>
       </c>
       <c r="U9">
-        <v>-0.31351889399999999</v>
+        <v>6.7516699999999998</v>
       </c>
       <c r="V9">
-        <v>-0.37307309300000002</v>
+        <v>5.7540300000000002</v>
+      </c>
+      <c r="W9">
+        <v>5.5949</v>
       </c>
       <c r="X9">
-        <v>7.7649999999999997E-2</v>
+        <v>5.6759199999999996</v>
       </c>
       <c r="Y9">
-        <v>6.5449999999999994E-2</v>
-      </c>
-      <c r="Z9">
-        <v>5.2269999999999997E-2</v>
+        <v>5.77658</v>
       </c>
       <c r="AA9">
-        <v>3.814E-2</v>
+        <v>6.7516699999999998</v>
       </c>
       <c r="AB9">
-        <v>2.3109999999999999E-2</v>
+        <v>5.7176099999999996</v>
       </c>
       <c r="AC9">
-        <v>7.1999999999999998E-3</v>
+        <v>5.5481100000000003</v>
       </c>
       <c r="AD9">
-        <v>-9.5499999999999995E-3</v>
+        <v>5.5807900000000004</v>
       </c>
       <c r="AE9">
-        <v>-2.7109999999999999E-2</v>
-      </c>
-      <c r="AF9">
-        <v>-4.5449999999999997E-2</v>
-      </c>
-      <c r="AG9">
-        <v>-6.4549999999999996E-2</v>
-      </c>
-      <c r="AH9">
-        <v>-8.4370000000000001E-2</v>
+        <v>5.7126700000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>-2.9000000000000001E-2</v>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>3.2329776261994542E-2</v>
+        <v>6.46997</v>
       </c>
       <c r="D10">
-        <v>6.79428298235959E-3</v>
+        <v>6.4458900000000003</v>
       </c>
       <c r="E10">
-        <v>-2.02987107648963E-2</v>
+        <v>6.1179100000000002</v>
       </c>
       <c r="F10">
-        <v>-4.8867466581410397E-2</v>
+        <v>6.2541799999999999</v>
       </c>
       <c r="G10">
-        <v>-7.883603005744548E-2</v>
-      </c>
-      <c r="H10">
-        <v>-0.11013292056451771</v>
+        <v>6.4096799999999998</v>
+      </c>
+      <c r="I10">
+        <v>6.6135099999999998</v>
       </c>
       <c r="J10">
-        <v>2.1079103380963068E-2</v>
+        <v>6.5665399999999998</v>
       </c>
       <c r="K10">
-        <v>-8.7560876359118103E-3</v>
+        <v>6.2806300000000004</v>
       </c>
       <c r="L10">
-        <v>-4.0216667593618333E-2</v>
+        <v>6.3670400000000003</v>
       </c>
       <c r="M10">
-        <v>-7.3212472293816694E-2</v>
-      </c>
-      <c r="N10">
-        <v>-0.1076594125027476</v>
+        <v>6.5027799999999996</v>
       </c>
       <c r="O10">
-        <v>-0.14347909064678041</v>
+        <v>6.9500900000000003</v>
+      </c>
+      <c r="P10">
+        <v>6.5792900000000003</v>
       </c>
       <c r="Q10">
-        <v>-0.120186082</v>
+        <v>6.2947100000000002</v>
       </c>
       <c r="R10">
-        <v>-0.170671076</v>
+        <v>6.4631699999999999</v>
       </c>
       <c r="S10">
-        <v>-0.22333318099999999</v>
-      </c>
-      <c r="T10">
-        <v>-0.27802027099999999</v>
+        <v>6.5611600000000001</v>
       </c>
       <c r="U10">
-        <v>-0.33459407600000002</v>
+        <v>7.0972</v>
       </c>
       <c r="V10">
-        <v>-0.39292883299999998</v>
+        <v>6.7022500000000003</v>
+      </c>
+      <c r="W10">
+        <v>6.4606000000000003</v>
       </c>
       <c r="X10">
-        <v>8.5290000000000005E-2</v>
+        <v>6.5784200000000004</v>
       </c>
       <c r="Y10">
-        <v>7.3230000000000003E-2</v>
-      </c>
-      <c r="Z10">
-        <v>6.0179999999999997E-2</v>
+        <v>6.6565399999999997</v>
       </c>
       <c r="AA10">
-        <v>4.6190000000000002E-2</v>
+        <v>7.0972</v>
       </c>
       <c r="AB10">
-        <v>3.1280000000000002E-2</v>
+        <v>6.6766699999999997</v>
       </c>
       <c r="AC10">
-        <v>1.55E-2</v>
+        <v>6.4280999999999997</v>
       </c>
       <c r="AD10">
-        <v>-1.14E-3</v>
+        <v>6.5014099999999999</v>
       </c>
       <c r="AE10">
-        <v>-1.8589999999999999E-2</v>
-      </c>
-      <c r="AF10">
-        <v>-3.6830000000000002E-2</v>
-      </c>
-      <c r="AG10">
-        <v>-5.5820000000000002E-2</v>
-      </c>
-      <c r="AH10">
-        <v>-7.5550000000000006E-2</v>
+        <v>6.6062700000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
-        <v>-0.19900000000000001</v>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11">
+        <v>5.9450000000000003</v>
       </c>
       <c r="C11">
-        <v>-3.2959371646610551E-2</v>
+        <v>5.8789899999999999</v>
       </c>
       <c r="D11">
-        <v>-6.1272270547884457E-2</v>
+        <v>5.9235300000000004</v>
       </c>
       <c r="E11">
-        <v>-9.1157421525328491E-2</v>
+        <v>5.7336900000000002</v>
       </c>
       <c r="F11">
-        <v>-0.12252535152473989</v>
+        <v>5.8350200000000001</v>
       </c>
       <c r="G11">
-        <v>-0.1552915189198798</v>
-      </c>
-      <c r="H11">
-        <v>-0.18937775058770059</v>
+        <v>5.9850099999999999</v>
+      </c>
+      <c r="I11">
+        <v>5.9996</v>
       </c>
       <c r="J11">
-        <v>-4.894262749152916E-2</v>
+        <v>6.01227</v>
       </c>
       <c r="K11">
-        <v>-8.2307098975137744E-2</v>
+        <v>5.8405699999999996</v>
       </c>
       <c r="L11">
-        <v>-0.1172873529920645</v>
+        <v>5.8994200000000001</v>
       </c>
       <c r="M11">
-        <v>-0.15378532387720131</v>
-      </c>
-      <c r="N11">
-        <v>-0.1917099606251845</v>
+        <v>6.0483200000000004</v>
       </c>
       <c r="O11">
-        <v>-0.2309767555804062</v>
+        <v>5.9531099999999997</v>
+      </c>
+      <c r="P11">
+        <v>6.0579700000000001</v>
       </c>
       <c r="Q11">
-        <v>-0.101662419</v>
+        <v>5.8936599999999997</v>
       </c>
       <c r="R11">
-        <v>-0.15666648399999999</v>
+        <v>6.1089000000000002</v>
       </c>
       <c r="S11">
-        <v>-0.213700058</v>
-      </c>
-      <c r="T11">
-        <v>-0.27261286600000001</v>
+        <v>6.1697499999999996</v>
       </c>
       <c r="U11">
-        <v>-0.333268658</v>
+        <v>6.0764199999999997</v>
       </c>
       <c r="V11">
-        <v>-0.39554379499999998</v>
+        <v>6.1490200000000002</v>
+      </c>
+      <c r="W11">
+        <v>6.0041000000000002</v>
       </c>
       <c r="X11">
-        <v>-8.8500000000000002E-3</v>
+        <v>6.1745000000000001</v>
       </c>
       <c r="Y11">
-        <v>-5.1799999999999997E-3</v>
-      </c>
-      <c r="Z11">
-        <v>-2.1729999999999999E-2</v>
+        <v>6.2346399999999997</v>
       </c>
       <c r="AA11">
-        <v>-4.147E-2</v>
+        <v>6.0764199999999997</v>
       </c>
       <c r="AB11">
-        <v>-6.2089999999999999E-2</v>
+        <v>6.1163600000000002</v>
       </c>
       <c r="AC11">
-        <v>-8.3449999999999996E-2</v>
+        <v>5.9583199999999996</v>
       </c>
       <c r="AD11">
-        <v>-0.10549</v>
+        <v>6.0423</v>
       </c>
       <c r="AE11">
-        <v>-0.12816</v>
-      </c>
-      <c r="AF11">
-        <v>-0.15145</v>
-      </c>
-      <c r="AG11">
-        <v>-0.17532</v>
-      </c>
-      <c r="AH11">
-        <v>-0.19975999999999999</v>
+        <v>6.1617100000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
-        <v>-0.30499999999999999</v>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12">
+        <v>6.923</v>
       </c>
       <c r="C12">
-        <v>-0.12267649568150581</v>
+        <v>6.8431600000000001</v>
       </c>
       <c r="D12">
-        <v>-0.1526386350437948</v>
+        <v>6.3953800000000003</v>
       </c>
       <c r="E12">
-        <v>-0.18434143875100781</v>
+        <v>5.9561999999999999</v>
       </c>
       <c r="F12">
-        <v>-0.21767820517851541</v>
+        <v>5.7942299999999998</v>
       </c>
       <c r="G12">
-        <v>-0.25255019501554887</v>
-      </c>
-      <c r="H12">
-        <v>-0.28886440115855472</v>
+        <v>6.2489100000000004</v>
+      </c>
+      <c r="I12">
+        <v>7.0754999999999999</v>
       </c>
       <c r="J12">
-        <v>-0.1616918408863468</v>
+        <v>6.5908100000000003</v>
       </c>
       <c r="K12">
-        <v>-0.1970203499165803</v>
+        <v>6.2039099999999996</v>
       </c>
       <c r="L12">
-        <v>-0.2341469362622812</v>
+        <v>5.9678800000000001</v>
       </c>
       <c r="M12">
-        <v>-0.27295414540999602</v>
-      </c>
-      <c r="N12">
-        <v>-0.31333359043364523</v>
+        <v>6.4067299999999996</v>
       </c>
       <c r="O12">
-        <v>-0.35518528603498473</v>
+        <v>6.9969700000000001</v>
+      </c>
+      <c r="P12">
+        <v>6.5853000000000002</v>
       </c>
       <c r="Q12">
-        <v>-0.34264759700000003</v>
+        <v>6.1830499999999997</v>
       </c>
       <c r="R12">
-        <v>-0.401169045</v>
+        <v>6.0551500000000003</v>
       </c>
       <c r="S12">
-        <v>-0.46199827900000001</v>
-      </c>
-      <c r="T12">
-        <v>-0.52494490400000005</v>
+        <v>6.4477700000000002</v>
       </c>
       <c r="U12">
-        <v>-0.58983831499999995</v>
+        <v>7.2289199999999996</v>
       </c>
       <c r="V12">
-        <v>-0.65652546499999997</v>
+        <v>6.7804700000000002</v>
+      </c>
+      <c r="W12">
+        <v>6.4303999999999997</v>
       </c>
       <c r="X12">
-        <v>-0.19067999999999999</v>
+        <v>6.2287699999999999</v>
       </c>
       <c r="Y12">
-        <v>-0.19116</v>
-      </c>
-      <c r="Z12">
-        <v>-0.19273999999999999</v>
+        <v>6.6062799999999999</v>
       </c>
       <c r="AA12">
-        <v>-0.19544</v>
+        <v>7.2289199999999996</v>
       </c>
       <c r="AB12">
-        <v>-0.19922999999999999</v>
+        <v>6.7287499999999998</v>
       </c>
       <c r="AC12">
-        <v>-0.20411000000000001</v>
+        <v>6.3649500000000003</v>
       </c>
       <c r="AD12">
-        <v>-0.21007000000000001</v>
+        <v>6.0811299999999999</v>
       </c>
       <c r="AE12">
-        <v>-0.21711</v>
-      </c>
-      <c r="AF12">
-        <v>-0.22523000000000001</v>
-      </c>
-      <c r="AG12">
-        <v>-0.2344</v>
-      </c>
-      <c r="AH12">
-        <v>-0.24462</v>
+        <v>6.5136700000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13">
+        <v>6.3890000000000002</v>
+      </c>
+      <c r="C13">
+        <v>6.3773099999999996</v>
+      </c>
+      <c r="D13">
+        <v>6.1761799999999996</v>
+      </c>
+      <c r="E13">
+        <v>5.8795799999999998</v>
+      </c>
+      <c r="F13">
+        <v>5.8297100000000004</v>
+      </c>
+      <c r="G13">
+        <v>6.1966299999999999</v>
+      </c>
+      <c r="I13">
+        <v>6.5934999999999997</v>
+      </c>
+      <c r="J13">
+        <v>6.3505700000000003</v>
+      </c>
+      <c r="K13">
+        <v>6.0795599999999999</v>
+      </c>
+      <c r="L13">
+        <v>5.9840099999999996</v>
+      </c>
+      <c r="M13">
+        <v>6.3427600000000002</v>
+      </c>
+      <c r="O13">
+        <v>6.5215699999999996</v>
+      </c>
+      <c r="P13">
+        <v>6.4155600000000002</v>
+      </c>
+      <c r="Q13">
+        <v>6.1639900000000001</v>
+      </c>
+      <c r="R13">
+        <v>6.2499799999999999</v>
+      </c>
+      <c r="S13">
+        <v>6.4754300000000002</v>
+      </c>
+      <c r="U13">
+        <v>6.7416099999999997</v>
+      </c>
+      <c r="V13">
+        <v>6.5928300000000002</v>
+      </c>
+      <c r="W13">
+        <v>6.3666999999999998</v>
+      </c>
+      <c r="X13">
+        <v>6.4047700000000001</v>
+      </c>
+      <c r="Y13">
+        <v>6.6254200000000001</v>
+      </c>
+      <c r="AA13">
+        <v>6.7416099999999997</v>
+      </c>
+      <c r="AB13">
+        <v>6.5083000000000002</v>
+      </c>
+      <c r="AC13">
+        <v>6.2497400000000001</v>
+      </c>
+      <c r="AD13">
+        <v>6.1386200000000004</v>
+      </c>
+      <c r="AE13">
+        <v>6.4661400000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14">
+        <v>3.8559999999999999</v>
+      </c>
+      <c r="C14">
+        <v>3.65008</v>
+      </c>
+      <c r="D14">
+        <v>3.6656599999999999</v>
+      </c>
+      <c r="E14">
+        <v>3.16778</v>
+      </c>
+      <c r="F14">
+        <v>3.9047200000000002</v>
+      </c>
+      <c r="G14">
+        <v>3.9011900000000002</v>
+      </c>
+      <c r="I14">
+        <v>4.13537</v>
+      </c>
+      <c r="J14">
+        <v>4.0565499999999997</v>
+      </c>
+      <c r="K14">
+        <v>3.6601599999999999</v>
+      </c>
+      <c r="L14">
+        <v>4.2520300000000004</v>
+      </c>
+      <c r="M14">
+        <v>4.1984899999999996</v>
+      </c>
+      <c r="O14">
+        <v>3.7237399999999998</v>
+      </c>
+      <c r="P14">
+        <v>3.7788499999999998</v>
+      </c>
+      <c r="Q14">
+        <v>3.27759</v>
+      </c>
+      <c r="R14">
+        <v>4.0714600000000001</v>
+      </c>
+      <c r="S14">
+        <v>4.0248100000000004</v>
+      </c>
+      <c r="U14">
+        <v>4.2098800000000001</v>
+      </c>
+      <c r="V14">
+        <v>4.1699000000000002</v>
+      </c>
+      <c r="W14">
+        <v>3.7770999999999999</v>
+      </c>
+      <c r="X14">
+        <v>4.4186699999999997</v>
+      </c>
+      <c r="Y14">
+        <v>4.3245500000000003</v>
+      </c>
+      <c r="AA14">
+        <v>4.2098800000000001</v>
+      </c>
+      <c r="AB14">
+        <v>4.1312300000000004</v>
+      </c>
+      <c r="AC14">
+        <v>3.7253500000000002</v>
+      </c>
+      <c r="AD14">
+        <v>4.32592</v>
+      </c>
+      <c r="AE14">
+        <v>4.2601699999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15">
+        <v>6.3250000000000002</v>
+      </c>
+      <c r="C15">
+        <v>6.3114999999999997</v>
+      </c>
+      <c r="D15">
+        <v>6.1025299999999998</v>
+      </c>
+      <c r="E15">
+        <v>5.7821199999999999</v>
+      </c>
+      <c r="F15">
+        <v>5.4802499999999998</v>
+      </c>
+      <c r="G15">
+        <v>6.00875</v>
+      </c>
+      <c r="I15">
+        <v>6.3975799999999996</v>
+      </c>
+      <c r="J15">
+        <v>6.1673400000000003</v>
+      </c>
+      <c r="K15">
+        <v>5.8662900000000002</v>
+      </c>
+      <c r="L15">
+        <v>5.5288300000000001</v>
+      </c>
+      <c r="M15">
+        <v>6.0600199999999997</v>
+      </c>
+      <c r="O15">
+        <v>6.4305899999999996</v>
+      </c>
+      <c r="P15">
+        <v>6.3204200000000004</v>
+      </c>
+      <c r="Q15">
+        <v>6.0387700000000004</v>
+      </c>
+      <c r="R15">
+        <v>5.8859399999999997</v>
+      </c>
+      <c r="S15">
+        <v>6.28444</v>
+      </c>
+      <c r="U15">
+        <v>6.51952</v>
+      </c>
+      <c r="V15">
+        <v>6.3880600000000003</v>
+      </c>
+      <c r="W15">
+        <v>6.1273999999999997</v>
+      </c>
+      <c r="X15">
+        <v>5.9365800000000002</v>
+      </c>
+      <c r="Y15">
+        <v>6.3382500000000004</v>
+      </c>
+      <c r="AA15">
+        <v>6.51952</v>
+      </c>
+      <c r="AB15">
+        <v>6.3092699999999997</v>
+      </c>
+      <c r="AC15">
+        <v>6.0160299999999998</v>
+      </c>
+      <c r="AD15">
+        <v>5.6403800000000004</v>
+      </c>
+      <c r="AE15">
+        <v>6.1726900000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16">
+        <v>5.1379999999999999</v>
+      </c>
+      <c r="C16">
+        <v>4.9756</v>
+      </c>
+      <c r="D16">
+        <v>4.9244300000000001</v>
+      </c>
+      <c r="E16">
+        <v>4.6650999999999998</v>
+      </c>
+      <c r="F16">
+        <v>4.7640900000000004</v>
+      </c>
+      <c r="G16">
+        <v>4.8620999999999999</v>
+      </c>
+      <c r="I16">
+        <v>5.0815999999999999</v>
+      </c>
+      <c r="J16">
+        <v>5.0096400000000001</v>
+      </c>
+      <c r="K16">
+        <v>4.77121</v>
+      </c>
+      <c r="L16">
+        <v>4.83596</v>
+      </c>
+      <c r="M16">
+        <v>4.9297700000000004</v>
+      </c>
+      <c r="O16">
+        <v>5.06128</v>
+      </c>
+      <c r="P16">
+        <v>5.0608199999999997</v>
+      </c>
+      <c r="Q16">
+        <v>4.8481500000000004</v>
+      </c>
+      <c r="R16">
+        <v>4.99824</v>
+      </c>
+      <c r="S16">
+        <v>5.0404099999999996</v>
+      </c>
+      <c r="U16">
+        <v>5.1705500000000004</v>
+      </c>
+      <c r="V16">
+        <v>5.1495600000000001</v>
+      </c>
+      <c r="W16">
+        <v>4.9584999999999999</v>
+      </c>
+      <c r="X16">
+        <v>5.0733699999999997</v>
+      </c>
+      <c r="Y16">
+        <v>5.1110699999999998</v>
+      </c>
+      <c r="AA16">
+        <v>5.1705500000000004</v>
+      </c>
+      <c r="AB16">
+        <v>5.1063599999999996</v>
+      </c>
+      <c r="AC16">
+        <v>4.8972600000000002</v>
+      </c>
+      <c r="AD16">
+        <v>4.9312399999999998</v>
+      </c>
+      <c r="AE16">
+        <v>5.0147700000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17">
+        <v>7.34</v>
+      </c>
+      <c r="C17">
+        <v>8.2261299999999995</v>
+      </c>
+      <c r="D17">
+        <v>7.8620799999999997</v>
+      </c>
+      <c r="E17">
+        <v>7.2978800000000001</v>
+      </c>
+      <c r="F17">
+        <v>7.3174700000000001</v>
+      </c>
+      <c r="G17">
+        <v>7.79901</v>
+      </c>
+      <c r="I17">
+        <v>8.2709200000000003</v>
+      </c>
+      <c r="J17">
+        <v>7.8924899999999996</v>
+      </c>
+      <c r="K17">
+        <v>7.3615700000000004</v>
+      </c>
+      <c r="L17">
+        <v>7.3345799999999999</v>
+      </c>
+      <c r="M17">
+        <v>7.8239200000000002</v>
+      </c>
+      <c r="O17">
+        <v>8.3429599999999997</v>
+      </c>
+      <c r="P17">
+        <v>8.0356799999999993</v>
+      </c>
+      <c r="Q17">
+        <v>7.49641</v>
+      </c>
+      <c r="R17">
+        <v>7.6011199999999999</v>
+      </c>
+      <c r="S17">
+        <v>8.0024200000000008</v>
+      </c>
+      <c r="U17">
+        <v>8.3879999999999999</v>
+      </c>
+      <c r="V17">
+        <v>8.0660299999999996</v>
+      </c>
+      <c r="W17">
+        <v>7.5627000000000004</v>
+      </c>
+      <c r="X17">
+        <v>7.6174099999999996</v>
+      </c>
+      <c r="Y17">
+        <v>8.0273000000000003</v>
+      </c>
+      <c r="AA17">
+        <v>8.3879999999999999</v>
+      </c>
+      <c r="AB17">
+        <v>7.98787</v>
+      </c>
+      <c r="AC17">
+        <v>7.4599000000000002</v>
+      </c>
+      <c r="AD17">
+        <v>7.3895099999999996</v>
+      </c>
+      <c r="AE17">
+        <v>7.8849999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18">
+        <v>4.34</v>
+      </c>
+      <c r="C18">
+        <v>4.33392</v>
+      </c>
+      <c r="D18">
+        <v>4.1085000000000003</v>
+      </c>
+      <c r="E18">
+        <v>3.9306899999999998</v>
+      </c>
+      <c r="F18">
+        <v>3.3314699999999999</v>
+      </c>
+      <c r="G18">
+        <v>3.9678100000000001</v>
+      </c>
+      <c r="I18">
+        <v>4.4246999999999996</v>
+      </c>
+      <c r="J18">
+        <v>4.2845800000000001</v>
+      </c>
+      <c r="K18">
+        <v>4.13706</v>
+      </c>
+      <c r="L18">
+        <v>3.5188600000000001</v>
+      </c>
+      <c r="M18">
+        <v>4.1363200000000004</v>
+      </c>
+      <c r="O18">
+        <v>4.4861199999999997</v>
+      </c>
+      <c r="P18">
+        <v>4.4010699999999998</v>
+      </c>
+      <c r="Q18">
+        <v>4.2675599999999996</v>
+      </c>
+      <c r="R18">
+        <v>3.8538700000000001</v>
+      </c>
+      <c r="S18">
+        <v>4.2905800000000003</v>
+      </c>
+      <c r="U18">
+        <v>4.58019</v>
+      </c>
+      <c r="V18">
+        <v>4.5793900000000001</v>
+      </c>
+      <c r="W18">
+        <v>4.476</v>
+      </c>
+      <c r="X18">
+        <v>4.0423099999999996</v>
+      </c>
+      <c r="Y18">
+        <v>4.4622000000000002</v>
+      </c>
+      <c r="AA18">
+        <v>4.58019</v>
+      </c>
+      <c r="AB18">
+        <v>4.5279299999999996</v>
+      </c>
+      <c r="AC18">
+        <v>4.4085700000000001</v>
+      </c>
+      <c r="AD18">
+        <v>3.88185</v>
+      </c>
+      <c r="AE18">
+        <v>4.3680300000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19">
+        <v>4.617</v>
+      </c>
+      <c r="C19">
+        <v>4.6782700000000004</v>
+      </c>
+      <c r="D19">
+        <v>4.2742100000000001</v>
+      </c>
+      <c r="E19">
+        <v>4.1455000000000002</v>
+      </c>
+      <c r="F19">
+        <v>3.5605000000000002</v>
+      </c>
+      <c r="G19">
+        <v>4.2126999999999999</v>
+      </c>
+      <c r="I19">
+        <v>4.8129299999999997</v>
+      </c>
+      <c r="J19">
+        <v>4.3867900000000004</v>
+      </c>
+      <c r="K19">
+        <v>4.26668</v>
+      </c>
+      <c r="L19">
+        <v>3.6653500000000001</v>
+      </c>
+      <c r="M19">
+        <v>4.3151999999999999</v>
+      </c>
+      <c r="O19">
+        <v>4.8655400000000002</v>
+      </c>
+      <c r="P19">
+        <v>4.6350699999999998</v>
+      </c>
+      <c r="Q19">
+        <v>4.5657899999999998</v>
+      </c>
+      <c r="R19">
+        <v>4.2923400000000003</v>
+      </c>
+      <c r="S19">
+        <v>4.6544499999999998</v>
+      </c>
+      <c r="U19">
+        <v>5.00718</v>
+      </c>
+      <c r="V19">
+        <v>4.75387</v>
+      </c>
+      <c r="W19">
+        <v>4.6933999999999996</v>
+      </c>
+      <c r="X19">
+        <v>4.4014300000000004</v>
+      </c>
+      <c r="Y19">
+        <v>4.7637</v>
+      </c>
+      <c r="AA19">
+        <v>5.00718</v>
+      </c>
+      <c r="AB19">
+        <v>4.6569000000000003</v>
+      </c>
+      <c r="AC19">
+        <v>4.5613799999999998</v>
+      </c>
+      <c r="AD19">
+        <v>4.0550699999999997</v>
+      </c>
+      <c r="AE19">
+        <v>4.5705900000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>255</v>
+      </c>
+      <c r="B20">
+        <v>6.1479999999999997</v>
+      </c>
+      <c r="C20">
+        <v>5.9503599999999999</v>
+      </c>
+      <c r="D20">
+        <v>6.0391399999999997</v>
+      </c>
+      <c r="E20">
+        <v>5.6969399999999997</v>
+      </c>
+      <c r="F20">
+        <v>6.1851200000000004</v>
+      </c>
+      <c r="G20">
+        <v>6.2167300000000001</v>
+      </c>
+      <c r="I20">
+        <v>6.2520199999999999</v>
+      </c>
+      <c r="J20">
+        <v>6.2794600000000003</v>
+      </c>
+      <c r="K20">
+        <v>5.9990199999999998</v>
+      </c>
+      <c r="L20">
+        <v>6.4059799999999996</v>
+      </c>
+      <c r="M20">
+        <v>6.4038899999999996</v>
+      </c>
+      <c r="O20">
+        <v>6.5945499999999999</v>
+      </c>
+      <c r="P20">
+        <v>6.1420899999999996</v>
+      </c>
+      <c r="Q20">
+        <v>5.8146300000000002</v>
+      </c>
+      <c r="R20">
+        <v>6.3517000000000001</v>
+      </c>
+      <c r="S20">
+        <v>6.3398700000000003</v>
+      </c>
+      <c r="U20">
+        <v>6.9</v>
+      </c>
+      <c r="V20">
+        <v>6.3852599999999997</v>
+      </c>
+      <c r="W20">
+        <v>6.1222000000000003</v>
+      </c>
+      <c r="X20">
+        <v>6.5764199999999997</v>
+      </c>
+      <c r="Y20">
+        <v>6.5309799999999996</v>
+      </c>
+      <c r="AA20">
+        <v>6.9</v>
+      </c>
+      <c r="AB20">
+        <v>6.3571200000000001</v>
+      </c>
+      <c r="AC20">
+        <v>6.0843800000000003</v>
+      </c>
+      <c r="AD20">
+        <v>6.5034900000000002</v>
+      </c>
+      <c r="AE20">
+        <v>6.4808599999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21">
+        <v>4.5609999999999999</v>
+      </c>
+      <c r="C21">
+        <v>4.3763500000000004</v>
+      </c>
+      <c r="D21">
+        <v>4.3522100000000004</v>
+      </c>
+      <c r="E21">
+        <v>4.0474600000000001</v>
+      </c>
+      <c r="F21">
+        <v>4.2801799999999997</v>
+      </c>
+      <c r="G21">
+        <v>4.4260799999999998</v>
+      </c>
+      <c r="I21">
+        <v>4.7791100000000002</v>
+      </c>
+      <c r="J21">
+        <v>4.6658200000000001</v>
+      </c>
+      <c r="K21">
+        <v>4.4412099999999999</v>
+      </c>
+      <c r="L21">
+        <v>4.5373999999999999</v>
+      </c>
+      <c r="M21">
+        <v>4.6617899999999999</v>
+      </c>
+      <c r="O21">
+        <v>4.5198400000000003</v>
+      </c>
+      <c r="P21">
+        <v>4.5292899999999996</v>
+      </c>
+      <c r="Q21">
+        <v>4.2757899999999998</v>
+      </c>
+      <c r="R21">
+        <v>4.52494</v>
+      </c>
+      <c r="S21">
+        <v>4.60839</v>
+      </c>
+      <c r="U21">
+        <v>4.9196099999999996</v>
+      </c>
+      <c r="V21">
+        <v>4.8411200000000001</v>
+      </c>
+      <c r="W21">
+        <v>4.6684000000000001</v>
+      </c>
+      <c r="X21">
+        <v>4.7813800000000004</v>
+      </c>
+      <c r="Y21">
+        <v>4.8449799999999996</v>
+      </c>
+      <c r="AA21">
+        <v>4.9196099999999996</v>
+      </c>
+      <c r="AB21">
+        <v>4.8072900000000001</v>
+      </c>
+      <c r="AC21">
+        <v>4.6242000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>4.6915399999999998</v>
+      </c>
+      <c r="AE21">
+        <v>4.7850999999999999</v>
       </c>
     </row>
   </sheetData>
